--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc38fqn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686E2E3A-B6BF-4272-BE8F-FAA492C09481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B87A07C-D537-4753-B783-9CA3ECFD8A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Jour</t>
   </si>
@@ -90,6 +90,27 @@
   </si>
   <si>
     <t>Configuration du depôt Git</t>
+  </si>
+  <si>
+    <t>Création du rapport de projet</t>
+  </si>
+  <si>
+    <t>Pris un peu de temps à réfléchir quoi poser comme information</t>
+  </si>
+  <si>
+    <t>Déterminer les tâches adaptées à leur niveau</t>
+  </si>
+  <si>
+    <t>Supervision du projet</t>
+  </si>
+  <si>
+    <t>Questions/Réponses</t>
+  </si>
+  <si>
+    <t>Réunion avec l'équipe et clarification des tâches</t>
+  </si>
+  <si>
+    <t>Solution apportée pour avoir un rythme linéaire</t>
   </si>
 </sst>
 </file>
@@ -805,7 +826,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -817,7 +838,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.3</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -826,7 +847,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1838,7 +1859,7 @@
   <dimension ref="A1:F500"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="26.625" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.375" style="15" customWidth="1"/>
     <col min="3" max="3" width="15.25" style="12" customWidth="1"/>
     <col min="4" max="4" width="24.75" style="5" customWidth="1"/>
@@ -1903,36 +1924,82 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="A4" s="6">
+        <v>46036</v>
+      </c>
+      <c r="B4" s="14">
+        <v>1</v>
+      </c>
+      <c r="C4" s="11">
+        <v>1.3</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
+      <c r="A5" s="6">
+        <v>46036</v>
+      </c>
+      <c r="B5" s="14">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="A6" s="6">
+        <v>46036</v>
+      </c>
+      <c r="B6" s="14">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="A7" s="6">
+        <v>46036</v>
+      </c>
+      <c r="B7" s="14">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
@@ -5935,7 +6002,7 @@
       </c>
       <c r="B2" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5971,7 +6038,7 @@
       </c>
       <c r="B6" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5998,7 +6065,7 @@
       </c>
       <c r="B9" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B87A07C-D537-4753-B783-9CA3ECFD8A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EA0C99-9679-4870-8B23-42C377AD509E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="0" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
   <si>
     <t>Jour</t>
   </si>
@@ -111,6 +111,21 @@
   </si>
   <si>
     <t>Solution apportée pour avoir un rythme linéaire</t>
+  </si>
+  <si>
+    <t>MCD et MLD</t>
+  </si>
+  <si>
+    <t>Manque de détails au niveau du CDC</t>
+  </si>
+  <si>
+    <t>Gestion de projet</t>
+  </si>
+  <si>
+    <t>Checking des Models proposés par l'équipe</t>
+  </si>
+  <si>
+    <t>Coup d'œil sur les spécificités du projet</t>
   </si>
 </sst>
 </file>
@@ -826,10 +841,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2.2999999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.3</c:v>
@@ -847,7 +862,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1549,8 +1564,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}" name="Tableau1" displayName="Tableau1" ref="A1:F300" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:F300" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}" name="Tableau1" displayName="Tableau1" ref="A1:F301" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:F301" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F1048576">
     <sortCondition descending="1" ref="D1:D1048576"/>
   </sortState>
@@ -1856,18 +1871,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F501"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="13.375" style="15" customWidth="1"/>
-    <col min="3" max="3" width="15.25" style="12" customWidth="1"/>
-    <col min="4" max="4" width="24.75" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="24.69921875" style="5" customWidth="1"/>
     <col min="5" max="5" width="68.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="82.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="82.19921875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1887,7 +1902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>46035</v>
       </c>
@@ -1905,7 +1920,7 @@
       </c>
       <c r="F2" s="8"/>
     </row>
-    <row r="3" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>46035</v>
       </c>
@@ -1923,7 +1938,7 @@
       </c>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>46036</v>
       </c>
@@ -1943,7 +1958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>46036</v>
       </c>
@@ -1961,7 +1976,7 @@
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>46036</v>
       </c>
@@ -1981,7 +1996,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>46036</v>
       </c>
@@ -2001,39 +2016,83 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
+    <row r="8" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>46037</v>
+      </c>
+      <c r="B8" s="14">
+        <v>1</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
+    <row r="9" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>46037</v>
+      </c>
+      <c r="B9" s="14">
+        <v>1</v>
+      </c>
+      <c r="C9" s="11">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>46037</v>
+      </c>
+      <c r="B10" s="14">
+        <v>1</v>
+      </c>
+      <c r="C10" s="11">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>46037</v>
+      </c>
+      <c r="B11" s="14">
+        <v>1</v>
+      </c>
+      <c r="C11" s="11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="14"/>
       <c r="C12" s="11"/>
@@ -2041,7 +2100,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="14"/>
       <c r="C13" s="11"/>
@@ -2049,7 +2108,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="14"/>
       <c r="C14" s="11"/>
@@ -2057,7 +2116,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="14"/>
       <c r="C15" s="11"/>
@@ -2065,7 +2124,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="14"/>
       <c r="C16" s="11"/>
@@ -2073,7 +2132,7 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="14"/>
       <c r="C17" s="11"/>
@@ -2081,7 +2140,7 @@
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="14"/>
       <c r="C18" s="11"/>
@@ -2089,7 +2148,7 @@
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="14"/>
       <c r="C19" s="11"/>
@@ -2097,7 +2156,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="14"/>
       <c r="C20" s="11"/>
@@ -2105,7 +2164,7 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="14"/>
       <c r="C21" s="11"/>
@@ -2113,7 +2172,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="14"/>
       <c r="C22" s="11"/>
@@ -2121,7 +2180,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="14"/>
       <c r="C23" s="11"/>
@@ -2129,7 +2188,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="14"/>
       <c r="C24" s="11"/>
@@ -2137,7 +2196,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="14"/>
       <c r="C25" s="11"/>
@@ -2145,7 +2204,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="14"/>
       <c r="C26" s="11"/>
@@ -2153,7 +2212,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="14"/>
       <c r="C27" s="11"/>
@@ -2161,7 +2220,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="14"/>
       <c r="C28" s="11"/>
@@ -2169,7 +2228,7 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="14"/>
       <c r="C29" s="11"/>
@@ -2177,7 +2236,7 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="14"/>
       <c r="C30" s="11"/>
@@ -2185,7 +2244,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="14"/>
       <c r="C31" s="11"/>
@@ -2193,7 +2252,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="14"/>
       <c r="C32" s="11"/>
@@ -2201,7 +2260,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="14"/>
       <c r="C33" s="11"/>
@@ -2209,7 +2268,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="14"/>
       <c r="C34" s="11"/>
@@ -2217,7 +2276,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="14"/>
       <c r="C35" s="11"/>
@@ -2225,7 +2284,7 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="14"/>
       <c r="C36" s="11"/>
@@ -2233,7 +2292,7 @@
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="14"/>
       <c r="C37" s="11"/>
@@ -2241,7 +2300,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="14"/>
       <c r="C38" s="11"/>
@@ -2249,7 +2308,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="14"/>
       <c r="C39" s="11"/>
@@ -2257,7 +2316,7 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" s="14"/>
       <c r="C40" s="11"/>
@@ -2265,7 +2324,7 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
     </row>
-    <row r="41" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="14"/>
       <c r="C41" s="11"/>
@@ -2273,7 +2332,7 @@
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="14"/>
       <c r="C42" s="11"/>
@@ -2281,7 +2340,7 @@
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="43" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="14"/>
       <c r="C43" s="11"/>
@@ -2289,7 +2348,7 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="14"/>
       <c r="C44" s="11"/>
@@ -2297,7 +2356,7 @@
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="14"/>
       <c r="C45" s="11"/>
@@ -2305,7 +2364,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
     </row>
-    <row r="46" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="B46" s="14"/>
       <c r="C46" s="11"/>
@@ -2313,7 +2372,7 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="14"/>
       <c r="C47" s="11"/>
@@ -2321,7 +2380,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="14"/>
       <c r="C48" s="11"/>
@@ -2329,7 +2388,7 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
     </row>
-    <row r="49" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="14"/>
       <c r="C49" s="11"/>
@@ -2337,7 +2396,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="14"/>
       <c r="C50" s="11"/>
@@ -2345,7 +2404,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
     </row>
-    <row r="51" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="14"/>
       <c r="C51" s="11"/>
@@ -2353,7 +2412,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="14"/>
       <c r="C52" s="11"/>
@@ -2361,7 +2420,7 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
     </row>
-    <row r="53" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="14"/>
       <c r="C53" s="11"/>
@@ -2369,7 +2428,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="14"/>
       <c r="C54" s="11"/>
@@ -2377,7 +2436,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="14"/>
       <c r="C55" s="11"/>
@@ -2385,7 +2444,7 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
     </row>
-    <row r="56" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="14"/>
       <c r="C56" s="11"/>
@@ -2393,7 +2452,7 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="14"/>
       <c r="C57" s="11"/>
@@ -2401,7 +2460,7 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
     </row>
-    <row r="58" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="14"/>
       <c r="C58" s="11"/>
@@ -2409,7 +2468,7 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
     </row>
-    <row r="59" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="14"/>
       <c r="C59" s="11"/>
@@ -2417,7 +2476,7 @@
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
     </row>
-    <row r="60" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="14"/>
       <c r="C60" s="11"/>
@@ -2425,7 +2484,7 @@
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="14"/>
       <c r="C61" s="11"/>
@@ -2433,7 +2492,7 @@
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
     </row>
-    <row r="62" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="14"/>
       <c r="C62" s="11"/>
@@ -2441,7 +2500,7 @@
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
     </row>
-    <row r="63" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="14"/>
       <c r="C63" s="11"/>
@@ -2449,7 +2508,7 @@
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
     </row>
-    <row r="64" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="14"/>
       <c r="C64" s="11"/>
@@ -2457,7 +2516,7 @@
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
     </row>
-    <row r="65" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="14"/>
       <c r="C65" s="11"/>
@@ -2465,7 +2524,7 @@
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
     </row>
-    <row r="66" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="14"/>
       <c r="C66" s="11"/>
@@ -2473,7 +2532,7 @@
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
     </row>
-    <row r="67" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="14"/>
       <c r="C67" s="11"/>
@@ -2481,7 +2540,7 @@
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
     </row>
-    <row r="68" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="14"/>
       <c r="C68" s="11"/>
@@ -2489,7 +2548,7 @@
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
     </row>
-    <row r="69" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="14"/>
       <c r="C69" s="11"/>
@@ -2497,7 +2556,7 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
     </row>
-    <row r="70" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="14"/>
       <c r="C70" s="11"/>
@@ -2505,7 +2564,7 @@
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
     </row>
-    <row r="71" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="14"/>
       <c r="C71" s="11"/>
@@ -2513,7 +2572,7 @@
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
     </row>
-    <row r="72" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="14"/>
       <c r="C72" s="11"/>
@@ -2521,7 +2580,7 @@
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
     </row>
-    <row r="73" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="14"/>
       <c r="C73" s="11"/>
@@ -2529,7 +2588,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
     </row>
-    <row r="74" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="14"/>
       <c r="C74" s="11"/>
@@ -2537,7 +2596,7 @@
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
     </row>
-    <row r="75" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="14"/>
       <c r="C75" s="11"/>
@@ -2545,7 +2604,7 @@
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
     </row>
-    <row r="76" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="14"/>
       <c r="C76" s="11"/>
@@ -2553,7 +2612,7 @@
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
     </row>
-    <row r="77" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="14"/>
       <c r="C77" s="11"/>
@@ -2561,7 +2620,7 @@
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
     </row>
-    <row r="78" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="14"/>
       <c r="C78" s="11"/>
@@ -2569,7 +2628,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
     </row>
-    <row r="79" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="14"/>
       <c r="C79" s="11"/>
@@ -2577,7 +2636,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
     </row>
-    <row r="80" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="14"/>
       <c r="C80" s="11"/>
@@ -2585,7 +2644,7 @@
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
     </row>
-    <row r="81" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="14"/>
       <c r="C81" s="11"/>
@@ -2593,7 +2652,7 @@
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
     </row>
-    <row r="82" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="14"/>
       <c r="C82" s="11"/>
@@ -2601,7 +2660,7 @@
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
     </row>
-    <row r="83" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="14"/>
       <c r="C83" s="11"/>
@@ -2609,7 +2668,7 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
     </row>
-    <row r="84" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="14"/>
       <c r="C84" s="11"/>
@@ -2617,7 +2676,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
     </row>
-    <row r="85" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="14"/>
       <c r="C85" s="11"/>
@@ -2625,7 +2684,7 @@
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
     </row>
-    <row r="86" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="14"/>
       <c r="C86" s="11"/>
@@ -2633,7 +2692,7 @@
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
     </row>
-    <row r="87" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="14"/>
       <c r="C87" s="11"/>
@@ -2641,7 +2700,7 @@
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
     </row>
-    <row r="88" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="14"/>
       <c r="C88" s="11"/>
@@ -2649,7 +2708,7 @@
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
     </row>
-    <row r="89" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="14"/>
       <c r="C89" s="11"/>
@@ -2657,7 +2716,7 @@
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
     </row>
-    <row r="90" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="14"/>
       <c r="C90" s="11"/>
@@ -2665,7 +2724,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
     </row>
-    <row r="91" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="14"/>
       <c r="C91" s="11"/>
@@ -2673,7 +2732,7 @@
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
     </row>
-    <row r="92" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="14"/>
       <c r="C92" s="11"/>
@@ -2681,7 +2740,7 @@
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
     </row>
-    <row r="93" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="14"/>
       <c r="C93" s="11"/>
@@ -2689,7 +2748,7 @@
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
     </row>
-    <row r="94" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="14"/>
       <c r="C94" s="11"/>
@@ -2697,7 +2756,7 @@
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
     </row>
-    <row r="95" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="14"/>
       <c r="C95" s="11"/>
@@ -2705,7 +2764,7 @@
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
     </row>
-    <row r="96" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="14"/>
       <c r="C96" s="11"/>
@@ -2713,7 +2772,7 @@
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
     </row>
-    <row r="97" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="14"/>
       <c r="C97" s="11"/>
@@ -2721,7 +2780,7 @@
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
     </row>
-    <row r="98" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="14"/>
       <c r="C98" s="11"/>
@@ -2729,7 +2788,7 @@
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
     </row>
-    <row r="99" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="14"/>
       <c r="C99" s="11"/>
@@ -2737,7 +2796,7 @@
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
     </row>
-    <row r="100" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
       <c r="B100" s="14"/>
       <c r="C100" s="11"/>
@@ -2745,7 +2804,7 @@
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
     </row>
-    <row r="101" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="14"/>
       <c r="C101" s="11"/>
@@ -2753,7 +2812,7 @@
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
     </row>
-    <row r="102" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="14"/>
       <c r="C102" s="11"/>
@@ -2761,7 +2820,7 @@
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
     </row>
-    <row r="103" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="14"/>
       <c r="C103" s="11"/>
@@ -2769,7 +2828,7 @@
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
     </row>
-    <row r="104" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
       <c r="B104" s="14"/>
       <c r="C104" s="11"/>
@@ -2777,7 +2836,7 @@
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
     </row>
-    <row r="105" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="B105" s="14"/>
       <c r="C105" s="11"/>
@@ -2785,7 +2844,7 @@
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
     </row>
-    <row r="106" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
       <c r="B106" s="14"/>
       <c r="C106" s="11"/>
@@ -2793,7 +2852,7 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
     </row>
-    <row r="107" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
       <c r="B107" s="14"/>
       <c r="C107" s="11"/>
@@ -2801,7 +2860,7 @@
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
     </row>
-    <row r="108" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
       <c r="B108" s="14"/>
       <c r="C108" s="11"/>
@@ -2809,7 +2868,7 @@
       <c r="E108" s="8"/>
       <c r="F108" s="8"/>
     </row>
-    <row r="109" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="14"/>
       <c r="C109" s="11"/>
@@ -2817,7 +2876,7 @@
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
     </row>
-    <row r="110" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="14"/>
       <c r="C110" s="11"/>
@@ -2825,7 +2884,7 @@
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
     </row>
-    <row r="111" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="14"/>
       <c r="C111" s="11"/>
@@ -2833,7 +2892,7 @@
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
     </row>
-    <row r="112" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
       <c r="B112" s="14"/>
       <c r="C112" s="11"/>
@@ -2841,7 +2900,7 @@
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
     </row>
-    <row r="113" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="B113" s="14"/>
       <c r="C113" s="11"/>
@@ -2849,7 +2908,7 @@
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
     </row>
-    <row r="114" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
       <c r="B114" s="14"/>
       <c r="C114" s="11"/>
@@ -2857,7 +2916,7 @@
       <c r="E114" s="8"/>
       <c r="F114" s="8"/>
     </row>
-    <row r="115" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="14"/>
       <c r="C115" s="11"/>
@@ -2865,7 +2924,7 @@
       <c r="E115" s="8"/>
       <c r="F115" s="8"/>
     </row>
-    <row r="116" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
       <c r="B116" s="14"/>
       <c r="C116" s="11"/>
@@ -2873,7 +2932,7 @@
       <c r="E116" s="8"/>
       <c r="F116" s="8"/>
     </row>
-    <row r="117" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="B117" s="14"/>
       <c r="C117" s="11"/>
@@ -2881,7 +2940,7 @@
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
     </row>
-    <row r="118" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="B118" s="14"/>
       <c r="C118" s="11"/>
@@ -2889,7 +2948,7 @@
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
     </row>
-    <row r="119" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="14"/>
       <c r="C119" s="11"/>
@@ -2897,7 +2956,7 @@
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
     </row>
-    <row r="120" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
       <c r="B120" s="14"/>
       <c r="C120" s="11"/>
@@ -2905,7 +2964,7 @@
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
     </row>
-    <row r="121" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="14"/>
       <c r="C121" s="11"/>
@@ -2913,7 +2972,7 @@
       <c r="E121" s="8"/>
       <c r="F121" s="8"/>
     </row>
-    <row r="122" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="B122" s="14"/>
       <c r="C122" s="11"/>
@@ -2921,7 +2980,7 @@
       <c r="E122" s="8"/>
       <c r="F122" s="8"/>
     </row>
-    <row r="123" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="14"/>
       <c r="C123" s="11"/>
@@ -2929,7 +2988,7 @@
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
     </row>
-    <row r="124" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
       <c r="B124" s="14"/>
       <c r="C124" s="11"/>
@@ -2937,7 +2996,7 @@
       <c r="E124" s="8"/>
       <c r="F124" s="8"/>
     </row>
-    <row r="125" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="14"/>
       <c r="C125" s="11"/>
@@ -2945,7 +3004,7 @@
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
     </row>
-    <row r="126" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="B126" s="14"/>
       <c r="C126" s="11"/>
@@ -2953,7 +3012,7 @@
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
     </row>
-    <row r="127" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="14"/>
       <c r="C127" s="11"/>
@@ -2961,7 +3020,7 @@
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
     </row>
-    <row r="128" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
       <c r="B128" s="14"/>
       <c r="C128" s="11"/>
@@ -2969,7 +3028,7 @@
       <c r="E128" s="8"/>
       <c r="F128" s="8"/>
     </row>
-    <row r="129" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="B129" s="14"/>
       <c r="C129" s="11"/>
@@ -2977,7 +3036,7 @@
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
     </row>
-    <row r="130" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
       <c r="B130" s="14"/>
       <c r="C130" s="11"/>
@@ -2985,7 +3044,7 @@
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
     </row>
-    <row r="131" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
       <c r="B131" s="14"/>
       <c r="C131" s="11"/>
@@ -2993,7 +3052,7 @@
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
     </row>
-    <row r="132" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6"/>
       <c r="B132" s="14"/>
       <c r="C132" s="11"/>
@@ -3001,7 +3060,7 @@
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
     </row>
-    <row r="133" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="B133" s="14"/>
       <c r="C133" s="11"/>
@@ -3009,7 +3068,7 @@
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
     </row>
-    <row r="134" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
       <c r="B134" s="14"/>
       <c r="C134" s="11"/>
@@ -3017,7 +3076,7 @@
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
     </row>
-    <row r="135" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
       <c r="B135" s="14"/>
       <c r="C135" s="11"/>
@@ -3025,7 +3084,7 @@
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
     </row>
-    <row r="136" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
       <c r="B136" s="14"/>
       <c r="C136" s="11"/>
@@ -3033,7 +3092,7 @@
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
     </row>
-    <row r="137" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
       <c r="B137" s="14"/>
       <c r="C137" s="11"/>
@@ -3041,7 +3100,7 @@
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
     </row>
-    <row r="138" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
       <c r="B138" s="14"/>
       <c r="C138" s="11"/>
@@ -3049,7 +3108,7 @@
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
     </row>
-    <row r="139" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
       <c r="B139" s="14"/>
       <c r="C139" s="11"/>
@@ -3057,7 +3116,7 @@
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
     </row>
-    <row r="140" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
       <c r="B140" s="14"/>
       <c r="C140" s="11"/>
@@ -3065,7 +3124,7 @@
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
     </row>
-    <row r="141" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
       <c r="B141" s="14"/>
       <c r="C141" s="11"/>
@@ -3073,7 +3132,7 @@
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
     </row>
-    <row r="142" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
       <c r="B142" s="14"/>
       <c r="C142" s="11"/>
@@ -3081,7 +3140,7 @@
       <c r="E142" s="8"/>
       <c r="F142" s="8"/>
     </row>
-    <row r="143" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
       <c r="B143" s="14"/>
       <c r="C143" s="11"/>
@@ -3089,7 +3148,7 @@
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
     </row>
-    <row r="144" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6"/>
       <c r="B144" s="14"/>
       <c r="C144" s="11"/>
@@ -3097,7 +3156,7 @@
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
     </row>
-    <row r="145" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
       <c r="B145" s="14"/>
       <c r="C145" s="11"/>
@@ -3105,7 +3164,7 @@
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
     </row>
-    <row r="146" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
       <c r="B146" s="14"/>
       <c r="C146" s="11"/>
@@ -3113,7 +3172,7 @@
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
     </row>
-    <row r="147" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
       <c r="B147" s="14"/>
       <c r="C147" s="11"/>
@@ -3121,7 +3180,7 @@
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
     </row>
-    <row r="148" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
       <c r="B148" s="14"/>
       <c r="C148" s="11"/>
@@ -3129,7 +3188,7 @@
       <c r="E148" s="8"/>
       <c r="F148" s="8"/>
     </row>
-    <row r="149" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
       <c r="B149" s="14"/>
       <c r="C149" s="11"/>
@@ -3137,7 +3196,7 @@
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
     </row>
-    <row r="150" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
       <c r="B150" s="14"/>
       <c r="C150" s="11"/>
@@ -3145,7 +3204,7 @@
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
     </row>
-    <row r="151" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
       <c r="B151" s="14"/>
       <c r="C151" s="11"/>
@@ -3153,7 +3212,7 @@
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
     </row>
-    <row r="152" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6"/>
       <c r="B152" s="14"/>
       <c r="C152" s="11"/>
@@ -3161,7 +3220,7 @@
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
     </row>
-    <row r="153" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
       <c r="B153" s="14"/>
       <c r="C153" s="11"/>
@@ -3169,7 +3228,7 @@
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
     </row>
-    <row r="154" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="B154" s="14"/>
       <c r="C154" s="11"/>
@@ -3177,7 +3236,7 @@
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
     </row>
-    <row r="155" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="B155" s="14"/>
       <c r="C155" s="11"/>
@@ -3185,7 +3244,7 @@
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
     </row>
-    <row r="156" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
       <c r="B156" s="14"/>
       <c r="C156" s="11"/>
@@ -3193,7 +3252,7 @@
       <c r="E156" s="8"/>
       <c r="F156" s="8"/>
     </row>
-    <row r="157" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
       <c r="B157" s="14"/>
       <c r="C157" s="11"/>
@@ -3201,7 +3260,7 @@
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
     </row>
-    <row r="158" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
       <c r="B158" s="14"/>
       <c r="C158" s="11"/>
@@ -3209,7 +3268,7 @@
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
     </row>
-    <row r="159" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
       <c r="B159" s="14"/>
       <c r="C159" s="11"/>
@@ -3217,7 +3276,7 @@
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
     </row>
-    <row r="160" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6"/>
       <c r="B160" s="14"/>
       <c r="C160" s="11"/>
@@ -3225,7 +3284,7 @@
       <c r="E160" s="8"/>
       <c r="F160" s="8"/>
     </row>
-    <row r="161" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
       <c r="B161" s="14"/>
       <c r="C161" s="11"/>
@@ -3233,7 +3292,7 @@
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
     </row>
-    <row r="162" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
       <c r="B162" s="14"/>
       <c r="C162" s="11"/>
@@ -3241,7 +3300,7 @@
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
     </row>
-    <row r="163" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
       <c r="B163" s="14"/>
       <c r="C163" s="11"/>
@@ -3249,7 +3308,7 @@
       <c r="E163" s="8"/>
       <c r="F163" s="8"/>
     </row>
-    <row r="164" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6"/>
       <c r="B164" s="14"/>
       <c r="C164" s="11"/>
@@ -3257,7 +3316,7 @@
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
     </row>
-    <row r="165" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
       <c r="B165" s="14"/>
       <c r="C165" s="11"/>
@@ -3265,7 +3324,7 @@
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
     </row>
-    <row r="166" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
       <c r="B166" s="14"/>
       <c r="C166" s="11"/>
@@ -3273,7 +3332,7 @@
       <c r="E166" s="8"/>
       <c r="F166" s="8"/>
     </row>
-    <row r="167" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6"/>
       <c r="B167" s="14"/>
       <c r="C167" s="11"/>
@@ -3281,7 +3340,7 @@
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
     </row>
-    <row r="168" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
       <c r="B168" s="14"/>
       <c r="C168" s="11"/>
@@ -3289,7 +3348,7 @@
       <c r="E168" s="8"/>
       <c r="F168" s="8"/>
     </row>
-    <row r="169" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6"/>
       <c r="B169" s="14"/>
       <c r="C169" s="11"/>
@@ -3297,7 +3356,7 @@
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
     </row>
-    <row r="170" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
       <c r="B170" s="14"/>
       <c r="C170" s="11"/>
@@ -3305,7 +3364,7 @@
       <c r="E170" s="8"/>
       <c r="F170" s="8"/>
     </row>
-    <row r="171" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="B171" s="14"/>
       <c r="C171" s="11"/>
@@ -3313,7 +3372,7 @@
       <c r="E171" s="8"/>
       <c r="F171" s="8"/>
     </row>
-    <row r="172" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
       <c r="B172" s="14"/>
       <c r="C172" s="11"/>
@@ -3321,7 +3380,7 @@
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
     </row>
-    <row r="173" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="B173" s="14"/>
       <c r="C173" s="11"/>
@@ -3329,7 +3388,7 @@
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
     </row>
-    <row r="174" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="B174" s="14"/>
       <c r="C174" s="11"/>
@@ -3337,7 +3396,7 @@
       <c r="E174" s="8"/>
       <c r="F174" s="8"/>
     </row>
-    <row r="175" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
       <c r="B175" s="14"/>
       <c r="C175" s="11"/>
@@ -3345,7 +3404,7 @@
       <c r="E175" s="8"/>
       <c r="F175" s="8"/>
     </row>
-    <row r="176" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
       <c r="B176" s="14"/>
       <c r="C176" s="11"/>
@@ -3353,7 +3412,7 @@
       <c r="E176" s="8"/>
       <c r="F176" s="8"/>
     </row>
-    <row r="177" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="B177" s="14"/>
       <c r="C177" s="11"/>
@@ -3361,7 +3420,7 @@
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
     </row>
-    <row r="178" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="B178" s="14"/>
       <c r="C178" s="11"/>
@@ -3369,7 +3428,7 @@
       <c r="E178" s="8"/>
       <c r="F178" s="8"/>
     </row>
-    <row r="179" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
       <c r="B179" s="14"/>
       <c r="C179" s="11"/>
@@ -3377,7 +3436,7 @@
       <c r="E179" s="8"/>
       <c r="F179" s="8"/>
     </row>
-    <row r="180" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
       <c r="B180" s="14"/>
       <c r="C180" s="11"/>
@@ -3385,7 +3444,7 @@
       <c r="E180" s="8"/>
       <c r="F180" s="8"/>
     </row>
-    <row r="181" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
       <c r="B181" s="14"/>
       <c r="C181" s="11"/>
@@ -3393,7 +3452,7 @@
       <c r="E181" s="8"/>
       <c r="F181" s="8"/>
     </row>
-    <row r="182" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
       <c r="B182" s="14"/>
       <c r="C182" s="11"/>
@@ -3401,7 +3460,7 @@
       <c r="E182" s="8"/>
       <c r="F182" s="8"/>
     </row>
-    <row r="183" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6"/>
       <c r="B183" s="14"/>
       <c r="C183" s="11"/>
@@ -3409,7 +3468,7 @@
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
     </row>
-    <row r="184" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
       <c r="B184" s="14"/>
       <c r="C184" s="11"/>
@@ -3417,7 +3476,7 @@
       <c r="E184" s="8"/>
       <c r="F184" s="8"/>
     </row>
-    <row r="185" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
       <c r="B185" s="14"/>
       <c r="C185" s="11"/>
@@ -3425,7 +3484,7 @@
       <c r="E185" s="8"/>
       <c r="F185" s="8"/>
     </row>
-    <row r="186" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
       <c r="B186" s="14"/>
       <c r="C186" s="11"/>
@@ -3433,7 +3492,7 @@
       <c r="E186" s="8"/>
       <c r="F186" s="8"/>
     </row>
-    <row r="187" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="B187" s="14"/>
       <c r="C187" s="11"/>
@@ -3441,7 +3500,7 @@
       <c r="E187" s="8"/>
       <c r="F187" s="8"/>
     </row>
-    <row r="188" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
       <c r="B188" s="14"/>
       <c r="C188" s="11"/>
@@ -3449,7 +3508,7 @@
       <c r="E188" s="8"/>
       <c r="F188" s="8"/>
     </row>
-    <row r="189" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
       <c r="B189" s="14"/>
       <c r="C189" s="11"/>
@@ -3457,7 +3516,7 @@
       <c r="E189" s="8"/>
       <c r="F189" s="8"/>
     </row>
-    <row r="190" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6"/>
       <c r="B190" s="14"/>
       <c r="C190" s="11"/>
@@ -3465,7 +3524,7 @@
       <c r="E190" s="8"/>
       <c r="F190" s="8"/>
     </row>
-    <row r="191" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
       <c r="B191" s="14"/>
       <c r="C191" s="11"/>
@@ -3473,7 +3532,7 @@
       <c r="E191" s="8"/>
       <c r="F191" s="8"/>
     </row>
-    <row r="192" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
       <c r="B192" s="14"/>
       <c r="C192" s="11"/>
@@ -3481,7 +3540,7 @@
       <c r="E192" s="8"/>
       <c r="F192" s="8"/>
     </row>
-    <row r="193" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
       <c r="B193" s="14"/>
       <c r="C193" s="11"/>
@@ -3489,7 +3548,7 @@
       <c r="E193" s="8"/>
       <c r="F193" s="8"/>
     </row>
-    <row r="194" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6"/>
       <c r="B194" s="14"/>
       <c r="C194" s="11"/>
@@ -3497,7 +3556,7 @@
       <c r="E194" s="8"/>
       <c r="F194" s="8"/>
     </row>
-    <row r="195" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
       <c r="B195" s="14"/>
       <c r="C195" s="11"/>
@@ -3505,7 +3564,7 @@
       <c r="E195" s="8"/>
       <c r="F195" s="8"/>
     </row>
-    <row r="196" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
       <c r="B196" s="14"/>
       <c r="C196" s="11"/>
@@ -3513,7 +3572,7 @@
       <c r="E196" s="8"/>
       <c r="F196" s="8"/>
     </row>
-    <row r="197" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
       <c r="B197" s="14"/>
       <c r="C197" s="11"/>
@@ -3521,7 +3580,7 @@
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
     </row>
-    <row r="198" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6"/>
       <c r="B198" s="14"/>
       <c r="C198" s="11"/>
@@ -3529,7 +3588,7 @@
       <c r="E198" s="8"/>
       <c r="F198" s="8"/>
     </row>
-    <row r="199" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
       <c r="B199" s="14"/>
       <c r="C199" s="11"/>
@@ -3537,7 +3596,7 @@
       <c r="E199" s="8"/>
       <c r="F199" s="8"/>
     </row>
-    <row r="200" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
       <c r="B200" s="14"/>
       <c r="C200" s="11"/>
@@ -3545,7 +3604,7 @@
       <c r="E200" s="8"/>
       <c r="F200" s="8"/>
     </row>
-    <row r="201" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
       <c r="B201" s="14"/>
       <c r="C201" s="11"/>
@@ -3553,7 +3612,7 @@
       <c r="E201" s="8"/>
       <c r="F201" s="8"/>
     </row>
-    <row r="202" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="B202" s="14"/>
       <c r="C202" s="11"/>
@@ -3561,7 +3620,7 @@
       <c r="E202" s="8"/>
       <c r="F202" s="8"/>
     </row>
-    <row r="203" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
       <c r="B203" s="14"/>
       <c r="C203" s="11"/>
@@ -3569,7 +3628,7 @@
       <c r="E203" s="8"/>
       <c r="F203" s="8"/>
     </row>
-    <row r="204" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="B204" s="14"/>
       <c r="C204" s="11"/>
@@ -3577,7 +3636,7 @@
       <c r="E204" s="8"/>
       <c r="F204" s="8"/>
     </row>
-    <row r="205" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
       <c r="B205" s="14"/>
       <c r="C205" s="11"/>
@@ -3585,7 +3644,7 @@
       <c r="E205" s="8"/>
       <c r="F205" s="8"/>
     </row>
-    <row r="206" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="B206" s="14"/>
       <c r="C206" s="11"/>
@@ -3593,7 +3652,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="B207" s="14"/>
       <c r="C207" s="11"/>
@@ -3601,7 +3660,7 @@
       <c r="E207" s="8"/>
       <c r="F207" s="8"/>
     </row>
-    <row r="208" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="B208" s="14"/>
       <c r="C208" s="11"/>
@@ -3609,7 +3668,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6"/>
       <c r="B209" s="14"/>
       <c r="C209" s="11"/>
@@ -3617,7 +3676,7 @@
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
       <c r="B210" s="14"/>
       <c r="C210" s="11"/>
@@ -3625,7 +3684,7 @@
       <c r="E210" s="8"/>
       <c r="F210" s="8"/>
     </row>
-    <row r="211" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
       <c r="B211" s="14"/>
       <c r="C211" s="11"/>
@@ -3633,7 +3692,7 @@
       <c r="E211" s="8"/>
       <c r="F211" s="8"/>
     </row>
-    <row r="212" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
       <c r="B212" s="14"/>
       <c r="C212" s="11"/>
@@ -3641,7 +3700,7 @@
       <c r="E212" s="8"/>
       <c r="F212" s="8"/>
     </row>
-    <row r="213" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6"/>
       <c r="B213" s="14"/>
       <c r="C213" s="11"/>
@@ -3649,7 +3708,7 @@
       <c r="E213" s="8"/>
       <c r="F213" s="8"/>
     </row>
-    <row r="214" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
       <c r="B214" s="14"/>
       <c r="C214" s="11"/>
@@ -3657,7 +3716,7 @@
       <c r="E214" s="8"/>
       <c r="F214" s="8"/>
     </row>
-    <row r="215" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
       <c r="B215" s="14"/>
       <c r="C215" s="11"/>
@@ -3665,7 +3724,7 @@
       <c r="E215" s="8"/>
       <c r="F215" s="8"/>
     </row>
-    <row r="216" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
       <c r="B216" s="14"/>
       <c r="C216" s="11"/>
@@ -3673,7 +3732,7 @@
       <c r="E216" s="8"/>
       <c r="F216" s="8"/>
     </row>
-    <row r="217" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6"/>
       <c r="B217" s="14"/>
       <c r="C217" s="11"/>
@@ -3681,7 +3740,7 @@
       <c r="E217" s="8"/>
       <c r="F217" s="8"/>
     </row>
-    <row r="218" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
       <c r="B218" s="14"/>
       <c r="C218" s="11"/>
@@ -3689,7 +3748,7 @@
       <c r="E218" s="8"/>
       <c r="F218" s="8"/>
     </row>
-    <row r="219" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
       <c r="B219" s="14"/>
       <c r="C219" s="11"/>
@@ -3697,7 +3756,7 @@
       <c r="E219" s="8"/>
       <c r="F219" s="8"/>
     </row>
-    <row r="220" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
       <c r="B220" s="14"/>
       <c r="C220" s="11"/>
@@ -3705,7 +3764,7 @@
       <c r="E220" s="8"/>
       <c r="F220" s="8"/>
     </row>
-    <row r="221" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6"/>
       <c r="B221" s="14"/>
       <c r="C221" s="11"/>
@@ -3713,7 +3772,7 @@
       <c r="E221" s="8"/>
       <c r="F221" s="8"/>
     </row>
-    <row r="222" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
       <c r="B222" s="14"/>
       <c r="C222" s="11"/>
@@ -3721,7 +3780,7 @@
       <c r="E222" s="8"/>
       <c r="F222" s="8"/>
     </row>
-    <row r="223" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
       <c r="B223" s="14"/>
       <c r="C223" s="11"/>
@@ -3729,7 +3788,7 @@
       <c r="E223" s="8"/>
       <c r="F223" s="8"/>
     </row>
-    <row r="224" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
       <c r="B224" s="14"/>
       <c r="C224" s="11"/>
@@ -3737,7 +3796,7 @@
       <c r="E224" s="8"/>
       <c r="F224" s="8"/>
     </row>
-    <row r="225" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
       <c r="B225" s="14"/>
       <c r="C225" s="11"/>
@@ -3745,7 +3804,7 @@
       <c r="E225" s="8"/>
       <c r="F225" s="8"/>
     </row>
-    <row r="226" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6"/>
       <c r="B226" s="14"/>
       <c r="C226" s="11"/>
@@ -3753,7 +3812,7 @@
       <c r="E226" s="8"/>
       <c r="F226" s="8"/>
     </row>
-    <row r="227" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
       <c r="B227" s="14"/>
       <c r="C227" s="11"/>
@@ -3761,7 +3820,7 @@
       <c r="E227" s="8"/>
       <c r="F227" s="8"/>
     </row>
-    <row r="228" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
       <c r="B228" s="14"/>
       <c r="C228" s="11"/>
@@ -3769,7 +3828,7 @@
       <c r="E228" s="8"/>
       <c r="F228" s="8"/>
     </row>
-    <row r="229" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
       <c r="B229" s="14"/>
       <c r="C229" s="11"/>
@@ -3777,7 +3836,7 @@
       <c r="E229" s="8"/>
       <c r="F229" s="8"/>
     </row>
-    <row r="230" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
       <c r="B230" s="14"/>
       <c r="C230" s="11"/>
@@ -3785,7 +3844,7 @@
       <c r="E230" s="8"/>
       <c r="F230" s="8"/>
     </row>
-    <row r="231" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
       <c r="B231" s="14"/>
       <c r="C231" s="11"/>
@@ -3793,7 +3852,7 @@
       <c r="E231" s="8"/>
       <c r="F231" s="8"/>
     </row>
-    <row r="232" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6"/>
       <c r="B232" s="14"/>
       <c r="C232" s="11"/>
@@ -3801,7 +3860,7 @@
       <c r="E232" s="8"/>
       <c r="F232" s="8"/>
     </row>
-    <row r="233" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
       <c r="B233" s="14"/>
       <c r="C233" s="11"/>
@@ -3809,7 +3868,7 @@
       <c r="E233" s="8"/>
       <c r="F233" s="8"/>
     </row>
-    <row r="234" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
       <c r="B234" s="14"/>
       <c r="C234" s="11"/>
@@ -3817,7 +3876,7 @@
       <c r="E234" s="8"/>
       <c r="F234" s="8"/>
     </row>
-    <row r="235" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6"/>
       <c r="B235" s="14"/>
       <c r="C235" s="11"/>
@@ -3825,7 +3884,7 @@
       <c r="E235" s="8"/>
       <c r="F235" s="8"/>
     </row>
-    <row r="236" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
       <c r="B236" s="14"/>
       <c r="C236" s="11"/>
@@ -3833,7 +3892,7 @@
       <c r="E236" s="8"/>
       <c r="F236" s="8"/>
     </row>
-    <row r="237" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
       <c r="B237" s="14"/>
       <c r="C237" s="11"/>
@@ -3841,7 +3900,7 @@
       <c r="E237" s="8"/>
       <c r="F237" s="8"/>
     </row>
-    <row r="238" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
       <c r="B238" s="14"/>
       <c r="C238" s="11"/>
@@ -3849,7 +3908,7 @@
       <c r="E238" s="8"/>
       <c r="F238" s="8"/>
     </row>
-    <row r="239" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6"/>
       <c r="B239" s="14"/>
       <c r="C239" s="11"/>
@@ -3857,7 +3916,7 @@
       <c r="E239" s="8"/>
       <c r="F239" s="8"/>
     </row>
-    <row r="240" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6"/>
       <c r="B240" s="14"/>
       <c r="C240" s="11"/>
@@ -3865,7 +3924,7 @@
       <c r="E240" s="8"/>
       <c r="F240" s="8"/>
     </row>
-    <row r="241" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
       <c r="B241" s="14"/>
       <c r="C241" s="11"/>
@@ -3873,7 +3932,7 @@
       <c r="E241" s="8"/>
       <c r="F241" s="8"/>
     </row>
-    <row r="242" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="B242" s="14"/>
       <c r="C242" s="11"/>
@@ -3881,7 +3940,7 @@
       <c r="E242" s="8"/>
       <c r="F242" s="8"/>
     </row>
-    <row r="243" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
       <c r="B243" s="14"/>
       <c r="C243" s="11"/>
@@ -3889,7 +3948,7 @@
       <c r="E243" s="8"/>
       <c r="F243" s="8"/>
     </row>
-    <row r="244" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
       <c r="B244" s="14"/>
       <c r="C244" s="11"/>
@@ -3897,7 +3956,7 @@
       <c r="E244" s="8"/>
       <c r="F244" s="8"/>
     </row>
-    <row r="245" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6"/>
       <c r="B245" s="14"/>
       <c r="C245" s="11"/>
@@ -3905,7 +3964,7 @@
       <c r="E245" s="8"/>
       <c r="F245" s="8"/>
     </row>
-    <row r="246" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
       <c r="B246" s="14"/>
       <c r="C246" s="11"/>
@@ -3913,7 +3972,7 @@
       <c r="E246" s="8"/>
       <c r="F246" s="8"/>
     </row>
-    <row r="247" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
       <c r="B247" s="14"/>
       <c r="C247" s="11"/>
@@ -3921,7 +3980,7 @@
       <c r="E247" s="8"/>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
       <c r="B248" s="14"/>
       <c r="C248" s="11"/>
@@ -3929,7 +3988,7 @@
       <c r="E248" s="8"/>
       <c r="F248" s="8"/>
     </row>
-    <row r="249" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6"/>
       <c r="B249" s="14"/>
       <c r="C249" s="11"/>
@@ -3937,7 +3996,7 @@
       <c r="E249" s="8"/>
       <c r="F249" s="8"/>
     </row>
-    <row r="250" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
       <c r="B250" s="14"/>
       <c r="C250" s="11"/>
@@ -3945,7 +4004,7 @@
       <c r="E250" s="8"/>
       <c r="F250" s="8"/>
     </row>
-    <row r="251" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6"/>
       <c r="B251" s="14"/>
       <c r="C251" s="11"/>
@@ -3953,7 +4012,7 @@
       <c r="E251" s="8"/>
       <c r="F251" s="8"/>
     </row>
-    <row r="252" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
       <c r="B252" s="14"/>
       <c r="C252" s="11"/>
@@ -3961,7 +4020,7 @@
       <c r="E252" s="8"/>
       <c r="F252" s="8"/>
     </row>
-    <row r="253" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
       <c r="B253" s="14"/>
       <c r="C253" s="11"/>
@@ -3969,7 +4028,7 @@
       <c r="E253" s="8"/>
       <c r="F253" s="8"/>
     </row>
-    <row r="254" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6"/>
       <c r="B254" s="14"/>
       <c r="C254" s="11"/>
@@ -3977,7 +4036,7 @@
       <c r="E254" s="8"/>
       <c r="F254" s="8"/>
     </row>
-    <row r="255" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6"/>
       <c r="B255" s="14"/>
       <c r="C255" s="11"/>
@@ -3985,7 +4044,7 @@
       <c r="E255" s="8"/>
       <c r="F255" s="8"/>
     </row>
-    <row r="256" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
       <c r="B256" s="14"/>
       <c r="C256" s="11"/>
@@ -3993,7 +4052,7 @@
       <c r="E256" s="8"/>
       <c r="F256" s="8"/>
     </row>
-    <row r="257" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6"/>
       <c r="B257" s="14"/>
       <c r="C257" s="11"/>
@@ -4001,7 +4060,7 @@
       <c r="E257" s="8"/>
       <c r="F257" s="8"/>
     </row>
-    <row r="258" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
       <c r="B258" s="14"/>
       <c r="C258" s="11"/>
@@ -4009,7 +4068,7 @@
       <c r="E258" s="8"/>
       <c r="F258" s="8"/>
     </row>
-    <row r="259" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6"/>
       <c r="B259" s="14"/>
       <c r="C259" s="11"/>
@@ -4017,7 +4076,7 @@
       <c r="E259" s="8"/>
       <c r="F259" s="8"/>
     </row>
-    <row r="260" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6"/>
       <c r="B260" s="14"/>
       <c r="C260" s="11"/>
@@ -4025,7 +4084,7 @@
       <c r="E260" s="8"/>
       <c r="F260" s="8"/>
     </row>
-    <row r="261" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6"/>
       <c r="B261" s="14"/>
       <c r="C261" s="11"/>
@@ -4033,7 +4092,7 @@
       <c r="E261" s="8"/>
       <c r="F261" s="8"/>
     </row>
-    <row r="262" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6"/>
       <c r="B262" s="14"/>
       <c r="C262" s="11"/>
@@ -4041,7 +4100,7 @@
       <c r="E262" s="8"/>
       <c r="F262" s="8"/>
     </row>
-    <row r="263" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6"/>
       <c r="B263" s="14"/>
       <c r="C263" s="11"/>
@@ -4049,7 +4108,7 @@
       <c r="E263" s="8"/>
       <c r="F263" s="8"/>
     </row>
-    <row r="264" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
       <c r="B264" s="14"/>
       <c r="C264" s="11"/>
@@ -4057,7 +4116,7 @@
       <c r="E264" s="8"/>
       <c r="F264" s="8"/>
     </row>
-    <row r="265" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
       <c r="B265" s="14"/>
       <c r="C265" s="11"/>
@@ -4065,7 +4124,7 @@
       <c r="E265" s="8"/>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
       <c r="B266" s="14"/>
       <c r="C266" s="11"/>
@@ -4073,7 +4132,7 @@
       <c r="E266" s="8"/>
       <c r="F266" s="8"/>
     </row>
-    <row r="267" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6"/>
       <c r="B267" s="14"/>
       <c r="C267" s="11"/>
@@ -4081,7 +4140,7 @@
       <c r="E267" s="8"/>
       <c r="F267" s="8"/>
     </row>
-    <row r="268" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
       <c r="B268" s="14"/>
       <c r="C268" s="11"/>
@@ -4089,7 +4148,7 @@
       <c r="E268" s="8"/>
       <c r="F268" s="8"/>
     </row>
-    <row r="269" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
       <c r="B269" s="14"/>
       <c r="C269" s="11"/>
@@ -4097,7 +4156,7 @@
       <c r="E269" s="8"/>
       <c r="F269" s="8"/>
     </row>
-    <row r="270" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6"/>
       <c r="B270" s="14"/>
       <c r="C270" s="11"/>
@@ -4105,7 +4164,7 @@
       <c r="E270" s="8"/>
       <c r="F270" s="8"/>
     </row>
-    <row r="271" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6"/>
       <c r="B271" s="14"/>
       <c r="C271" s="11"/>
@@ -4113,7 +4172,7 @@
       <c r="E271" s="8"/>
       <c r="F271" s="8"/>
     </row>
-    <row r="272" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
       <c r="B272" s="14"/>
       <c r="C272" s="11"/>
@@ -4121,7 +4180,7 @@
       <c r="E272" s="8"/>
       <c r="F272" s="8"/>
     </row>
-    <row r="273" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6"/>
       <c r="B273" s="14"/>
       <c r="C273" s="11"/>
@@ -4129,7 +4188,7 @@
       <c r="E273" s="8"/>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
       <c r="B274" s="14"/>
       <c r="C274" s="11"/>
@@ -4137,7 +4196,7 @@
       <c r="E274" s="8"/>
       <c r="F274" s="8"/>
     </row>
-    <row r="275" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
       <c r="B275" s="14"/>
       <c r="C275" s="11"/>
@@ -4145,7 +4204,7 @@
       <c r="E275" s="8"/>
       <c r="F275" s="8"/>
     </row>
-    <row r="276" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
       <c r="B276" s="14"/>
       <c r="C276" s="11"/>
@@ -4153,7 +4212,7 @@
       <c r="E276" s="8"/>
       <c r="F276" s="8"/>
     </row>
-    <row r="277" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6"/>
       <c r="B277" s="14"/>
       <c r="C277" s="11"/>
@@ -4161,7 +4220,7 @@
       <c r="E277" s="8"/>
       <c r="F277" s="8"/>
     </row>
-    <row r="278" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
       <c r="B278" s="14"/>
       <c r="C278" s="11"/>
@@ -4169,7 +4228,7 @@
       <c r="E278" s="8"/>
       <c r="F278" s="8"/>
     </row>
-    <row r="279" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
       <c r="B279" s="14"/>
       <c r="C279" s="11"/>
@@ -4177,7 +4236,7 @@
       <c r="E279" s="8"/>
       <c r="F279" s="8"/>
     </row>
-    <row r="280" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
       <c r="B280" s="14"/>
       <c r="C280" s="11"/>
@@ -4185,7 +4244,7 @@
       <c r="E280" s="8"/>
       <c r="F280" s="8"/>
     </row>
-    <row r="281" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6"/>
       <c r="B281" s="14"/>
       <c r="C281" s="11"/>
@@ -4193,7 +4252,7 @@
       <c r="E281" s="8"/>
       <c r="F281" s="8"/>
     </row>
-    <row r="282" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6"/>
       <c r="B282" s="14"/>
       <c r="C282" s="11"/>
@@ -4201,7 +4260,7 @@
       <c r="E282" s="8"/>
       <c r="F282" s="8"/>
     </row>
-    <row r="283" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
       <c r="B283" s="14"/>
       <c r="C283" s="11"/>
@@ -4209,7 +4268,7 @@
       <c r="E283" s="8"/>
       <c r="F283" s="8"/>
     </row>
-    <row r="284" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
       <c r="B284" s="14"/>
       <c r="C284" s="11"/>
@@ -4217,7 +4276,7 @@
       <c r="E284" s="8"/>
       <c r="F284" s="8"/>
     </row>
-    <row r="285" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6"/>
       <c r="B285" s="14"/>
       <c r="C285" s="11"/>
@@ -4225,7 +4284,7 @@
       <c r="E285" s="8"/>
       <c r="F285" s="8"/>
     </row>
-    <row r="286" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
       <c r="B286" s="14"/>
       <c r="C286" s="11"/>
@@ -4233,7 +4292,7 @@
       <c r="E286" s="8"/>
       <c r="F286" s="8"/>
     </row>
-    <row r="287" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6"/>
       <c r="B287" s="14"/>
       <c r="C287" s="11"/>
@@ -4241,7 +4300,7 @@
       <c r="E287" s="8"/>
       <c r="F287" s="8"/>
     </row>
-    <row r="288" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
       <c r="B288" s="14"/>
       <c r="C288" s="11"/>
@@ -4249,7 +4308,7 @@
       <c r="E288" s="8"/>
       <c r="F288" s="8"/>
     </row>
-    <row r="289" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6"/>
       <c r="B289" s="14"/>
       <c r="C289" s="11"/>
@@ -4257,7 +4316,7 @@
       <c r="E289" s="8"/>
       <c r="F289" s="8"/>
     </row>
-    <row r="290" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
       <c r="B290" s="14"/>
       <c r="C290" s="11"/>
@@ -4265,7 +4324,7 @@
       <c r="E290" s="8"/>
       <c r="F290" s="8"/>
     </row>
-    <row r="291" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6"/>
       <c r="B291" s="14"/>
       <c r="C291" s="11"/>
@@ -4273,7 +4332,7 @@
       <c r="E291" s="8"/>
       <c r="F291" s="8"/>
     </row>
-    <row r="292" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6"/>
       <c r="B292" s="14"/>
       <c r="C292" s="11"/>
@@ -4281,7 +4340,7 @@
       <c r="E292" s="8"/>
       <c r="F292" s="8"/>
     </row>
-    <row r="293" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
       <c r="B293" s="14"/>
       <c r="C293" s="11"/>
@@ -4289,7 +4348,7 @@
       <c r="E293" s="8"/>
       <c r="F293" s="8"/>
     </row>
-    <row r="294" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
       <c r="B294" s="14"/>
       <c r="C294" s="11"/>
@@ -4297,7 +4356,7 @@
       <c r="E294" s="8"/>
       <c r="F294" s="8"/>
     </row>
-    <row r="295" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6"/>
       <c r="B295" s="14"/>
       <c r="C295" s="11"/>
@@ -4305,7 +4364,7 @@
       <c r="E295" s="8"/>
       <c r="F295" s="8"/>
     </row>
-    <row r="296" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
       <c r="B296" s="14"/>
       <c r="C296" s="11"/>
@@ -4313,7 +4372,7 @@
       <c r="E296" s="8"/>
       <c r="F296" s="8"/>
     </row>
-    <row r="297" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
       <c r="B297" s="14"/>
       <c r="C297" s="11"/>
@@ -4321,7 +4380,7 @@
       <c r="E297" s="8"/>
       <c r="F297" s="8"/>
     </row>
-    <row r="298" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
       <c r="B298" s="14"/>
       <c r="C298" s="11"/>
@@ -4329,7 +4388,7 @@
       <c r="E298" s="8"/>
       <c r="F298" s="8"/>
     </row>
-    <row r="299" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6"/>
       <c r="B299" s="14"/>
       <c r="C299" s="11"/>
@@ -4337,7 +4396,7 @@
       <c r="E299" s="8"/>
       <c r="F299" s="8"/>
     </row>
-    <row r="300" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6"/>
       <c r="B300" s="14"/>
       <c r="C300" s="11"/>
@@ -4345,7 +4404,7 @@
       <c r="E300" s="8"/>
       <c r="F300" s="8"/>
     </row>
-    <row r="301" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6"/>
       <c r="B301" s="14"/>
       <c r="C301" s="11"/>
@@ -4353,7 +4412,7 @@
       <c r="E301" s="8"/>
       <c r="F301" s="8"/>
     </row>
-    <row r="302" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6"/>
       <c r="B302" s="14"/>
       <c r="C302" s="11"/>
@@ -4361,7 +4420,7 @@
       <c r="E302" s="8"/>
       <c r="F302" s="8"/>
     </row>
-    <row r="303" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6"/>
       <c r="B303" s="14"/>
       <c r="C303" s="11"/>
@@ -4369,7 +4428,7 @@
       <c r="E303" s="8"/>
       <c r="F303" s="8"/>
     </row>
-    <row r="304" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6"/>
       <c r="B304" s="14"/>
       <c r="C304" s="11"/>
@@ -4377,7 +4436,7 @@
       <c r="E304" s="8"/>
       <c r="F304" s="8"/>
     </row>
-    <row r="305" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6"/>
       <c r="B305" s="14"/>
       <c r="C305" s="11"/>
@@ -4385,7 +4444,7 @@
       <c r="E305" s="8"/>
       <c r="F305" s="8"/>
     </row>
-    <row r="306" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6"/>
       <c r="B306" s="14"/>
       <c r="C306" s="11"/>
@@ -4393,7 +4452,7 @@
       <c r="E306" s="8"/>
       <c r="F306" s="8"/>
     </row>
-    <row r="307" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6"/>
       <c r="B307" s="14"/>
       <c r="C307" s="11"/>
@@ -4401,7 +4460,7 @@
       <c r="E307" s="8"/>
       <c r="F307" s="8"/>
     </row>
-    <row r="308" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6"/>
       <c r="B308" s="14"/>
       <c r="C308" s="11"/>
@@ -4409,7 +4468,7 @@
       <c r="E308" s="8"/>
       <c r="F308" s="8"/>
     </row>
-    <row r="309" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="6"/>
       <c r="B309" s="14"/>
       <c r="C309" s="11"/>
@@ -4417,7 +4476,7 @@
       <c r="E309" s="8"/>
       <c r="F309" s="8"/>
     </row>
-    <row r="310" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6"/>
       <c r="B310" s="14"/>
       <c r="C310" s="11"/>
@@ -4425,7 +4484,7 @@
       <c r="E310" s="8"/>
       <c r="F310" s="8"/>
     </row>
-    <row r="311" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="6"/>
       <c r="B311" s="14"/>
       <c r="C311" s="11"/>
@@ -4433,7 +4492,7 @@
       <c r="E311" s="8"/>
       <c r="F311" s="8"/>
     </row>
-    <row r="312" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6"/>
       <c r="B312" s="14"/>
       <c r="C312" s="11"/>
@@ -4441,7 +4500,7 @@
       <c r="E312" s="8"/>
       <c r="F312" s="8"/>
     </row>
-    <row r="313" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="6"/>
       <c r="B313" s="14"/>
       <c r="C313" s="11"/>
@@ -4449,7 +4508,7 @@
       <c r="E313" s="8"/>
       <c r="F313" s="8"/>
     </row>
-    <row r="314" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6"/>
       <c r="B314" s="14"/>
       <c r="C314" s="11"/>
@@ -4457,7 +4516,7 @@
       <c r="E314" s="8"/>
       <c r="F314" s="8"/>
     </row>
-    <row r="315" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="6"/>
       <c r="B315" s="14"/>
       <c r="C315" s="11"/>
@@ -4465,7 +4524,7 @@
       <c r="E315" s="8"/>
       <c r="F315" s="8"/>
     </row>
-    <row r="316" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="6"/>
       <c r="B316" s="14"/>
       <c r="C316" s="11"/>
@@ -4473,7 +4532,7 @@
       <c r="E316" s="8"/>
       <c r="F316" s="8"/>
     </row>
-    <row r="317" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="6"/>
       <c r="B317" s="14"/>
       <c r="C317" s="11"/>
@@ -4481,7 +4540,7 @@
       <c r="E317" s="8"/>
       <c r="F317" s="8"/>
     </row>
-    <row r="318" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6"/>
       <c r="B318" s="14"/>
       <c r="C318" s="11"/>
@@ -4489,7 +4548,7 @@
       <c r="E318" s="8"/>
       <c r="F318" s="8"/>
     </row>
-    <row r="319" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="6"/>
       <c r="B319" s="14"/>
       <c r="C319" s="11"/>
@@ -4497,7 +4556,7 @@
       <c r="E319" s="8"/>
       <c r="F319" s="8"/>
     </row>
-    <row r="320" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="6"/>
       <c r="B320" s="14"/>
       <c r="C320" s="11"/>
@@ -4505,7 +4564,7 @@
       <c r="E320" s="8"/>
       <c r="F320" s="8"/>
     </row>
-    <row r="321" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6"/>
       <c r="B321" s="14"/>
       <c r="C321" s="11"/>
@@ -4513,7 +4572,7 @@
       <c r="E321" s="8"/>
       <c r="F321" s="8"/>
     </row>
-    <row r="322" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="6"/>
       <c r="B322" s="14"/>
       <c r="C322" s="11"/>
@@ -4521,7 +4580,7 @@
       <c r="E322" s="8"/>
       <c r="F322" s="8"/>
     </row>
-    <row r="323" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="6"/>
       <c r="B323" s="14"/>
       <c r="C323" s="11"/>
@@ -4529,7 +4588,7 @@
       <c r="E323" s="8"/>
       <c r="F323" s="8"/>
     </row>
-    <row r="324" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6"/>
       <c r="B324" s="14"/>
       <c r="C324" s="11"/>
@@ -4537,7 +4596,7 @@
       <c r="E324" s="8"/>
       <c r="F324" s="8"/>
     </row>
-    <row r="325" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="6"/>
       <c r="B325" s="14"/>
       <c r="C325" s="11"/>
@@ -4545,7 +4604,7 @@
       <c r="E325" s="8"/>
       <c r="F325" s="8"/>
     </row>
-    <row r="326" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="6"/>
       <c r="B326" s="14"/>
       <c r="C326" s="11"/>
@@ -4553,7 +4612,7 @@
       <c r="E326" s="8"/>
       <c r="F326" s="8"/>
     </row>
-    <row r="327" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="6"/>
       <c r="B327" s="14"/>
       <c r="C327" s="11"/>
@@ -4561,7 +4620,7 @@
       <c r="E327" s="8"/>
       <c r="F327" s="8"/>
     </row>
-    <row r="328" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="6"/>
       <c r="B328" s="14"/>
       <c r="C328" s="11"/>
@@ -4569,7 +4628,7 @@
       <c r="E328" s="8"/>
       <c r="F328" s="8"/>
     </row>
-    <row r="329" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="6"/>
       <c r="B329" s="14"/>
       <c r="C329" s="11"/>
@@ -4577,7 +4636,7 @@
       <c r="E329" s="8"/>
       <c r="F329" s="8"/>
     </row>
-    <row r="330" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="6"/>
       <c r="B330" s="14"/>
       <c r="C330" s="11"/>
@@ -4585,7 +4644,7 @@
       <c r="E330" s="8"/>
       <c r="F330" s="8"/>
     </row>
-    <row r="331" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="6"/>
       <c r="B331" s="14"/>
       <c r="C331" s="11"/>
@@ -4593,7 +4652,7 @@
       <c r="E331" s="8"/>
       <c r="F331" s="8"/>
     </row>
-    <row r="332" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6"/>
       <c r="B332" s="14"/>
       <c r="C332" s="11"/>
@@ -4601,7 +4660,7 @@
       <c r="E332" s="8"/>
       <c r="F332" s="8"/>
     </row>
-    <row r="333" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="6"/>
       <c r="B333" s="14"/>
       <c r="C333" s="11"/>
@@ -4609,7 +4668,7 @@
       <c r="E333" s="8"/>
       <c r="F333" s="8"/>
     </row>
-    <row r="334" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="6"/>
       <c r="B334" s="14"/>
       <c r="C334" s="11"/>
@@ -4617,7 +4676,7 @@
       <c r="E334" s="8"/>
       <c r="F334" s="8"/>
     </row>
-    <row r="335" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="6"/>
       <c r="B335" s="14"/>
       <c r="C335" s="11"/>
@@ -4625,7 +4684,7 @@
       <c r="E335" s="8"/>
       <c r="F335" s="8"/>
     </row>
-    <row r="336" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="6"/>
       <c r="B336" s="14"/>
       <c r="C336" s="11"/>
@@ -4633,7 +4692,7 @@
       <c r="E336" s="8"/>
       <c r="F336" s="8"/>
     </row>
-    <row r="337" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="6"/>
       <c r="B337" s="14"/>
       <c r="C337" s="11"/>
@@ -4641,7 +4700,7 @@
       <c r="E337" s="8"/>
       <c r="F337" s="8"/>
     </row>
-    <row r="338" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="6"/>
       <c r="B338" s="14"/>
       <c r="C338" s="11"/>
@@ -4649,7 +4708,7 @@
       <c r="E338" s="8"/>
       <c r="F338" s="8"/>
     </row>
-    <row r="339" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="6"/>
       <c r="B339" s="14"/>
       <c r="C339" s="11"/>
@@ -4657,7 +4716,7 @@
       <c r="E339" s="8"/>
       <c r="F339" s="8"/>
     </row>
-    <row r="340" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="6"/>
       <c r="B340" s="14"/>
       <c r="C340" s="11"/>
@@ -4665,7 +4724,7 @@
       <c r="E340" s="8"/>
       <c r="F340" s="8"/>
     </row>
-    <row r="341" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="6"/>
       <c r="B341" s="14"/>
       <c r="C341" s="11"/>
@@ -4673,7 +4732,7 @@
       <c r="E341" s="8"/>
       <c r="F341" s="8"/>
     </row>
-    <row r="342" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="6"/>
       <c r="B342" s="14"/>
       <c r="C342" s="11"/>
@@ -4681,7 +4740,7 @@
       <c r="E342" s="8"/>
       <c r="F342" s="8"/>
     </row>
-    <row r="343" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="6"/>
       <c r="B343" s="14"/>
       <c r="C343" s="11"/>
@@ -4689,7 +4748,7 @@
       <c r="E343" s="8"/>
       <c r="F343" s="8"/>
     </row>
-    <row r="344" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6"/>
       <c r="B344" s="14"/>
       <c r="C344" s="11"/>
@@ -4697,7 +4756,7 @@
       <c r="E344" s="8"/>
       <c r="F344" s="8"/>
     </row>
-    <row r="345" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="6"/>
       <c r="B345" s="14"/>
       <c r="C345" s="11"/>
@@ -4705,7 +4764,7 @@
       <c r="E345" s="8"/>
       <c r="F345" s="8"/>
     </row>
-    <row r="346" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="6"/>
       <c r="B346" s="14"/>
       <c r="C346" s="11"/>
@@ -4713,7 +4772,7 @@
       <c r="E346" s="8"/>
       <c r="F346" s="8"/>
     </row>
-    <row r="347" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="6"/>
       <c r="B347" s="14"/>
       <c r="C347" s="11"/>
@@ -4721,7 +4780,7 @@
       <c r="E347" s="8"/>
       <c r="F347" s="8"/>
     </row>
-    <row r="348" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="6"/>
       <c r="B348" s="14"/>
       <c r="C348" s="11"/>
@@ -4729,7 +4788,7 @@
       <c r="E348" s="8"/>
       <c r="F348" s="8"/>
     </row>
-    <row r="349" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="6"/>
       <c r="B349" s="14"/>
       <c r="C349" s="11"/>
@@ -4737,7 +4796,7 @@
       <c r="E349" s="8"/>
       <c r="F349" s="8"/>
     </row>
-    <row r="350" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="6"/>
       <c r="B350" s="14"/>
       <c r="C350" s="11"/>
@@ -4745,7 +4804,7 @@
       <c r="E350" s="8"/>
       <c r="F350" s="8"/>
     </row>
-    <row r="351" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="6"/>
       <c r="B351" s="14"/>
       <c r="C351" s="11"/>
@@ -4753,7 +4812,7 @@
       <c r="E351" s="8"/>
       <c r="F351" s="8"/>
     </row>
-    <row r="352" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="6"/>
       <c r="B352" s="14"/>
       <c r="C352" s="11"/>
@@ -4761,7 +4820,7 @@
       <c r="E352" s="8"/>
       <c r="F352" s="8"/>
     </row>
-    <row r="353" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="6"/>
       <c r="B353" s="14"/>
       <c r="C353" s="11"/>
@@ -4769,7 +4828,7 @@
       <c r="E353" s="8"/>
       <c r="F353" s="8"/>
     </row>
-    <row r="354" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="6"/>
       <c r="B354" s="14"/>
       <c r="C354" s="11"/>
@@ -4777,7 +4836,7 @@
       <c r="E354" s="8"/>
       <c r="F354" s="8"/>
     </row>
-    <row r="355" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="6"/>
       <c r="B355" s="14"/>
       <c r="C355" s="11"/>
@@ -4785,7 +4844,7 @@
       <c r="E355" s="8"/>
       <c r="F355" s="8"/>
     </row>
-    <row r="356" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="6"/>
       <c r="B356" s="14"/>
       <c r="C356" s="11"/>
@@ -4793,7 +4852,7 @@
       <c r="E356" s="8"/>
       <c r="F356" s="8"/>
     </row>
-    <row r="357" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="6"/>
       <c r="B357" s="14"/>
       <c r="C357" s="11"/>
@@ -4801,7 +4860,7 @@
       <c r="E357" s="8"/>
       <c r="F357" s="8"/>
     </row>
-    <row r="358" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6"/>
       <c r="B358" s="14"/>
       <c r="C358" s="11"/>
@@ -4809,7 +4868,7 @@
       <c r="E358" s="8"/>
       <c r="F358" s="8"/>
     </row>
-    <row r="359" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="6"/>
       <c r="B359" s="14"/>
       <c r="C359" s="11"/>
@@ -4817,7 +4876,7 @@
       <c r="E359" s="8"/>
       <c r="F359" s="8"/>
     </row>
-    <row r="360" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="6"/>
       <c r="B360" s="14"/>
       <c r="C360" s="11"/>
@@ -4825,7 +4884,7 @@
       <c r="E360" s="8"/>
       <c r="F360" s="8"/>
     </row>
-    <row r="361" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="6"/>
       <c r="B361" s="14"/>
       <c r="C361" s="11"/>
@@ -4833,7 +4892,7 @@
       <c r="E361" s="8"/>
       <c r="F361" s="8"/>
     </row>
-    <row r="362" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="6"/>
       <c r="B362" s="14"/>
       <c r="C362" s="11"/>
@@ -4841,7 +4900,7 @@
       <c r="E362" s="8"/>
       <c r="F362" s="8"/>
     </row>
-    <row r="363" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="6"/>
       <c r="B363" s="14"/>
       <c r="C363" s="11"/>
@@ -4849,7 +4908,7 @@
       <c r="E363" s="8"/>
       <c r="F363" s="8"/>
     </row>
-    <row r="364" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="6"/>
       <c r="B364" s="14"/>
       <c r="C364" s="11"/>
@@ -4857,7 +4916,7 @@
       <c r="E364" s="8"/>
       <c r="F364" s="8"/>
     </row>
-    <row r="365" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="6"/>
       <c r="B365" s="14"/>
       <c r="C365" s="11"/>
@@ -4865,7 +4924,7 @@
       <c r="E365" s="8"/>
       <c r="F365" s="8"/>
     </row>
-    <row r="366" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6"/>
       <c r="B366" s="14"/>
       <c r="C366" s="11"/>
@@ -4873,7 +4932,7 @@
       <c r="E366" s="8"/>
       <c r="F366" s="8"/>
     </row>
-    <row r="367" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="6"/>
       <c r="B367" s="14"/>
       <c r="C367" s="11"/>
@@ -4881,7 +4940,7 @@
       <c r="E367" s="8"/>
       <c r="F367" s="8"/>
     </row>
-    <row r="368" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="6"/>
       <c r="B368" s="14"/>
       <c r="C368" s="11"/>
@@ -4889,7 +4948,7 @@
       <c r="E368" s="8"/>
       <c r="F368" s="8"/>
     </row>
-    <row r="369" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="6"/>
       <c r="B369" s="14"/>
       <c r="C369" s="11"/>
@@ -4897,7 +4956,7 @@
       <c r="E369" s="8"/>
       <c r="F369" s="8"/>
     </row>
-    <row r="370" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="6"/>
       <c r="B370" s="14"/>
       <c r="C370" s="11"/>
@@ -4905,7 +4964,7 @@
       <c r="E370" s="8"/>
       <c r="F370" s="8"/>
     </row>
-    <row r="371" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="6"/>
       <c r="B371" s="14"/>
       <c r="C371" s="11"/>
@@ -4913,7 +4972,7 @@
       <c r="E371" s="8"/>
       <c r="F371" s="8"/>
     </row>
-    <row r="372" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="6"/>
       <c r="B372" s="14"/>
       <c r="C372" s="11"/>
@@ -4921,7 +4980,7 @@
       <c r="E372" s="8"/>
       <c r="F372" s="8"/>
     </row>
-    <row r="373" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="6"/>
       <c r="B373" s="14"/>
       <c r="C373" s="11"/>
@@ -4929,7 +4988,7 @@
       <c r="E373" s="8"/>
       <c r="F373" s="8"/>
     </row>
-    <row r="374" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="6"/>
       <c r="B374" s="14"/>
       <c r="C374" s="11"/>
@@ -4937,7 +4996,7 @@
       <c r="E374" s="8"/>
       <c r="F374" s="8"/>
     </row>
-    <row r="375" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="6"/>
       <c r="B375" s="14"/>
       <c r="C375" s="11"/>
@@ -4945,7 +5004,7 @@
       <c r="E375" s="8"/>
       <c r="F375" s="8"/>
     </row>
-    <row r="376" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6"/>
       <c r="B376" s="14"/>
       <c r="C376" s="11"/>
@@ -4953,7 +5012,7 @@
       <c r="E376" s="8"/>
       <c r="F376" s="8"/>
     </row>
-    <row r="377" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="6"/>
       <c r="B377" s="14"/>
       <c r="C377" s="11"/>
@@ -4961,7 +5020,7 @@
       <c r="E377" s="8"/>
       <c r="F377" s="8"/>
     </row>
-    <row r="378" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6"/>
       <c r="B378" s="14"/>
       <c r="C378" s="11"/>
@@ -4969,7 +5028,7 @@
       <c r="E378" s="8"/>
       <c r="F378" s="8"/>
     </row>
-    <row r="379" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="6"/>
       <c r="B379" s="14"/>
       <c r="C379" s="11"/>
@@ -4977,7 +5036,7 @@
       <c r="E379" s="8"/>
       <c r="F379" s="8"/>
     </row>
-    <row r="380" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6"/>
       <c r="B380" s="14"/>
       <c r="C380" s="11"/>
@@ -4985,7 +5044,7 @@
       <c r="E380" s="8"/>
       <c r="F380" s="8"/>
     </row>
-    <row r="381" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="6"/>
       <c r="B381" s="14"/>
       <c r="C381" s="11"/>
@@ -4993,7 +5052,7 @@
       <c r="E381" s="8"/>
       <c r="F381" s="8"/>
     </row>
-    <row r="382" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6"/>
       <c r="B382" s="14"/>
       <c r="C382" s="11"/>
@@ -5001,7 +5060,7 @@
       <c r="E382" s="8"/>
       <c r="F382" s="8"/>
     </row>
-    <row r="383" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="6"/>
       <c r="B383" s="14"/>
       <c r="C383" s="11"/>
@@ -5009,7 +5068,7 @@
       <c r="E383" s="8"/>
       <c r="F383" s="8"/>
     </row>
-    <row r="384" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6"/>
       <c r="B384" s="14"/>
       <c r="C384" s="11"/>
@@ -5017,7 +5076,7 @@
       <c r="E384" s="8"/>
       <c r="F384" s="8"/>
     </row>
-    <row r="385" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="6"/>
       <c r="B385" s="14"/>
       <c r="C385" s="11"/>
@@ -5025,7 +5084,7 @@
       <c r="E385" s="8"/>
       <c r="F385" s="8"/>
     </row>
-    <row r="386" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6"/>
       <c r="B386" s="14"/>
       <c r="C386" s="11"/>
@@ -5033,7 +5092,7 @@
       <c r="E386" s="8"/>
       <c r="F386" s="8"/>
     </row>
-    <row r="387" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6"/>
       <c r="B387" s="14"/>
       <c r="C387" s="11"/>
@@ -5041,7 +5100,7 @@
       <c r="E387" s="8"/>
       <c r="F387" s="8"/>
     </row>
-    <row r="388" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6"/>
       <c r="B388" s="14"/>
       <c r="C388" s="11"/>
@@ -5049,7 +5108,7 @@
       <c r="E388" s="8"/>
       <c r="F388" s="8"/>
     </row>
-    <row r="389" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6"/>
       <c r="B389" s="14"/>
       <c r="C389" s="11"/>
@@ -5057,7 +5116,7 @@
       <c r="E389" s="8"/>
       <c r="F389" s="8"/>
     </row>
-    <row r="390" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6"/>
       <c r="B390" s="14"/>
       <c r="C390" s="11"/>
@@ -5065,7 +5124,7 @@
       <c r="E390" s="8"/>
       <c r="F390" s="8"/>
     </row>
-    <row r="391" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="6"/>
       <c r="B391" s="14"/>
       <c r="C391" s="11"/>
@@ -5073,7 +5132,7 @@
       <c r="E391" s="8"/>
       <c r="F391" s="8"/>
     </row>
-    <row r="392" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6"/>
       <c r="B392" s="14"/>
       <c r="C392" s="11"/>
@@ -5081,7 +5140,7 @@
       <c r="E392" s="8"/>
       <c r="F392" s="8"/>
     </row>
-    <row r="393" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="6"/>
       <c r="B393" s="14"/>
       <c r="C393" s="11"/>
@@ -5089,7 +5148,7 @@
       <c r="E393" s="8"/>
       <c r="F393" s="8"/>
     </row>
-    <row r="394" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="6"/>
       <c r="B394" s="14"/>
       <c r="C394" s="11"/>
@@ -5097,7 +5156,7 @@
       <c r="E394" s="8"/>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="6"/>
       <c r="B395" s="14"/>
       <c r="C395" s="11"/>
@@ -5105,7 +5164,7 @@
       <c r="E395" s="8"/>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="6"/>
       <c r="B396" s="14"/>
       <c r="C396" s="11"/>
@@ -5113,7 +5172,7 @@
       <c r="E396" s="8"/>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="6"/>
       <c r="B397" s="14"/>
       <c r="C397" s="11"/>
@@ -5121,7 +5180,7 @@
       <c r="E397" s="8"/>
       <c r="F397" s="8"/>
     </row>
-    <row r="398" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="6"/>
       <c r="B398" s="14"/>
       <c r="C398" s="11"/>
@@ -5129,7 +5188,7 @@
       <c r="E398" s="8"/>
       <c r="F398" s="8"/>
     </row>
-    <row r="399" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="6"/>
       <c r="B399" s="14"/>
       <c r="C399" s="11"/>
@@ -5137,7 +5196,7 @@
       <c r="E399" s="8"/>
       <c r="F399" s="8"/>
     </row>
-    <row r="400" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6"/>
       <c r="B400" s="14"/>
       <c r="C400" s="11"/>
@@ -5145,7 +5204,7 @@
       <c r="E400" s="8"/>
       <c r="F400" s="8"/>
     </row>
-    <row r="401" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="6"/>
       <c r="B401" s="14"/>
       <c r="C401" s="11"/>
@@ -5153,7 +5212,7 @@
       <c r="E401" s="8"/>
       <c r="F401" s="8"/>
     </row>
-    <row r="402" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="6"/>
       <c r="B402" s="14"/>
       <c r="C402" s="11"/>
@@ -5161,7 +5220,7 @@
       <c r="E402" s="8"/>
       <c r="F402" s="8"/>
     </row>
-    <row r="403" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="6"/>
       <c r="B403" s="14"/>
       <c r="C403" s="11"/>
@@ -5169,7 +5228,7 @@
       <c r="E403" s="8"/>
       <c r="F403" s="8"/>
     </row>
-    <row r="404" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="6"/>
       <c r="B404" s="14"/>
       <c r="C404" s="11"/>
@@ -5177,7 +5236,7 @@
       <c r="E404" s="8"/>
       <c r="F404" s="8"/>
     </row>
-    <row r="405" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="6"/>
       <c r="B405" s="14"/>
       <c r="C405" s="11"/>
@@ -5185,7 +5244,7 @@
       <c r="E405" s="8"/>
       <c r="F405" s="8"/>
     </row>
-    <row r="406" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="6"/>
       <c r="B406" s="14"/>
       <c r="C406" s="11"/>
@@ -5193,7 +5252,7 @@
       <c r="E406" s="8"/>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="6"/>
       <c r="B407" s="14"/>
       <c r="C407" s="11"/>
@@ -5201,7 +5260,7 @@
       <c r="E407" s="8"/>
       <c r="F407" s="8"/>
     </row>
-    <row r="408" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="6"/>
       <c r="B408" s="14"/>
       <c r="C408" s="11"/>
@@ -5209,7 +5268,7 @@
       <c r="E408" s="8"/>
       <c r="F408" s="8"/>
     </row>
-    <row r="409" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="6"/>
       <c r="B409" s="14"/>
       <c r="C409" s="11"/>
@@ -5217,7 +5276,7 @@
       <c r="E409" s="8"/>
       <c r="F409" s="8"/>
     </row>
-    <row r="410" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="6"/>
       <c r="B410" s="14"/>
       <c r="C410" s="11"/>
@@ -5225,7 +5284,7 @@
       <c r="E410" s="8"/>
       <c r="F410" s="8"/>
     </row>
-    <row r="411" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="6"/>
       <c r="B411" s="14"/>
       <c r="C411" s="11"/>
@@ -5233,7 +5292,7 @@
       <c r="E411" s="8"/>
       <c r="F411" s="8"/>
     </row>
-    <row r="412" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="6"/>
       <c r="B412" s="14"/>
       <c r="C412" s="11"/>
@@ -5241,7 +5300,7 @@
       <c r="E412" s="8"/>
       <c r="F412" s="8"/>
     </row>
-    <row r="413" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="6"/>
       <c r="B413" s="14"/>
       <c r="C413" s="11"/>
@@ -5249,7 +5308,7 @@
       <c r="E413" s="8"/>
       <c r="F413" s="8"/>
     </row>
-    <row r="414" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="6"/>
       <c r="B414" s="14"/>
       <c r="C414" s="11"/>
@@ -5257,7 +5316,7 @@
       <c r="E414" s="8"/>
       <c r="F414" s="8"/>
     </row>
-    <row r="415" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="6"/>
       <c r="B415" s="14"/>
       <c r="C415" s="11"/>
@@ -5265,7 +5324,7 @@
       <c r="E415" s="8"/>
       <c r="F415" s="8"/>
     </row>
-    <row r="416" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="6"/>
       <c r="B416" s="14"/>
       <c r="C416" s="11"/>
@@ -5273,7 +5332,7 @@
       <c r="E416" s="8"/>
       <c r="F416" s="8"/>
     </row>
-    <row r="417" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6"/>
       <c r="B417" s="14"/>
       <c r="C417" s="11"/>
@@ -5281,7 +5340,7 @@
       <c r="E417" s="8"/>
       <c r="F417" s="8"/>
     </row>
-    <row r="418" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="6"/>
       <c r="B418" s="14"/>
       <c r="C418" s="11"/>
@@ -5289,7 +5348,7 @@
       <c r="E418" s="8"/>
       <c r="F418" s="8"/>
     </row>
-    <row r="419" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="6"/>
       <c r="B419" s="14"/>
       <c r="C419" s="11"/>
@@ -5297,7 +5356,7 @@
       <c r="E419" s="8"/>
       <c r="F419" s="8"/>
     </row>
-    <row r="420" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="6"/>
       <c r="B420" s="14"/>
       <c r="C420" s="11"/>
@@ -5305,7 +5364,7 @@
       <c r="E420" s="8"/>
       <c r="F420" s="8"/>
     </row>
-    <row r="421" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="6"/>
       <c r="B421" s="14"/>
       <c r="C421" s="11"/>
@@ -5313,7 +5372,7 @@
       <c r="E421" s="8"/>
       <c r="F421" s="8"/>
     </row>
-    <row r="422" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="6"/>
       <c r="B422" s="14"/>
       <c r="C422" s="11"/>
@@ -5321,7 +5380,7 @@
       <c r="E422" s="8"/>
       <c r="F422" s="8"/>
     </row>
-    <row r="423" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="6"/>
       <c r="B423" s="14"/>
       <c r="C423" s="11"/>
@@ -5329,7 +5388,7 @@
       <c r="E423" s="8"/>
       <c r="F423" s="8"/>
     </row>
-    <row r="424" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="6"/>
       <c r="B424" s="14"/>
       <c r="C424" s="11"/>
@@ -5337,7 +5396,7 @@
       <c r="E424" s="8"/>
       <c r="F424" s="8"/>
     </row>
-    <row r="425" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="6"/>
       <c r="B425" s="14"/>
       <c r="C425" s="11"/>
@@ -5345,7 +5404,7 @@
       <c r="E425" s="8"/>
       <c r="F425" s="8"/>
     </row>
-    <row r="426" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="6"/>
       <c r="B426" s="14"/>
       <c r="C426" s="11"/>
@@ -5353,7 +5412,7 @@
       <c r="E426" s="8"/>
       <c r="F426" s="8"/>
     </row>
-    <row r="427" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="6"/>
       <c r="B427" s="14"/>
       <c r="C427" s="11"/>
@@ -5361,7 +5420,7 @@
       <c r="E427" s="8"/>
       <c r="F427" s="8"/>
     </row>
-    <row r="428" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="6"/>
       <c r="B428" s="14"/>
       <c r="C428" s="11"/>
@@ -5369,7 +5428,7 @@
       <c r="E428" s="8"/>
       <c r="F428" s="8"/>
     </row>
-    <row r="429" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="6"/>
       <c r="B429" s="14"/>
       <c r="C429" s="11"/>
@@ -5377,7 +5436,7 @@
       <c r="E429" s="8"/>
       <c r="F429" s="8"/>
     </row>
-    <row r="430" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="6"/>
       <c r="B430" s="14"/>
       <c r="C430" s="11"/>
@@ -5385,7 +5444,7 @@
       <c r="E430" s="8"/>
       <c r="F430" s="8"/>
     </row>
-    <row r="431" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="6"/>
       <c r="B431" s="14"/>
       <c r="C431" s="11"/>
@@ -5393,7 +5452,7 @@
       <c r="E431" s="8"/>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="6"/>
       <c r="B432" s="14"/>
       <c r="C432" s="11"/>
@@ -5401,7 +5460,7 @@
       <c r="E432" s="8"/>
       <c r="F432" s="8"/>
     </row>
-    <row r="433" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="6"/>
       <c r="B433" s="14"/>
       <c r="C433" s="11"/>
@@ -5409,7 +5468,7 @@
       <c r="E433" s="8"/>
       <c r="F433" s="8"/>
     </row>
-    <row r="434" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="6"/>
       <c r="B434" s="14"/>
       <c r="C434" s="11"/>
@@ -5417,7 +5476,7 @@
       <c r="E434" s="8"/>
       <c r="F434" s="8"/>
     </row>
-    <row r="435" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="6"/>
       <c r="B435" s="14"/>
       <c r="C435" s="11"/>
@@ -5425,7 +5484,7 @@
       <c r="E435" s="8"/>
       <c r="F435" s="8"/>
     </row>
-    <row r="436" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="6"/>
       <c r="B436" s="14"/>
       <c r="C436" s="11"/>
@@ -5433,7 +5492,7 @@
       <c r="E436" s="8"/>
       <c r="F436" s="8"/>
     </row>
-    <row r="437" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="6"/>
       <c r="B437" s="14"/>
       <c r="C437" s="11"/>
@@ -5441,7 +5500,7 @@
       <c r="E437" s="8"/>
       <c r="F437" s="8"/>
     </row>
-    <row r="438" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="6"/>
       <c r="B438" s="14"/>
       <c r="C438" s="11"/>
@@ -5449,7 +5508,7 @@
       <c r="E438" s="8"/>
       <c r="F438" s="8"/>
     </row>
-    <row r="439" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="6"/>
       <c r="B439" s="14"/>
       <c r="C439" s="11"/>
@@ -5457,7 +5516,7 @@
       <c r="E439" s="8"/>
       <c r="F439" s="8"/>
     </row>
-    <row r="440" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="6"/>
       <c r="B440" s="14"/>
       <c r="C440" s="11"/>
@@ -5465,7 +5524,7 @@
       <c r="E440" s="8"/>
       <c r="F440" s="8"/>
     </row>
-    <row r="441" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="6"/>
       <c r="B441" s="14"/>
       <c r="C441" s="11"/>
@@ -5473,7 +5532,7 @@
       <c r="E441" s="8"/>
       <c r="F441" s="8"/>
     </row>
-    <row r="442" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="6"/>
       <c r="B442" s="14"/>
       <c r="C442" s="11"/>
@@ -5481,7 +5540,7 @@
       <c r="E442" s="8"/>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="6"/>
       <c r="B443" s="14"/>
       <c r="C443" s="11"/>
@@ -5489,7 +5548,7 @@
       <c r="E443" s="8"/>
       <c r="F443" s="8"/>
     </row>
-    <row r="444" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="6"/>
       <c r="B444" s="14"/>
       <c r="C444" s="11"/>
@@ -5497,7 +5556,7 @@
       <c r="E444" s="8"/>
       <c r="F444" s="8"/>
     </row>
-    <row r="445" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="6"/>
       <c r="B445" s="14"/>
       <c r="C445" s="11"/>
@@ -5505,7 +5564,7 @@
       <c r="E445" s="8"/>
       <c r="F445" s="8"/>
     </row>
-    <row r="446" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="6"/>
       <c r="B446" s="14"/>
       <c r="C446" s="11"/>
@@ -5513,7 +5572,7 @@
       <c r="E446" s="8"/>
       <c r="F446" s="8"/>
     </row>
-    <row r="447" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="6"/>
       <c r="B447" s="14"/>
       <c r="C447" s="11"/>
@@ -5521,7 +5580,7 @@
       <c r="E447" s="8"/>
       <c r="F447" s="8"/>
     </row>
-    <row r="448" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="6"/>
       <c r="B448" s="14"/>
       <c r="C448" s="11"/>
@@ -5529,7 +5588,7 @@
       <c r="E448" s="8"/>
       <c r="F448" s="8"/>
     </row>
-    <row r="449" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="6"/>
       <c r="B449" s="14"/>
       <c r="C449" s="11"/>
@@ -5537,7 +5596,7 @@
       <c r="E449" s="8"/>
       <c r="F449" s="8"/>
     </row>
-    <row r="450" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="6"/>
       <c r="B450" s="14"/>
       <c r="C450" s="11"/>
@@ -5545,7 +5604,7 @@
       <c r="E450" s="8"/>
       <c r="F450" s="8"/>
     </row>
-    <row r="451" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="6"/>
       <c r="B451" s="14"/>
       <c r="C451" s="11"/>
@@ -5553,7 +5612,7 @@
       <c r="E451" s="8"/>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="6"/>
       <c r="B452" s="14"/>
       <c r="C452" s="11"/>
@@ -5561,7 +5620,7 @@
       <c r="E452" s="8"/>
       <c r="F452" s="8"/>
     </row>
-    <row r="453" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="6"/>
       <c r="B453" s="14"/>
       <c r="C453" s="11"/>
@@ -5569,7 +5628,7 @@
       <c r="E453" s="8"/>
       <c r="F453" s="8"/>
     </row>
-    <row r="454" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="6"/>
       <c r="B454" s="14"/>
       <c r="C454" s="11"/>
@@ -5577,7 +5636,7 @@
       <c r="E454" s="8"/>
       <c r="F454" s="8"/>
     </row>
-    <row r="455" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="6"/>
       <c r="B455" s="14"/>
       <c r="C455" s="11"/>
@@ -5585,7 +5644,7 @@
       <c r="E455" s="8"/>
       <c r="F455" s="8"/>
     </row>
-    <row r="456" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="6"/>
       <c r="B456" s="14"/>
       <c r="C456" s="11"/>
@@ -5593,7 +5652,7 @@
       <c r="E456" s="8"/>
       <c r="F456" s="8"/>
     </row>
-    <row r="457" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="6"/>
       <c r="B457" s="14"/>
       <c r="C457" s="11"/>
@@ -5601,7 +5660,7 @@
       <c r="E457" s="8"/>
       <c r="F457" s="8"/>
     </row>
-    <row r="458" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="6"/>
       <c r="B458" s="14"/>
       <c r="C458" s="11"/>
@@ -5609,7 +5668,7 @@
       <c r="E458" s="8"/>
       <c r="F458" s="8"/>
     </row>
-    <row r="459" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="6"/>
       <c r="B459" s="14"/>
       <c r="C459" s="11"/>
@@ -5617,7 +5676,7 @@
       <c r="E459" s="8"/>
       <c r="F459" s="8"/>
     </row>
-    <row r="460" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="6"/>
       <c r="B460" s="14"/>
       <c r="C460" s="11"/>
@@ -5625,7 +5684,7 @@
       <c r="E460" s="8"/>
       <c r="F460" s="8"/>
     </row>
-    <row r="461" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="6"/>
       <c r="B461" s="14"/>
       <c r="C461" s="11"/>
@@ -5633,7 +5692,7 @@
       <c r="E461" s="8"/>
       <c r="F461" s="8"/>
     </row>
-    <row r="462" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="6"/>
       <c r="B462" s="14"/>
       <c r="C462" s="11"/>
@@ -5641,7 +5700,7 @@
       <c r="E462" s="8"/>
       <c r="F462" s="8"/>
     </row>
-    <row r="463" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="6"/>
       <c r="B463" s="14"/>
       <c r="C463" s="11"/>
@@ -5649,7 +5708,7 @@
       <c r="E463" s="8"/>
       <c r="F463" s="8"/>
     </row>
-    <row r="464" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="6"/>
       <c r="B464" s="14"/>
       <c r="C464" s="11"/>
@@ -5657,7 +5716,7 @@
       <c r="E464" s="8"/>
       <c r="F464" s="8"/>
     </row>
-    <row r="465" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="6"/>
       <c r="B465" s="14"/>
       <c r="C465" s="11"/>
@@ -5665,7 +5724,7 @@
       <c r="E465" s="8"/>
       <c r="F465" s="8"/>
     </row>
-    <row r="466" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="6"/>
       <c r="B466" s="14"/>
       <c r="C466" s="11"/>
@@ -5673,7 +5732,7 @@
       <c r="E466" s="8"/>
       <c r="F466" s="8"/>
     </row>
-    <row r="467" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="6"/>
       <c r="B467" s="14"/>
       <c r="C467" s="11"/>
@@ -5681,7 +5740,7 @@
       <c r="E467" s="8"/>
       <c r="F467" s="8"/>
     </row>
-    <row r="468" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="6"/>
       <c r="B468" s="14"/>
       <c r="C468" s="11"/>
@@ -5689,7 +5748,7 @@
       <c r="E468" s="8"/>
       <c r="F468" s="8"/>
     </row>
-    <row r="469" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="6"/>
       <c r="B469" s="14"/>
       <c r="C469" s="11"/>
@@ -5697,7 +5756,7 @@
       <c r="E469" s="8"/>
       <c r="F469" s="8"/>
     </row>
-    <row r="470" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="6"/>
       <c r="B470" s="14"/>
       <c r="C470" s="11"/>
@@ -5705,7 +5764,7 @@
       <c r="E470" s="8"/>
       <c r="F470" s="8"/>
     </row>
-    <row r="471" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="6"/>
       <c r="B471" s="14"/>
       <c r="C471" s="11"/>
@@ -5713,7 +5772,7 @@
       <c r="E471" s="8"/>
       <c r="F471" s="8"/>
     </row>
-    <row r="472" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="6"/>
       <c r="B472" s="14"/>
       <c r="C472" s="11"/>
@@ -5721,7 +5780,7 @@
       <c r="E472" s="8"/>
       <c r="F472" s="8"/>
     </row>
-    <row r="473" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="6"/>
       <c r="B473" s="14"/>
       <c r="C473" s="11"/>
@@ -5729,7 +5788,7 @@
       <c r="E473" s="8"/>
       <c r="F473" s="8"/>
     </row>
-    <row r="474" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="6"/>
       <c r="B474" s="14"/>
       <c r="C474" s="11"/>
@@ -5737,7 +5796,7 @@
       <c r="E474" s="8"/>
       <c r="F474" s="8"/>
     </row>
-    <row r="475" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="6"/>
       <c r="B475" s="14"/>
       <c r="C475" s="11"/>
@@ -5745,7 +5804,7 @@
       <c r="E475" s="8"/>
       <c r="F475" s="8"/>
     </row>
-    <row r="476" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6"/>
       <c r="B476" s="14"/>
       <c r="C476" s="11"/>
@@ -5753,7 +5812,7 @@
       <c r="E476" s="8"/>
       <c r="F476" s="8"/>
     </row>
-    <row r="477" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="6"/>
       <c r="B477" s="14"/>
       <c r="C477" s="11"/>
@@ -5761,7 +5820,7 @@
       <c r="E477" s="8"/>
       <c r="F477" s="8"/>
     </row>
-    <row r="478" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="6"/>
       <c r="B478" s="14"/>
       <c r="C478" s="11"/>
@@ -5769,7 +5828,7 @@
       <c r="E478" s="8"/>
       <c r="F478" s="8"/>
     </row>
-    <row r="479" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="6"/>
       <c r="B479" s="14"/>
       <c r="C479" s="11"/>
@@ -5777,7 +5836,7 @@
       <c r="E479" s="8"/>
       <c r="F479" s="8"/>
     </row>
-    <row r="480" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="6"/>
       <c r="B480" s="14"/>
       <c r="C480" s="11"/>
@@ -5785,7 +5844,7 @@
       <c r="E480" s="8"/>
       <c r="F480" s="8"/>
     </row>
-    <row r="481" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="6"/>
       <c r="B481" s="14"/>
       <c r="C481" s="11"/>
@@ -5793,7 +5852,7 @@
       <c r="E481" s="8"/>
       <c r="F481" s="8"/>
     </row>
-    <row r="482" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="6"/>
       <c r="B482" s="14"/>
       <c r="C482" s="11"/>
@@ -5801,7 +5860,7 @@
       <c r="E482" s="8"/>
       <c r="F482" s="8"/>
     </row>
-    <row r="483" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="6"/>
       <c r="B483" s="14"/>
       <c r="C483" s="11"/>
@@ -5809,7 +5868,7 @@
       <c r="E483" s="8"/>
       <c r="F483" s="8"/>
     </row>
-    <row r="484" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="6"/>
       <c r="B484" s="14"/>
       <c r="C484" s="11"/>
@@ -5817,7 +5876,7 @@
       <c r="E484" s="8"/>
       <c r="F484" s="8"/>
     </row>
-    <row r="485" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="6"/>
       <c r="B485" s="14"/>
       <c r="C485" s="11"/>
@@ -5825,7 +5884,7 @@
       <c r="E485" s="8"/>
       <c r="F485" s="8"/>
     </row>
-    <row r="486" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="6"/>
       <c r="B486" s="14"/>
       <c r="C486" s="11"/>
@@ -5833,7 +5892,7 @@
       <c r="E486" s="8"/>
       <c r="F486" s="8"/>
     </row>
-    <row r="487" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="6"/>
       <c r="B487" s="14"/>
       <c r="C487" s="11"/>
@@ -5841,7 +5900,7 @@
       <c r="E487" s="8"/>
       <c r="F487" s="8"/>
     </row>
-    <row r="488" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="6"/>
       <c r="B488" s="14"/>
       <c r="C488" s="11"/>
@@ -5849,7 +5908,7 @@
       <c r="E488" s="8"/>
       <c r="F488" s="8"/>
     </row>
-    <row r="489" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="6"/>
       <c r="B489" s="14"/>
       <c r="C489" s="11"/>
@@ -5857,7 +5916,7 @@
       <c r="E489" s="8"/>
       <c r="F489" s="8"/>
     </row>
-    <row r="490" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="6"/>
       <c r="B490" s="14"/>
       <c r="C490" s="11"/>
@@ -5865,7 +5924,7 @@
       <c r="E490" s="8"/>
       <c r="F490" s="8"/>
     </row>
-    <row r="491" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="6"/>
       <c r="B491" s="14"/>
       <c r="C491" s="11"/>
@@ -5873,7 +5932,7 @@
       <c r="E491" s="8"/>
       <c r="F491" s="8"/>
     </row>
-    <row r="492" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="6"/>
       <c r="B492" s="14"/>
       <c r="C492" s="11"/>
@@ -5881,7 +5940,7 @@
       <c r="E492" s="8"/>
       <c r="F492" s="8"/>
     </row>
-    <row r="493" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="6"/>
       <c r="B493" s="14"/>
       <c r="C493" s="11"/>
@@ -5889,7 +5948,7 @@
       <c r="E493" s="8"/>
       <c r="F493" s="8"/>
     </row>
-    <row r="494" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="6"/>
       <c r="B494" s="14"/>
       <c r="C494" s="11"/>
@@ -5897,7 +5956,7 @@
       <c r="E494" s="8"/>
       <c r="F494" s="8"/>
     </row>
-    <row r="495" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="6"/>
       <c r="B495" s="14"/>
       <c r="C495" s="11"/>
@@ -5905,7 +5964,7 @@
       <c r="E495" s="8"/>
       <c r="F495" s="8"/>
     </row>
-    <row r="496" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="6"/>
       <c r="B496" s="14"/>
       <c r="C496" s="11"/>
@@ -5913,7 +5972,7 @@
       <c r="E496" s="8"/>
       <c r="F496" s="8"/>
     </row>
-    <row r="497" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="6"/>
       <c r="B497" s="14"/>
       <c r="C497" s="11"/>
@@ -5921,7 +5980,7 @@
       <c r="E497" s="8"/>
       <c r="F497" s="8"/>
     </row>
-    <row r="498" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="6"/>
       <c r="B498" s="14"/>
       <c r="C498" s="11"/>
@@ -5929,7 +5988,7 @@
       <c r="E498" s="8"/>
       <c r="F498" s="8"/>
     </row>
-    <row r="499" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="6"/>
       <c r="B499" s="14"/>
       <c r="C499" s="11"/>
@@ -5937,7 +5996,7 @@
       <c r="E499" s="8"/>
       <c r="F499" s="8"/>
     </row>
-    <row r="500" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="6"/>
       <c r="B500" s="14"/>
       <c r="C500" s="11"/>
@@ -5945,13 +6004,21 @@
       <c r="E500" s="8"/>
       <c r="F500" s="8"/>
     </row>
+    <row r="501" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A501" s="6"/>
+      <c r="B501" s="14"/>
+      <c r="C501" s="11"/>
+      <c r="D501" s="7"/>
+      <c r="E501" s="8"/>
+      <c r="F501" s="8"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B300" xr:uid="{E1FCDE41-ACF1-4A68-9483-C062BB428146}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B301" xr:uid="{E1FCDE41-ACF1-4A68-9483-C062BB428146}">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C300" xr:uid="{48106778-5E48-49BE-9E53-EB975C533ABF}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C301" xr:uid="{48106778-5E48-49BE-9E53-EB975C533ABF}">
       <formula1>0.25</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -5971,7 +6038,7 @@
           <x14:formula1>
             <xm:f>Listes!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D1:D300</xm:sqref>
+          <xm:sqref>D1:D301</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5982,13 +6049,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC8CEF3-AF3E-4D54-8188-1302D62F0F60}">
   <dimension ref="A1:B500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.25" style="12" customWidth="1"/>
+    <col min="1" max="1" width="24.8984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.19921875" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
@@ -5996,2039 +6063,2039 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="11">
-        <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="11">
-        <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="11">
-        <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
+        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="11">
-        <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
+        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="11">
-        <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
+        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="11">
-        <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
+        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="11">
-        <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
+        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="11">
-        <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="11"/>
     </row>
-    <row r="12" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="11"/>
     </row>
-    <row r="13" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="11"/>
     </row>
-    <row r="14" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="11"/>
     </row>
-    <row r="15" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="11"/>
     </row>
-    <row r="16" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="11"/>
     </row>
-    <row r="17" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="11"/>
     </row>
-    <row r="18" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="11"/>
     </row>
-    <row r="19" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="11"/>
     </row>
-    <row r="20" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="11"/>
     </row>
-    <row r="21" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="11"/>
     </row>
-    <row r="22" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="11"/>
     </row>
-    <row r="23" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="11"/>
     </row>
-    <row r="24" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="11"/>
     </row>
-    <row r="25" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="11"/>
     </row>
-    <row r="27" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="11"/>
     </row>
-    <row r="28" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="11"/>
     </row>
-    <row r="29" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="11"/>
     </row>
-    <row r="30" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="11"/>
     </row>
-    <row r="31" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="11"/>
     </row>
-    <row r="32" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="11"/>
     </row>
-    <row r="33" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="11"/>
     </row>
-    <row r="34" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="11"/>
     </row>
-    <row r="35" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="11"/>
     </row>
-    <row r="36" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="11"/>
     </row>
-    <row r="37" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="11"/>
     </row>
-    <row r="38" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="11"/>
     </row>
-    <row r="39" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="11"/>
     </row>
-    <row r="40" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" s="11"/>
     </row>
-    <row r="41" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="11"/>
     </row>
-    <row r="42" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="11"/>
     </row>
-    <row r="43" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="11"/>
     </row>
-    <row r="44" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="11"/>
     </row>
-    <row r="45" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="11"/>
     </row>
-    <row r="46" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="B46" s="11"/>
     </row>
-    <row r="47" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="11"/>
     </row>
-    <row r="48" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="11"/>
     </row>
-    <row r="49" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="11"/>
     </row>
-    <row r="50" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="11"/>
     </row>
-    <row r="51" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="11"/>
     </row>
-    <row r="52" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="11"/>
     </row>
-    <row r="53" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="11"/>
     </row>
-    <row r="54" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="11"/>
     </row>
-    <row r="55" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="11"/>
     </row>
-    <row r="56" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="11"/>
     </row>
-    <row r="57" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="11"/>
     </row>
-    <row r="58" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="11"/>
     </row>
-    <row r="59" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="11"/>
     </row>
-    <row r="60" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="11"/>
     </row>
-    <row r="61" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="11"/>
     </row>
-    <row r="62" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="11"/>
     </row>
-    <row r="63" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="11"/>
     </row>
-    <row r="64" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="11"/>
     </row>
-    <row r="65" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="11"/>
     </row>
-    <row r="66" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="11"/>
     </row>
-    <row r="67" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="11"/>
     </row>
-    <row r="68" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="11"/>
     </row>
-    <row r="69" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="11"/>
     </row>
-    <row r="70" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="11"/>
     </row>
-    <row r="71" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="11"/>
     </row>
-    <row r="72" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="11"/>
     </row>
-    <row r="73" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="11"/>
     </row>
-    <row r="74" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="11"/>
     </row>
-    <row r="75" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="11"/>
     </row>
-    <row r="76" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="11"/>
     </row>
-    <row r="77" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="11"/>
     </row>
-    <row r="78" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="11"/>
     </row>
-    <row r="79" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="11"/>
     </row>
-    <row r="80" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="11"/>
     </row>
-    <row r="81" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="11"/>
     </row>
-    <row r="82" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="11"/>
     </row>
-    <row r="83" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="11"/>
     </row>
-    <row r="84" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="11"/>
     </row>
-    <row r="85" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="11"/>
     </row>
-    <row r="86" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="11"/>
     </row>
-    <row r="87" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="11"/>
     </row>
-    <row r="88" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="11"/>
     </row>
-    <row r="89" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="11"/>
     </row>
-    <row r="90" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="11"/>
     </row>
-    <row r="91" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="11"/>
     </row>
-    <row r="92" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="11"/>
     </row>
-    <row r="93" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="11"/>
     </row>
-    <row r="94" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="11"/>
     </row>
-    <row r="95" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="11"/>
     </row>
-    <row r="96" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="11"/>
     </row>
-    <row r="97" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="11"/>
     </row>
-    <row r="98" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="11"/>
     </row>
-    <row r="99" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="11"/>
     </row>
-    <row r="100" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
       <c r="B100" s="11"/>
     </row>
-    <row r="101" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="11"/>
     </row>
-    <row r="102" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="11"/>
     </row>
-    <row r="103" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="11"/>
     </row>
-    <row r="104" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
       <c r="B104" s="11"/>
     </row>
-    <row r="105" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="B105" s="11"/>
     </row>
-    <row r="106" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
       <c r="B106" s="11"/>
     </row>
-    <row r="107" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
       <c r="B107" s="11"/>
     </row>
-    <row r="108" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
       <c r="B108" s="11"/>
     </row>
-    <row r="109" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="11"/>
     </row>
-    <row r="110" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="11"/>
     </row>
-    <row r="111" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="11"/>
     </row>
-    <row r="112" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
       <c r="B112" s="11"/>
     </row>
-    <row r="113" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="B113" s="11"/>
     </row>
-    <row r="114" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
       <c r="B114" s="11"/>
     </row>
-    <row r="115" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="11"/>
     </row>
-    <row r="116" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
       <c r="B116" s="11"/>
     </row>
-    <row r="117" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="B117" s="11"/>
     </row>
-    <row r="118" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="B118" s="11"/>
     </row>
-    <row r="119" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="11"/>
     </row>
-    <row r="120" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
       <c r="B120" s="11"/>
     </row>
-    <row r="121" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="11"/>
     </row>
-    <row r="122" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="B122" s="11"/>
     </row>
-    <row r="123" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="11"/>
     </row>
-    <row r="124" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
       <c r="B124" s="11"/>
     </row>
-    <row r="125" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="11"/>
     </row>
-    <row r="126" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="B126" s="11"/>
     </row>
-    <row r="127" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="11"/>
     </row>
-    <row r="128" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
       <c r="B128" s="11"/>
     </row>
-    <row r="129" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="B129" s="11"/>
     </row>
-    <row r="130" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
       <c r="B130" s="11"/>
     </row>
-    <row r="131" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
       <c r="B131" s="11"/>
     </row>
-    <row r="132" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6"/>
       <c r="B132" s="11"/>
     </row>
-    <row r="133" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="B133" s="11"/>
     </row>
-    <row r="134" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
       <c r="B134" s="11"/>
     </row>
-    <row r="135" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
       <c r="B135" s="11"/>
     </row>
-    <row r="136" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
       <c r="B136" s="11"/>
     </row>
-    <row r="137" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
       <c r="B137" s="11"/>
     </row>
-    <row r="138" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
       <c r="B138" s="11"/>
     </row>
-    <row r="139" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
       <c r="B139" s="11"/>
     </row>
-    <row r="140" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
       <c r="B140" s="11"/>
     </row>
-    <row r="141" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
       <c r="B141" s="11"/>
     </row>
-    <row r="142" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
       <c r="B142" s="11"/>
     </row>
-    <row r="143" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
       <c r="B143" s="11"/>
     </row>
-    <row r="144" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6"/>
       <c r="B144" s="11"/>
     </row>
-    <row r="145" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
       <c r="B145" s="11"/>
     </row>
-    <row r="146" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
       <c r="B146" s="11"/>
     </row>
-    <row r="147" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
       <c r="B147" s="11"/>
     </row>
-    <row r="148" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
       <c r="B148" s="11"/>
     </row>
-    <row r="149" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
       <c r="B149" s="11"/>
     </row>
-    <row r="150" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
       <c r="B150" s="11"/>
     </row>
-    <row r="151" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
       <c r="B151" s="11"/>
     </row>
-    <row r="152" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6"/>
       <c r="B152" s="11"/>
     </row>
-    <row r="153" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
       <c r="B153" s="11"/>
     </row>
-    <row r="154" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="B154" s="11"/>
     </row>
-    <row r="155" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="B155" s="11"/>
     </row>
-    <row r="156" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
       <c r="B156" s="11"/>
     </row>
-    <row r="157" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
       <c r="B157" s="11"/>
     </row>
-    <row r="158" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
       <c r="B158" s="11"/>
     </row>
-    <row r="159" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
       <c r="B159" s="11"/>
     </row>
-    <row r="160" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6"/>
       <c r="B160" s="11"/>
     </row>
-    <row r="161" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
       <c r="B161" s="11"/>
     </row>
-    <row r="162" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
       <c r="B162" s="11"/>
     </row>
-    <row r="163" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
       <c r="B163" s="11"/>
     </row>
-    <row r="164" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6"/>
       <c r="B164" s="11"/>
     </row>
-    <row r="165" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
       <c r="B165" s="11"/>
     </row>
-    <row r="166" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
       <c r="B166" s="11"/>
     </row>
-    <row r="167" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6"/>
       <c r="B167" s="11"/>
     </row>
-    <row r="168" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
       <c r="B168" s="11"/>
     </row>
-    <row r="169" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6"/>
       <c r="B169" s="11"/>
     </row>
-    <row r="170" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
       <c r="B170" s="11"/>
     </row>
-    <row r="171" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="B171" s="11"/>
     </row>
-    <row r="172" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
       <c r="B172" s="11"/>
     </row>
-    <row r="173" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="B173" s="11"/>
     </row>
-    <row r="174" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="B174" s="11"/>
     </row>
-    <row r="175" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
       <c r="B175" s="11"/>
     </row>
-    <row r="176" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
       <c r="B176" s="11"/>
     </row>
-    <row r="177" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="B177" s="11"/>
     </row>
-    <row r="178" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="B178" s="11"/>
     </row>
-    <row r="179" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
       <c r="B179" s="11"/>
     </row>
-    <row r="180" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
       <c r="B180" s="11"/>
     </row>
-    <row r="181" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
       <c r="B181" s="11"/>
     </row>
-    <row r="182" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
       <c r="B182" s="11"/>
     </row>
-    <row r="183" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6"/>
       <c r="B183" s="11"/>
     </row>
-    <row r="184" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
       <c r="B184" s="11"/>
     </row>
-    <row r="185" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
       <c r="B185" s="11"/>
     </row>
-    <row r="186" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
       <c r="B186" s="11"/>
     </row>
-    <row r="187" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="B187" s="11"/>
     </row>
-    <row r="188" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
       <c r="B188" s="11"/>
     </row>
-    <row r="189" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
       <c r="B189" s="11"/>
     </row>
-    <row r="190" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6"/>
       <c r="B190" s="11"/>
     </row>
-    <row r="191" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
       <c r="B191" s="11"/>
     </row>
-    <row r="192" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
       <c r="B192" s="11"/>
     </row>
-    <row r="193" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
       <c r="B193" s="11"/>
     </row>
-    <row r="194" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6"/>
       <c r="B194" s="11"/>
     </row>
-    <row r="195" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
       <c r="B195" s="11"/>
     </row>
-    <row r="196" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
       <c r="B196" s="11"/>
     </row>
-    <row r="197" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
       <c r="B197" s="11"/>
     </row>
-    <row r="198" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6"/>
       <c r="B198" s="11"/>
     </row>
-    <row r="199" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
       <c r="B199" s="11"/>
     </row>
-    <row r="200" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
       <c r="B200" s="11"/>
     </row>
-    <row r="201" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
       <c r="B201" s="11"/>
     </row>
-    <row r="202" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="B202" s="11"/>
     </row>
-    <row r="203" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
       <c r="B203" s="11"/>
     </row>
-    <row r="204" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="B204" s="11"/>
     </row>
-    <row r="205" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
       <c r="B205" s="11"/>
     </row>
-    <row r="206" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="B206" s="11"/>
     </row>
-    <row r="207" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="B207" s="11"/>
     </row>
-    <row r="208" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="B208" s="11"/>
     </row>
-    <row r="209" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6"/>
       <c r="B209" s="11"/>
     </row>
-    <row r="210" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
       <c r="B210" s="11"/>
     </row>
-    <row r="211" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
       <c r="B211" s="11"/>
     </row>
-    <row r="212" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
       <c r="B212" s="11"/>
     </row>
-    <row r="213" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6"/>
       <c r="B213" s="11"/>
     </row>
-    <row r="214" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
       <c r="B214" s="11"/>
     </row>
-    <row r="215" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
       <c r="B215" s="11"/>
     </row>
-    <row r="216" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
       <c r="B216" s="11"/>
     </row>
-    <row r="217" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6"/>
       <c r="B217" s="11"/>
     </row>
-    <row r="218" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
       <c r="B218" s="11"/>
     </row>
-    <row r="219" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
       <c r="B219" s="11"/>
     </row>
-    <row r="220" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
       <c r="B220" s="11"/>
     </row>
-    <row r="221" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6"/>
       <c r="B221" s="11"/>
     </row>
-    <row r="222" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
       <c r="B222" s="11"/>
     </row>
-    <row r="223" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
       <c r="B223" s="11"/>
     </row>
-    <row r="224" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
       <c r="B224" s="11"/>
     </row>
-    <row r="225" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
       <c r="B225" s="11"/>
     </row>
-    <row r="226" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6"/>
       <c r="B226" s="11"/>
     </row>
-    <row r="227" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
       <c r="B227" s="11"/>
     </row>
-    <row r="228" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
       <c r="B228" s="11"/>
     </row>
-    <row r="229" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
       <c r="B229" s="11"/>
     </row>
-    <row r="230" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
       <c r="B230" s="11"/>
     </row>
-    <row r="231" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
       <c r="B231" s="11"/>
     </row>
-    <row r="232" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6"/>
       <c r="B232" s="11"/>
     </row>
-    <row r="233" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
       <c r="B233" s="11"/>
     </row>
-    <row r="234" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
       <c r="B234" s="11"/>
     </row>
-    <row r="235" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6"/>
       <c r="B235" s="11"/>
     </row>
-    <row r="236" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
       <c r="B236" s="11"/>
     </row>
-    <row r="237" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
       <c r="B237" s="11"/>
     </row>
-    <row r="238" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
       <c r="B238" s="11"/>
     </row>
-    <row r="239" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6"/>
       <c r="B239" s="11"/>
     </row>
-    <row r="240" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6"/>
       <c r="B240" s="11"/>
     </row>
-    <row r="241" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
       <c r="B241" s="11"/>
     </row>
-    <row r="242" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="B242" s="11"/>
     </row>
-    <row r="243" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
       <c r="B243" s="11"/>
     </row>
-    <row r="244" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
       <c r="B244" s="11"/>
     </row>
-    <row r="245" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6"/>
       <c r="B245" s="11"/>
     </row>
-    <row r="246" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
       <c r="B246" s="11"/>
     </row>
-    <row r="247" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
       <c r="B247" s="11"/>
     </row>
-    <row r="248" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
       <c r="B248" s="11"/>
     </row>
-    <row r="249" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6"/>
       <c r="B249" s="11"/>
     </row>
-    <row r="250" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
       <c r="B250" s="11"/>
     </row>
-    <row r="251" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6"/>
       <c r="B251" s="11"/>
     </row>
-    <row r="252" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
       <c r="B252" s="11"/>
     </row>
-    <row r="253" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
       <c r="B253" s="11"/>
     </row>
-    <row r="254" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6"/>
       <c r="B254" s="11"/>
     </row>
-    <row r="255" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6"/>
       <c r="B255" s="11"/>
     </row>
-    <row r="256" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
       <c r="B256" s="11"/>
     </row>
-    <row r="257" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6"/>
       <c r="B257" s="11"/>
     </row>
-    <row r="258" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
       <c r="B258" s="11"/>
     </row>
-    <row r="259" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6"/>
       <c r="B259" s="11"/>
     </row>
-    <row r="260" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6"/>
       <c r="B260" s="11"/>
     </row>
-    <row r="261" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6"/>
       <c r="B261" s="11"/>
     </row>
-    <row r="262" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6"/>
       <c r="B262" s="11"/>
     </row>
-    <row r="263" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6"/>
       <c r="B263" s="11"/>
     </row>
-    <row r="264" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
       <c r="B264" s="11"/>
     </row>
-    <row r="265" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
       <c r="B265" s="11"/>
     </row>
-    <row r="266" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
       <c r="B266" s="11"/>
     </row>
-    <row r="267" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6"/>
       <c r="B267" s="11"/>
     </row>
-    <row r="268" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
       <c r="B268" s="11"/>
     </row>
-    <row r="269" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
       <c r="B269" s="11"/>
     </row>
-    <row r="270" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6"/>
       <c r="B270" s="11"/>
     </row>
-    <row r="271" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6"/>
       <c r="B271" s="11"/>
     </row>
-    <row r="272" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
       <c r="B272" s="11"/>
     </row>
-    <row r="273" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6"/>
       <c r="B273" s="11"/>
     </row>
-    <row r="274" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
       <c r="B274" s="11"/>
     </row>
-    <row r="275" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
       <c r="B275" s="11"/>
     </row>
-    <row r="276" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
       <c r="B276" s="11"/>
     </row>
-    <row r="277" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6"/>
       <c r="B277" s="11"/>
     </row>
-    <row r="278" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
       <c r="B278" s="11"/>
     </row>
-    <row r="279" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
       <c r="B279" s="11"/>
     </row>
-    <row r="280" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
       <c r="B280" s="11"/>
     </row>
-    <row r="281" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6"/>
       <c r="B281" s="11"/>
     </row>
-    <row r="282" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6"/>
       <c r="B282" s="11"/>
     </row>
-    <row r="283" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
       <c r="B283" s="11"/>
     </row>
-    <row r="284" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
       <c r="B284" s="11"/>
     </row>
-    <row r="285" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6"/>
       <c r="B285" s="11"/>
     </row>
-    <row r="286" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
       <c r="B286" s="11"/>
     </row>
-    <row r="287" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6"/>
       <c r="B287" s="11"/>
     </row>
-    <row r="288" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
       <c r="B288" s="11"/>
     </row>
-    <row r="289" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6"/>
       <c r="B289" s="11"/>
     </row>
-    <row r="290" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
       <c r="B290" s="11"/>
     </row>
-    <row r="291" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6"/>
       <c r="B291" s="11"/>
     </row>
-    <row r="292" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6"/>
       <c r="B292" s="11"/>
     </row>
-    <row r="293" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
       <c r="B293" s="11"/>
     </row>
-    <row r="294" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
       <c r="B294" s="11"/>
     </row>
-    <row r="295" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6"/>
       <c r="B295" s="11"/>
     </row>
-    <row r="296" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
       <c r="B296" s="11"/>
     </row>
-    <row r="297" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
       <c r="B297" s="11"/>
     </row>
-    <row r="298" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
       <c r="B298" s="11"/>
     </row>
-    <row r="299" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6"/>
       <c r="B299" s="11"/>
     </row>
-    <row r="300" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6"/>
       <c r="B300" s="11"/>
     </row>
-    <row r="301" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6"/>
       <c r="B301" s="11"/>
     </row>
-    <row r="302" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6"/>
       <c r="B302" s="11"/>
     </row>
-    <row r="303" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6"/>
       <c r="B303" s="11"/>
     </row>
-    <row r="304" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6"/>
       <c r="B304" s="11"/>
     </row>
-    <row r="305" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6"/>
       <c r="B305" s="11"/>
     </row>
-    <row r="306" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6"/>
       <c r="B306" s="11"/>
     </row>
-    <row r="307" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6"/>
       <c r="B307" s="11"/>
     </row>
-    <row r="308" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6"/>
       <c r="B308" s="11"/>
     </row>
-    <row r="309" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="6"/>
       <c r="B309" s="11"/>
     </row>
-    <row r="310" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6"/>
       <c r="B310" s="11"/>
     </row>
-    <row r="311" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="6"/>
       <c r="B311" s="11"/>
     </row>
-    <row r="312" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6"/>
       <c r="B312" s="11"/>
     </row>
-    <row r="313" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="6"/>
       <c r="B313" s="11"/>
     </row>
-    <row r="314" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6"/>
       <c r="B314" s="11"/>
     </row>
-    <row r="315" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="6"/>
       <c r="B315" s="11"/>
     </row>
-    <row r="316" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="6"/>
       <c r="B316" s="11"/>
     </row>
-    <row r="317" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="6"/>
       <c r="B317" s="11"/>
     </row>
-    <row r="318" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6"/>
       <c r="B318" s="11"/>
     </row>
-    <row r="319" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="6"/>
       <c r="B319" s="11"/>
     </row>
-    <row r="320" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="6"/>
       <c r="B320" s="11"/>
     </row>
-    <row r="321" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6"/>
       <c r="B321" s="11"/>
     </row>
-    <row r="322" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="6"/>
       <c r="B322" s="11"/>
     </row>
-    <row r="323" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="6"/>
       <c r="B323" s="11"/>
     </row>
-    <row r="324" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6"/>
       <c r="B324" s="11"/>
     </row>
-    <row r="325" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="6"/>
       <c r="B325" s="11"/>
     </row>
-    <row r="326" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="6"/>
       <c r="B326" s="11"/>
     </row>
-    <row r="327" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="6"/>
       <c r="B327" s="11"/>
     </row>
-    <row r="328" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="6"/>
       <c r="B328" s="11"/>
     </row>
-    <row r="329" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="6"/>
       <c r="B329" s="11"/>
     </row>
-    <row r="330" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="6"/>
       <c r="B330" s="11"/>
     </row>
-    <row r="331" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="6"/>
       <c r="B331" s="11"/>
     </row>
-    <row r="332" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6"/>
       <c r="B332" s="11"/>
     </row>
-    <row r="333" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="6"/>
       <c r="B333" s="11"/>
     </row>
-    <row r="334" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="6"/>
       <c r="B334" s="11"/>
     </row>
-    <row r="335" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="6"/>
       <c r="B335" s="11"/>
     </row>
-    <row r="336" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="6"/>
       <c r="B336" s="11"/>
     </row>
-    <row r="337" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="6"/>
       <c r="B337" s="11"/>
     </row>
-    <row r="338" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="6"/>
       <c r="B338" s="11"/>
     </row>
-    <row r="339" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="6"/>
       <c r="B339" s="11"/>
     </row>
-    <row r="340" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="6"/>
       <c r="B340" s="11"/>
     </row>
-    <row r="341" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="6"/>
       <c r="B341" s="11"/>
     </row>
-    <row r="342" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="6"/>
       <c r="B342" s="11"/>
     </row>
-    <row r="343" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="6"/>
       <c r="B343" s="11"/>
     </row>
-    <row r="344" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6"/>
       <c r="B344" s="11"/>
     </row>
-    <row r="345" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="6"/>
       <c r="B345" s="11"/>
     </row>
-    <row r="346" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="6"/>
       <c r="B346" s="11"/>
     </row>
-    <row r="347" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="6"/>
       <c r="B347" s="11"/>
     </row>
-    <row r="348" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="6"/>
       <c r="B348" s="11"/>
     </row>
-    <row r="349" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="6"/>
       <c r="B349" s="11"/>
     </row>
-    <row r="350" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="6"/>
       <c r="B350" s="11"/>
     </row>
-    <row r="351" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="6"/>
       <c r="B351" s="11"/>
     </row>
-    <row r="352" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="6"/>
       <c r="B352" s="11"/>
     </row>
-    <row r="353" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="6"/>
       <c r="B353" s="11"/>
     </row>
-    <row r="354" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="6"/>
       <c r="B354" s="11"/>
     </row>
-    <row r="355" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="6"/>
       <c r="B355" s="11"/>
     </row>
-    <row r="356" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="6"/>
       <c r="B356" s="11"/>
     </row>
-    <row r="357" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="6"/>
       <c r="B357" s="11"/>
     </row>
-    <row r="358" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6"/>
       <c r="B358" s="11"/>
     </row>
-    <row r="359" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="6"/>
       <c r="B359" s="11"/>
     </row>
-    <row r="360" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="6"/>
       <c r="B360" s="11"/>
     </row>
-    <row r="361" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="6"/>
       <c r="B361" s="11"/>
     </row>
-    <row r="362" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="6"/>
       <c r="B362" s="11"/>
     </row>
-    <row r="363" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="6"/>
       <c r="B363" s="11"/>
     </row>
-    <row r="364" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="6"/>
       <c r="B364" s="11"/>
     </row>
-    <row r="365" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="6"/>
       <c r="B365" s="11"/>
     </row>
-    <row r="366" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6"/>
       <c r="B366" s="11"/>
     </row>
-    <row r="367" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="6"/>
       <c r="B367" s="11"/>
     </row>
-    <row r="368" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="6"/>
       <c r="B368" s="11"/>
     </row>
-    <row r="369" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="6"/>
       <c r="B369" s="11"/>
     </row>
-    <row r="370" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="6"/>
       <c r="B370" s="11"/>
     </row>
-    <row r="371" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="6"/>
       <c r="B371" s="11"/>
     </row>
-    <row r="372" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="6"/>
       <c r="B372" s="11"/>
     </row>
-    <row r="373" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="6"/>
       <c r="B373" s="11"/>
     </row>
-    <row r="374" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="6"/>
       <c r="B374" s="11"/>
     </row>
-    <row r="375" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="6"/>
       <c r="B375" s="11"/>
     </row>
-    <row r="376" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6"/>
       <c r="B376" s="11"/>
     </row>
-    <row r="377" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="6"/>
       <c r="B377" s="11"/>
     </row>
-    <row r="378" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6"/>
       <c r="B378" s="11"/>
     </row>
-    <row r="379" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="6"/>
       <c r="B379" s="11"/>
     </row>
-    <row r="380" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6"/>
       <c r="B380" s="11"/>
     </row>
-    <row r="381" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="6"/>
       <c r="B381" s="11"/>
     </row>
-    <row r="382" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6"/>
       <c r="B382" s="11"/>
     </row>
-    <row r="383" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="6"/>
       <c r="B383" s="11"/>
     </row>
-    <row r="384" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6"/>
       <c r="B384" s="11"/>
     </row>
-    <row r="385" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="6"/>
       <c r="B385" s="11"/>
     </row>
-    <row r="386" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6"/>
       <c r="B386" s="11"/>
     </row>
-    <row r="387" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6"/>
       <c r="B387" s="11"/>
     </row>
-    <row r="388" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6"/>
       <c r="B388" s="11"/>
     </row>
-    <row r="389" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6"/>
       <c r="B389" s="11"/>
     </row>
-    <row r="390" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6"/>
       <c r="B390" s="11"/>
     </row>
-    <row r="391" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="6"/>
       <c r="B391" s="11"/>
     </row>
-    <row r="392" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6"/>
       <c r="B392" s="11"/>
     </row>
-    <row r="393" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="6"/>
       <c r="B393" s="11"/>
     </row>
-    <row r="394" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="6"/>
       <c r="B394" s="11"/>
     </row>
-    <row r="395" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="6"/>
       <c r="B395" s="11"/>
     </row>
-    <row r="396" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="6"/>
       <c r="B396" s="11"/>
     </row>
-    <row r="397" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="6"/>
       <c r="B397" s="11"/>
     </row>
-    <row r="398" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="6"/>
       <c r="B398" s="11"/>
     </row>
-    <row r="399" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="6"/>
       <c r="B399" s="11"/>
     </row>
-    <row r="400" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6"/>
       <c r="B400" s="11"/>
     </row>
-    <row r="401" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="6"/>
       <c r="B401" s="11"/>
     </row>
-    <row r="402" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="6"/>
       <c r="B402" s="11"/>
     </row>
-    <row r="403" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="6"/>
       <c r="B403" s="11"/>
     </row>
-    <row r="404" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="6"/>
       <c r="B404" s="11"/>
     </row>
-    <row r="405" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="6"/>
       <c r="B405" s="11"/>
     </row>
-    <row r="406" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="6"/>
       <c r="B406" s="11"/>
     </row>
-    <row r="407" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="6"/>
       <c r="B407" s="11"/>
     </row>
-    <row r="408" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="6"/>
       <c r="B408" s="11"/>
     </row>
-    <row r="409" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="6"/>
       <c r="B409" s="11"/>
     </row>
-    <row r="410" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="6"/>
       <c r="B410" s="11"/>
     </row>
-    <row r="411" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="6"/>
       <c r="B411" s="11"/>
     </row>
-    <row r="412" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="6"/>
       <c r="B412" s="11"/>
     </row>
-    <row r="413" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="6"/>
       <c r="B413" s="11"/>
     </row>
-    <row r="414" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="6"/>
       <c r="B414" s="11"/>
     </row>
-    <row r="415" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="6"/>
       <c r="B415" s="11"/>
     </row>
-    <row r="416" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="6"/>
       <c r="B416" s="11"/>
     </row>
-    <row r="417" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6"/>
       <c r="B417" s="11"/>
     </row>
-    <row r="418" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="6"/>
       <c r="B418" s="11"/>
     </row>
-    <row r="419" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="6"/>
       <c r="B419" s="11"/>
     </row>
-    <row r="420" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="6"/>
       <c r="B420" s="11"/>
     </row>
-    <row r="421" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="6"/>
       <c r="B421" s="11"/>
     </row>
-    <row r="422" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="6"/>
       <c r="B422" s="11"/>
     </row>
-    <row r="423" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="6"/>
       <c r="B423" s="11"/>
     </row>
-    <row r="424" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="6"/>
       <c r="B424" s="11"/>
     </row>
-    <row r="425" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="6"/>
       <c r="B425" s="11"/>
     </row>
-    <row r="426" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="6"/>
       <c r="B426" s="11"/>
     </row>
-    <row r="427" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="6"/>
       <c r="B427" s="11"/>
     </row>
-    <row r="428" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="6"/>
       <c r="B428" s="11"/>
     </row>
-    <row r="429" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="6"/>
       <c r="B429" s="11"/>
     </row>
-    <row r="430" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="6"/>
       <c r="B430" s="11"/>
     </row>
-    <row r="431" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="6"/>
       <c r="B431" s="11"/>
     </row>
-    <row r="432" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="6"/>
       <c r="B432" s="11"/>
     </row>
-    <row r="433" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="6"/>
       <c r="B433" s="11"/>
     </row>
-    <row r="434" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="6"/>
       <c r="B434" s="11"/>
     </row>
-    <row r="435" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="6"/>
       <c r="B435" s="11"/>
     </row>
-    <row r="436" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="6"/>
       <c r="B436" s="11"/>
     </row>
-    <row r="437" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="6"/>
       <c r="B437" s="11"/>
     </row>
-    <row r="438" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="6"/>
       <c r="B438" s="11"/>
     </row>
-    <row r="439" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="6"/>
       <c r="B439" s="11"/>
     </row>
-    <row r="440" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="6"/>
       <c r="B440" s="11"/>
     </row>
-    <row r="441" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="6"/>
       <c r="B441" s="11"/>
     </row>
-    <row r="442" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="6"/>
       <c r="B442" s="11"/>
     </row>
-    <row r="443" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="6"/>
       <c r="B443" s="11"/>
     </row>
-    <row r="444" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="6"/>
       <c r="B444" s="11"/>
     </row>
-    <row r="445" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="6"/>
       <c r="B445" s="11"/>
     </row>
-    <row r="446" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="6"/>
       <c r="B446" s="11"/>
     </row>
-    <row r="447" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="6"/>
       <c r="B447" s="11"/>
     </row>
-    <row r="448" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="6"/>
       <c r="B448" s="11"/>
     </row>
-    <row r="449" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="6"/>
       <c r="B449" s="11"/>
     </row>
-    <row r="450" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="6"/>
       <c r="B450" s="11"/>
     </row>
-    <row r="451" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="6"/>
       <c r="B451" s="11"/>
     </row>
-    <row r="452" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="6"/>
       <c r="B452" s="11"/>
     </row>
-    <row r="453" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="6"/>
       <c r="B453" s="11"/>
     </row>
-    <row r="454" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="6"/>
       <c r="B454" s="11"/>
     </row>
-    <row r="455" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="6"/>
       <c r="B455" s="11"/>
     </row>
-    <row r="456" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="6"/>
       <c r="B456" s="11"/>
     </row>
-    <row r="457" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="6"/>
       <c r="B457" s="11"/>
     </row>
-    <row r="458" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="6"/>
       <c r="B458" s="11"/>
     </row>
-    <row r="459" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="6"/>
       <c r="B459" s="11"/>
     </row>
-    <row r="460" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="6"/>
       <c r="B460" s="11"/>
     </row>
-    <row r="461" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="6"/>
       <c r="B461" s="11"/>
     </row>
-    <row r="462" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="6"/>
       <c r="B462" s="11"/>
     </row>
-    <row r="463" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="6"/>
       <c r="B463" s="11"/>
     </row>
-    <row r="464" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="6"/>
       <c r="B464" s="11"/>
     </row>
-    <row r="465" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="6"/>
       <c r="B465" s="11"/>
     </row>
-    <row r="466" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="6"/>
       <c r="B466" s="11"/>
     </row>
-    <row r="467" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="6"/>
       <c r="B467" s="11"/>
     </row>
-    <row r="468" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="6"/>
       <c r="B468" s="11"/>
     </row>
-    <row r="469" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="6"/>
       <c r="B469" s="11"/>
     </row>
-    <row r="470" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="6"/>
       <c r="B470" s="11"/>
     </row>
-    <row r="471" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="6"/>
       <c r="B471" s="11"/>
     </row>
-    <row r="472" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="6"/>
       <c r="B472" s="11"/>
     </row>
-    <row r="473" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="6"/>
       <c r="B473" s="11"/>
     </row>
-    <row r="474" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="6"/>
       <c r="B474" s="11"/>
     </row>
-    <row r="475" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="6"/>
       <c r="B475" s="11"/>
     </row>
-    <row r="476" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6"/>
       <c r="B476" s="11"/>
     </row>
-    <row r="477" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="6"/>
       <c r="B477" s="11"/>
     </row>
-    <row r="478" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="6"/>
       <c r="B478" s="11"/>
     </row>
-    <row r="479" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="6"/>
       <c r="B479" s="11"/>
     </row>
-    <row r="480" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="6"/>
       <c r="B480" s="11"/>
     </row>
-    <row r="481" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="6"/>
       <c r="B481" s="11"/>
     </row>
-    <row r="482" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="6"/>
       <c r="B482" s="11"/>
     </row>
-    <row r="483" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="6"/>
       <c r="B483" s="11"/>
     </row>
-    <row r="484" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="6"/>
       <c r="B484" s="11"/>
     </row>
-    <row r="485" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="6"/>
       <c r="B485" s="11"/>
     </row>
-    <row r="486" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="6"/>
       <c r="B486" s="11"/>
     </row>
-    <row r="487" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="6"/>
       <c r="B487" s="11"/>
     </row>
-    <row r="488" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="6"/>
       <c r="B488" s="11"/>
     </row>
-    <row r="489" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="6"/>
       <c r="B489" s="11"/>
     </row>
-    <row r="490" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="6"/>
       <c r="B490" s="11"/>
     </row>
-    <row r="491" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="6"/>
       <c r="B491" s="11"/>
     </row>
-    <row r="492" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="6"/>
       <c r="B492" s="11"/>
     </row>
-    <row r="493" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="6"/>
       <c r="B493" s="11"/>
     </row>
-    <row r="494" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="6"/>
       <c r="B494" s="11"/>
     </row>
-    <row r="495" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="6"/>
       <c r="B495" s="11"/>
     </row>
-    <row r="496" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="6"/>
       <c r="B496" s="11"/>
     </row>
-    <row r="497" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="6"/>
       <c r="B497" s="11"/>
     </row>
-    <row r="498" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="6"/>
       <c r="B498" s="11"/>
     </row>
-    <row r="499" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="6"/>
       <c r="B499" s="11"/>
     </row>
-    <row r="500" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="6"/>
       <c r="B500" s="11"/>
     </row>
@@ -8053,52 +8120,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E34FD7-1B73-4707-A12E-62E00BDCA8A2}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EA0C99-9679-4870-8B23-42C377AD509E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BC1F10-8274-468D-A11F-0659CCCD57A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="0" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
   <si>
     <t>Jour</t>
   </si>
@@ -126,6 +126,36 @@
   </si>
   <si>
     <t>Coup d'œil sur les spécificités du projet</t>
+  </si>
+  <si>
+    <t>Réunion debrief avec le chef de projet</t>
+  </si>
+  <si>
+    <t>Questions/Réponses + Clarification de détails CDC</t>
+  </si>
+  <si>
+    <t>Discussion sur l'application map</t>
+  </si>
+  <si>
+    <t>Dictionnaire de données pour le MCD/MLD</t>
+  </si>
+  <si>
+    <t>Diffusion du MCD/MLD</t>
+  </si>
+  <si>
+    <t>Aucune question de la part de l'équipe</t>
+  </si>
+  <si>
+    <t>Changement du format de rendu rapport de projet</t>
+  </si>
+  <si>
+    <t>Passage sur .docx</t>
+  </si>
+  <si>
+    <t>Ajout d'une nouvelle table demandée</t>
+  </si>
+  <si>
+    <t>Finalisation</t>
   </si>
 </sst>
 </file>
@@ -841,19 +871,19 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>2.2999999999999998</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -1564,8 +1594,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}" name="Tableau1" displayName="Tableau1" ref="A1:F301" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:F301" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}" name="Tableau1" displayName="Tableau1" ref="A1:F303" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:F303" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F1048576">
     <sortCondition descending="1" ref="D1:D1048576"/>
   </sortState>
@@ -1871,18 +1901,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F501"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F503"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.59765625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="13.3984375" style="15" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="24.69921875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="15.25" style="12" customWidth="1"/>
+    <col min="4" max="4" width="24.75" style="5" customWidth="1"/>
     <col min="5" max="5" width="68.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="82.19921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="82.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1902,7 +1932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>46035</v>
       </c>
@@ -1920,7 +1950,7 @@
       </c>
       <c r="F2" s="8"/>
     </row>
-    <row r="3" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>46035</v>
       </c>
@@ -1928,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="11">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>9</v>
@@ -1938,7 +1968,7 @@
       </c>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>46036</v>
       </c>
@@ -1946,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="11">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>11</v>
@@ -1958,7 +1988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>46036</v>
       </c>
@@ -1976,7 +2006,7 @@
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>46036</v>
       </c>
@@ -1996,7 +2026,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>46036</v>
       </c>
@@ -2016,7 +2046,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>46037</v>
       </c>
@@ -2024,7 +2054,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="11">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>7</v>
@@ -2034,7 +2064,7 @@
       </c>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>46037</v>
       </c>
@@ -2054,7 +2084,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>46037</v>
       </c>
@@ -2074,7 +2104,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>46037</v>
       </c>
@@ -2092,63 +2122,143 @@
       </c>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
+    <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <v>46038</v>
+      </c>
+      <c r="B12" s="14">
+        <v>1</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
+    <row r="13" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>46038</v>
+      </c>
+      <c r="B13" s="14">
+        <v>1</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
+        <v>46038</v>
+      </c>
+      <c r="B14" s="14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <v>46038</v>
+      </c>
+      <c r="B15" s="14">
+        <v>1</v>
+      </c>
+      <c r="C15" s="11">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <v>46038</v>
+      </c>
+      <c r="B16" s="14">
+        <v>1</v>
+      </c>
+      <c r="C16" s="11">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <v>46038</v>
+      </c>
+      <c r="B17" s="14">
+        <v>1</v>
+      </c>
+      <c r="C17" s="11">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <v>46041</v>
+      </c>
+      <c r="B18" s="14">
+        <v>2</v>
+      </c>
+      <c r="C18" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="14"/>
       <c r="C19" s="11"/>
@@ -2156,7 +2266,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="14"/>
       <c r="C20" s="11"/>
@@ -2164,7 +2274,7 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="14"/>
       <c r="C21" s="11"/>
@@ -2172,7 +2282,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="14"/>
       <c r="C22" s="11"/>
@@ -2180,7 +2290,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="14"/>
       <c r="C23" s="11"/>
@@ -2188,7 +2298,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="14"/>
       <c r="C24" s="11"/>
@@ -2196,7 +2306,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="14"/>
       <c r="C25" s="11"/>
@@ -2204,7 +2314,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="14"/>
       <c r="C26" s="11"/>
@@ -2212,7 +2322,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="14"/>
       <c r="C27" s="11"/>
@@ -2220,7 +2330,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="14"/>
       <c r="C28" s="11"/>
@@ -2228,7 +2338,7 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="14"/>
       <c r="C29" s="11"/>
@@ -2236,7 +2346,7 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="14"/>
       <c r="C30" s="11"/>
@@ -2244,7 +2354,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="14"/>
       <c r="C31" s="11"/>
@@ -2252,7 +2362,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="14"/>
       <c r="C32" s="11"/>
@@ -2260,7 +2370,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="14"/>
       <c r="C33" s="11"/>
@@ -2268,7 +2378,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="14"/>
       <c r="C34" s="11"/>
@@ -2276,7 +2386,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="14"/>
       <c r="C35" s="11"/>
@@ -2284,7 +2394,7 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="14"/>
       <c r="C36" s="11"/>
@@ -2292,7 +2402,7 @@
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="14"/>
       <c r="C37" s="11"/>
@@ -2300,7 +2410,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="14"/>
       <c r="C38" s="11"/>
@@ -2308,7 +2418,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="14"/>
       <c r="C39" s="11"/>
@@ -2316,7 +2426,7 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="14"/>
       <c r="C40" s="11"/>
@@ -2324,7 +2434,7 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
     </row>
-    <row r="41" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="14"/>
       <c r="C41" s="11"/>
@@ -2332,7 +2442,7 @@
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="14"/>
       <c r="C42" s="11"/>
@@ -2340,7 +2450,7 @@
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="43" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="14"/>
       <c r="C43" s="11"/>
@@ -2348,7 +2458,7 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="14"/>
       <c r="C44" s="11"/>
@@ -2356,7 +2466,7 @@
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="14"/>
       <c r="C45" s="11"/>
@@ -2364,7 +2474,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
     </row>
-    <row r="46" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="14"/>
       <c r="C46" s="11"/>
@@ -2372,7 +2482,7 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="14"/>
       <c r="C47" s="11"/>
@@ -2380,7 +2490,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="14"/>
       <c r="C48" s="11"/>
@@ -2388,7 +2498,7 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
     </row>
-    <row r="49" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="14"/>
       <c r="C49" s="11"/>
@@ -2396,7 +2506,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="14"/>
       <c r="C50" s="11"/>
@@ -2404,7 +2514,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
     </row>
-    <row r="51" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="14"/>
       <c r="C51" s="11"/>
@@ -2412,7 +2522,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="14"/>
       <c r="C52" s="11"/>
@@ -2420,7 +2530,7 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
     </row>
-    <row r="53" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="14"/>
       <c r="C53" s="11"/>
@@ -2428,7 +2538,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="14"/>
       <c r="C54" s="11"/>
@@ -2436,7 +2546,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="14"/>
       <c r="C55" s="11"/>
@@ -2444,7 +2554,7 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
     </row>
-    <row r="56" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="14"/>
       <c r="C56" s="11"/>
@@ -2452,7 +2562,7 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="14"/>
       <c r="C57" s="11"/>
@@ -2460,7 +2570,7 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
     </row>
-    <row r="58" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="14"/>
       <c r="C58" s="11"/>
@@ -2468,7 +2578,7 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
     </row>
-    <row r="59" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="14"/>
       <c r="C59" s="11"/>
@@ -2476,7 +2586,7 @@
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
     </row>
-    <row r="60" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="14"/>
       <c r="C60" s="11"/>
@@ -2484,7 +2594,7 @@
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="14"/>
       <c r="C61" s="11"/>
@@ -2492,7 +2602,7 @@
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
     </row>
-    <row r="62" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="14"/>
       <c r="C62" s="11"/>
@@ -2500,7 +2610,7 @@
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
     </row>
-    <row r="63" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="14"/>
       <c r="C63" s="11"/>
@@ -2508,7 +2618,7 @@
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
     </row>
-    <row r="64" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="14"/>
       <c r="C64" s="11"/>
@@ -2516,7 +2626,7 @@
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
     </row>
-    <row r="65" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="14"/>
       <c r="C65" s="11"/>
@@ -2524,7 +2634,7 @@
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
     </row>
-    <row r="66" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="14"/>
       <c r="C66" s="11"/>
@@ -2532,7 +2642,7 @@
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
     </row>
-    <row r="67" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="14"/>
       <c r="C67" s="11"/>
@@ -2540,7 +2650,7 @@
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
     </row>
-    <row r="68" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="14"/>
       <c r="C68" s="11"/>
@@ -2548,7 +2658,7 @@
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
     </row>
-    <row r="69" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="14"/>
       <c r="C69" s="11"/>
@@ -2556,7 +2666,7 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
     </row>
-    <row r="70" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="14"/>
       <c r="C70" s="11"/>
@@ -2564,7 +2674,7 @@
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
     </row>
-    <row r="71" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
       <c r="B71" s="14"/>
       <c r="C71" s="11"/>
@@ -2572,7 +2682,7 @@
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
     </row>
-    <row r="72" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="14"/>
       <c r="C72" s="11"/>
@@ -2580,7 +2690,7 @@
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
     </row>
-    <row r="73" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="14"/>
       <c r="C73" s="11"/>
@@ -2588,7 +2698,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
     </row>
-    <row r="74" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="14"/>
       <c r="C74" s="11"/>
@@ -2596,7 +2706,7 @@
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
     </row>
-    <row r="75" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="14"/>
       <c r="C75" s="11"/>
@@ -2604,7 +2714,7 @@
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
     </row>
-    <row r="76" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="14"/>
       <c r="C76" s="11"/>
@@ -2612,7 +2722,7 @@
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
     </row>
-    <row r="77" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="14"/>
       <c r="C77" s="11"/>
@@ -2620,7 +2730,7 @@
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
     </row>
-    <row r="78" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="14"/>
       <c r="C78" s="11"/>
@@ -2628,7 +2738,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
     </row>
-    <row r="79" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="14"/>
       <c r="C79" s="11"/>
@@ -2636,7 +2746,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
     </row>
-    <row r="80" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="14"/>
       <c r="C80" s="11"/>
@@ -2644,7 +2754,7 @@
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
     </row>
-    <row r="81" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="14"/>
       <c r="C81" s="11"/>
@@ -2652,7 +2762,7 @@
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
     </row>
-    <row r="82" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="14"/>
       <c r="C82" s="11"/>
@@ -2660,7 +2770,7 @@
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
     </row>
-    <row r="83" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="14"/>
       <c r="C83" s="11"/>
@@ -2668,7 +2778,7 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
     </row>
-    <row r="84" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="14"/>
       <c r="C84" s="11"/>
@@ -2676,7 +2786,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
     </row>
-    <row r="85" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="14"/>
       <c r="C85" s="11"/>
@@ -2684,7 +2794,7 @@
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
     </row>
-    <row r="86" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="14"/>
       <c r="C86" s="11"/>
@@ -2692,7 +2802,7 @@
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
     </row>
-    <row r="87" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="14"/>
       <c r="C87" s="11"/>
@@ -2700,7 +2810,7 @@
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
     </row>
-    <row r="88" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="14"/>
       <c r="C88" s="11"/>
@@ -2708,7 +2818,7 @@
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
     </row>
-    <row r="89" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="14"/>
       <c r="C89" s="11"/>
@@ -2716,7 +2826,7 @@
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
     </row>
-    <row r="90" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="14"/>
       <c r="C90" s="11"/>
@@ -2724,7 +2834,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
     </row>
-    <row r="91" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="14"/>
       <c r="C91" s="11"/>
@@ -2732,7 +2842,7 @@
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
     </row>
-    <row r="92" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="14"/>
       <c r="C92" s="11"/>
@@ -2740,7 +2850,7 @@
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
     </row>
-    <row r="93" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="14"/>
       <c r="C93" s="11"/>
@@ -2748,7 +2858,7 @@
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
     </row>
-    <row r="94" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="14"/>
       <c r="C94" s="11"/>
@@ -2756,7 +2866,7 @@
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
     </row>
-    <row r="95" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="14"/>
       <c r="C95" s="11"/>
@@ -2764,7 +2874,7 @@
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
     </row>
-    <row r="96" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="14"/>
       <c r="C96" s="11"/>
@@ -2772,7 +2882,7 @@
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
     </row>
-    <row r="97" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="14"/>
       <c r="C97" s="11"/>
@@ -2780,7 +2890,7 @@
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
     </row>
-    <row r="98" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="14"/>
       <c r="C98" s="11"/>
@@ -2788,7 +2898,7 @@
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
     </row>
-    <row r="99" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="14"/>
       <c r="C99" s="11"/>
@@ -2796,7 +2906,7 @@
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
     </row>
-    <row r="100" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="14"/>
       <c r="C100" s="11"/>
@@ -2804,7 +2914,7 @@
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
     </row>
-    <row r="101" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
       <c r="B101" s="14"/>
       <c r="C101" s="11"/>
@@ -2812,7 +2922,7 @@
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
     </row>
-    <row r="102" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="14"/>
       <c r="C102" s="11"/>
@@ -2820,7 +2930,7 @@
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
     </row>
-    <row r="103" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="14"/>
       <c r="C103" s="11"/>
@@ -2828,7 +2938,7 @@
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
     </row>
-    <row r="104" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6"/>
       <c r="B104" s="14"/>
       <c r="C104" s="11"/>
@@ -2836,7 +2946,7 @@
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
     </row>
-    <row r="105" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6"/>
       <c r="B105" s="14"/>
       <c r="C105" s="11"/>
@@ -2844,7 +2954,7 @@
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
     </row>
-    <row r="106" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6"/>
       <c r="B106" s="14"/>
       <c r="C106" s="11"/>
@@ -2852,7 +2962,7 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
     </row>
-    <row r="107" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="B107" s="14"/>
       <c r="C107" s="11"/>
@@ -2860,7 +2970,7 @@
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
     </row>
-    <row r="108" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="B108" s="14"/>
       <c r="C108" s="11"/>
@@ -2868,7 +2978,7 @@
       <c r="E108" s="8"/>
       <c r="F108" s="8"/>
     </row>
-    <row r="109" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="B109" s="14"/>
       <c r="C109" s="11"/>
@@ -2876,7 +2986,7 @@
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
     </row>
-    <row r="110" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="B110" s="14"/>
       <c r="C110" s="11"/>
@@ -2884,7 +2994,7 @@
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
     </row>
-    <row r="111" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6"/>
       <c r="B111" s="14"/>
       <c r="C111" s="11"/>
@@ -2892,7 +3002,7 @@
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
     </row>
-    <row r="112" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6"/>
       <c r="B112" s="14"/>
       <c r="C112" s="11"/>
@@ -2900,7 +3010,7 @@
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
     </row>
-    <row r="113" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
       <c r="B113" s="14"/>
       <c r="C113" s="11"/>
@@ -2908,7 +3018,7 @@
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
     </row>
-    <row r="114" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6"/>
       <c r="B114" s="14"/>
       <c r="C114" s="11"/>
@@ -2916,7 +3026,7 @@
       <c r="E114" s="8"/>
       <c r="F114" s="8"/>
     </row>
-    <row r="115" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6"/>
       <c r="B115" s="14"/>
       <c r="C115" s="11"/>
@@ -2924,7 +3034,7 @@
       <c r="E115" s="8"/>
       <c r="F115" s="8"/>
     </row>
-    <row r="116" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6"/>
       <c r="B116" s="14"/>
       <c r="C116" s="11"/>
@@ -2932,7 +3042,7 @@
       <c r="E116" s="8"/>
       <c r="F116" s="8"/>
     </row>
-    <row r="117" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6"/>
       <c r="B117" s="14"/>
       <c r="C117" s="11"/>
@@ -2940,7 +3050,7 @@
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
     </row>
-    <row r="118" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6"/>
       <c r="B118" s="14"/>
       <c r="C118" s="11"/>
@@ -2948,7 +3058,7 @@
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
     </row>
-    <row r="119" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6"/>
       <c r="B119" s="14"/>
       <c r="C119" s="11"/>
@@ -2956,7 +3066,7 @@
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
     </row>
-    <row r="120" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6"/>
       <c r="B120" s="14"/>
       <c r="C120" s="11"/>
@@ -2964,7 +3074,7 @@
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
     </row>
-    <row r="121" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6"/>
       <c r="B121" s="14"/>
       <c r="C121" s="11"/>
@@ -2972,7 +3082,7 @@
       <c r="E121" s="8"/>
       <c r="F121" s="8"/>
     </row>
-    <row r="122" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6"/>
       <c r="B122" s="14"/>
       <c r="C122" s="11"/>
@@ -2980,7 +3090,7 @@
       <c r="E122" s="8"/>
       <c r="F122" s="8"/>
     </row>
-    <row r="123" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6"/>
       <c r="B123" s="14"/>
       <c r="C123" s="11"/>
@@ -2988,7 +3098,7 @@
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
     </row>
-    <row r="124" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6"/>
       <c r="B124" s="14"/>
       <c r="C124" s="11"/>
@@ -2996,7 +3106,7 @@
       <c r="E124" s="8"/>
       <c r="F124" s="8"/>
     </row>
-    <row r="125" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6"/>
       <c r="B125" s="14"/>
       <c r="C125" s="11"/>
@@ -3004,7 +3114,7 @@
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
     </row>
-    <row r="126" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6"/>
       <c r="B126" s="14"/>
       <c r="C126" s="11"/>
@@ -3012,7 +3122,7 @@
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
     </row>
-    <row r="127" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6"/>
       <c r="B127" s="14"/>
       <c r="C127" s="11"/>
@@ -3020,7 +3130,7 @@
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
     </row>
-    <row r="128" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6"/>
       <c r="B128" s="14"/>
       <c r="C128" s="11"/>
@@ -3028,7 +3138,7 @@
       <c r="E128" s="8"/>
       <c r="F128" s="8"/>
     </row>
-    <row r="129" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6"/>
       <c r="B129" s="14"/>
       <c r="C129" s="11"/>
@@ -3036,7 +3146,7 @@
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
     </row>
-    <row r="130" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6"/>
       <c r="B130" s="14"/>
       <c r="C130" s="11"/>
@@ -3044,7 +3154,7 @@
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
     </row>
-    <row r="131" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6"/>
       <c r="B131" s="14"/>
       <c r="C131" s="11"/>
@@ -3052,7 +3162,7 @@
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
     </row>
-    <row r="132" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6"/>
       <c r="B132" s="14"/>
       <c r="C132" s="11"/>
@@ -3060,7 +3170,7 @@
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
     </row>
-    <row r="133" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6"/>
       <c r="B133" s="14"/>
       <c r="C133" s="11"/>
@@ -3068,7 +3178,7 @@
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
     </row>
-    <row r="134" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6"/>
       <c r="B134" s="14"/>
       <c r="C134" s="11"/>
@@ -3076,7 +3186,7 @@
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
     </row>
-    <row r="135" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6"/>
       <c r="B135" s="14"/>
       <c r="C135" s="11"/>
@@ -3084,7 +3194,7 @@
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
     </row>
-    <row r="136" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6"/>
       <c r="B136" s="14"/>
       <c r="C136" s="11"/>
@@ -3092,7 +3202,7 @@
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
     </row>
-    <row r="137" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6"/>
       <c r="B137" s="14"/>
       <c r="C137" s="11"/>
@@ -3100,7 +3210,7 @@
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
     </row>
-    <row r="138" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6"/>
       <c r="B138" s="14"/>
       <c r="C138" s="11"/>
@@ -3108,7 +3218,7 @@
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
     </row>
-    <row r="139" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6"/>
       <c r="B139" s="14"/>
       <c r="C139" s="11"/>
@@ -3116,7 +3226,7 @@
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
     </row>
-    <row r="140" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6"/>
       <c r="B140" s="14"/>
       <c r="C140" s="11"/>
@@ -3124,7 +3234,7 @@
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
     </row>
-    <row r="141" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6"/>
       <c r="B141" s="14"/>
       <c r="C141" s="11"/>
@@ -3132,7 +3242,7 @@
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
     </row>
-    <row r="142" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6"/>
       <c r="B142" s="14"/>
       <c r="C142" s="11"/>
@@ -3140,7 +3250,7 @@
       <c r="E142" s="8"/>
       <c r="F142" s="8"/>
     </row>
-    <row r="143" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6"/>
       <c r="B143" s="14"/>
       <c r="C143" s="11"/>
@@ -3148,7 +3258,7 @@
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
     </row>
-    <row r="144" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6"/>
       <c r="B144" s="14"/>
       <c r="C144" s="11"/>
@@ -3156,7 +3266,7 @@
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
     </row>
-    <row r="145" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6"/>
       <c r="B145" s="14"/>
       <c r="C145" s="11"/>
@@ -3164,7 +3274,7 @@
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
     </row>
-    <row r="146" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6"/>
       <c r="B146" s="14"/>
       <c r="C146" s="11"/>
@@ -3172,7 +3282,7 @@
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
     </row>
-    <row r="147" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6"/>
       <c r="B147" s="14"/>
       <c r="C147" s="11"/>
@@ -3180,7 +3290,7 @@
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
     </row>
-    <row r="148" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6"/>
       <c r="B148" s="14"/>
       <c r="C148" s="11"/>
@@ -3188,7 +3298,7 @@
       <c r="E148" s="8"/>
       <c r="F148" s="8"/>
     </row>
-    <row r="149" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6"/>
       <c r="B149" s="14"/>
       <c r="C149" s="11"/>
@@ -3196,7 +3306,7 @@
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
     </row>
-    <row r="150" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6"/>
       <c r="B150" s="14"/>
       <c r="C150" s="11"/>
@@ -3204,7 +3314,7 @@
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
     </row>
-    <row r="151" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6"/>
       <c r="B151" s="14"/>
       <c r="C151" s="11"/>
@@ -3212,7 +3322,7 @@
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
     </row>
-    <row r="152" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6"/>
       <c r="B152" s="14"/>
       <c r="C152" s="11"/>
@@ -3220,7 +3330,7 @@
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
     </row>
-    <row r="153" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6"/>
       <c r="B153" s="14"/>
       <c r="C153" s="11"/>
@@ -3228,7 +3338,7 @@
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
     </row>
-    <row r="154" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6"/>
       <c r="B154" s="14"/>
       <c r="C154" s="11"/>
@@ -3236,7 +3346,7 @@
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
     </row>
-    <row r="155" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6"/>
       <c r="B155" s="14"/>
       <c r="C155" s="11"/>
@@ -3244,7 +3354,7 @@
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
     </row>
-    <row r="156" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6"/>
       <c r="B156" s="14"/>
       <c r="C156" s="11"/>
@@ -3252,7 +3362,7 @@
       <c r="E156" s="8"/>
       <c r="F156" s="8"/>
     </row>
-    <row r="157" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6"/>
       <c r="B157" s="14"/>
       <c r="C157" s="11"/>
@@ -3260,7 +3370,7 @@
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
     </row>
-    <row r="158" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6"/>
       <c r="B158" s="14"/>
       <c r="C158" s="11"/>
@@ -3268,7 +3378,7 @@
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
     </row>
-    <row r="159" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6"/>
       <c r="B159" s="14"/>
       <c r="C159" s="11"/>
@@ -3276,7 +3386,7 @@
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
     </row>
-    <row r="160" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6"/>
       <c r="B160" s="14"/>
       <c r="C160" s="11"/>
@@ -3284,7 +3394,7 @@
       <c r="E160" s="8"/>
       <c r="F160" s="8"/>
     </row>
-    <row r="161" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6"/>
       <c r="B161" s="14"/>
       <c r="C161" s="11"/>
@@ -3292,7 +3402,7 @@
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
     </row>
-    <row r="162" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6"/>
       <c r="B162" s="14"/>
       <c r="C162" s="11"/>
@@ -3300,7 +3410,7 @@
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
     </row>
-    <row r="163" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6"/>
       <c r="B163" s="14"/>
       <c r="C163" s="11"/>
@@ -3308,7 +3418,7 @@
       <c r="E163" s="8"/>
       <c r="F163" s="8"/>
     </row>
-    <row r="164" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6"/>
       <c r="B164" s="14"/>
       <c r="C164" s="11"/>
@@ -3316,7 +3426,7 @@
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
     </row>
-    <row r="165" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6"/>
       <c r="B165" s="14"/>
       <c r="C165" s="11"/>
@@ -3324,7 +3434,7 @@
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
     </row>
-    <row r="166" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6"/>
       <c r="B166" s="14"/>
       <c r="C166" s="11"/>
@@ -3332,7 +3442,7 @@
       <c r="E166" s="8"/>
       <c r="F166" s="8"/>
     </row>
-    <row r="167" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6"/>
       <c r="B167" s="14"/>
       <c r="C167" s="11"/>
@@ -3340,7 +3450,7 @@
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
     </row>
-    <row r="168" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6"/>
       <c r="B168" s="14"/>
       <c r="C168" s="11"/>
@@ -3348,7 +3458,7 @@
       <c r="E168" s="8"/>
       <c r="F168" s="8"/>
     </row>
-    <row r="169" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6"/>
       <c r="B169" s="14"/>
       <c r="C169" s="11"/>
@@ -3356,7 +3466,7 @@
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
     </row>
-    <row r="170" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6"/>
       <c r="B170" s="14"/>
       <c r="C170" s="11"/>
@@ -3364,7 +3474,7 @@
       <c r="E170" s="8"/>
       <c r="F170" s="8"/>
     </row>
-    <row r="171" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6"/>
       <c r="B171" s="14"/>
       <c r="C171" s="11"/>
@@ -3372,7 +3482,7 @@
       <c r="E171" s="8"/>
       <c r="F171" s="8"/>
     </row>
-    <row r="172" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6"/>
       <c r="B172" s="14"/>
       <c r="C172" s="11"/>
@@ -3380,7 +3490,7 @@
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
     </row>
-    <row r="173" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6"/>
       <c r="B173" s="14"/>
       <c r="C173" s="11"/>
@@ -3388,7 +3498,7 @@
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
     </row>
-    <row r="174" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6"/>
       <c r="B174" s="14"/>
       <c r="C174" s="11"/>
@@ -3396,7 +3506,7 @@
       <c r="E174" s="8"/>
       <c r="F174" s="8"/>
     </row>
-    <row r="175" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6"/>
       <c r="B175" s="14"/>
       <c r="C175" s="11"/>
@@ -3404,7 +3514,7 @@
       <c r="E175" s="8"/>
       <c r="F175" s="8"/>
     </row>
-    <row r="176" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6"/>
       <c r="B176" s="14"/>
       <c r="C176" s="11"/>
@@ -3412,7 +3522,7 @@
       <c r="E176" s="8"/>
       <c r="F176" s="8"/>
     </row>
-    <row r="177" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6"/>
       <c r="B177" s="14"/>
       <c r="C177" s="11"/>
@@ -3420,7 +3530,7 @@
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
     </row>
-    <row r="178" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6"/>
       <c r="B178" s="14"/>
       <c r="C178" s="11"/>
@@ -3428,7 +3538,7 @@
       <c r="E178" s="8"/>
       <c r="F178" s="8"/>
     </row>
-    <row r="179" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6"/>
       <c r="B179" s="14"/>
       <c r="C179" s="11"/>
@@ -3436,7 +3546,7 @@
       <c r="E179" s="8"/>
       <c r="F179" s="8"/>
     </row>
-    <row r="180" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6"/>
       <c r="B180" s="14"/>
       <c r="C180" s="11"/>
@@ -3444,7 +3554,7 @@
       <c r="E180" s="8"/>
       <c r="F180" s="8"/>
     </row>
-    <row r="181" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6"/>
       <c r="B181" s="14"/>
       <c r="C181" s="11"/>
@@ -3452,7 +3562,7 @@
       <c r="E181" s="8"/>
       <c r="F181" s="8"/>
     </row>
-    <row r="182" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6"/>
       <c r="B182" s="14"/>
       <c r="C182" s="11"/>
@@ -3460,7 +3570,7 @@
       <c r="E182" s="8"/>
       <c r="F182" s="8"/>
     </row>
-    <row r="183" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6"/>
       <c r="B183" s="14"/>
       <c r="C183" s="11"/>
@@ -3468,7 +3578,7 @@
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
     </row>
-    <row r="184" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6"/>
       <c r="B184" s="14"/>
       <c r="C184" s="11"/>
@@ -3476,7 +3586,7 @@
       <c r="E184" s="8"/>
       <c r="F184" s="8"/>
     </row>
-    <row r="185" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6"/>
       <c r="B185" s="14"/>
       <c r="C185" s="11"/>
@@ -3484,7 +3594,7 @@
       <c r="E185" s="8"/>
       <c r="F185" s="8"/>
     </row>
-    <row r="186" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6"/>
       <c r="B186" s="14"/>
       <c r="C186" s="11"/>
@@ -3492,7 +3602,7 @@
       <c r="E186" s="8"/>
       <c r="F186" s="8"/>
     </row>
-    <row r="187" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6"/>
       <c r="B187" s="14"/>
       <c r="C187" s="11"/>
@@ -3500,7 +3610,7 @@
       <c r="E187" s="8"/>
       <c r="F187" s="8"/>
     </row>
-    <row r="188" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6"/>
       <c r="B188" s="14"/>
       <c r="C188" s="11"/>
@@ -3508,7 +3618,7 @@
       <c r="E188" s="8"/>
       <c r="F188" s="8"/>
     </row>
-    <row r="189" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6"/>
       <c r="B189" s="14"/>
       <c r="C189" s="11"/>
@@ -3516,7 +3626,7 @@
       <c r="E189" s="8"/>
       <c r="F189" s="8"/>
     </row>
-    <row r="190" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6"/>
       <c r="B190" s="14"/>
       <c r="C190" s="11"/>
@@ -3524,7 +3634,7 @@
       <c r="E190" s="8"/>
       <c r="F190" s="8"/>
     </row>
-    <row r="191" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6"/>
       <c r="B191" s="14"/>
       <c r="C191" s="11"/>
@@ -3532,7 +3642,7 @@
       <c r="E191" s="8"/>
       <c r="F191" s="8"/>
     </row>
-    <row r="192" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6"/>
       <c r="B192" s="14"/>
       <c r="C192" s="11"/>
@@ -3540,7 +3650,7 @@
       <c r="E192" s="8"/>
       <c r="F192" s="8"/>
     </row>
-    <row r="193" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6"/>
       <c r="B193" s="14"/>
       <c r="C193" s="11"/>
@@ -3548,7 +3658,7 @@
       <c r="E193" s="8"/>
       <c r="F193" s="8"/>
     </row>
-    <row r="194" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6"/>
       <c r="B194" s="14"/>
       <c r="C194" s="11"/>
@@ -3556,7 +3666,7 @@
       <c r="E194" s="8"/>
       <c r="F194" s="8"/>
     </row>
-    <row r="195" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6"/>
       <c r="B195" s="14"/>
       <c r="C195" s="11"/>
@@ -3564,7 +3674,7 @@
       <c r="E195" s="8"/>
       <c r="F195" s="8"/>
     </row>
-    <row r="196" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6"/>
       <c r="B196" s="14"/>
       <c r="C196" s="11"/>
@@ -3572,7 +3682,7 @@
       <c r="E196" s="8"/>
       <c r="F196" s="8"/>
     </row>
-    <row r="197" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6"/>
       <c r="B197" s="14"/>
       <c r="C197" s="11"/>
@@ -3580,7 +3690,7 @@
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
     </row>
-    <row r="198" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6"/>
       <c r="B198" s="14"/>
       <c r="C198" s="11"/>
@@ -3588,7 +3698,7 @@
       <c r="E198" s="8"/>
       <c r="F198" s="8"/>
     </row>
-    <row r="199" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6"/>
       <c r="B199" s="14"/>
       <c r="C199" s="11"/>
@@ -3596,7 +3706,7 @@
       <c r="E199" s="8"/>
       <c r="F199" s="8"/>
     </row>
-    <row r="200" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6"/>
       <c r="B200" s="14"/>
       <c r="C200" s="11"/>
@@ -3604,7 +3714,7 @@
       <c r="E200" s="8"/>
       <c r="F200" s="8"/>
     </row>
-    <row r="201" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6"/>
       <c r="B201" s="14"/>
       <c r="C201" s="11"/>
@@ -3612,7 +3722,7 @@
       <c r="E201" s="8"/>
       <c r="F201" s="8"/>
     </row>
-    <row r="202" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6"/>
       <c r="B202" s="14"/>
       <c r="C202" s="11"/>
@@ -3620,7 +3730,7 @@
       <c r="E202" s="8"/>
       <c r="F202" s="8"/>
     </row>
-    <row r="203" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6"/>
       <c r="B203" s="14"/>
       <c r="C203" s="11"/>
@@ -3628,7 +3738,7 @@
       <c r="E203" s="8"/>
       <c r="F203" s="8"/>
     </row>
-    <row r="204" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6"/>
       <c r="B204" s="14"/>
       <c r="C204" s="11"/>
@@ -3636,7 +3746,7 @@
       <c r="E204" s="8"/>
       <c r="F204" s="8"/>
     </row>
-    <row r="205" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6"/>
       <c r="B205" s="14"/>
       <c r="C205" s="11"/>
@@ -3644,7 +3754,7 @@
       <c r="E205" s="8"/>
       <c r="F205" s="8"/>
     </row>
-    <row r="206" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6"/>
       <c r="B206" s="14"/>
       <c r="C206" s="11"/>
@@ -3652,7 +3762,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6"/>
       <c r="B207" s="14"/>
       <c r="C207" s="11"/>
@@ -3660,7 +3770,7 @@
       <c r="E207" s="8"/>
       <c r="F207" s="8"/>
     </row>
-    <row r="208" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6"/>
       <c r="B208" s="14"/>
       <c r="C208" s="11"/>
@@ -3668,7 +3778,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6"/>
       <c r="B209" s="14"/>
       <c r="C209" s="11"/>
@@ -3676,7 +3786,7 @@
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6"/>
       <c r="B210" s="14"/>
       <c r="C210" s="11"/>
@@ -3684,7 +3794,7 @@
       <c r="E210" s="8"/>
       <c r="F210" s="8"/>
     </row>
-    <row r="211" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6"/>
       <c r="B211" s="14"/>
       <c r="C211" s="11"/>
@@ -3692,7 +3802,7 @@
       <c r="E211" s="8"/>
       <c r="F211" s="8"/>
     </row>
-    <row r="212" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6"/>
       <c r="B212" s="14"/>
       <c r="C212" s="11"/>
@@ -3700,7 +3810,7 @@
       <c r="E212" s="8"/>
       <c r="F212" s="8"/>
     </row>
-    <row r="213" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6"/>
       <c r="B213" s="14"/>
       <c r="C213" s="11"/>
@@ -3708,7 +3818,7 @@
       <c r="E213" s="8"/>
       <c r="F213" s="8"/>
     </row>
-    <row r="214" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6"/>
       <c r="B214" s="14"/>
       <c r="C214" s="11"/>
@@ -3716,7 +3826,7 @@
       <c r="E214" s="8"/>
       <c r="F214" s="8"/>
     </row>
-    <row r="215" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6"/>
       <c r="B215" s="14"/>
       <c r="C215" s="11"/>
@@ -3724,7 +3834,7 @@
       <c r="E215" s="8"/>
       <c r="F215" s="8"/>
     </row>
-    <row r="216" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6"/>
       <c r="B216" s="14"/>
       <c r="C216" s="11"/>
@@ -3732,7 +3842,7 @@
       <c r="E216" s="8"/>
       <c r="F216" s="8"/>
     </row>
-    <row r="217" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6"/>
       <c r="B217" s="14"/>
       <c r="C217" s="11"/>
@@ -3740,7 +3850,7 @@
       <c r="E217" s="8"/>
       <c r="F217" s="8"/>
     </row>
-    <row r="218" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6"/>
       <c r="B218" s="14"/>
       <c r="C218" s="11"/>
@@ -3748,7 +3858,7 @@
       <c r="E218" s="8"/>
       <c r="F218" s="8"/>
     </row>
-    <row r="219" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6"/>
       <c r="B219" s="14"/>
       <c r="C219" s="11"/>
@@ -3756,7 +3866,7 @@
       <c r="E219" s="8"/>
       <c r="F219" s="8"/>
     </row>
-    <row r="220" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6"/>
       <c r="B220" s="14"/>
       <c r="C220" s="11"/>
@@ -3764,7 +3874,7 @@
       <c r="E220" s="8"/>
       <c r="F220" s="8"/>
     </row>
-    <row r="221" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6"/>
       <c r="B221" s="14"/>
       <c r="C221" s="11"/>
@@ -3772,7 +3882,7 @@
       <c r="E221" s="8"/>
       <c r="F221" s="8"/>
     </row>
-    <row r="222" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6"/>
       <c r="B222" s="14"/>
       <c r="C222" s="11"/>
@@ -3780,7 +3890,7 @@
       <c r="E222" s="8"/>
       <c r="F222" s="8"/>
     </row>
-    <row r="223" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6"/>
       <c r="B223" s="14"/>
       <c r="C223" s="11"/>
@@ -3788,7 +3898,7 @@
       <c r="E223" s="8"/>
       <c r="F223" s="8"/>
     </row>
-    <row r="224" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6"/>
       <c r="B224" s="14"/>
       <c r="C224" s="11"/>
@@ -3796,7 +3906,7 @@
       <c r="E224" s="8"/>
       <c r="F224" s="8"/>
     </row>
-    <row r="225" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6"/>
       <c r="B225" s="14"/>
       <c r="C225" s="11"/>
@@ -3804,7 +3914,7 @@
       <c r="E225" s="8"/>
       <c r="F225" s="8"/>
     </row>
-    <row r="226" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6"/>
       <c r="B226" s="14"/>
       <c r="C226" s="11"/>
@@ -3812,7 +3922,7 @@
       <c r="E226" s="8"/>
       <c r="F226" s="8"/>
     </row>
-    <row r="227" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6"/>
       <c r="B227" s="14"/>
       <c r="C227" s="11"/>
@@ -3820,7 +3930,7 @@
       <c r="E227" s="8"/>
       <c r="F227" s="8"/>
     </row>
-    <row r="228" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6"/>
       <c r="B228" s="14"/>
       <c r="C228" s="11"/>
@@ -3828,7 +3938,7 @@
       <c r="E228" s="8"/>
       <c r="F228" s="8"/>
     </row>
-    <row r="229" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6"/>
       <c r="B229" s="14"/>
       <c r="C229" s="11"/>
@@ -3836,7 +3946,7 @@
       <c r="E229" s="8"/>
       <c r="F229" s="8"/>
     </row>
-    <row r="230" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6"/>
       <c r="B230" s="14"/>
       <c r="C230" s="11"/>
@@ -3844,7 +3954,7 @@
       <c r="E230" s="8"/>
       <c r="F230" s="8"/>
     </row>
-    <row r="231" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6"/>
       <c r="B231" s="14"/>
       <c r="C231" s="11"/>
@@ -3852,7 +3962,7 @@
       <c r="E231" s="8"/>
       <c r="F231" s="8"/>
     </row>
-    <row r="232" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6"/>
       <c r="B232" s="14"/>
       <c r="C232" s="11"/>
@@ -3860,7 +3970,7 @@
       <c r="E232" s="8"/>
       <c r="F232" s="8"/>
     </row>
-    <row r="233" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6"/>
       <c r="B233" s="14"/>
       <c r="C233" s="11"/>
@@ -3868,7 +3978,7 @@
       <c r="E233" s="8"/>
       <c r="F233" s="8"/>
     </row>
-    <row r="234" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6"/>
       <c r="B234" s="14"/>
       <c r="C234" s="11"/>
@@ -3876,7 +3986,7 @@
       <c r="E234" s="8"/>
       <c r="F234" s="8"/>
     </row>
-    <row r="235" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6"/>
       <c r="B235" s="14"/>
       <c r="C235" s="11"/>
@@ -3884,7 +3994,7 @@
       <c r="E235" s="8"/>
       <c r="F235" s="8"/>
     </row>
-    <row r="236" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6"/>
       <c r="B236" s="14"/>
       <c r="C236" s="11"/>
@@ -3892,7 +4002,7 @@
       <c r="E236" s="8"/>
       <c r="F236" s="8"/>
     </row>
-    <row r="237" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6"/>
       <c r="B237" s="14"/>
       <c r="C237" s="11"/>
@@ -3900,7 +4010,7 @@
       <c r="E237" s="8"/>
       <c r="F237" s="8"/>
     </row>
-    <row r="238" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6"/>
       <c r="B238" s="14"/>
       <c r="C238" s="11"/>
@@ -3908,7 +4018,7 @@
       <c r="E238" s="8"/>
       <c r="F238" s="8"/>
     </row>
-    <row r="239" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6"/>
       <c r="B239" s="14"/>
       <c r="C239" s="11"/>
@@ -3916,7 +4026,7 @@
       <c r="E239" s="8"/>
       <c r="F239" s="8"/>
     </row>
-    <row r="240" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6"/>
       <c r="B240" s="14"/>
       <c r="C240" s="11"/>
@@ -3924,7 +4034,7 @@
       <c r="E240" s="8"/>
       <c r="F240" s="8"/>
     </row>
-    <row r="241" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6"/>
       <c r="B241" s="14"/>
       <c r="C241" s="11"/>
@@ -3932,7 +4042,7 @@
       <c r="E241" s="8"/>
       <c r="F241" s="8"/>
     </row>
-    <row r="242" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6"/>
       <c r="B242" s="14"/>
       <c r="C242" s="11"/>
@@ -3940,7 +4050,7 @@
       <c r="E242" s="8"/>
       <c r="F242" s="8"/>
     </row>
-    <row r="243" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6"/>
       <c r="B243" s="14"/>
       <c r="C243" s="11"/>
@@ -3948,7 +4058,7 @@
       <c r="E243" s="8"/>
       <c r="F243" s="8"/>
     </row>
-    <row r="244" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6"/>
       <c r="B244" s="14"/>
       <c r="C244" s="11"/>
@@ -3956,7 +4066,7 @@
       <c r="E244" s="8"/>
       <c r="F244" s="8"/>
     </row>
-    <row r="245" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6"/>
       <c r="B245" s="14"/>
       <c r="C245" s="11"/>
@@ -3964,7 +4074,7 @@
       <c r="E245" s="8"/>
       <c r="F245" s="8"/>
     </row>
-    <row r="246" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6"/>
       <c r="B246" s="14"/>
       <c r="C246" s="11"/>
@@ -3972,7 +4082,7 @@
       <c r="E246" s="8"/>
       <c r="F246" s="8"/>
     </row>
-    <row r="247" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6"/>
       <c r="B247" s="14"/>
       <c r="C247" s="11"/>
@@ -3980,7 +4090,7 @@
       <c r="E247" s="8"/>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6"/>
       <c r="B248" s="14"/>
       <c r="C248" s="11"/>
@@ -3988,7 +4098,7 @@
       <c r="E248" s="8"/>
       <c r="F248" s="8"/>
     </row>
-    <row r="249" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6"/>
       <c r="B249" s="14"/>
       <c r="C249" s="11"/>
@@ -3996,7 +4106,7 @@
       <c r="E249" s="8"/>
       <c r="F249" s="8"/>
     </row>
-    <row r="250" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6"/>
       <c r="B250" s="14"/>
       <c r="C250" s="11"/>
@@ -4004,7 +4114,7 @@
       <c r="E250" s="8"/>
       <c r="F250" s="8"/>
     </row>
-    <row r="251" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6"/>
       <c r="B251" s="14"/>
       <c r="C251" s="11"/>
@@ -4012,7 +4122,7 @@
       <c r="E251" s="8"/>
       <c r="F251" s="8"/>
     </row>
-    <row r="252" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6"/>
       <c r="B252" s="14"/>
       <c r="C252" s="11"/>
@@ -4020,7 +4130,7 @@
       <c r="E252" s="8"/>
       <c r="F252" s="8"/>
     </row>
-    <row r="253" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6"/>
       <c r="B253" s="14"/>
       <c r="C253" s="11"/>
@@ -4028,7 +4138,7 @@
       <c r="E253" s="8"/>
       <c r="F253" s="8"/>
     </row>
-    <row r="254" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6"/>
       <c r="B254" s="14"/>
       <c r="C254" s="11"/>
@@ -4036,7 +4146,7 @@
       <c r="E254" s="8"/>
       <c r="F254" s="8"/>
     </row>
-    <row r="255" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6"/>
       <c r="B255" s="14"/>
       <c r="C255" s="11"/>
@@ -4044,7 +4154,7 @@
       <c r="E255" s="8"/>
       <c r="F255" s="8"/>
     </row>
-    <row r="256" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6"/>
       <c r="B256" s="14"/>
       <c r="C256" s="11"/>
@@ -4052,7 +4162,7 @@
       <c r="E256" s="8"/>
       <c r="F256" s="8"/>
     </row>
-    <row r="257" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6"/>
       <c r="B257" s="14"/>
       <c r="C257" s="11"/>
@@ -4060,7 +4170,7 @@
       <c r="E257" s="8"/>
       <c r="F257" s="8"/>
     </row>
-    <row r="258" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6"/>
       <c r="B258" s="14"/>
       <c r="C258" s="11"/>
@@ -4068,7 +4178,7 @@
       <c r="E258" s="8"/>
       <c r="F258" s="8"/>
     </row>
-    <row r="259" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6"/>
       <c r="B259" s="14"/>
       <c r="C259" s="11"/>
@@ -4076,7 +4186,7 @@
       <c r="E259" s="8"/>
       <c r="F259" s="8"/>
     </row>
-    <row r="260" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6"/>
       <c r="B260" s="14"/>
       <c r="C260" s="11"/>
@@ -4084,7 +4194,7 @@
       <c r="E260" s="8"/>
       <c r="F260" s="8"/>
     </row>
-    <row r="261" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6"/>
       <c r="B261" s="14"/>
       <c r="C261" s="11"/>
@@ -4092,7 +4202,7 @@
       <c r="E261" s="8"/>
       <c r="F261" s="8"/>
     </row>
-    <row r="262" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6"/>
       <c r="B262" s="14"/>
       <c r="C262" s="11"/>
@@ -4100,7 +4210,7 @@
       <c r="E262" s="8"/>
       <c r="F262" s="8"/>
     </row>
-    <row r="263" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6"/>
       <c r="B263" s="14"/>
       <c r="C263" s="11"/>
@@ -4108,7 +4218,7 @@
       <c r="E263" s="8"/>
       <c r="F263" s="8"/>
     </row>
-    <row r="264" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6"/>
       <c r="B264" s="14"/>
       <c r="C264" s="11"/>
@@ -4116,7 +4226,7 @@
       <c r="E264" s="8"/>
       <c r="F264" s="8"/>
     </row>
-    <row r="265" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6"/>
       <c r="B265" s="14"/>
       <c r="C265" s="11"/>
@@ -4124,7 +4234,7 @@
       <c r="E265" s="8"/>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6"/>
       <c r="B266" s="14"/>
       <c r="C266" s="11"/>
@@ -4132,7 +4242,7 @@
       <c r="E266" s="8"/>
       <c r="F266" s="8"/>
     </row>
-    <row r="267" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6"/>
       <c r="B267" s="14"/>
       <c r="C267" s="11"/>
@@ -4140,7 +4250,7 @@
       <c r="E267" s="8"/>
       <c r="F267" s="8"/>
     </row>
-    <row r="268" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6"/>
       <c r="B268" s="14"/>
       <c r="C268" s="11"/>
@@ -4148,7 +4258,7 @@
       <c r="E268" s="8"/>
       <c r="F268" s="8"/>
     </row>
-    <row r="269" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6"/>
       <c r="B269" s="14"/>
       <c r="C269" s="11"/>
@@ -4156,7 +4266,7 @@
       <c r="E269" s="8"/>
       <c r="F269" s="8"/>
     </row>
-    <row r="270" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6"/>
       <c r="B270" s="14"/>
       <c r="C270" s="11"/>
@@ -4164,7 +4274,7 @@
       <c r="E270" s="8"/>
       <c r="F270" s="8"/>
     </row>
-    <row r="271" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6"/>
       <c r="B271" s="14"/>
       <c r="C271" s="11"/>
@@ -4172,7 +4282,7 @@
       <c r="E271" s="8"/>
       <c r="F271" s="8"/>
     </row>
-    <row r="272" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6"/>
       <c r="B272" s="14"/>
       <c r="C272" s="11"/>
@@ -4180,7 +4290,7 @@
       <c r="E272" s="8"/>
       <c r="F272" s="8"/>
     </row>
-    <row r="273" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6"/>
       <c r="B273" s="14"/>
       <c r="C273" s="11"/>
@@ -4188,7 +4298,7 @@
       <c r="E273" s="8"/>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6"/>
       <c r="B274" s="14"/>
       <c r="C274" s="11"/>
@@ -4196,7 +4306,7 @@
       <c r="E274" s="8"/>
       <c r="F274" s="8"/>
     </row>
-    <row r="275" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6"/>
       <c r="B275" s="14"/>
       <c r="C275" s="11"/>
@@ -4204,7 +4314,7 @@
       <c r="E275" s="8"/>
       <c r="F275" s="8"/>
     </row>
-    <row r="276" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6"/>
       <c r="B276" s="14"/>
       <c r="C276" s="11"/>
@@ -4212,7 +4322,7 @@
       <c r="E276" s="8"/>
       <c r="F276" s="8"/>
     </row>
-    <row r="277" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6"/>
       <c r="B277" s="14"/>
       <c r="C277" s="11"/>
@@ -4220,7 +4330,7 @@
       <c r="E277" s="8"/>
       <c r="F277" s="8"/>
     </row>
-    <row r="278" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6"/>
       <c r="B278" s="14"/>
       <c r="C278" s="11"/>
@@ -4228,7 +4338,7 @@
       <c r="E278" s="8"/>
       <c r="F278" s="8"/>
     </row>
-    <row r="279" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6"/>
       <c r="B279" s="14"/>
       <c r="C279" s="11"/>
@@ -4236,7 +4346,7 @@
       <c r="E279" s="8"/>
       <c r="F279" s="8"/>
     </row>
-    <row r="280" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6"/>
       <c r="B280" s="14"/>
       <c r="C280" s="11"/>
@@ -4244,7 +4354,7 @@
       <c r="E280" s="8"/>
       <c r="F280" s="8"/>
     </row>
-    <row r="281" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6"/>
       <c r="B281" s="14"/>
       <c r="C281" s="11"/>
@@ -4252,7 +4362,7 @@
       <c r="E281" s="8"/>
       <c r="F281" s="8"/>
     </row>
-    <row r="282" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6"/>
       <c r="B282" s="14"/>
       <c r="C282" s="11"/>
@@ -4260,7 +4370,7 @@
       <c r="E282" s="8"/>
       <c r="F282" s="8"/>
     </row>
-    <row r="283" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6"/>
       <c r="B283" s="14"/>
       <c r="C283" s="11"/>
@@ -4268,7 +4378,7 @@
       <c r="E283" s="8"/>
       <c r="F283" s="8"/>
     </row>
-    <row r="284" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6"/>
       <c r="B284" s="14"/>
       <c r="C284" s="11"/>
@@ -4276,7 +4386,7 @@
       <c r="E284" s="8"/>
       <c r="F284" s="8"/>
     </row>
-    <row r="285" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6"/>
       <c r="B285" s="14"/>
       <c r="C285" s="11"/>
@@ -4284,7 +4394,7 @@
       <c r="E285" s="8"/>
       <c r="F285" s="8"/>
     </row>
-    <row r="286" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6"/>
       <c r="B286" s="14"/>
       <c r="C286" s="11"/>
@@ -4292,7 +4402,7 @@
       <c r="E286" s="8"/>
       <c r="F286" s="8"/>
     </row>
-    <row r="287" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6"/>
       <c r="B287" s="14"/>
       <c r="C287" s="11"/>
@@ -4300,7 +4410,7 @@
       <c r="E287" s="8"/>
       <c r="F287" s="8"/>
     </row>
-    <row r="288" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6"/>
       <c r="B288" s="14"/>
       <c r="C288" s="11"/>
@@ -4308,7 +4418,7 @@
       <c r="E288" s="8"/>
       <c r="F288" s="8"/>
     </row>
-    <row r="289" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6"/>
       <c r="B289" s="14"/>
       <c r="C289" s="11"/>
@@ -4316,7 +4426,7 @@
       <c r="E289" s="8"/>
       <c r="F289" s="8"/>
     </row>
-    <row r="290" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6"/>
       <c r="B290" s="14"/>
       <c r="C290" s="11"/>
@@ -4324,7 +4434,7 @@
       <c r="E290" s="8"/>
       <c r="F290" s="8"/>
     </row>
-    <row r="291" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6"/>
       <c r="B291" s="14"/>
       <c r="C291" s="11"/>
@@ -4332,7 +4442,7 @@
       <c r="E291" s="8"/>
       <c r="F291" s="8"/>
     </row>
-    <row r="292" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6"/>
       <c r="B292" s="14"/>
       <c r="C292" s="11"/>
@@ -4340,7 +4450,7 @@
       <c r="E292" s="8"/>
       <c r="F292" s="8"/>
     </row>
-    <row r="293" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6"/>
       <c r="B293" s="14"/>
       <c r="C293" s="11"/>
@@ -4348,7 +4458,7 @@
       <c r="E293" s="8"/>
       <c r="F293" s="8"/>
     </row>
-    <row r="294" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6"/>
       <c r="B294" s="14"/>
       <c r="C294" s="11"/>
@@ -4356,7 +4466,7 @@
       <c r="E294" s="8"/>
       <c r="F294" s="8"/>
     </row>
-    <row r="295" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6"/>
       <c r="B295" s="14"/>
       <c r="C295" s="11"/>
@@ -4364,7 +4474,7 @@
       <c r="E295" s="8"/>
       <c r="F295" s="8"/>
     </row>
-    <row r="296" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6"/>
       <c r="B296" s="14"/>
       <c r="C296" s="11"/>
@@ -4372,7 +4482,7 @@
       <c r="E296" s="8"/>
       <c r="F296" s="8"/>
     </row>
-    <row r="297" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6"/>
       <c r="B297" s="14"/>
       <c r="C297" s="11"/>
@@ -4380,7 +4490,7 @@
       <c r="E297" s="8"/>
       <c r="F297" s="8"/>
     </row>
-    <row r="298" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6"/>
       <c r="B298" s="14"/>
       <c r="C298" s="11"/>
@@ -4388,7 +4498,7 @@
       <c r="E298" s="8"/>
       <c r="F298" s="8"/>
     </row>
-    <row r="299" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6"/>
       <c r="B299" s="14"/>
       <c r="C299" s="11"/>
@@ -4396,7 +4506,7 @@
       <c r="E299" s="8"/>
       <c r="F299" s="8"/>
     </row>
-    <row r="300" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6"/>
       <c r="B300" s="14"/>
       <c r="C300" s="11"/>
@@ -4404,7 +4514,7 @@
       <c r="E300" s="8"/>
       <c r="F300" s="8"/>
     </row>
-    <row r="301" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6"/>
       <c r="B301" s="14"/>
       <c r="C301" s="11"/>
@@ -4412,7 +4522,7 @@
       <c r="E301" s="8"/>
       <c r="F301" s="8"/>
     </row>
-    <row r="302" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6"/>
       <c r="B302" s="14"/>
       <c r="C302" s="11"/>
@@ -4420,7 +4530,7 @@
       <c r="E302" s="8"/>
       <c r="F302" s="8"/>
     </row>
-    <row r="303" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6"/>
       <c r="B303" s="14"/>
       <c r="C303" s="11"/>
@@ -4428,7 +4538,7 @@
       <c r="E303" s="8"/>
       <c r="F303" s="8"/>
     </row>
-    <row r="304" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6"/>
       <c r="B304" s="14"/>
       <c r="C304" s="11"/>
@@ -4436,7 +4546,7 @@
       <c r="E304" s="8"/>
       <c r="F304" s="8"/>
     </row>
-    <row r="305" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6"/>
       <c r="B305" s="14"/>
       <c r="C305" s="11"/>
@@ -4444,7 +4554,7 @@
       <c r="E305" s="8"/>
       <c r="F305" s="8"/>
     </row>
-    <row r="306" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6"/>
       <c r="B306" s="14"/>
       <c r="C306" s="11"/>
@@ -4452,7 +4562,7 @@
       <c r="E306" s="8"/>
       <c r="F306" s="8"/>
     </row>
-    <row r="307" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6"/>
       <c r="B307" s="14"/>
       <c r="C307" s="11"/>
@@ -4460,7 +4570,7 @@
       <c r="E307" s="8"/>
       <c r="F307" s="8"/>
     </row>
-    <row r="308" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6"/>
       <c r="B308" s="14"/>
       <c r="C308" s="11"/>
@@ -4468,7 +4578,7 @@
       <c r="E308" s="8"/>
       <c r="F308" s="8"/>
     </row>
-    <row r="309" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6"/>
       <c r="B309" s="14"/>
       <c r="C309" s="11"/>
@@ -4476,7 +4586,7 @@
       <c r="E309" s="8"/>
       <c r="F309" s="8"/>
     </row>
-    <row r="310" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6"/>
       <c r="B310" s="14"/>
       <c r="C310" s="11"/>
@@ -4484,7 +4594,7 @@
       <c r="E310" s="8"/>
       <c r="F310" s="8"/>
     </row>
-    <row r="311" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6"/>
       <c r="B311" s="14"/>
       <c r="C311" s="11"/>
@@ -4492,7 +4602,7 @@
       <c r="E311" s="8"/>
       <c r="F311" s="8"/>
     </row>
-    <row r="312" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6"/>
       <c r="B312" s="14"/>
       <c r="C312" s="11"/>
@@ -4500,7 +4610,7 @@
       <c r="E312" s="8"/>
       <c r="F312" s="8"/>
     </row>
-    <row r="313" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6"/>
       <c r="B313" s="14"/>
       <c r="C313" s="11"/>
@@ -4508,7 +4618,7 @@
       <c r="E313" s="8"/>
       <c r="F313" s="8"/>
     </row>
-    <row r="314" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6"/>
       <c r="B314" s="14"/>
       <c r="C314" s="11"/>
@@ -4516,7 +4626,7 @@
       <c r="E314" s="8"/>
       <c r="F314" s="8"/>
     </row>
-    <row r="315" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6"/>
       <c r="B315" s="14"/>
       <c r="C315" s="11"/>
@@ -4524,7 +4634,7 @@
       <c r="E315" s="8"/>
       <c r="F315" s="8"/>
     </row>
-    <row r="316" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6"/>
       <c r="B316" s="14"/>
       <c r="C316" s="11"/>
@@ -4532,7 +4642,7 @@
       <c r="E316" s="8"/>
       <c r="F316" s="8"/>
     </row>
-    <row r="317" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6"/>
       <c r="B317" s="14"/>
       <c r="C317" s="11"/>
@@ -4540,7 +4650,7 @@
       <c r="E317" s="8"/>
       <c r="F317" s="8"/>
     </row>
-    <row r="318" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6"/>
       <c r="B318" s="14"/>
       <c r="C318" s="11"/>
@@ -4548,7 +4658,7 @@
       <c r="E318" s="8"/>
       <c r="F318" s="8"/>
     </row>
-    <row r="319" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6"/>
       <c r="B319" s="14"/>
       <c r="C319" s="11"/>
@@ -4556,7 +4666,7 @@
       <c r="E319" s="8"/>
       <c r="F319" s="8"/>
     </row>
-    <row r="320" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6"/>
       <c r="B320" s="14"/>
       <c r="C320" s="11"/>
@@ -4564,7 +4674,7 @@
       <c r="E320" s="8"/>
       <c r="F320" s="8"/>
     </row>
-    <row r="321" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6"/>
       <c r="B321" s="14"/>
       <c r="C321" s="11"/>
@@ -4572,7 +4682,7 @@
       <c r="E321" s="8"/>
       <c r="F321" s="8"/>
     </row>
-    <row r="322" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6"/>
       <c r="B322" s="14"/>
       <c r="C322" s="11"/>
@@ -4580,7 +4690,7 @@
       <c r="E322" s="8"/>
       <c r="F322" s="8"/>
     </row>
-    <row r="323" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6"/>
       <c r="B323" s="14"/>
       <c r="C323" s="11"/>
@@ -4588,7 +4698,7 @@
       <c r="E323" s="8"/>
       <c r="F323" s="8"/>
     </row>
-    <row r="324" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6"/>
       <c r="B324" s="14"/>
       <c r="C324" s="11"/>
@@ -4596,7 +4706,7 @@
       <c r="E324" s="8"/>
       <c r="F324" s="8"/>
     </row>
-    <row r="325" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6"/>
       <c r="B325" s="14"/>
       <c r="C325" s="11"/>
@@ -4604,7 +4714,7 @@
       <c r="E325" s="8"/>
       <c r="F325" s="8"/>
     </row>
-    <row r="326" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6"/>
       <c r="B326" s="14"/>
       <c r="C326" s="11"/>
@@ -4612,7 +4722,7 @@
       <c r="E326" s="8"/>
       <c r="F326" s="8"/>
     </row>
-    <row r="327" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6"/>
       <c r="B327" s="14"/>
       <c r="C327" s="11"/>
@@ -4620,7 +4730,7 @@
       <c r="E327" s="8"/>
       <c r="F327" s="8"/>
     </row>
-    <row r="328" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6"/>
       <c r="B328" s="14"/>
       <c r="C328" s="11"/>
@@ -4628,7 +4738,7 @@
       <c r="E328" s="8"/>
       <c r="F328" s="8"/>
     </row>
-    <row r="329" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6"/>
       <c r="B329" s="14"/>
       <c r="C329" s="11"/>
@@ -4636,7 +4746,7 @@
       <c r="E329" s="8"/>
       <c r="F329" s="8"/>
     </row>
-    <row r="330" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6"/>
       <c r="B330" s="14"/>
       <c r="C330" s="11"/>
@@ -4644,7 +4754,7 @@
       <c r="E330" s="8"/>
       <c r="F330" s="8"/>
     </row>
-    <row r="331" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6"/>
       <c r="B331" s="14"/>
       <c r="C331" s="11"/>
@@ -4652,7 +4762,7 @@
       <c r="E331" s="8"/>
       <c r="F331" s="8"/>
     </row>
-    <row r="332" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6"/>
       <c r="B332" s="14"/>
       <c r="C332" s="11"/>
@@ -4660,7 +4770,7 @@
       <c r="E332" s="8"/>
       <c r="F332" s="8"/>
     </row>
-    <row r="333" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6"/>
       <c r="B333" s="14"/>
       <c r="C333" s="11"/>
@@ -4668,7 +4778,7 @@
       <c r="E333" s="8"/>
       <c r="F333" s="8"/>
     </row>
-    <row r="334" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6"/>
       <c r="B334" s="14"/>
       <c r="C334" s="11"/>
@@ -4676,7 +4786,7 @@
       <c r="E334" s="8"/>
       <c r="F334" s="8"/>
     </row>
-    <row r="335" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6"/>
       <c r="B335" s="14"/>
       <c r="C335" s="11"/>
@@ -4684,7 +4794,7 @@
       <c r="E335" s="8"/>
       <c r="F335" s="8"/>
     </row>
-    <row r="336" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6"/>
       <c r="B336" s="14"/>
       <c r="C336" s="11"/>
@@ -4692,7 +4802,7 @@
       <c r="E336" s="8"/>
       <c r="F336" s="8"/>
     </row>
-    <row r="337" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6"/>
       <c r="B337" s="14"/>
       <c r="C337" s="11"/>
@@ -4700,7 +4810,7 @@
       <c r="E337" s="8"/>
       <c r="F337" s="8"/>
     </row>
-    <row r="338" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6"/>
       <c r="B338" s="14"/>
       <c r="C338" s="11"/>
@@ -4708,7 +4818,7 @@
       <c r="E338" s="8"/>
       <c r="F338" s="8"/>
     </row>
-    <row r="339" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6"/>
       <c r="B339" s="14"/>
       <c r="C339" s="11"/>
@@ -4716,7 +4826,7 @@
       <c r="E339" s="8"/>
       <c r="F339" s="8"/>
     </row>
-    <row r="340" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6"/>
       <c r="B340" s="14"/>
       <c r="C340" s="11"/>
@@ -4724,7 +4834,7 @@
       <c r="E340" s="8"/>
       <c r="F340" s="8"/>
     </row>
-    <row r="341" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6"/>
       <c r="B341" s="14"/>
       <c r="C341" s="11"/>
@@ -4732,7 +4842,7 @@
       <c r="E341" s="8"/>
       <c r="F341" s="8"/>
     </row>
-    <row r="342" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6"/>
       <c r="B342" s="14"/>
       <c r="C342" s="11"/>
@@ -4740,7 +4850,7 @@
       <c r="E342" s="8"/>
       <c r="F342" s="8"/>
     </row>
-    <row r="343" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6"/>
       <c r="B343" s="14"/>
       <c r="C343" s="11"/>
@@ -4748,7 +4858,7 @@
       <c r="E343" s="8"/>
       <c r="F343" s="8"/>
     </row>
-    <row r="344" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6"/>
       <c r="B344" s="14"/>
       <c r="C344" s="11"/>
@@ -4756,7 +4866,7 @@
       <c r="E344" s="8"/>
       <c r="F344" s="8"/>
     </row>
-    <row r="345" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6"/>
       <c r="B345" s="14"/>
       <c r="C345" s="11"/>
@@ -4764,7 +4874,7 @@
       <c r="E345" s="8"/>
       <c r="F345" s="8"/>
     </row>
-    <row r="346" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6"/>
       <c r="B346" s="14"/>
       <c r="C346" s="11"/>
@@ -4772,7 +4882,7 @@
       <c r="E346" s="8"/>
       <c r="F346" s="8"/>
     </row>
-    <row r="347" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6"/>
       <c r="B347" s="14"/>
       <c r="C347" s="11"/>
@@ -4780,7 +4890,7 @@
       <c r="E347" s="8"/>
       <c r="F347" s="8"/>
     </row>
-    <row r="348" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6"/>
       <c r="B348" s="14"/>
       <c r="C348" s="11"/>
@@ -4788,7 +4898,7 @@
       <c r="E348" s="8"/>
       <c r="F348" s="8"/>
     </row>
-    <row r="349" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6"/>
       <c r="B349" s="14"/>
       <c r="C349" s="11"/>
@@ -4796,7 +4906,7 @@
       <c r="E349" s="8"/>
       <c r="F349" s="8"/>
     </row>
-    <row r="350" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6"/>
       <c r="B350" s="14"/>
       <c r="C350" s="11"/>
@@ -4804,7 +4914,7 @@
       <c r="E350" s="8"/>
       <c r="F350" s="8"/>
     </row>
-    <row r="351" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6"/>
       <c r="B351" s="14"/>
       <c r="C351" s="11"/>
@@ -4812,7 +4922,7 @@
       <c r="E351" s="8"/>
       <c r="F351" s="8"/>
     </row>
-    <row r="352" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6"/>
       <c r="B352" s="14"/>
       <c r="C352" s="11"/>
@@ -4820,7 +4930,7 @@
       <c r="E352" s="8"/>
       <c r="F352" s="8"/>
     </row>
-    <row r="353" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6"/>
       <c r="B353" s="14"/>
       <c r="C353" s="11"/>
@@ -4828,7 +4938,7 @@
       <c r="E353" s="8"/>
       <c r="F353" s="8"/>
     </row>
-    <row r="354" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6"/>
       <c r="B354" s="14"/>
       <c r="C354" s="11"/>
@@ -4836,7 +4946,7 @@
       <c r="E354" s="8"/>
       <c r="F354" s="8"/>
     </row>
-    <row r="355" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6"/>
       <c r="B355" s="14"/>
       <c r="C355" s="11"/>
@@ -4844,7 +4954,7 @@
       <c r="E355" s="8"/>
       <c r="F355" s="8"/>
     </row>
-    <row r="356" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6"/>
       <c r="B356" s="14"/>
       <c r="C356" s="11"/>
@@ -4852,7 +4962,7 @@
       <c r="E356" s="8"/>
       <c r="F356" s="8"/>
     </row>
-    <row r="357" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6"/>
       <c r="B357" s="14"/>
       <c r="C357" s="11"/>
@@ -4860,7 +4970,7 @@
       <c r="E357" s="8"/>
       <c r="F357" s="8"/>
     </row>
-    <row r="358" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6"/>
       <c r="B358" s="14"/>
       <c r="C358" s="11"/>
@@ -4868,7 +4978,7 @@
       <c r="E358" s="8"/>
       <c r="F358" s="8"/>
     </row>
-    <row r="359" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6"/>
       <c r="B359" s="14"/>
       <c r="C359" s="11"/>
@@ -4876,7 +4986,7 @@
       <c r="E359" s="8"/>
       <c r="F359" s="8"/>
     </row>
-    <row r="360" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6"/>
       <c r="B360" s="14"/>
       <c r="C360" s="11"/>
@@ -4884,7 +4994,7 @@
       <c r="E360" s="8"/>
       <c r="F360" s="8"/>
     </row>
-    <row r="361" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6"/>
       <c r="B361" s="14"/>
       <c r="C361" s="11"/>
@@ -4892,7 +5002,7 @@
       <c r="E361" s="8"/>
       <c r="F361" s="8"/>
     </row>
-    <row r="362" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6"/>
       <c r="B362" s="14"/>
       <c r="C362" s="11"/>
@@ -4900,7 +5010,7 @@
       <c r="E362" s="8"/>
       <c r="F362" s="8"/>
     </row>
-    <row r="363" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6"/>
       <c r="B363" s="14"/>
       <c r="C363" s="11"/>
@@ -4908,7 +5018,7 @@
       <c r="E363" s="8"/>
       <c r="F363" s="8"/>
     </row>
-    <row r="364" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6"/>
       <c r="B364" s="14"/>
       <c r="C364" s="11"/>
@@ -4916,7 +5026,7 @@
       <c r="E364" s="8"/>
       <c r="F364" s="8"/>
     </row>
-    <row r="365" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6"/>
       <c r="B365" s="14"/>
       <c r="C365" s="11"/>
@@ -4924,7 +5034,7 @@
       <c r="E365" s="8"/>
       <c r="F365" s="8"/>
     </row>
-    <row r="366" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6"/>
       <c r="B366" s="14"/>
       <c r="C366" s="11"/>
@@ -4932,7 +5042,7 @@
       <c r="E366" s="8"/>
       <c r="F366" s="8"/>
     </row>
-    <row r="367" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6"/>
       <c r="B367" s="14"/>
       <c r="C367" s="11"/>
@@ -4940,7 +5050,7 @@
       <c r="E367" s="8"/>
       <c r="F367" s="8"/>
     </row>
-    <row r="368" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6"/>
       <c r="B368" s="14"/>
       <c r="C368" s="11"/>
@@ -4948,7 +5058,7 @@
       <c r="E368" s="8"/>
       <c r="F368" s="8"/>
     </row>
-    <row r="369" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6"/>
       <c r="B369" s="14"/>
       <c r="C369" s="11"/>
@@ -4956,7 +5066,7 @@
       <c r="E369" s="8"/>
       <c r="F369" s="8"/>
     </row>
-    <row r="370" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6"/>
       <c r="B370" s="14"/>
       <c r="C370" s="11"/>
@@ -4964,7 +5074,7 @@
       <c r="E370" s="8"/>
       <c r="F370" s="8"/>
     </row>
-    <row r="371" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6"/>
       <c r="B371" s="14"/>
       <c r="C371" s="11"/>
@@ -4972,7 +5082,7 @@
       <c r="E371" s="8"/>
       <c r="F371" s="8"/>
     </row>
-    <row r="372" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6"/>
       <c r="B372" s="14"/>
       <c r="C372" s="11"/>
@@ -4980,7 +5090,7 @@
       <c r="E372" s="8"/>
       <c r="F372" s="8"/>
     </row>
-    <row r="373" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6"/>
       <c r="B373" s="14"/>
       <c r="C373" s="11"/>
@@ -4988,7 +5098,7 @@
       <c r="E373" s="8"/>
       <c r="F373" s="8"/>
     </row>
-    <row r="374" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6"/>
       <c r="B374" s="14"/>
       <c r="C374" s="11"/>
@@ -4996,7 +5106,7 @@
       <c r="E374" s="8"/>
       <c r="F374" s="8"/>
     </row>
-    <row r="375" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6"/>
       <c r="B375" s="14"/>
       <c r="C375" s="11"/>
@@ -5004,7 +5114,7 @@
       <c r="E375" s="8"/>
       <c r="F375" s="8"/>
     </row>
-    <row r="376" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6"/>
       <c r="B376" s="14"/>
       <c r="C376" s="11"/>
@@ -5012,7 +5122,7 @@
       <c r="E376" s="8"/>
       <c r="F376" s="8"/>
     </row>
-    <row r="377" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6"/>
       <c r="B377" s="14"/>
       <c r="C377" s="11"/>
@@ -5020,7 +5130,7 @@
       <c r="E377" s="8"/>
       <c r="F377" s="8"/>
     </row>
-    <row r="378" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6"/>
       <c r="B378" s="14"/>
       <c r="C378" s="11"/>
@@ -5028,7 +5138,7 @@
       <c r="E378" s="8"/>
       <c r="F378" s="8"/>
     </row>
-    <row r="379" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6"/>
       <c r="B379" s="14"/>
       <c r="C379" s="11"/>
@@ -5036,7 +5146,7 @@
       <c r="E379" s="8"/>
       <c r="F379" s="8"/>
     </row>
-    <row r="380" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6"/>
       <c r="B380" s="14"/>
       <c r="C380" s="11"/>
@@ -5044,7 +5154,7 @@
       <c r="E380" s="8"/>
       <c r="F380" s="8"/>
     </row>
-    <row r="381" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6"/>
       <c r="B381" s="14"/>
       <c r="C381" s="11"/>
@@ -5052,7 +5162,7 @@
       <c r="E381" s="8"/>
       <c r="F381" s="8"/>
     </row>
-    <row r="382" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6"/>
       <c r="B382" s="14"/>
       <c r="C382" s="11"/>
@@ -5060,7 +5170,7 @@
       <c r="E382" s="8"/>
       <c r="F382" s="8"/>
     </row>
-    <row r="383" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6"/>
       <c r="B383" s="14"/>
       <c r="C383" s="11"/>
@@ -5068,7 +5178,7 @@
       <c r="E383" s="8"/>
       <c r="F383" s="8"/>
     </row>
-    <row r="384" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6"/>
       <c r="B384" s="14"/>
       <c r="C384" s="11"/>
@@ -5076,7 +5186,7 @@
       <c r="E384" s="8"/>
       <c r="F384" s="8"/>
     </row>
-    <row r="385" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6"/>
       <c r="B385" s="14"/>
       <c r="C385" s="11"/>
@@ -5084,7 +5194,7 @@
       <c r="E385" s="8"/>
       <c r="F385" s="8"/>
     </row>
-    <row r="386" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6"/>
       <c r="B386" s="14"/>
       <c r="C386" s="11"/>
@@ -5092,7 +5202,7 @@
       <c r="E386" s="8"/>
       <c r="F386" s="8"/>
     </row>
-    <row r="387" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6"/>
       <c r="B387" s="14"/>
       <c r="C387" s="11"/>
@@ -5100,7 +5210,7 @@
       <c r="E387" s="8"/>
       <c r="F387" s="8"/>
     </row>
-    <row r="388" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6"/>
       <c r="B388" s="14"/>
       <c r="C388" s="11"/>
@@ -5108,7 +5218,7 @@
       <c r="E388" s="8"/>
       <c r="F388" s="8"/>
     </row>
-    <row r="389" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6"/>
       <c r="B389" s="14"/>
       <c r="C389" s="11"/>
@@ -5116,7 +5226,7 @@
       <c r="E389" s="8"/>
       <c r="F389" s="8"/>
     </row>
-    <row r="390" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6"/>
       <c r="B390" s="14"/>
       <c r="C390" s="11"/>
@@ -5124,7 +5234,7 @@
       <c r="E390" s="8"/>
       <c r="F390" s="8"/>
     </row>
-    <row r="391" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6"/>
       <c r="B391" s="14"/>
       <c r="C391" s="11"/>
@@ -5132,7 +5242,7 @@
       <c r="E391" s="8"/>
       <c r="F391" s="8"/>
     </row>
-    <row r="392" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6"/>
       <c r="B392" s="14"/>
       <c r="C392" s="11"/>
@@ -5140,7 +5250,7 @@
       <c r="E392" s="8"/>
       <c r="F392" s="8"/>
     </row>
-    <row r="393" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6"/>
       <c r="B393" s="14"/>
       <c r="C393" s="11"/>
@@ -5148,7 +5258,7 @@
       <c r="E393" s="8"/>
       <c r="F393" s="8"/>
     </row>
-    <row r="394" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6"/>
       <c r="B394" s="14"/>
       <c r="C394" s="11"/>
@@ -5156,7 +5266,7 @@
       <c r="E394" s="8"/>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6"/>
       <c r="B395" s="14"/>
       <c r="C395" s="11"/>
@@ -5164,7 +5274,7 @@
       <c r="E395" s="8"/>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6"/>
       <c r="B396" s="14"/>
       <c r="C396" s="11"/>
@@ -5172,7 +5282,7 @@
       <c r="E396" s="8"/>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6"/>
       <c r="B397" s="14"/>
       <c r="C397" s="11"/>
@@ -5180,7 +5290,7 @@
       <c r="E397" s="8"/>
       <c r="F397" s="8"/>
     </row>
-    <row r="398" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6"/>
       <c r="B398" s="14"/>
       <c r="C398" s="11"/>
@@ -5188,7 +5298,7 @@
       <c r="E398" s="8"/>
       <c r="F398" s="8"/>
     </row>
-    <row r="399" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6"/>
       <c r="B399" s="14"/>
       <c r="C399" s="11"/>
@@ -5196,7 +5306,7 @@
       <c r="E399" s="8"/>
       <c r="F399" s="8"/>
     </row>
-    <row r="400" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6"/>
       <c r="B400" s="14"/>
       <c r="C400" s="11"/>
@@ -5204,7 +5314,7 @@
       <c r="E400" s="8"/>
       <c r="F400" s="8"/>
     </row>
-    <row r="401" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6"/>
       <c r="B401" s="14"/>
       <c r="C401" s="11"/>
@@ -5212,7 +5322,7 @@
       <c r="E401" s="8"/>
       <c r="F401" s="8"/>
     </row>
-    <row r="402" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6"/>
       <c r="B402" s="14"/>
       <c r="C402" s="11"/>
@@ -5220,7 +5330,7 @@
       <c r="E402" s="8"/>
       <c r="F402" s="8"/>
     </row>
-    <row r="403" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6"/>
       <c r="B403" s="14"/>
       <c r="C403" s="11"/>
@@ -5228,7 +5338,7 @@
       <c r="E403" s="8"/>
       <c r="F403" s="8"/>
     </row>
-    <row r="404" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6"/>
       <c r="B404" s="14"/>
       <c r="C404" s="11"/>
@@ -5236,7 +5346,7 @@
       <c r="E404" s="8"/>
       <c r="F404" s="8"/>
     </row>
-    <row r="405" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6"/>
       <c r="B405" s="14"/>
       <c r="C405" s="11"/>
@@ -5244,7 +5354,7 @@
       <c r="E405" s="8"/>
       <c r="F405" s="8"/>
     </row>
-    <row r="406" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6"/>
       <c r="B406" s="14"/>
       <c r="C406" s="11"/>
@@ -5252,7 +5362,7 @@
       <c r="E406" s="8"/>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6"/>
       <c r="B407" s="14"/>
       <c r="C407" s="11"/>
@@ -5260,7 +5370,7 @@
       <c r="E407" s="8"/>
       <c r="F407" s="8"/>
     </row>
-    <row r="408" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6"/>
       <c r="B408" s="14"/>
       <c r="C408" s="11"/>
@@ -5268,7 +5378,7 @@
       <c r="E408" s="8"/>
       <c r="F408" s="8"/>
     </row>
-    <row r="409" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6"/>
       <c r="B409" s="14"/>
       <c r="C409" s="11"/>
@@ -5276,7 +5386,7 @@
       <c r="E409" s="8"/>
       <c r="F409" s="8"/>
     </row>
-    <row r="410" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6"/>
       <c r="B410" s="14"/>
       <c r="C410" s="11"/>
@@ -5284,7 +5394,7 @@
       <c r="E410" s="8"/>
       <c r="F410" s="8"/>
     </row>
-    <row r="411" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6"/>
       <c r="B411" s="14"/>
       <c r="C411" s="11"/>
@@ -5292,7 +5402,7 @@
       <c r="E411" s="8"/>
       <c r="F411" s="8"/>
     </row>
-    <row r="412" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6"/>
       <c r="B412" s="14"/>
       <c r="C412" s="11"/>
@@ -5300,7 +5410,7 @@
       <c r="E412" s="8"/>
       <c r="F412" s="8"/>
     </row>
-    <row r="413" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6"/>
       <c r="B413" s="14"/>
       <c r="C413" s="11"/>
@@ -5308,7 +5418,7 @@
       <c r="E413" s="8"/>
       <c r="F413" s="8"/>
     </row>
-    <row r="414" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6"/>
       <c r="B414" s="14"/>
       <c r="C414" s="11"/>
@@ -5316,7 +5426,7 @@
       <c r="E414" s="8"/>
       <c r="F414" s="8"/>
     </row>
-    <row r="415" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6"/>
       <c r="B415" s="14"/>
       <c r="C415" s="11"/>
@@ -5324,7 +5434,7 @@
       <c r="E415" s="8"/>
       <c r="F415" s="8"/>
     </row>
-    <row r="416" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6"/>
       <c r="B416" s="14"/>
       <c r="C416" s="11"/>
@@ -5332,7 +5442,7 @@
       <c r="E416" s="8"/>
       <c r="F416" s="8"/>
     </row>
-    <row r="417" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6"/>
       <c r="B417" s="14"/>
       <c r="C417" s="11"/>
@@ -5340,7 +5450,7 @@
       <c r="E417" s="8"/>
       <c r="F417" s="8"/>
     </row>
-    <row r="418" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6"/>
       <c r="B418" s="14"/>
       <c r="C418" s="11"/>
@@ -5348,7 +5458,7 @@
       <c r="E418" s="8"/>
       <c r="F418" s="8"/>
     </row>
-    <row r="419" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6"/>
       <c r="B419" s="14"/>
       <c r="C419" s="11"/>
@@ -5356,7 +5466,7 @@
       <c r="E419" s="8"/>
       <c r="F419" s="8"/>
     </row>
-    <row r="420" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6"/>
       <c r="B420" s="14"/>
       <c r="C420" s="11"/>
@@ -5364,7 +5474,7 @@
       <c r="E420" s="8"/>
       <c r="F420" s="8"/>
     </row>
-    <row r="421" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6"/>
       <c r="B421" s="14"/>
       <c r="C421" s="11"/>
@@ -5372,7 +5482,7 @@
       <c r="E421" s="8"/>
       <c r="F421" s="8"/>
     </row>
-    <row r="422" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6"/>
       <c r="B422" s="14"/>
       <c r="C422" s="11"/>
@@ -5380,7 +5490,7 @@
       <c r="E422" s="8"/>
       <c r="F422" s="8"/>
     </row>
-    <row r="423" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6"/>
       <c r="B423" s="14"/>
       <c r="C423" s="11"/>
@@ -5388,7 +5498,7 @@
       <c r="E423" s="8"/>
       <c r="F423" s="8"/>
     </row>
-    <row r="424" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6"/>
       <c r="B424" s="14"/>
       <c r="C424" s="11"/>
@@ -5396,7 +5506,7 @@
       <c r="E424" s="8"/>
       <c r="F424" s="8"/>
     </row>
-    <row r="425" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6"/>
       <c r="B425" s="14"/>
       <c r="C425" s="11"/>
@@ -5404,7 +5514,7 @@
       <c r="E425" s="8"/>
       <c r="F425" s="8"/>
     </row>
-    <row r="426" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="6"/>
       <c r="B426" s="14"/>
       <c r="C426" s="11"/>
@@ -5412,7 +5522,7 @@
       <c r="E426" s="8"/>
       <c r="F426" s="8"/>
     </row>
-    <row r="427" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="6"/>
       <c r="B427" s="14"/>
       <c r="C427" s="11"/>
@@ -5420,7 +5530,7 @@
       <c r="E427" s="8"/>
       <c r="F427" s="8"/>
     </row>
-    <row r="428" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="6"/>
       <c r="B428" s="14"/>
       <c r="C428" s="11"/>
@@ -5428,7 +5538,7 @@
       <c r="E428" s="8"/>
       <c r="F428" s="8"/>
     </row>
-    <row r="429" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="6"/>
       <c r="B429" s="14"/>
       <c r="C429" s="11"/>
@@ -5436,7 +5546,7 @@
       <c r="E429" s="8"/>
       <c r="F429" s="8"/>
     </row>
-    <row r="430" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="6"/>
       <c r="B430" s="14"/>
       <c r="C430" s="11"/>
@@ -5444,7 +5554,7 @@
       <c r="E430" s="8"/>
       <c r="F430" s="8"/>
     </row>
-    <row r="431" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="6"/>
       <c r="B431" s="14"/>
       <c r="C431" s="11"/>
@@ -5452,7 +5562,7 @@
       <c r="E431" s="8"/>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="6"/>
       <c r="B432" s="14"/>
       <c r="C432" s="11"/>
@@ -5460,7 +5570,7 @@
       <c r="E432" s="8"/>
       <c r="F432" s="8"/>
     </row>
-    <row r="433" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="6"/>
       <c r="B433" s="14"/>
       <c r="C433" s="11"/>
@@ -5468,7 +5578,7 @@
       <c r="E433" s="8"/>
       <c r="F433" s="8"/>
     </row>
-    <row r="434" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="6"/>
       <c r="B434" s="14"/>
       <c r="C434" s="11"/>
@@ -5476,7 +5586,7 @@
       <c r="E434" s="8"/>
       <c r="F434" s="8"/>
     </row>
-    <row r="435" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="6"/>
       <c r="B435" s="14"/>
       <c r="C435" s="11"/>
@@ -5484,7 +5594,7 @@
       <c r="E435" s="8"/>
       <c r="F435" s="8"/>
     </row>
-    <row r="436" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="6"/>
       <c r="B436" s="14"/>
       <c r="C436" s="11"/>
@@ -5492,7 +5602,7 @@
       <c r="E436" s="8"/>
       <c r="F436" s="8"/>
     </row>
-    <row r="437" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="6"/>
       <c r="B437" s="14"/>
       <c r="C437" s="11"/>
@@ -5500,7 +5610,7 @@
       <c r="E437" s="8"/>
       <c r="F437" s="8"/>
     </row>
-    <row r="438" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="6"/>
       <c r="B438" s="14"/>
       <c r="C438" s="11"/>
@@ -5508,7 +5618,7 @@
       <c r="E438" s="8"/>
       <c r="F438" s="8"/>
     </row>
-    <row r="439" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="6"/>
       <c r="B439" s="14"/>
       <c r="C439" s="11"/>
@@ -5516,7 +5626,7 @@
       <c r="E439" s="8"/>
       <c r="F439" s="8"/>
     </row>
-    <row r="440" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="6"/>
       <c r="B440" s="14"/>
       <c r="C440" s="11"/>
@@ -5524,7 +5634,7 @@
       <c r="E440" s="8"/>
       <c r="F440" s="8"/>
     </row>
-    <row r="441" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="6"/>
       <c r="B441" s="14"/>
       <c r="C441" s="11"/>
@@ -5532,7 +5642,7 @@
       <c r="E441" s="8"/>
       <c r="F441" s="8"/>
     </row>
-    <row r="442" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="6"/>
       <c r="B442" s="14"/>
       <c r="C442" s="11"/>
@@ -5540,7 +5650,7 @@
       <c r="E442" s="8"/>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="6"/>
       <c r="B443" s="14"/>
       <c r="C443" s="11"/>
@@ -5548,7 +5658,7 @@
       <c r="E443" s="8"/>
       <c r="F443" s="8"/>
     </row>
-    <row r="444" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="6"/>
       <c r="B444" s="14"/>
       <c r="C444" s="11"/>
@@ -5556,7 +5666,7 @@
       <c r="E444" s="8"/>
       <c r="F444" s="8"/>
     </row>
-    <row r="445" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="6"/>
       <c r="B445" s="14"/>
       <c r="C445" s="11"/>
@@ -5564,7 +5674,7 @@
       <c r="E445" s="8"/>
       <c r="F445" s="8"/>
     </row>
-    <row r="446" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="6"/>
       <c r="B446" s="14"/>
       <c r="C446" s="11"/>
@@ -5572,7 +5682,7 @@
       <c r="E446" s="8"/>
       <c r="F446" s="8"/>
     </row>
-    <row r="447" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="6"/>
       <c r="B447" s="14"/>
       <c r="C447" s="11"/>
@@ -5580,7 +5690,7 @@
       <c r="E447" s="8"/>
       <c r="F447" s="8"/>
     </row>
-    <row r="448" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="6"/>
       <c r="B448" s="14"/>
       <c r="C448" s="11"/>
@@ -5588,7 +5698,7 @@
       <c r="E448" s="8"/>
       <c r="F448" s="8"/>
     </row>
-    <row r="449" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="6"/>
       <c r="B449" s="14"/>
       <c r="C449" s="11"/>
@@ -5596,7 +5706,7 @@
       <c r="E449" s="8"/>
       <c r="F449" s="8"/>
     </row>
-    <row r="450" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="6"/>
       <c r="B450" s="14"/>
       <c r="C450" s="11"/>
@@ -5604,7 +5714,7 @@
       <c r="E450" s="8"/>
       <c r="F450" s="8"/>
     </row>
-    <row r="451" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="6"/>
       <c r="B451" s="14"/>
       <c r="C451" s="11"/>
@@ -5612,7 +5722,7 @@
       <c r="E451" s="8"/>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="6"/>
       <c r="B452" s="14"/>
       <c r="C452" s="11"/>
@@ -5620,7 +5730,7 @@
       <c r="E452" s="8"/>
       <c r="F452" s="8"/>
     </row>
-    <row r="453" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="6"/>
       <c r="B453" s="14"/>
       <c r="C453" s="11"/>
@@ -5628,7 +5738,7 @@
       <c r="E453" s="8"/>
       <c r="F453" s="8"/>
     </row>
-    <row r="454" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="6"/>
       <c r="B454" s="14"/>
       <c r="C454" s="11"/>
@@ -5636,7 +5746,7 @@
       <c r="E454" s="8"/>
       <c r="F454" s="8"/>
     </row>
-    <row r="455" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="6"/>
       <c r="B455" s="14"/>
       <c r="C455" s="11"/>
@@ -5644,7 +5754,7 @@
       <c r="E455" s="8"/>
       <c r="F455" s="8"/>
     </row>
-    <row r="456" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="6"/>
       <c r="B456" s="14"/>
       <c r="C456" s="11"/>
@@ -5652,7 +5762,7 @@
       <c r="E456" s="8"/>
       <c r="F456" s="8"/>
     </row>
-    <row r="457" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="6"/>
       <c r="B457" s="14"/>
       <c r="C457" s="11"/>
@@ -5660,7 +5770,7 @@
       <c r="E457" s="8"/>
       <c r="F457" s="8"/>
     </row>
-    <row r="458" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="6"/>
       <c r="B458" s="14"/>
       <c r="C458" s="11"/>
@@ -5668,7 +5778,7 @@
       <c r="E458" s="8"/>
       <c r="F458" s="8"/>
     </row>
-    <row r="459" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="6"/>
       <c r="B459" s="14"/>
       <c r="C459" s="11"/>
@@ -5676,7 +5786,7 @@
       <c r="E459" s="8"/>
       <c r="F459" s="8"/>
     </row>
-    <row r="460" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="6"/>
       <c r="B460" s="14"/>
       <c r="C460" s="11"/>
@@ -5684,7 +5794,7 @@
       <c r="E460" s="8"/>
       <c r="F460" s="8"/>
     </row>
-    <row r="461" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="6"/>
       <c r="B461" s="14"/>
       <c r="C461" s="11"/>
@@ -5692,7 +5802,7 @@
       <c r="E461" s="8"/>
       <c r="F461" s="8"/>
     </row>
-    <row r="462" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="6"/>
       <c r="B462" s="14"/>
       <c r="C462" s="11"/>
@@ -5700,7 +5810,7 @@
       <c r="E462" s="8"/>
       <c r="F462" s="8"/>
     </row>
-    <row r="463" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="6"/>
       <c r="B463" s="14"/>
       <c r="C463" s="11"/>
@@ -5708,7 +5818,7 @@
       <c r="E463" s="8"/>
       <c r="F463" s="8"/>
     </row>
-    <row r="464" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="6"/>
       <c r="B464" s="14"/>
       <c r="C464" s="11"/>
@@ -5716,7 +5826,7 @@
       <c r="E464" s="8"/>
       <c r="F464" s="8"/>
     </row>
-    <row r="465" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="6"/>
       <c r="B465" s="14"/>
       <c r="C465" s="11"/>
@@ -5724,7 +5834,7 @@
       <c r="E465" s="8"/>
       <c r="F465" s="8"/>
     </row>
-    <row r="466" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="6"/>
       <c r="B466" s="14"/>
       <c r="C466" s="11"/>
@@ -5732,7 +5842,7 @@
       <c r="E466" s="8"/>
       <c r="F466" s="8"/>
     </row>
-    <row r="467" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="6"/>
       <c r="B467" s="14"/>
       <c r="C467" s="11"/>
@@ -5740,7 +5850,7 @@
       <c r="E467" s="8"/>
       <c r="F467" s="8"/>
     </row>
-    <row r="468" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="6"/>
       <c r="B468" s="14"/>
       <c r="C468" s="11"/>
@@ -5748,7 +5858,7 @@
       <c r="E468" s="8"/>
       <c r="F468" s="8"/>
     </row>
-    <row r="469" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="6"/>
       <c r="B469" s="14"/>
       <c r="C469" s="11"/>
@@ -5756,7 +5866,7 @@
       <c r="E469" s="8"/>
       <c r="F469" s="8"/>
     </row>
-    <row r="470" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="6"/>
       <c r="B470" s="14"/>
       <c r="C470" s="11"/>
@@ -5764,7 +5874,7 @@
       <c r="E470" s="8"/>
       <c r="F470" s="8"/>
     </row>
-    <row r="471" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="6"/>
       <c r="B471" s="14"/>
       <c r="C471" s="11"/>
@@ -5772,7 +5882,7 @@
       <c r="E471" s="8"/>
       <c r="F471" s="8"/>
     </row>
-    <row r="472" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="6"/>
       <c r="B472" s="14"/>
       <c r="C472" s="11"/>
@@ -5780,7 +5890,7 @@
       <c r="E472" s="8"/>
       <c r="F472" s="8"/>
     </row>
-    <row r="473" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="6"/>
       <c r="B473" s="14"/>
       <c r="C473" s="11"/>
@@ -5788,7 +5898,7 @@
       <c r="E473" s="8"/>
       <c r="F473" s="8"/>
     </row>
-    <row r="474" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="6"/>
       <c r="B474" s="14"/>
       <c r="C474" s="11"/>
@@ -5796,7 +5906,7 @@
       <c r="E474" s="8"/>
       <c r="F474" s="8"/>
     </row>
-    <row r="475" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="6"/>
       <c r="B475" s="14"/>
       <c r="C475" s="11"/>
@@ -5804,7 +5914,7 @@
       <c r="E475" s="8"/>
       <c r="F475" s="8"/>
     </row>
-    <row r="476" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="6"/>
       <c r="B476" s="14"/>
       <c r="C476" s="11"/>
@@ -5812,7 +5922,7 @@
       <c r="E476" s="8"/>
       <c r="F476" s="8"/>
     </row>
-    <row r="477" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="6"/>
       <c r="B477" s="14"/>
       <c r="C477" s="11"/>
@@ -5820,7 +5930,7 @@
       <c r="E477" s="8"/>
       <c r="F477" s="8"/>
     </row>
-    <row r="478" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="6"/>
       <c r="B478" s="14"/>
       <c r="C478" s="11"/>
@@ -5828,7 +5938,7 @@
       <c r="E478" s="8"/>
       <c r="F478" s="8"/>
     </row>
-    <row r="479" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="6"/>
       <c r="B479" s="14"/>
       <c r="C479" s="11"/>
@@ -5836,7 +5946,7 @@
       <c r="E479" s="8"/>
       <c r="F479" s="8"/>
     </row>
-    <row r="480" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="6"/>
       <c r="B480" s="14"/>
       <c r="C480" s="11"/>
@@ -5844,7 +5954,7 @@
       <c r="E480" s="8"/>
       <c r="F480" s="8"/>
     </row>
-    <row r="481" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="6"/>
       <c r="B481" s="14"/>
       <c r="C481" s="11"/>
@@ -5852,7 +5962,7 @@
       <c r="E481" s="8"/>
       <c r="F481" s="8"/>
     </row>
-    <row r="482" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="6"/>
       <c r="B482" s="14"/>
       <c r="C482" s="11"/>
@@ -5860,7 +5970,7 @@
       <c r="E482" s="8"/>
       <c r="F482" s="8"/>
     </row>
-    <row r="483" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="6"/>
       <c r="B483" s="14"/>
       <c r="C483" s="11"/>
@@ -5868,7 +5978,7 @@
       <c r="E483" s="8"/>
       <c r="F483" s="8"/>
     </row>
-    <row r="484" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="6"/>
       <c r="B484" s="14"/>
       <c r="C484" s="11"/>
@@ -5876,7 +5986,7 @@
       <c r="E484" s="8"/>
       <c r="F484" s="8"/>
     </row>
-    <row r="485" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="6"/>
       <c r="B485" s="14"/>
       <c r="C485" s="11"/>
@@ -5884,7 +5994,7 @@
       <c r="E485" s="8"/>
       <c r="F485" s="8"/>
     </row>
-    <row r="486" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="6"/>
       <c r="B486" s="14"/>
       <c r="C486" s="11"/>
@@ -5892,7 +6002,7 @@
       <c r="E486" s="8"/>
       <c r="F486" s="8"/>
     </row>
-    <row r="487" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="6"/>
       <c r="B487" s="14"/>
       <c r="C487" s="11"/>
@@ -5900,7 +6010,7 @@
       <c r="E487" s="8"/>
       <c r="F487" s="8"/>
     </row>
-    <row r="488" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="6"/>
       <c r="B488" s="14"/>
       <c r="C488" s="11"/>
@@ -5908,7 +6018,7 @@
       <c r="E488" s="8"/>
       <c r="F488" s="8"/>
     </row>
-    <row r="489" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="6"/>
       <c r="B489" s="14"/>
       <c r="C489" s="11"/>
@@ -5916,7 +6026,7 @@
       <c r="E489" s="8"/>
       <c r="F489" s="8"/>
     </row>
-    <row r="490" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="6"/>
       <c r="B490" s="14"/>
       <c r="C490" s="11"/>
@@ -5924,7 +6034,7 @@
       <c r="E490" s="8"/>
       <c r="F490" s="8"/>
     </row>
-    <row r="491" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="6"/>
       <c r="B491" s="14"/>
       <c r="C491" s="11"/>
@@ -5932,7 +6042,7 @@
       <c r="E491" s="8"/>
       <c r="F491" s="8"/>
     </row>
-    <row r="492" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="6"/>
       <c r="B492" s="14"/>
       <c r="C492" s="11"/>
@@ -5940,7 +6050,7 @@
       <c r="E492" s="8"/>
       <c r="F492" s="8"/>
     </row>
-    <row r="493" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="6"/>
       <c r="B493" s="14"/>
       <c r="C493" s="11"/>
@@ -5948,7 +6058,7 @@
       <c r="E493" s="8"/>
       <c r="F493" s="8"/>
     </row>
-    <row r="494" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="6"/>
       <c r="B494" s="14"/>
       <c r="C494" s="11"/>
@@ -5956,7 +6066,7 @@
       <c r="E494" s="8"/>
       <c r="F494" s="8"/>
     </row>
-    <row r="495" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="6"/>
       <c r="B495" s="14"/>
       <c r="C495" s="11"/>
@@ -5964,7 +6074,7 @@
       <c r="E495" s="8"/>
       <c r="F495" s="8"/>
     </row>
-    <row r="496" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="6"/>
       <c r="B496" s="14"/>
       <c r="C496" s="11"/>
@@ -5972,7 +6082,7 @@
       <c r="E496" s="8"/>
       <c r="F496" s="8"/>
     </row>
-    <row r="497" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="6"/>
       <c r="B497" s="14"/>
       <c r="C497" s="11"/>
@@ -5980,7 +6090,7 @@
       <c r="E497" s="8"/>
       <c r="F497" s="8"/>
     </row>
-    <row r="498" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="6"/>
       <c r="B498" s="14"/>
       <c r="C498" s="11"/>
@@ -5988,7 +6098,7 @@
       <c r="E498" s="8"/>
       <c r="F498" s="8"/>
     </row>
-    <row r="499" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="6"/>
       <c r="B499" s="14"/>
       <c r="C499" s="11"/>
@@ -5996,7 +6106,7 @@
       <c r="E499" s="8"/>
       <c r="F499" s="8"/>
     </row>
-    <row r="500" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="6"/>
       <c r="B500" s="14"/>
       <c r="C500" s="11"/>
@@ -6004,7 +6114,7 @@
       <c r="E500" s="8"/>
       <c r="F500" s="8"/>
     </row>
-    <row r="501" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A501" s="6"/>
       <c r="B501" s="14"/>
       <c r="C501" s="11"/>
@@ -6012,13 +6122,29 @@
       <c r="E501" s="8"/>
       <c r="F501" s="8"/>
     </row>
+    <row r="502" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A502" s="6"/>
+      <c r="B502" s="14"/>
+      <c r="C502" s="11"/>
+      <c r="D502" s="7"/>
+      <c r="E502" s="8"/>
+      <c r="F502" s="8"/>
+    </row>
+    <row r="503" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A503" s="6"/>
+      <c r="B503" s="14"/>
+      <c r="C503" s="11"/>
+      <c r="D503" s="7"/>
+      <c r="E503" s="8"/>
+      <c r="F503" s="8"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B301" xr:uid="{E1FCDE41-ACF1-4A68-9483-C062BB428146}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B303" xr:uid="{E1FCDE41-ACF1-4A68-9483-C062BB428146}">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C301" xr:uid="{48106778-5E48-49BE-9E53-EB975C533ABF}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C303" xr:uid="{48106778-5E48-49BE-9E53-EB975C533ABF}">
       <formula1>0.25</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -6038,7 +6164,7 @@
           <x14:formula1>
             <xm:f>Listes!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D1:D301</xm:sqref>
+          <xm:sqref>D1:D303</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6049,13 +6175,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC8CEF3-AF3E-4D54-8188-1302D62F0F60}">
   <dimension ref="A1:B500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.8984375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.19921875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="24.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.25" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
@@ -6063,2039 +6189,2039 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="11">
-        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+        <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="11">
-        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+        <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="11">
-        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+        <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="11">
-        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
+        <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="11">
-        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+        <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="11">
-        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
+        <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="11">
-        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
+        <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="11">
-        <f>SUMIF(Journal!$D$2:$D$161,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$161)</f>
+        <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="11"/>
     </row>
-    <row r="12" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="11"/>
     </row>
-    <row r="13" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="11"/>
     </row>
-    <row r="14" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="11"/>
     </row>
-    <row r="15" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="11"/>
     </row>
-    <row r="16" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="11"/>
     </row>
-    <row r="17" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="11"/>
     </row>
-    <row r="18" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="11"/>
     </row>
-    <row r="19" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="11"/>
     </row>
-    <row r="20" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="11"/>
     </row>
-    <row r="21" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="11"/>
     </row>
-    <row r="22" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="11"/>
     </row>
-    <row r="23" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="11"/>
     </row>
-    <row r="24" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="11"/>
     </row>
-    <row r="25" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="11"/>
     </row>
-    <row r="27" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="11"/>
     </row>
-    <row r="28" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="11"/>
     </row>
-    <row r="29" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="11"/>
     </row>
-    <row r="30" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="11"/>
     </row>
-    <row r="31" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="11"/>
     </row>
-    <row r="32" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="11"/>
     </row>
-    <row r="33" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="11"/>
     </row>
-    <row r="34" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="11"/>
     </row>
-    <row r="35" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="11"/>
     </row>
-    <row r="36" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="11"/>
     </row>
-    <row r="37" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="11"/>
     </row>
-    <row r="38" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="11"/>
     </row>
-    <row r="39" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="11"/>
     </row>
-    <row r="40" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="11"/>
     </row>
-    <row r="41" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="11"/>
     </row>
-    <row r="42" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="11"/>
     </row>
-    <row r="43" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="11"/>
     </row>
-    <row r="44" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="11"/>
     </row>
-    <row r="45" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="11"/>
     </row>
-    <row r="46" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="11"/>
     </row>
-    <row r="47" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="11"/>
     </row>
-    <row r="48" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="11"/>
     </row>
-    <row r="49" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="11"/>
     </row>
-    <row r="50" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="11"/>
     </row>
-    <row r="51" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="11"/>
     </row>
-    <row r="52" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="11"/>
     </row>
-    <row r="53" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="11"/>
     </row>
-    <row r="54" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="11"/>
     </row>
-    <row r="55" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="11"/>
     </row>
-    <row r="56" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="11"/>
     </row>
-    <row r="57" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="11"/>
     </row>
-    <row r="58" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="11"/>
     </row>
-    <row r="59" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="11"/>
     </row>
-    <row r="60" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="11"/>
     </row>
-    <row r="61" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="11"/>
     </row>
-    <row r="62" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="11"/>
     </row>
-    <row r="63" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="11"/>
     </row>
-    <row r="64" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="11"/>
     </row>
-    <row r="65" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="11"/>
     </row>
-    <row r="66" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="11"/>
     </row>
-    <row r="67" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="11"/>
     </row>
-    <row r="68" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="11"/>
     </row>
-    <row r="69" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="11"/>
     </row>
-    <row r="70" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="11"/>
     </row>
-    <row r="71" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
       <c r="B71" s="11"/>
     </row>
-    <row r="72" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="11"/>
     </row>
-    <row r="73" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="11"/>
     </row>
-    <row r="74" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="11"/>
     </row>
-    <row r="75" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="11"/>
     </row>
-    <row r="76" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="11"/>
     </row>
-    <row r="77" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="11"/>
     </row>
-    <row r="78" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="11"/>
     </row>
-    <row r="79" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="11"/>
     </row>
-    <row r="80" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="11"/>
     </row>
-    <row r="81" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="11"/>
     </row>
-    <row r="82" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="11"/>
     </row>
-    <row r="83" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="11"/>
     </row>
-    <row r="84" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="11"/>
     </row>
-    <row r="85" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="11"/>
     </row>
-    <row r="86" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="11"/>
     </row>
-    <row r="87" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="11"/>
     </row>
-    <row r="88" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="11"/>
     </row>
-    <row r="89" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="11"/>
     </row>
-    <row r="90" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="11"/>
     </row>
-    <row r="91" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="11"/>
     </row>
-    <row r="92" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="11"/>
     </row>
-    <row r="93" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="11"/>
     </row>
-    <row r="94" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="11"/>
     </row>
-    <row r="95" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="11"/>
     </row>
-    <row r="96" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="11"/>
     </row>
-    <row r="97" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="11"/>
     </row>
-    <row r="98" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="11"/>
     </row>
-    <row r="99" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="11"/>
     </row>
-    <row r="100" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="11"/>
     </row>
-    <row r="101" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
       <c r="B101" s="11"/>
     </row>
-    <row r="102" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="11"/>
     </row>
-    <row r="103" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="11"/>
     </row>
-    <row r="104" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6"/>
       <c r="B104" s="11"/>
     </row>
-    <row r="105" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6"/>
       <c r="B105" s="11"/>
     </row>
-    <row r="106" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6"/>
       <c r="B106" s="11"/>
     </row>
-    <row r="107" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="B107" s="11"/>
     </row>
-    <row r="108" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="B108" s="11"/>
     </row>
-    <row r="109" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="B109" s="11"/>
     </row>
-    <row r="110" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="B110" s="11"/>
     </row>
-    <row r="111" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6"/>
       <c r="B111" s="11"/>
     </row>
-    <row r="112" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6"/>
       <c r="B112" s="11"/>
     </row>
-    <row r="113" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
       <c r="B113" s="11"/>
     </row>
-    <row r="114" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6"/>
       <c r="B114" s="11"/>
     </row>
-    <row r="115" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6"/>
       <c r="B115" s="11"/>
     </row>
-    <row r="116" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6"/>
       <c r="B116" s="11"/>
     </row>
-    <row r="117" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6"/>
       <c r="B117" s="11"/>
     </row>
-    <row r="118" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6"/>
       <c r="B118" s="11"/>
     </row>
-    <row r="119" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6"/>
       <c r="B119" s="11"/>
     </row>
-    <row r="120" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6"/>
       <c r="B120" s="11"/>
     </row>
-    <row r="121" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6"/>
       <c r="B121" s="11"/>
     </row>
-    <row r="122" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6"/>
       <c r="B122" s="11"/>
     </row>
-    <row r="123" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6"/>
       <c r="B123" s="11"/>
     </row>
-    <row r="124" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6"/>
       <c r="B124" s="11"/>
     </row>
-    <row r="125" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6"/>
       <c r="B125" s="11"/>
     </row>
-    <row r="126" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6"/>
       <c r="B126" s="11"/>
     </row>
-    <row r="127" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6"/>
       <c r="B127" s="11"/>
     </row>
-    <row r="128" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6"/>
       <c r="B128" s="11"/>
     </row>
-    <row r="129" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6"/>
       <c r="B129" s="11"/>
     </row>
-    <row r="130" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6"/>
       <c r="B130" s="11"/>
     </row>
-    <row r="131" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6"/>
       <c r="B131" s="11"/>
     </row>
-    <row r="132" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6"/>
       <c r="B132" s="11"/>
     </row>
-    <row r="133" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6"/>
       <c r="B133" s="11"/>
     </row>
-    <row r="134" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6"/>
       <c r="B134" s="11"/>
     </row>
-    <row r="135" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6"/>
       <c r="B135" s="11"/>
     </row>
-    <row r="136" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6"/>
       <c r="B136" s="11"/>
     </row>
-    <row r="137" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6"/>
       <c r="B137" s="11"/>
     </row>
-    <row r="138" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6"/>
       <c r="B138" s="11"/>
     </row>
-    <row r="139" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6"/>
       <c r="B139" s="11"/>
     </row>
-    <row r="140" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6"/>
       <c r="B140" s="11"/>
     </row>
-    <row r="141" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6"/>
       <c r="B141" s="11"/>
     </row>
-    <row r="142" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6"/>
       <c r="B142" s="11"/>
     </row>
-    <row r="143" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6"/>
       <c r="B143" s="11"/>
     </row>
-    <row r="144" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6"/>
       <c r="B144" s="11"/>
     </row>
-    <row r="145" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6"/>
       <c r="B145" s="11"/>
     </row>
-    <row r="146" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6"/>
       <c r="B146" s="11"/>
     </row>
-    <row r="147" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6"/>
       <c r="B147" s="11"/>
     </row>
-    <row r="148" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6"/>
       <c r="B148" s="11"/>
     </row>
-    <row r="149" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6"/>
       <c r="B149" s="11"/>
     </row>
-    <row r="150" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6"/>
       <c r="B150" s="11"/>
     </row>
-    <row r="151" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6"/>
       <c r="B151" s="11"/>
     </row>
-    <row r="152" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6"/>
       <c r="B152" s="11"/>
     </row>
-    <row r="153" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6"/>
       <c r="B153" s="11"/>
     </row>
-    <row r="154" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6"/>
       <c r="B154" s="11"/>
     </row>
-    <row r="155" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6"/>
       <c r="B155" s="11"/>
     </row>
-    <row r="156" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6"/>
       <c r="B156" s="11"/>
     </row>
-    <row r="157" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6"/>
       <c r="B157" s="11"/>
     </row>
-    <row r="158" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6"/>
       <c r="B158" s="11"/>
     </row>
-    <row r="159" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6"/>
       <c r="B159" s="11"/>
     </row>
-    <row r="160" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6"/>
       <c r="B160" s="11"/>
     </row>
-    <row r="161" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6"/>
       <c r="B161" s="11"/>
     </row>
-    <row r="162" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6"/>
       <c r="B162" s="11"/>
     </row>
-    <row r="163" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6"/>
       <c r="B163" s="11"/>
     </row>
-    <row r="164" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6"/>
       <c r="B164" s="11"/>
     </row>
-    <row r="165" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6"/>
       <c r="B165" s="11"/>
     </row>
-    <row r="166" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6"/>
       <c r="B166" s="11"/>
     </row>
-    <row r="167" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6"/>
       <c r="B167" s="11"/>
     </row>
-    <row r="168" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6"/>
       <c r="B168" s="11"/>
     </row>
-    <row r="169" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6"/>
       <c r="B169" s="11"/>
     </row>
-    <row r="170" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6"/>
       <c r="B170" s="11"/>
     </row>
-    <row r="171" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6"/>
       <c r="B171" s="11"/>
     </row>
-    <row r="172" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6"/>
       <c r="B172" s="11"/>
     </row>
-    <row r="173" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6"/>
       <c r="B173" s="11"/>
     </row>
-    <row r="174" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6"/>
       <c r="B174" s="11"/>
     </row>
-    <row r="175" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6"/>
       <c r="B175" s="11"/>
     </row>
-    <row r="176" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6"/>
       <c r="B176" s="11"/>
     </row>
-    <row r="177" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6"/>
       <c r="B177" s="11"/>
     </row>
-    <row r="178" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6"/>
       <c r="B178" s="11"/>
     </row>
-    <row r="179" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6"/>
       <c r="B179" s="11"/>
     </row>
-    <row r="180" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6"/>
       <c r="B180" s="11"/>
     </row>
-    <row r="181" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6"/>
       <c r="B181" s="11"/>
     </row>
-    <row r="182" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6"/>
       <c r="B182" s="11"/>
     </row>
-    <row r="183" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6"/>
       <c r="B183" s="11"/>
     </row>
-    <row r="184" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6"/>
       <c r="B184" s="11"/>
     </row>
-    <row r="185" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6"/>
       <c r="B185" s="11"/>
     </row>
-    <row r="186" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6"/>
       <c r="B186" s="11"/>
     </row>
-    <row r="187" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6"/>
       <c r="B187" s="11"/>
     </row>
-    <row r="188" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6"/>
       <c r="B188" s="11"/>
     </row>
-    <row r="189" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6"/>
       <c r="B189" s="11"/>
     </row>
-    <row r="190" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6"/>
       <c r="B190" s="11"/>
     </row>
-    <row r="191" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6"/>
       <c r="B191" s="11"/>
     </row>
-    <row r="192" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6"/>
       <c r="B192" s="11"/>
     </row>
-    <row r="193" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6"/>
       <c r="B193" s="11"/>
     </row>
-    <row r="194" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6"/>
       <c r="B194" s="11"/>
     </row>
-    <row r="195" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6"/>
       <c r="B195" s="11"/>
     </row>
-    <row r="196" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6"/>
       <c r="B196" s="11"/>
     </row>
-    <row r="197" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6"/>
       <c r="B197" s="11"/>
     </row>
-    <row r="198" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6"/>
       <c r="B198" s="11"/>
     </row>
-    <row r="199" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6"/>
       <c r="B199" s="11"/>
     </row>
-    <row r="200" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6"/>
       <c r="B200" s="11"/>
     </row>
-    <row r="201" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6"/>
       <c r="B201" s="11"/>
     </row>
-    <row r="202" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6"/>
       <c r="B202" s="11"/>
     </row>
-    <row r="203" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6"/>
       <c r="B203" s="11"/>
     </row>
-    <row r="204" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6"/>
       <c r="B204" s="11"/>
     </row>
-    <row r="205" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6"/>
       <c r="B205" s="11"/>
     </row>
-    <row r="206" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6"/>
       <c r="B206" s="11"/>
     </row>
-    <row r="207" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6"/>
       <c r="B207" s="11"/>
     </row>
-    <row r="208" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6"/>
       <c r="B208" s="11"/>
     </row>
-    <row r="209" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6"/>
       <c r="B209" s="11"/>
     </row>
-    <row r="210" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6"/>
       <c r="B210" s="11"/>
     </row>
-    <row r="211" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6"/>
       <c r="B211" s="11"/>
     </row>
-    <row r="212" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6"/>
       <c r="B212" s="11"/>
     </row>
-    <row r="213" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6"/>
       <c r="B213" s="11"/>
     </row>
-    <row r="214" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6"/>
       <c r="B214" s="11"/>
     </row>
-    <row r="215" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6"/>
       <c r="B215" s="11"/>
     </row>
-    <row r="216" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6"/>
       <c r="B216" s="11"/>
     </row>
-    <row r="217" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6"/>
       <c r="B217" s="11"/>
     </row>
-    <row r="218" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6"/>
       <c r="B218" s="11"/>
     </row>
-    <row r="219" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6"/>
       <c r="B219" s="11"/>
     </row>
-    <row r="220" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6"/>
       <c r="B220" s="11"/>
     </row>
-    <row r="221" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6"/>
       <c r="B221" s="11"/>
     </row>
-    <row r="222" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6"/>
       <c r="B222" s="11"/>
     </row>
-    <row r="223" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6"/>
       <c r="B223" s="11"/>
     </row>
-    <row r="224" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6"/>
       <c r="B224" s="11"/>
     </row>
-    <row r="225" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6"/>
       <c r="B225" s="11"/>
     </row>
-    <row r="226" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6"/>
       <c r="B226" s="11"/>
     </row>
-    <row r="227" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6"/>
       <c r="B227" s="11"/>
     </row>
-    <row r="228" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6"/>
       <c r="B228" s="11"/>
     </row>
-    <row r="229" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6"/>
       <c r="B229" s="11"/>
     </row>
-    <row r="230" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6"/>
       <c r="B230" s="11"/>
     </row>
-    <row r="231" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6"/>
       <c r="B231" s="11"/>
     </row>
-    <row r="232" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6"/>
       <c r="B232" s="11"/>
     </row>
-    <row r="233" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6"/>
       <c r="B233" s="11"/>
     </row>
-    <row r="234" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6"/>
       <c r="B234" s="11"/>
     </row>
-    <row r="235" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6"/>
       <c r="B235" s="11"/>
     </row>
-    <row r="236" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6"/>
       <c r="B236" s="11"/>
     </row>
-    <row r="237" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6"/>
       <c r="B237" s="11"/>
     </row>
-    <row r="238" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6"/>
       <c r="B238" s="11"/>
     </row>
-    <row r="239" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6"/>
       <c r="B239" s="11"/>
     </row>
-    <row r="240" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6"/>
       <c r="B240" s="11"/>
     </row>
-    <row r="241" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6"/>
       <c r="B241" s="11"/>
     </row>
-    <row r="242" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6"/>
       <c r="B242" s="11"/>
     </row>
-    <row r="243" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6"/>
       <c r="B243" s="11"/>
     </row>
-    <row r="244" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6"/>
       <c r="B244" s="11"/>
     </row>
-    <row r="245" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6"/>
       <c r="B245" s="11"/>
     </row>
-    <row r="246" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6"/>
       <c r="B246" s="11"/>
     </row>
-    <row r="247" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6"/>
       <c r="B247" s="11"/>
     </row>
-    <row r="248" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6"/>
       <c r="B248" s="11"/>
     </row>
-    <row r="249" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6"/>
       <c r="B249" s="11"/>
     </row>
-    <row r="250" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6"/>
       <c r="B250" s="11"/>
     </row>
-    <row r="251" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6"/>
       <c r="B251" s="11"/>
     </row>
-    <row r="252" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6"/>
       <c r="B252" s="11"/>
     </row>
-    <row r="253" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6"/>
       <c r="B253" s="11"/>
     </row>
-    <row r="254" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6"/>
       <c r="B254" s="11"/>
     </row>
-    <row r="255" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6"/>
       <c r="B255" s="11"/>
     </row>
-    <row r="256" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6"/>
       <c r="B256" s="11"/>
     </row>
-    <row r="257" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6"/>
       <c r="B257" s="11"/>
     </row>
-    <row r="258" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6"/>
       <c r="B258" s="11"/>
     </row>
-    <row r="259" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6"/>
       <c r="B259" s="11"/>
     </row>
-    <row r="260" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6"/>
       <c r="B260" s="11"/>
     </row>
-    <row r="261" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6"/>
       <c r="B261" s="11"/>
     </row>
-    <row r="262" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6"/>
       <c r="B262" s="11"/>
     </row>
-    <row r="263" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6"/>
       <c r="B263" s="11"/>
     </row>
-    <row r="264" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6"/>
       <c r="B264" s="11"/>
     </row>
-    <row r="265" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6"/>
       <c r="B265" s="11"/>
     </row>
-    <row r="266" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6"/>
       <c r="B266" s="11"/>
     </row>
-    <row r="267" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6"/>
       <c r="B267" s="11"/>
     </row>
-    <row r="268" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6"/>
       <c r="B268" s="11"/>
     </row>
-    <row r="269" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6"/>
       <c r="B269" s="11"/>
     </row>
-    <row r="270" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6"/>
       <c r="B270" s="11"/>
     </row>
-    <row r="271" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6"/>
       <c r="B271" s="11"/>
     </row>
-    <row r="272" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6"/>
       <c r="B272" s="11"/>
     </row>
-    <row r="273" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6"/>
       <c r="B273" s="11"/>
     </row>
-    <row r="274" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6"/>
       <c r="B274" s="11"/>
     </row>
-    <row r="275" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6"/>
       <c r="B275" s="11"/>
     </row>
-    <row r="276" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6"/>
       <c r="B276" s="11"/>
     </row>
-    <row r="277" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6"/>
       <c r="B277" s="11"/>
     </row>
-    <row r="278" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6"/>
       <c r="B278" s="11"/>
     </row>
-    <row r="279" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6"/>
       <c r="B279" s="11"/>
     </row>
-    <row r="280" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6"/>
       <c r="B280" s="11"/>
     </row>
-    <row r="281" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6"/>
       <c r="B281" s="11"/>
     </row>
-    <row r="282" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6"/>
       <c r="B282" s="11"/>
     </row>
-    <row r="283" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6"/>
       <c r="B283" s="11"/>
     </row>
-    <row r="284" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6"/>
       <c r="B284" s="11"/>
     </row>
-    <row r="285" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6"/>
       <c r="B285" s="11"/>
     </row>
-    <row r="286" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6"/>
       <c r="B286" s="11"/>
     </row>
-    <row r="287" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6"/>
       <c r="B287" s="11"/>
     </row>
-    <row r="288" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6"/>
       <c r="B288" s="11"/>
     </row>
-    <row r="289" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6"/>
       <c r="B289" s="11"/>
     </row>
-    <row r="290" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6"/>
       <c r="B290" s="11"/>
     </row>
-    <row r="291" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6"/>
       <c r="B291" s="11"/>
     </row>
-    <row r="292" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6"/>
       <c r="B292" s="11"/>
     </row>
-    <row r="293" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6"/>
       <c r="B293" s="11"/>
     </row>
-    <row r="294" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6"/>
       <c r="B294" s="11"/>
     </row>
-    <row r="295" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6"/>
       <c r="B295" s="11"/>
     </row>
-    <row r="296" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6"/>
       <c r="B296" s="11"/>
     </row>
-    <row r="297" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6"/>
       <c r="B297" s="11"/>
     </row>
-    <row r="298" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6"/>
       <c r="B298" s="11"/>
     </row>
-    <row r="299" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6"/>
       <c r="B299" s="11"/>
     </row>
-    <row r="300" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6"/>
       <c r="B300" s="11"/>
     </row>
-    <row r="301" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6"/>
       <c r="B301" s="11"/>
     </row>
-    <row r="302" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6"/>
       <c r="B302" s="11"/>
     </row>
-    <row r="303" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6"/>
       <c r="B303" s="11"/>
     </row>
-    <row r="304" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6"/>
       <c r="B304" s="11"/>
     </row>
-    <row r="305" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6"/>
       <c r="B305" s="11"/>
     </row>
-    <row r="306" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6"/>
       <c r="B306" s="11"/>
     </row>
-    <row r="307" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6"/>
       <c r="B307" s="11"/>
     </row>
-    <row r="308" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6"/>
       <c r="B308" s="11"/>
     </row>
-    <row r="309" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6"/>
       <c r="B309" s="11"/>
     </row>
-    <row r="310" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6"/>
       <c r="B310" s="11"/>
     </row>
-    <row r="311" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6"/>
       <c r="B311" s="11"/>
     </row>
-    <row r="312" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6"/>
       <c r="B312" s="11"/>
     </row>
-    <row r="313" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6"/>
       <c r="B313" s="11"/>
     </row>
-    <row r="314" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6"/>
       <c r="B314" s="11"/>
     </row>
-    <row r="315" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6"/>
       <c r="B315" s="11"/>
     </row>
-    <row r="316" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6"/>
       <c r="B316" s="11"/>
     </row>
-    <row r="317" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6"/>
       <c r="B317" s="11"/>
     </row>
-    <row r="318" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6"/>
       <c r="B318" s="11"/>
     </row>
-    <row r="319" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6"/>
       <c r="B319" s="11"/>
     </row>
-    <row r="320" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6"/>
       <c r="B320" s="11"/>
     </row>
-    <row r="321" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6"/>
       <c r="B321" s="11"/>
     </row>
-    <row r="322" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6"/>
       <c r="B322" s="11"/>
     </row>
-    <row r="323" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6"/>
       <c r="B323" s="11"/>
     </row>
-    <row r="324" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6"/>
       <c r="B324" s="11"/>
     </row>
-    <row r="325" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6"/>
       <c r="B325" s="11"/>
     </row>
-    <row r="326" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6"/>
       <c r="B326" s="11"/>
     </row>
-    <row r="327" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6"/>
       <c r="B327" s="11"/>
     </row>
-    <row r="328" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6"/>
       <c r="B328" s="11"/>
     </row>
-    <row r="329" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6"/>
       <c r="B329" s="11"/>
     </row>
-    <row r="330" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6"/>
       <c r="B330" s="11"/>
     </row>
-    <row r="331" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6"/>
       <c r="B331" s="11"/>
     </row>
-    <row r="332" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6"/>
       <c r="B332" s="11"/>
     </row>
-    <row r="333" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6"/>
       <c r="B333" s="11"/>
     </row>
-    <row r="334" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6"/>
       <c r="B334" s="11"/>
     </row>
-    <row r="335" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6"/>
       <c r="B335" s="11"/>
     </row>
-    <row r="336" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6"/>
       <c r="B336" s="11"/>
     </row>
-    <row r="337" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6"/>
       <c r="B337" s="11"/>
     </row>
-    <row r="338" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6"/>
       <c r="B338" s="11"/>
     </row>
-    <row r="339" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6"/>
       <c r="B339" s="11"/>
     </row>
-    <row r="340" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6"/>
       <c r="B340" s="11"/>
     </row>
-    <row r="341" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6"/>
       <c r="B341" s="11"/>
     </row>
-    <row r="342" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6"/>
       <c r="B342" s="11"/>
     </row>
-    <row r="343" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6"/>
       <c r="B343" s="11"/>
     </row>
-    <row r="344" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6"/>
       <c r="B344" s="11"/>
     </row>
-    <row r="345" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6"/>
       <c r="B345" s="11"/>
     </row>
-    <row r="346" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6"/>
       <c r="B346" s="11"/>
     </row>
-    <row r="347" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6"/>
       <c r="B347" s="11"/>
     </row>
-    <row r="348" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6"/>
       <c r="B348" s="11"/>
     </row>
-    <row r="349" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6"/>
       <c r="B349" s="11"/>
     </row>
-    <row r="350" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6"/>
       <c r="B350" s="11"/>
     </row>
-    <row r="351" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6"/>
       <c r="B351" s="11"/>
     </row>
-    <row r="352" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6"/>
       <c r="B352" s="11"/>
     </row>
-    <row r="353" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6"/>
       <c r="B353" s="11"/>
     </row>
-    <row r="354" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6"/>
       <c r="B354" s="11"/>
     </row>
-    <row r="355" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6"/>
       <c r="B355" s="11"/>
     </row>
-    <row r="356" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6"/>
       <c r="B356" s="11"/>
     </row>
-    <row r="357" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6"/>
       <c r="B357" s="11"/>
     </row>
-    <row r="358" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6"/>
       <c r="B358" s="11"/>
     </row>
-    <row r="359" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6"/>
       <c r="B359" s="11"/>
     </row>
-    <row r="360" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6"/>
       <c r="B360" s="11"/>
     </row>
-    <row r="361" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6"/>
       <c r="B361" s="11"/>
     </row>
-    <row r="362" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6"/>
       <c r="B362" s="11"/>
     </row>
-    <row r="363" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6"/>
       <c r="B363" s="11"/>
     </row>
-    <row r="364" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6"/>
       <c r="B364" s="11"/>
     </row>
-    <row r="365" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6"/>
       <c r="B365" s="11"/>
     </row>
-    <row r="366" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6"/>
       <c r="B366" s="11"/>
     </row>
-    <row r="367" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6"/>
       <c r="B367" s="11"/>
     </row>
-    <row r="368" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6"/>
       <c r="B368" s="11"/>
     </row>
-    <row r="369" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6"/>
       <c r="B369" s="11"/>
     </row>
-    <row r="370" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6"/>
       <c r="B370" s="11"/>
     </row>
-    <row r="371" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6"/>
       <c r="B371" s="11"/>
     </row>
-    <row r="372" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6"/>
       <c r="B372" s="11"/>
     </row>
-    <row r="373" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6"/>
       <c r="B373" s="11"/>
     </row>
-    <row r="374" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6"/>
       <c r="B374" s="11"/>
     </row>
-    <row r="375" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6"/>
       <c r="B375" s="11"/>
     </row>
-    <row r="376" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6"/>
       <c r="B376" s="11"/>
     </row>
-    <row r="377" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6"/>
       <c r="B377" s="11"/>
     </row>
-    <row r="378" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6"/>
       <c r="B378" s="11"/>
     </row>
-    <row r="379" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6"/>
       <c r="B379" s="11"/>
     </row>
-    <row r="380" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6"/>
       <c r="B380" s="11"/>
     </row>
-    <row r="381" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6"/>
       <c r="B381" s="11"/>
     </row>
-    <row r="382" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6"/>
       <c r="B382" s="11"/>
     </row>
-    <row r="383" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6"/>
       <c r="B383" s="11"/>
     </row>
-    <row r="384" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6"/>
       <c r="B384" s="11"/>
     </row>
-    <row r="385" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6"/>
       <c r="B385" s="11"/>
     </row>
-    <row r="386" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6"/>
       <c r="B386" s="11"/>
     </row>
-    <row r="387" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6"/>
       <c r="B387" s="11"/>
     </row>
-    <row r="388" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6"/>
       <c r="B388" s="11"/>
     </row>
-    <row r="389" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6"/>
       <c r="B389" s="11"/>
     </row>
-    <row r="390" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6"/>
       <c r="B390" s="11"/>
     </row>
-    <row r="391" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6"/>
       <c r="B391" s="11"/>
     </row>
-    <row r="392" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6"/>
       <c r="B392" s="11"/>
     </row>
-    <row r="393" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6"/>
       <c r="B393" s="11"/>
     </row>
-    <row r="394" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6"/>
       <c r="B394" s="11"/>
     </row>
-    <row r="395" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6"/>
       <c r="B395" s="11"/>
     </row>
-    <row r="396" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6"/>
       <c r="B396" s="11"/>
     </row>
-    <row r="397" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6"/>
       <c r="B397" s="11"/>
     </row>
-    <row r="398" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6"/>
       <c r="B398" s="11"/>
     </row>
-    <row r="399" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6"/>
       <c r="B399" s="11"/>
     </row>
-    <row r="400" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6"/>
       <c r="B400" s="11"/>
     </row>
-    <row r="401" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6"/>
       <c r="B401" s="11"/>
     </row>
-    <row r="402" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6"/>
       <c r="B402" s="11"/>
     </row>
-    <row r="403" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6"/>
       <c r="B403" s="11"/>
     </row>
-    <row r="404" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6"/>
       <c r="B404" s="11"/>
     </row>
-    <row r="405" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6"/>
       <c r="B405" s="11"/>
     </row>
-    <row r="406" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6"/>
       <c r="B406" s="11"/>
     </row>
-    <row r="407" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6"/>
       <c r="B407" s="11"/>
     </row>
-    <row r="408" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6"/>
       <c r="B408" s="11"/>
     </row>
-    <row r="409" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6"/>
       <c r="B409" s="11"/>
     </row>
-    <row r="410" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6"/>
       <c r="B410" s="11"/>
     </row>
-    <row r="411" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6"/>
       <c r="B411" s="11"/>
     </row>
-    <row r="412" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6"/>
       <c r="B412" s="11"/>
     </row>
-    <row r="413" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6"/>
       <c r="B413" s="11"/>
     </row>
-    <row r="414" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6"/>
       <c r="B414" s="11"/>
     </row>
-    <row r="415" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6"/>
       <c r="B415" s="11"/>
     </row>
-    <row r="416" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6"/>
       <c r="B416" s="11"/>
     </row>
-    <row r="417" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6"/>
       <c r="B417" s="11"/>
     </row>
-    <row r="418" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6"/>
       <c r="B418" s="11"/>
     </row>
-    <row r="419" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6"/>
       <c r="B419" s="11"/>
     </row>
-    <row r="420" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6"/>
       <c r="B420" s="11"/>
     </row>
-    <row r="421" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6"/>
       <c r="B421" s="11"/>
     </row>
-    <row r="422" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6"/>
       <c r="B422" s="11"/>
     </row>
-    <row r="423" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6"/>
       <c r="B423" s="11"/>
     </row>
-    <row r="424" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6"/>
       <c r="B424" s="11"/>
     </row>
-    <row r="425" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6"/>
       <c r="B425" s="11"/>
     </row>
-    <row r="426" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="6"/>
       <c r="B426" s="11"/>
     </row>
-    <row r="427" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="6"/>
       <c r="B427" s="11"/>
     </row>
-    <row r="428" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="6"/>
       <c r="B428" s="11"/>
     </row>
-    <row r="429" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="6"/>
       <c r="B429" s="11"/>
     </row>
-    <row r="430" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="6"/>
       <c r="B430" s="11"/>
     </row>
-    <row r="431" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="6"/>
       <c r="B431" s="11"/>
     </row>
-    <row r="432" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="6"/>
       <c r="B432" s="11"/>
     </row>
-    <row r="433" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="6"/>
       <c r="B433" s="11"/>
     </row>
-    <row r="434" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="6"/>
       <c r="B434" s="11"/>
     </row>
-    <row r="435" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="6"/>
       <c r="B435" s="11"/>
     </row>
-    <row r="436" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="6"/>
       <c r="B436" s="11"/>
     </row>
-    <row r="437" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="6"/>
       <c r="B437" s="11"/>
     </row>
-    <row r="438" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="6"/>
       <c r="B438" s="11"/>
     </row>
-    <row r="439" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="6"/>
       <c r="B439" s="11"/>
     </row>
-    <row r="440" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="6"/>
       <c r="B440" s="11"/>
     </row>
-    <row r="441" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="6"/>
       <c r="B441" s="11"/>
     </row>
-    <row r="442" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="6"/>
       <c r="B442" s="11"/>
     </row>
-    <row r="443" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="6"/>
       <c r="B443" s="11"/>
     </row>
-    <row r="444" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="6"/>
       <c r="B444" s="11"/>
     </row>
-    <row r="445" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="6"/>
       <c r="B445" s="11"/>
     </row>
-    <row r="446" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="6"/>
       <c r="B446" s="11"/>
     </row>
-    <row r="447" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="6"/>
       <c r="B447" s="11"/>
     </row>
-    <row r="448" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="6"/>
       <c r="B448" s="11"/>
     </row>
-    <row r="449" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="6"/>
       <c r="B449" s="11"/>
     </row>
-    <row r="450" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="6"/>
       <c r="B450" s="11"/>
     </row>
-    <row r="451" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="6"/>
       <c r="B451" s="11"/>
     </row>
-    <row r="452" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="6"/>
       <c r="B452" s="11"/>
     </row>
-    <row r="453" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="6"/>
       <c r="B453" s="11"/>
     </row>
-    <row r="454" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="6"/>
       <c r="B454" s="11"/>
     </row>
-    <row r="455" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="6"/>
       <c r="B455" s="11"/>
     </row>
-    <row r="456" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="6"/>
       <c r="B456" s="11"/>
     </row>
-    <row r="457" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="6"/>
       <c r="B457" s="11"/>
     </row>
-    <row r="458" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="6"/>
       <c r="B458" s="11"/>
     </row>
-    <row r="459" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="6"/>
       <c r="B459" s="11"/>
     </row>
-    <row r="460" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="6"/>
       <c r="B460" s="11"/>
     </row>
-    <row r="461" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="6"/>
       <c r="B461" s="11"/>
     </row>
-    <row r="462" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="6"/>
       <c r="B462" s="11"/>
     </row>
-    <row r="463" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="6"/>
       <c r="B463" s="11"/>
     </row>
-    <row r="464" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="6"/>
       <c r="B464" s="11"/>
     </row>
-    <row r="465" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="6"/>
       <c r="B465" s="11"/>
     </row>
-    <row r="466" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="6"/>
       <c r="B466" s="11"/>
     </row>
-    <row r="467" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="6"/>
       <c r="B467" s="11"/>
     </row>
-    <row r="468" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="6"/>
       <c r="B468" s="11"/>
     </row>
-    <row r="469" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="6"/>
       <c r="B469" s="11"/>
     </row>
-    <row r="470" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="6"/>
       <c r="B470" s="11"/>
     </row>
-    <row r="471" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="6"/>
       <c r="B471" s="11"/>
     </row>
-    <row r="472" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="6"/>
       <c r="B472" s="11"/>
     </row>
-    <row r="473" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="6"/>
       <c r="B473" s="11"/>
     </row>
-    <row r="474" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="6"/>
       <c r="B474" s="11"/>
     </row>
-    <row r="475" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="6"/>
       <c r="B475" s="11"/>
     </row>
-    <row r="476" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="6"/>
       <c r="B476" s="11"/>
     </row>
-    <row r="477" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="6"/>
       <c r="B477" s="11"/>
     </row>
-    <row r="478" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="6"/>
       <c r="B478" s="11"/>
     </row>
-    <row r="479" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="6"/>
       <c r="B479" s="11"/>
     </row>
-    <row r="480" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="6"/>
       <c r="B480" s="11"/>
     </row>
-    <row r="481" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="6"/>
       <c r="B481" s="11"/>
     </row>
-    <row r="482" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="6"/>
       <c r="B482" s="11"/>
     </row>
-    <row r="483" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="6"/>
       <c r="B483" s="11"/>
     </row>
-    <row r="484" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="6"/>
       <c r="B484" s="11"/>
     </row>
-    <row r="485" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="6"/>
       <c r="B485" s="11"/>
     </row>
-    <row r="486" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="6"/>
       <c r="B486" s="11"/>
     </row>
-    <row r="487" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="6"/>
       <c r="B487" s="11"/>
     </row>
-    <row r="488" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="6"/>
       <c r="B488" s="11"/>
     </row>
-    <row r="489" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="6"/>
       <c r="B489" s="11"/>
     </row>
-    <row r="490" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="6"/>
       <c r="B490" s="11"/>
     </row>
-    <row r="491" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="6"/>
       <c r="B491" s="11"/>
     </row>
-    <row r="492" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="6"/>
       <c r="B492" s="11"/>
     </row>
-    <row r="493" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="6"/>
       <c r="B493" s="11"/>
     </row>
-    <row r="494" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="6"/>
       <c r="B494" s="11"/>
     </row>
-    <row r="495" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="6"/>
       <c r="B495" s="11"/>
     </row>
-    <row r="496" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="6"/>
       <c r="B496" s="11"/>
     </row>
-    <row r="497" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="6"/>
       <c r="B497" s="11"/>
     </row>
-    <row r="498" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="6"/>
       <c r="B498" s="11"/>
     </row>
-    <row r="499" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="6"/>
       <c r="B499" s="11"/>
     </row>
-    <row r="500" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="6"/>
       <c r="B500" s="11"/>
     </row>
@@ -8120,52 +8246,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E34FD7-1B73-4707-A12E-62E00BDCA8A2}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BC1F10-8274-468D-A11F-0659CCCD57A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44631F5D-99E6-4F65-8005-23A1011BF937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
   <si>
     <t>Jour</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>Finalisation</t>
+  </si>
+  <si>
+    <t>Ajout des données mises à jour sur le MCD</t>
   </si>
 </sst>
 </file>
@@ -874,7 +877,7 @@
                   <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>6.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.5</c:v>
@@ -2259,12 +2262,24 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="A19" s="6">
+        <v>46041</v>
+      </c>
+      <c r="B19" s="14">
+        <v>2</v>
+      </c>
+      <c r="C19" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -6204,7 +6219,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44631F5D-99E6-4F65-8005-23A1011BF937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C47679F-EEE2-4ED0-8943-B88CB7B7FE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="48">
   <si>
     <t>Jour</t>
   </si>
@@ -159,6 +159,30 @@
   </si>
   <si>
     <t>Ajout des données mises à jour sur le MCD</t>
+  </si>
+  <si>
+    <t>Application Map</t>
+  </si>
+  <si>
+    <t>Maquette Web</t>
+  </si>
+  <si>
+    <t>User Flow</t>
+  </si>
+  <si>
+    <t>Pas de login public</t>
+  </si>
+  <si>
+    <t>Flux d'utilisateur (navigation sur les pages)</t>
+  </si>
+  <si>
+    <t>Discussion sur le projet</t>
+  </si>
+  <si>
+    <t>Intervention du chef de projet pour valider le concept design</t>
+  </si>
+  <si>
+    <t>Modifications apportées</t>
   </si>
 </sst>
 </file>
@@ -877,7 +901,7 @@
                   <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.25</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.5</c:v>
@@ -2282,44 +2306,102 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="A20" s="6">
+        <v>46041</v>
+      </c>
+      <c r="B20" s="14">
+        <v>2</v>
+      </c>
+      <c r="C20" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
+      <c r="A21" s="6">
+        <v>46041</v>
+      </c>
+      <c r="B21" s="14">
+        <v>2</v>
+      </c>
+      <c r="C21" s="11">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="A22" s="6">
+        <v>46041</v>
+      </c>
+      <c r="B22" s="14">
+        <v>2</v>
+      </c>
+      <c r="C22" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="A23" s="6">
+        <v>46042</v>
+      </c>
+      <c r="B23" s="14">
+        <v>2</v>
+      </c>
+      <c r="C23" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="A24" s="6">
+        <v>46042</v>
+      </c>
+      <c r="B24" s="14">
+        <v>2</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="25" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
@@ -6219,7 +6301,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>6.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C47679F-EEE2-4ED0-8943-B88CB7B7FE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD94BA-0864-4D7F-807B-BB478C8FA13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="54">
   <si>
     <t>Jour</t>
   </si>
@@ -183,6 +183,24 @@
   </si>
   <si>
     <t>Modifications apportées</t>
+  </si>
+  <si>
+    <t>Mise en place du système de gestion de base de données</t>
+  </si>
+  <si>
+    <t>MariaDB</t>
+  </si>
+  <si>
+    <t>Discussion des maquettes/charte graphique</t>
+  </si>
+  <si>
+    <t>Discussion avec le chef de projet sur ses préférences</t>
+  </si>
+  <si>
+    <t>Changement du build details dans le userflow (user et admin)</t>
+  </si>
+  <si>
+    <t>Disposition changée suite à la demande du chef de projet</t>
   </si>
 </sst>
 </file>
@@ -901,10 +919,10 @@
                   <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>10.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2404,28 +2422,64 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
+      <c r="A25" s="6">
+        <v>46043</v>
+      </c>
+      <c r="B25" s="14">
+        <v>2</v>
+      </c>
+      <c r="C25" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
+      <c r="A26" s="6">
+        <v>46043</v>
+      </c>
+      <c r="B26" s="14">
+        <v>2</v>
+      </c>
+      <c r="C26" s="11">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
+      <c r="A27" s="6">
+        <v>46043</v>
+      </c>
+      <c r="B27" s="14">
+        <v>2</v>
+      </c>
+      <c r="C27" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -6301,7 +6355,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>10</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6310,7 +6364,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD94BA-0864-4D7F-807B-BB478C8FA13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8D6294-9C46-44AC-B4FA-548E4F00EA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
   <si>
     <t>Jour</t>
   </si>
@@ -194,13 +194,22 @@
     <t>Discussion des maquettes/charte graphique</t>
   </si>
   <si>
-    <t>Discussion avec le chef de projet sur ses préférences</t>
-  </si>
-  <si>
     <t>Changement du build details dans le userflow (user et admin)</t>
   </si>
   <si>
     <t>Disposition changée suite à la demande du chef de projet</t>
+  </si>
+  <si>
+    <t>Création de la base de données</t>
+  </si>
+  <si>
+    <t>Modifications/corrections apportées</t>
+  </si>
+  <si>
+    <t>Discussion avec le chef de projet sur ses préférences (logo/palette)</t>
+  </si>
+  <si>
+    <t>Tests de l'interaction de la base de données</t>
   </si>
 </sst>
 </file>
@@ -922,7 +931,7 @@
                   <c:v>10.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75</c:v>
+                  <c:v>2.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2458,7 +2467,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2475,27 +2484,51 @@
         <v>8</v>
       </c>
       <c r="E27" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="8" t="s">
+    </row>
+    <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="6">
+        <v>46043</v>
+      </c>
+      <c r="B28" s="14">
+        <v>2</v>
+      </c>
+      <c r="C28" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
+      <c r="F28" s="8" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
+      <c r="A29" s="6">
+        <v>46043</v>
+      </c>
+      <c r="B29" s="14">
+        <v>2</v>
+      </c>
+      <c r="C29" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
@@ -6364,7 +6397,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>0.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8D6294-9C46-44AC-B4FA-548E4F00EA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEB4FF0-8A88-4E6E-A6A6-334C21EB9BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
   <si>
     <t>Jour</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>Tests de l'interaction de la base de données</t>
+  </si>
+  <si>
+    <t>Finalisation des écrans utilisateur</t>
   </si>
 </sst>
 </file>
@@ -931,7 +934,7 @@
                   <c:v>10.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.75</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2438,7 +2441,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="11">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>9</v>
@@ -2531,12 +2534,24 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
+      <c r="A30" s="6">
+        <v>46044</v>
+      </c>
+      <c r="B30" s="14">
+        <v>2</v>
+      </c>
+      <c r="C30" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
@@ -6397,7 +6412,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEB4FF0-8A88-4E6E-A6A6-334C21EB9BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF27040-F01B-4B57-BC48-414C1EACE208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="63">
   <si>
     <t>Jour</t>
   </si>
@@ -212,7 +212,22 @@
     <t>Tests de l'interaction de la base de données</t>
   </si>
   <si>
-    <t>Finalisation des écrans utilisateur</t>
+    <t>Écrans utilisateur et admin finis + vérification logique UX</t>
+  </si>
+  <si>
+    <t>Mise à jour du readme</t>
+  </si>
+  <si>
+    <t>Version d'environnement/technologie</t>
+  </si>
+  <si>
+    <t>Base de données</t>
+  </si>
+  <si>
+    <t>Correction du MLD et Base de données</t>
+  </si>
+  <si>
+    <t>Rapport de projet</t>
   </si>
 </sst>
 </file>
@@ -931,16 +946,16 @@
                   <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.25</c:v>
+                  <c:v>10.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.5</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -2541,7 +2556,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="11">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>9</v>
@@ -2554,27 +2569,61 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="A31" s="6">
+        <v>46044</v>
+      </c>
+      <c r="B31" s="14">
+        <v>2</v>
+      </c>
+      <c r="C31" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
+      <c r="A32" s="6">
+        <v>46044</v>
+      </c>
+      <c r="B32" s="14">
+        <v>2</v>
+      </c>
+      <c r="C32" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="8"/>
+      <c r="A33" s="6">
+        <v>46044</v>
+      </c>
+      <c r="B33" s="14">
+        <v>2</v>
+      </c>
+      <c r="C33" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6403,7 +6452,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>10.25</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6412,7 +6461,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6430,7 +6479,7 @@
       </c>
       <c r="B6" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF27040-F01B-4B57-BC48-414C1EACE208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FEAD99-E607-46CC-A0D4-A1D4E9802A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="65">
   <si>
     <t>Jour</t>
   </si>
@@ -228,6 +228,12 @@
   </si>
   <si>
     <t>Rapport de projet</t>
+  </si>
+  <si>
+    <t>Base de données et conceptions</t>
+  </si>
+  <si>
+    <t>Correction d'un attribut</t>
   </si>
 </sst>
 </file>
@@ -949,7 +955,7 @@
                   <c:v>10.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6</c:v>
+                  <c:v>6.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2627,12 +2633,24 @@
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
+      <c r="A34" s="6">
+        <v>46045</v>
+      </c>
+      <c r="B34" s="14">
+        <v>2</v>
+      </c>
+      <c r="C34" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
@@ -6461,7 +6479,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FEAD99-E607-46CC-A0D4-A1D4E9802A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8632C4F2-D55B-4314-A189-A26C43AA635D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="71">
   <si>
     <t>Jour</t>
   </si>
@@ -234,6 +234,24 @@
   </si>
   <si>
     <t>Correction d'un attribut</t>
+  </si>
+  <si>
+    <t>Connectivité base de données et projet</t>
+  </si>
+  <si>
+    <t>Réunion hebdomadaire avec l'équipe et chef de projet</t>
+  </si>
+  <si>
+    <t>Retours positifs du projet et approbation du project design</t>
+  </si>
+  <si>
+    <t>Mise en place du pont de connexion entre Laravel et MariaDB</t>
+  </si>
+  <si>
+    <t>Debuggage de la connexion à la base de données</t>
+  </si>
+  <si>
+    <t>Coding backend</t>
   </si>
 </sst>
 </file>
@@ -955,7 +973,7 @@
                   <c:v>10.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.25</c:v>
+                  <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2653,35 +2671,81 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
+      <c r="A35" s="6">
+        <v>46045</v>
+      </c>
+      <c r="B35" s="14">
+        <v>2</v>
+      </c>
+      <c r="C35" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="6"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
+      <c r="A36" s="6">
+        <v>46045</v>
+      </c>
+      <c r="B36" s="14">
+        <v>2</v>
+      </c>
+      <c r="C36" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="37" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
+      <c r="A37" s="6">
+        <v>46045</v>
+      </c>
+      <c r="B37" s="14">
+        <v>2</v>
+      </c>
+      <c r="C37" s="11">
+        <v>1</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="8"/>
+      <c r="A38" s="6">
+        <v>46045</v>
+      </c>
+      <c r="B38" s="14">
+        <v>2</v>
+      </c>
+      <c r="C38" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="F38" s="8"/>
     </row>
     <row r="39" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6479,7 +6543,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>6.25</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8632C4F2-D55B-4314-A189-A26C43AA635D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF3319B-D02D-4CC8-B6A1-42BAA7CA0EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="72">
   <si>
     <t>Jour</t>
   </si>
@@ -252,6 +252,9 @@
   </si>
   <si>
     <t>Coding backend</t>
+  </si>
+  <si>
+    <t>Création des modèles et mise en place des premières règles</t>
   </si>
 </sst>
 </file>
@@ -2746,7 +2749,9 @@
       <c r="E38" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="8"/>
+      <c r="F38" s="8" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="39" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF3319B-D02D-4CC8-B6A1-42BAA7CA0EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B893F26-D61E-4F90-85F9-4F98CB962979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
   <si>
     <t>Jour</t>
   </si>
@@ -255,6 +255,15 @@
   </si>
   <si>
     <t>Création des modèles et mise en place des premières règles</t>
+  </si>
+  <si>
+    <t>Finalisation des modèles des données</t>
+  </si>
+  <si>
+    <t>Debug github</t>
+  </si>
+  <si>
+    <t>Conflit branche develop et feature/database</t>
   </si>
 </sst>
 </file>
@@ -976,7 +985,7 @@
                   <c:v>10.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.5</c:v>
+                  <c:v>10.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -991,7 +1000,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2754,20 +2763,44 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
+      <c r="A39" s="6">
+        <v>46048</v>
+      </c>
+      <c r="B39" s="14">
+        <v>3</v>
+      </c>
+      <c r="C39" s="11">
+        <v>1.75</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="40" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="6"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
+      <c r="A40" s="6">
+        <v>46048</v>
+      </c>
+      <c r="B40" s="14">
+        <v>3</v>
+      </c>
+      <c r="C40" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="41" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
@@ -6548,7 +6581,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>8.5</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6593,7 +6626,7 @@
       </c>
       <c r="B9" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B893F26-D61E-4F90-85F9-4F98CB962979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD02BB01-6633-4074-84A9-97D88DCC1A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="76">
   <si>
     <t>Jour</t>
   </si>
@@ -251,19 +251,22 @@
     <t>Debuggage de la connexion à la base de données</t>
   </si>
   <si>
-    <t>Coding backend</t>
-  </si>
-  <si>
-    <t>Création des modèles et mise en place des premières règles</t>
-  </si>
-  <si>
-    <t>Finalisation des modèles des données</t>
-  </si>
-  <si>
     <t>Debug github</t>
   </si>
   <si>
     <t>Conflit branche develop et feature/database</t>
+  </si>
+  <si>
+    <t>Développement backend</t>
+  </si>
+  <si>
+    <t>Création des contrôleurs dédiés à l'interface utilisateur</t>
+  </si>
+  <si>
+    <t>Création des modèles et définition des premières règles</t>
+  </si>
+  <si>
+    <t>Finalisation des modèles de données</t>
   </si>
 </sst>
 </file>
@@ -985,7 +988,7 @@
                   <c:v>10.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.25</c:v>
+                  <c:v>11.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2756,10 +2759,10 @@
         <v>9</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2776,10 +2779,10 @@
         <v>9</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2796,19 +2799,31 @@
         <v>13</v>
       </c>
       <c r="E40" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="6">
+        <v>46048</v>
+      </c>
+      <c r="B41" s="14">
+        <v>3</v>
+      </c>
+      <c r="C41" s="11">
+        <v>1</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F40" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
     </row>
     <row r="42" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
@@ -6581,7 +6596,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>10.25</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD02BB01-6633-4074-84A9-97D88DCC1A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56641218-56A3-48B3-8A52-B532218E01EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="80">
   <si>
     <t>Jour</t>
   </si>
@@ -267,6 +267,18 @@
   </si>
   <si>
     <t>Finalisation des modèles de données</t>
+  </si>
+  <si>
+    <t>Création des vues dédiées à l'interface utilisateur</t>
+  </si>
+  <si>
+    <t>Debug développement</t>
+  </si>
+  <si>
+    <t>environnement de développement, problème de version</t>
+  </si>
+  <si>
+    <t>Création des routes dédiées à l'interface utilisateur</t>
   </si>
 </sst>
 </file>
@@ -988,7 +1000,7 @@
                   <c:v>10.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.25</c:v>
+                  <c:v>12.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1003,7 +1015,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.5</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2013,17 +2025,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F503"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="13.375" style="15" customWidth="1"/>
-    <col min="3" max="3" width="15.25" style="12" customWidth="1"/>
-    <col min="4" max="4" width="24.75" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="24.69921875" style="5" customWidth="1"/>
     <col min="5" max="5" width="68.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="82.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="82.19921875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2043,7 +2055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>46035</v>
       </c>
@@ -2061,7 +2073,7 @@
       </c>
       <c r="F2" s="8"/>
     </row>
-    <row r="3" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>46035</v>
       </c>
@@ -2079,7 +2091,7 @@
       </c>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>46036</v>
       </c>
@@ -2099,7 +2111,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>46036</v>
       </c>
@@ -2117,7 +2129,7 @@
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>46036</v>
       </c>
@@ -2137,7 +2149,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>46036</v>
       </c>
@@ -2157,7 +2169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>46037</v>
       </c>
@@ -2175,7 +2187,7 @@
       </c>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>46037</v>
       </c>
@@ -2195,7 +2207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>46037</v>
       </c>
@@ -2215,7 +2227,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>46037</v>
       </c>
@@ -2233,7 +2245,7 @@
       </c>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>46038</v>
       </c>
@@ -2251,7 +2263,7 @@
       </c>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>46038</v>
       </c>
@@ -2271,7 +2283,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>46038</v>
       </c>
@@ -2289,7 +2301,7 @@
       </c>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>46038</v>
       </c>
@@ -2309,7 +2321,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>46038</v>
       </c>
@@ -2329,7 +2341,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>46038</v>
       </c>
@@ -2349,7 +2361,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>46041</v>
       </c>
@@ -2369,7 +2381,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>46041</v>
       </c>
@@ -2389,7 +2401,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>46041</v>
       </c>
@@ -2409,7 +2421,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>46041</v>
       </c>
@@ -2427,7 +2439,7 @@
       </c>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>46041</v>
       </c>
@@ -2447,7 +2459,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>46042</v>
       </c>
@@ -2467,7 +2479,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>46042</v>
       </c>
@@ -2487,7 +2499,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>46043</v>
       </c>
@@ -2507,7 +2519,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>46043</v>
       </c>
@@ -2527,7 +2539,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>46043</v>
       </c>
@@ -2547,7 +2559,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>46043</v>
       </c>
@@ -2567,7 +2579,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>46043</v>
       </c>
@@ -2587,7 +2599,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>46044</v>
       </c>
@@ -2607,7 +2619,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>46044</v>
       </c>
@@ -2627,7 +2639,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>46044</v>
       </c>
@@ -2647,7 +2659,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>46044</v>
       </c>
@@ -2665,7 +2677,7 @@
       </c>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>46045</v>
       </c>
@@ -2685,7 +2697,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>46045</v>
       </c>
@@ -2705,7 +2717,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>46045</v>
       </c>
@@ -2725,7 +2737,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>46045</v>
       </c>
@@ -2745,7 +2757,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>46045</v>
       </c>
@@ -2765,7 +2777,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>46048</v>
       </c>
@@ -2785,7 +2797,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>46048</v>
       </c>
@@ -2805,7 +2817,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>46048</v>
       </c>
@@ -2825,31 +2837,67 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-    </row>
-    <row r="43" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-    </row>
-    <row r="44" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-    </row>
-    <row r="45" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>46049</v>
+      </c>
+      <c r="B42" s="14">
+        <v>3</v>
+      </c>
+      <c r="C42" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>46049</v>
+      </c>
+      <c r="B43" s="14">
+        <v>3</v>
+      </c>
+      <c r="C43" s="11">
+        <v>1</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>46049</v>
+      </c>
+      <c r="B44" s="14">
+        <v>3</v>
+      </c>
+      <c r="C44" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="14"/>
       <c r="C45" s="11"/>
@@ -2857,7 +2905,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
     </row>
-    <row r="46" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="B46" s="14"/>
       <c r="C46" s="11"/>
@@ -2865,7 +2913,7 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="14"/>
       <c r="C47" s="11"/>
@@ -2873,7 +2921,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="14"/>
       <c r="C48" s="11"/>
@@ -2881,7 +2929,7 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
     </row>
-    <row r="49" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="14"/>
       <c r="C49" s="11"/>
@@ -2889,7 +2937,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="14"/>
       <c r="C50" s="11"/>
@@ -2897,7 +2945,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
     </row>
-    <row r="51" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="14"/>
       <c r="C51" s="11"/>
@@ -2905,7 +2953,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="14"/>
       <c r="C52" s="11"/>
@@ -2913,7 +2961,7 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
     </row>
-    <row r="53" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="14"/>
       <c r="C53" s="11"/>
@@ -2921,7 +2969,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="14"/>
       <c r="C54" s="11"/>
@@ -2929,7 +2977,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="14"/>
       <c r="C55" s="11"/>
@@ -2937,7 +2985,7 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
     </row>
-    <row r="56" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="14"/>
       <c r="C56" s="11"/>
@@ -2945,7 +2993,7 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="14"/>
       <c r="C57" s="11"/>
@@ -2953,7 +3001,7 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
     </row>
-    <row r="58" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="14"/>
       <c r="C58" s="11"/>
@@ -2961,7 +3009,7 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
     </row>
-    <row r="59" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="14"/>
       <c r="C59" s="11"/>
@@ -2969,7 +3017,7 @@
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
     </row>
-    <row r="60" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="14"/>
       <c r="C60" s="11"/>
@@ -2977,7 +3025,7 @@
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="14"/>
       <c r="C61" s="11"/>
@@ -2985,7 +3033,7 @@
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
     </row>
-    <row r="62" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="14"/>
       <c r="C62" s="11"/>
@@ -2993,7 +3041,7 @@
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
     </row>
-    <row r="63" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="14"/>
       <c r="C63" s="11"/>
@@ -3001,7 +3049,7 @@
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
     </row>
-    <row r="64" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="14"/>
       <c r="C64" s="11"/>
@@ -3009,7 +3057,7 @@
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
     </row>
-    <row r="65" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="14"/>
       <c r="C65" s="11"/>
@@ -3017,7 +3065,7 @@
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
     </row>
-    <row r="66" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="14"/>
       <c r="C66" s="11"/>
@@ -3025,7 +3073,7 @@
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
     </row>
-    <row r="67" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="14"/>
       <c r="C67" s="11"/>
@@ -3033,7 +3081,7 @@
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
     </row>
-    <row r="68" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="14"/>
       <c r="C68" s="11"/>
@@ -3041,7 +3089,7 @@
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
     </row>
-    <row r="69" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="14"/>
       <c r="C69" s="11"/>
@@ -3049,7 +3097,7 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
     </row>
-    <row r="70" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="14"/>
       <c r="C70" s="11"/>
@@ -3057,7 +3105,7 @@
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
     </row>
-    <row r="71" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="14"/>
       <c r="C71" s="11"/>
@@ -3065,7 +3113,7 @@
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
     </row>
-    <row r="72" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="14"/>
       <c r="C72" s="11"/>
@@ -3073,7 +3121,7 @@
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
     </row>
-    <row r="73" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="14"/>
       <c r="C73" s="11"/>
@@ -3081,7 +3129,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
     </row>
-    <row r="74" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="14"/>
       <c r="C74" s="11"/>
@@ -3089,7 +3137,7 @@
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
     </row>
-    <row r="75" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="14"/>
       <c r="C75" s="11"/>
@@ -3097,7 +3145,7 @@
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
     </row>
-    <row r="76" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="14"/>
       <c r="C76" s="11"/>
@@ -3105,7 +3153,7 @@
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
     </row>
-    <row r="77" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="14"/>
       <c r="C77" s="11"/>
@@ -3113,7 +3161,7 @@
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
     </row>
-    <row r="78" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="14"/>
       <c r="C78" s="11"/>
@@ -3121,7 +3169,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
     </row>
-    <row r="79" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="14"/>
       <c r="C79" s="11"/>
@@ -3129,7 +3177,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
     </row>
-    <row r="80" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="14"/>
       <c r="C80" s="11"/>
@@ -3137,7 +3185,7 @@
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
     </row>
-    <row r="81" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="14"/>
       <c r="C81" s="11"/>
@@ -3145,7 +3193,7 @@
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
     </row>
-    <row r="82" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="14"/>
       <c r="C82" s="11"/>
@@ -3153,7 +3201,7 @@
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
     </row>
-    <row r="83" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="14"/>
       <c r="C83" s="11"/>
@@ -3161,7 +3209,7 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
     </row>
-    <row r="84" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="14"/>
       <c r="C84" s="11"/>
@@ -3169,7 +3217,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
     </row>
-    <row r="85" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="14"/>
       <c r="C85" s="11"/>
@@ -3177,7 +3225,7 @@
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
     </row>
-    <row r="86" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="14"/>
       <c r="C86" s="11"/>
@@ -3185,7 +3233,7 @@
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
     </row>
-    <row r="87" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="14"/>
       <c r="C87" s="11"/>
@@ -3193,7 +3241,7 @@
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
     </row>
-    <row r="88" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="14"/>
       <c r="C88" s="11"/>
@@ -3201,7 +3249,7 @@
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
     </row>
-    <row r="89" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="14"/>
       <c r="C89" s="11"/>
@@ -3209,7 +3257,7 @@
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
     </row>
-    <row r="90" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="14"/>
       <c r="C90" s="11"/>
@@ -3217,7 +3265,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
     </row>
-    <row r="91" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="14"/>
       <c r="C91" s="11"/>
@@ -3225,7 +3273,7 @@
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
     </row>
-    <row r="92" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="14"/>
       <c r="C92" s="11"/>
@@ -3233,7 +3281,7 @@
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
     </row>
-    <row r="93" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="14"/>
       <c r="C93" s="11"/>
@@ -3241,7 +3289,7 @@
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
     </row>
-    <row r="94" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="14"/>
       <c r="C94" s="11"/>
@@ -3249,7 +3297,7 @@
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
     </row>
-    <row r="95" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="14"/>
       <c r="C95" s="11"/>
@@ -3257,7 +3305,7 @@
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
     </row>
-    <row r="96" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="14"/>
       <c r="C96" s="11"/>
@@ -3265,7 +3313,7 @@
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
     </row>
-    <row r="97" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="14"/>
       <c r="C97" s="11"/>
@@ -3273,7 +3321,7 @@
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
     </row>
-    <row r="98" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="14"/>
       <c r="C98" s="11"/>
@@ -3281,7 +3329,7 @@
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
     </row>
-    <row r="99" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="14"/>
       <c r="C99" s="11"/>
@@ -3289,7 +3337,7 @@
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
     </row>
-    <row r="100" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
       <c r="B100" s="14"/>
       <c r="C100" s="11"/>
@@ -3297,7 +3345,7 @@
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
     </row>
-    <row r="101" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="14"/>
       <c r="C101" s="11"/>
@@ -3305,7 +3353,7 @@
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
     </row>
-    <row r="102" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="14"/>
       <c r="C102" s="11"/>
@@ -3313,7 +3361,7 @@
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
     </row>
-    <row r="103" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="14"/>
       <c r="C103" s="11"/>
@@ -3321,7 +3369,7 @@
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
     </row>
-    <row r="104" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
       <c r="B104" s="14"/>
       <c r="C104" s="11"/>
@@ -3329,7 +3377,7 @@
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
     </row>
-    <row r="105" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="B105" s="14"/>
       <c r="C105" s="11"/>
@@ -3337,7 +3385,7 @@
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
     </row>
-    <row r="106" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
       <c r="B106" s="14"/>
       <c r="C106" s="11"/>
@@ -3345,7 +3393,7 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
     </row>
-    <row r="107" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
       <c r="B107" s="14"/>
       <c r="C107" s="11"/>
@@ -3353,7 +3401,7 @@
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
     </row>
-    <row r="108" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
       <c r="B108" s="14"/>
       <c r="C108" s="11"/>
@@ -3361,7 +3409,7 @@
       <c r="E108" s="8"/>
       <c r="F108" s="8"/>
     </row>
-    <row r="109" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="14"/>
       <c r="C109" s="11"/>
@@ -3369,7 +3417,7 @@
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
     </row>
-    <row r="110" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="14"/>
       <c r="C110" s="11"/>
@@ -3377,7 +3425,7 @@
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
     </row>
-    <row r="111" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="14"/>
       <c r="C111" s="11"/>
@@ -3385,7 +3433,7 @@
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
     </row>
-    <row r="112" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
       <c r="B112" s="14"/>
       <c r="C112" s="11"/>
@@ -3393,7 +3441,7 @@
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
     </row>
-    <row r="113" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="B113" s="14"/>
       <c r="C113" s="11"/>
@@ -3401,7 +3449,7 @@
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
     </row>
-    <row r="114" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
       <c r="B114" s="14"/>
       <c r="C114" s="11"/>
@@ -3409,7 +3457,7 @@
       <c r="E114" s="8"/>
       <c r="F114" s="8"/>
     </row>
-    <row r="115" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="14"/>
       <c r="C115" s="11"/>
@@ -3417,7 +3465,7 @@
       <c r="E115" s="8"/>
       <c r="F115" s="8"/>
     </row>
-    <row r="116" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
       <c r="B116" s="14"/>
       <c r="C116" s="11"/>
@@ -3425,7 +3473,7 @@
       <c r="E116" s="8"/>
       <c r="F116" s="8"/>
     </row>
-    <row r="117" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="B117" s="14"/>
       <c r="C117" s="11"/>
@@ -3433,7 +3481,7 @@
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
     </row>
-    <row r="118" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="B118" s="14"/>
       <c r="C118" s="11"/>
@@ -3441,7 +3489,7 @@
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
     </row>
-    <row r="119" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="14"/>
       <c r="C119" s="11"/>
@@ -3449,7 +3497,7 @@
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
     </row>
-    <row r="120" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
       <c r="B120" s="14"/>
       <c r="C120" s="11"/>
@@ -3457,7 +3505,7 @@
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
     </row>
-    <row r="121" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="14"/>
       <c r="C121" s="11"/>
@@ -3465,7 +3513,7 @@
       <c r="E121" s="8"/>
       <c r="F121" s="8"/>
     </row>
-    <row r="122" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="B122" s="14"/>
       <c r="C122" s="11"/>
@@ -3473,7 +3521,7 @@
       <c r="E122" s="8"/>
       <c r="F122" s="8"/>
     </row>
-    <row r="123" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="14"/>
       <c r="C123" s="11"/>
@@ -3481,7 +3529,7 @@
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
     </row>
-    <row r="124" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
       <c r="B124" s="14"/>
       <c r="C124" s="11"/>
@@ -3489,7 +3537,7 @@
       <c r="E124" s="8"/>
       <c r="F124" s="8"/>
     </row>
-    <row r="125" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="14"/>
       <c r="C125" s="11"/>
@@ -3497,7 +3545,7 @@
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
     </row>
-    <row r="126" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="B126" s="14"/>
       <c r="C126" s="11"/>
@@ -3505,7 +3553,7 @@
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
     </row>
-    <row r="127" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="14"/>
       <c r="C127" s="11"/>
@@ -3513,7 +3561,7 @@
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
     </row>
-    <row r="128" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
       <c r="B128" s="14"/>
       <c r="C128" s="11"/>
@@ -3521,7 +3569,7 @@
       <c r="E128" s="8"/>
       <c r="F128" s="8"/>
     </row>
-    <row r="129" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="B129" s="14"/>
       <c r="C129" s="11"/>
@@ -3529,7 +3577,7 @@
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
     </row>
-    <row r="130" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
       <c r="B130" s="14"/>
       <c r="C130" s="11"/>
@@ -3537,7 +3585,7 @@
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
     </row>
-    <row r="131" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
       <c r="B131" s="14"/>
       <c r="C131" s="11"/>
@@ -3545,7 +3593,7 @@
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
     </row>
-    <row r="132" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6"/>
       <c r="B132" s="14"/>
       <c r="C132" s="11"/>
@@ -3553,7 +3601,7 @@
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
     </row>
-    <row r="133" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="B133" s="14"/>
       <c r="C133" s="11"/>
@@ -3561,7 +3609,7 @@
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
     </row>
-    <row r="134" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
       <c r="B134" s="14"/>
       <c r="C134" s="11"/>
@@ -3569,7 +3617,7 @@
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
     </row>
-    <row r="135" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
       <c r="B135" s="14"/>
       <c r="C135" s="11"/>
@@ -3577,7 +3625,7 @@
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
     </row>
-    <row r="136" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
       <c r="B136" s="14"/>
       <c r="C136" s="11"/>
@@ -3585,7 +3633,7 @@
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
     </row>
-    <row r="137" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
       <c r="B137" s="14"/>
       <c r="C137" s="11"/>
@@ -3593,7 +3641,7 @@
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
     </row>
-    <row r="138" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
       <c r="B138" s="14"/>
       <c r="C138" s="11"/>
@@ -3601,7 +3649,7 @@
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
     </row>
-    <row r="139" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
       <c r="B139" s="14"/>
       <c r="C139" s="11"/>
@@ -3609,7 +3657,7 @@
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
     </row>
-    <row r="140" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
       <c r="B140" s="14"/>
       <c r="C140" s="11"/>
@@ -3617,7 +3665,7 @@
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
     </row>
-    <row r="141" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
       <c r="B141" s="14"/>
       <c r="C141" s="11"/>
@@ -3625,7 +3673,7 @@
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
     </row>
-    <row r="142" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
       <c r="B142" s="14"/>
       <c r="C142" s="11"/>
@@ -3633,7 +3681,7 @@
       <c r="E142" s="8"/>
       <c r="F142" s="8"/>
     </row>
-    <row r="143" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
       <c r="B143" s="14"/>
       <c r="C143" s="11"/>
@@ -3641,7 +3689,7 @@
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
     </row>
-    <row r="144" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6"/>
       <c r="B144" s="14"/>
       <c r="C144" s="11"/>
@@ -3649,7 +3697,7 @@
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
     </row>
-    <row r="145" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
       <c r="B145" s="14"/>
       <c r="C145" s="11"/>
@@ -3657,7 +3705,7 @@
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
     </row>
-    <row r="146" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
       <c r="B146" s="14"/>
       <c r="C146" s="11"/>
@@ -3665,7 +3713,7 @@
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
     </row>
-    <row r="147" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
       <c r="B147" s="14"/>
       <c r="C147" s="11"/>
@@ -3673,7 +3721,7 @@
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
     </row>
-    <row r="148" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
       <c r="B148" s="14"/>
       <c r="C148" s="11"/>
@@ -3681,7 +3729,7 @@
       <c r="E148" s="8"/>
       <c r="F148" s="8"/>
     </row>
-    <row r="149" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
       <c r="B149" s="14"/>
       <c r="C149" s="11"/>
@@ -3689,7 +3737,7 @@
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
     </row>
-    <row r="150" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
       <c r="B150" s="14"/>
       <c r="C150" s="11"/>
@@ -3697,7 +3745,7 @@
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
     </row>
-    <row r="151" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
       <c r="B151" s="14"/>
       <c r="C151" s="11"/>
@@ -3705,7 +3753,7 @@
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
     </row>
-    <row r="152" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6"/>
       <c r="B152" s="14"/>
       <c r="C152" s="11"/>
@@ -3713,7 +3761,7 @@
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
     </row>
-    <row r="153" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
       <c r="B153" s="14"/>
       <c r="C153" s="11"/>
@@ -3721,7 +3769,7 @@
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
     </row>
-    <row r="154" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="B154" s="14"/>
       <c r="C154" s="11"/>
@@ -3729,7 +3777,7 @@
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
     </row>
-    <row r="155" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="B155" s="14"/>
       <c r="C155" s="11"/>
@@ -3737,7 +3785,7 @@
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
     </row>
-    <row r="156" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
       <c r="B156" s="14"/>
       <c r="C156" s="11"/>
@@ -3745,7 +3793,7 @@
       <c r="E156" s="8"/>
       <c r="F156" s="8"/>
     </row>
-    <row r="157" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
       <c r="B157" s="14"/>
       <c r="C157" s="11"/>
@@ -3753,7 +3801,7 @@
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
     </row>
-    <row r="158" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
       <c r="B158" s="14"/>
       <c r="C158" s="11"/>
@@ -3761,7 +3809,7 @@
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
     </row>
-    <row r="159" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
       <c r="B159" s="14"/>
       <c r="C159" s="11"/>
@@ -3769,7 +3817,7 @@
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
     </row>
-    <row r="160" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6"/>
       <c r="B160" s="14"/>
       <c r="C160" s="11"/>
@@ -3777,7 +3825,7 @@
       <c r="E160" s="8"/>
       <c r="F160" s="8"/>
     </row>
-    <row r="161" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
       <c r="B161" s="14"/>
       <c r="C161" s="11"/>
@@ -3785,7 +3833,7 @@
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
     </row>
-    <row r="162" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
       <c r="B162" s="14"/>
       <c r="C162" s="11"/>
@@ -3793,7 +3841,7 @@
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
     </row>
-    <row r="163" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
       <c r="B163" s="14"/>
       <c r="C163" s="11"/>
@@ -3801,7 +3849,7 @@
       <c r="E163" s="8"/>
       <c r="F163" s="8"/>
     </row>
-    <row r="164" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6"/>
       <c r="B164" s="14"/>
       <c r="C164" s="11"/>
@@ -3809,7 +3857,7 @@
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
     </row>
-    <row r="165" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
       <c r="B165" s="14"/>
       <c r="C165" s="11"/>
@@ -3817,7 +3865,7 @@
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
     </row>
-    <row r="166" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
       <c r="B166" s="14"/>
       <c r="C166" s="11"/>
@@ -3825,7 +3873,7 @@
       <c r="E166" s="8"/>
       <c r="F166" s="8"/>
     </row>
-    <row r="167" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6"/>
       <c r="B167" s="14"/>
       <c r="C167" s="11"/>
@@ -3833,7 +3881,7 @@
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
     </row>
-    <row r="168" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
       <c r="B168" s="14"/>
       <c r="C168" s="11"/>
@@ -3841,7 +3889,7 @@
       <c r="E168" s="8"/>
       <c r="F168" s="8"/>
     </row>
-    <row r="169" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6"/>
       <c r="B169" s="14"/>
       <c r="C169" s="11"/>
@@ -3849,7 +3897,7 @@
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
     </row>
-    <row r="170" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
       <c r="B170" s="14"/>
       <c r="C170" s="11"/>
@@ -3857,7 +3905,7 @@
       <c r="E170" s="8"/>
       <c r="F170" s="8"/>
     </row>
-    <row r="171" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="B171" s="14"/>
       <c r="C171" s="11"/>
@@ -3865,7 +3913,7 @@
       <c r="E171" s="8"/>
       <c r="F171" s="8"/>
     </row>
-    <row r="172" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
       <c r="B172" s="14"/>
       <c r="C172" s="11"/>
@@ -3873,7 +3921,7 @@
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
     </row>
-    <row r="173" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="B173" s="14"/>
       <c r="C173" s="11"/>
@@ -3881,7 +3929,7 @@
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
     </row>
-    <row r="174" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="B174" s="14"/>
       <c r="C174" s="11"/>
@@ -3889,7 +3937,7 @@
       <c r="E174" s="8"/>
       <c r="F174" s="8"/>
     </row>
-    <row r="175" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
       <c r="B175" s="14"/>
       <c r="C175" s="11"/>
@@ -3897,7 +3945,7 @@
       <c r="E175" s="8"/>
       <c r="F175" s="8"/>
     </row>
-    <row r="176" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
       <c r="B176" s="14"/>
       <c r="C176" s="11"/>
@@ -3905,7 +3953,7 @@
       <c r="E176" s="8"/>
       <c r="F176" s="8"/>
     </row>
-    <row r="177" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="B177" s="14"/>
       <c r="C177" s="11"/>
@@ -3913,7 +3961,7 @@
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
     </row>
-    <row r="178" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="B178" s="14"/>
       <c r="C178" s="11"/>
@@ -3921,7 +3969,7 @@
       <c r="E178" s="8"/>
       <c r="F178" s="8"/>
     </row>
-    <row r="179" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
       <c r="B179" s="14"/>
       <c r="C179" s="11"/>
@@ -3929,7 +3977,7 @@
       <c r="E179" s="8"/>
       <c r="F179" s="8"/>
     </row>
-    <row r="180" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
       <c r="B180" s="14"/>
       <c r="C180" s="11"/>
@@ -3937,7 +3985,7 @@
       <c r="E180" s="8"/>
       <c r="F180" s="8"/>
     </row>
-    <row r="181" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
       <c r="B181" s="14"/>
       <c r="C181" s="11"/>
@@ -3945,7 +3993,7 @@
       <c r="E181" s="8"/>
       <c r="F181" s="8"/>
     </row>
-    <row r="182" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
       <c r="B182" s="14"/>
       <c r="C182" s="11"/>
@@ -3953,7 +4001,7 @@
       <c r="E182" s="8"/>
       <c r="F182" s="8"/>
     </row>
-    <row r="183" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6"/>
       <c r="B183" s="14"/>
       <c r="C183" s="11"/>
@@ -3961,7 +4009,7 @@
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
     </row>
-    <row r="184" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
       <c r="B184" s="14"/>
       <c r="C184" s="11"/>
@@ -3969,7 +4017,7 @@
       <c r="E184" s="8"/>
       <c r="F184" s="8"/>
     </row>
-    <row r="185" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
       <c r="B185" s="14"/>
       <c r="C185" s="11"/>
@@ -3977,7 +4025,7 @@
       <c r="E185" s="8"/>
       <c r="F185" s="8"/>
     </row>
-    <row r="186" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
       <c r="B186" s="14"/>
       <c r="C186" s="11"/>
@@ -3985,7 +4033,7 @@
       <c r="E186" s="8"/>
       <c r="F186" s="8"/>
     </row>
-    <row r="187" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="B187" s="14"/>
       <c r="C187" s="11"/>
@@ -3993,7 +4041,7 @@
       <c r="E187" s="8"/>
       <c r="F187" s="8"/>
     </row>
-    <row r="188" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
       <c r="B188" s="14"/>
       <c r="C188" s="11"/>
@@ -4001,7 +4049,7 @@
       <c r="E188" s="8"/>
       <c r="F188" s="8"/>
     </row>
-    <row r="189" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
       <c r="B189" s="14"/>
       <c r="C189" s="11"/>
@@ -4009,7 +4057,7 @@
       <c r="E189" s="8"/>
       <c r="F189" s="8"/>
     </row>
-    <row r="190" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6"/>
       <c r="B190" s="14"/>
       <c r="C190" s="11"/>
@@ -4017,7 +4065,7 @@
       <c r="E190" s="8"/>
       <c r="F190" s="8"/>
     </row>
-    <row r="191" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
       <c r="B191" s="14"/>
       <c r="C191" s="11"/>
@@ -4025,7 +4073,7 @@
       <c r="E191" s="8"/>
       <c r="F191" s="8"/>
     </row>
-    <row r="192" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
       <c r="B192" s="14"/>
       <c r="C192" s="11"/>
@@ -4033,7 +4081,7 @@
       <c r="E192" s="8"/>
       <c r="F192" s="8"/>
     </row>
-    <row r="193" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
       <c r="B193" s="14"/>
       <c r="C193" s="11"/>
@@ -4041,7 +4089,7 @@
       <c r="E193" s="8"/>
       <c r="F193" s="8"/>
     </row>
-    <row r="194" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6"/>
       <c r="B194" s="14"/>
       <c r="C194" s="11"/>
@@ -4049,7 +4097,7 @@
       <c r="E194" s="8"/>
       <c r="F194" s="8"/>
     </row>
-    <row r="195" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
       <c r="B195" s="14"/>
       <c r="C195" s="11"/>
@@ -4057,7 +4105,7 @@
       <c r="E195" s="8"/>
       <c r="F195" s="8"/>
     </row>
-    <row r="196" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
       <c r="B196" s="14"/>
       <c r="C196" s="11"/>
@@ -4065,7 +4113,7 @@
       <c r="E196" s="8"/>
       <c r="F196" s="8"/>
     </row>
-    <row r="197" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
       <c r="B197" s="14"/>
       <c r="C197" s="11"/>
@@ -4073,7 +4121,7 @@
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
     </row>
-    <row r="198" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6"/>
       <c r="B198" s="14"/>
       <c r="C198" s="11"/>
@@ -4081,7 +4129,7 @@
       <c r="E198" s="8"/>
       <c r="F198" s="8"/>
     </row>
-    <row r="199" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
       <c r="B199" s="14"/>
       <c r="C199" s="11"/>
@@ -4089,7 +4137,7 @@
       <c r="E199" s="8"/>
       <c r="F199" s="8"/>
     </row>
-    <row r="200" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
       <c r="B200" s="14"/>
       <c r="C200" s="11"/>
@@ -4097,7 +4145,7 @@
       <c r="E200" s="8"/>
       <c r="F200" s="8"/>
     </row>
-    <row r="201" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
       <c r="B201" s="14"/>
       <c r="C201" s="11"/>
@@ -4105,7 +4153,7 @@
       <c r="E201" s="8"/>
       <c r="F201" s="8"/>
     </row>
-    <row r="202" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="B202" s="14"/>
       <c r="C202" s="11"/>
@@ -4113,7 +4161,7 @@
       <c r="E202" s="8"/>
       <c r="F202" s="8"/>
     </row>
-    <row r="203" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
       <c r="B203" s="14"/>
       <c r="C203" s="11"/>
@@ -4121,7 +4169,7 @@
       <c r="E203" s="8"/>
       <c r="F203" s="8"/>
     </row>
-    <row r="204" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="B204" s="14"/>
       <c r="C204" s="11"/>
@@ -4129,7 +4177,7 @@
       <c r="E204" s="8"/>
       <c r="F204" s="8"/>
     </row>
-    <row r="205" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
       <c r="B205" s="14"/>
       <c r="C205" s="11"/>
@@ -4137,7 +4185,7 @@
       <c r="E205" s="8"/>
       <c r="F205" s="8"/>
     </row>
-    <row r="206" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="B206" s="14"/>
       <c r="C206" s="11"/>
@@ -4145,7 +4193,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="B207" s="14"/>
       <c r="C207" s="11"/>
@@ -4153,7 +4201,7 @@
       <c r="E207" s="8"/>
       <c r="F207" s="8"/>
     </row>
-    <row r="208" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="B208" s="14"/>
       <c r="C208" s="11"/>
@@ -4161,7 +4209,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6"/>
       <c r="B209" s="14"/>
       <c r="C209" s="11"/>
@@ -4169,7 +4217,7 @@
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
       <c r="B210" s="14"/>
       <c r="C210" s="11"/>
@@ -4177,7 +4225,7 @@
       <c r="E210" s="8"/>
       <c r="F210" s="8"/>
     </row>
-    <row r="211" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
       <c r="B211" s="14"/>
       <c r="C211" s="11"/>
@@ -4185,7 +4233,7 @@
       <c r="E211" s="8"/>
       <c r="F211" s="8"/>
     </row>
-    <row r="212" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
       <c r="B212" s="14"/>
       <c r="C212" s="11"/>
@@ -4193,7 +4241,7 @@
       <c r="E212" s="8"/>
       <c r="F212" s="8"/>
     </row>
-    <row r="213" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6"/>
       <c r="B213" s="14"/>
       <c r="C213" s="11"/>
@@ -4201,7 +4249,7 @@
       <c r="E213" s="8"/>
       <c r="F213" s="8"/>
     </row>
-    <row r="214" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
       <c r="B214" s="14"/>
       <c r="C214" s="11"/>
@@ -4209,7 +4257,7 @@
       <c r="E214" s="8"/>
       <c r="F214" s="8"/>
     </row>
-    <row r="215" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
       <c r="B215" s="14"/>
       <c r="C215" s="11"/>
@@ -4217,7 +4265,7 @@
       <c r="E215" s="8"/>
       <c r="F215" s="8"/>
     </row>
-    <row r="216" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
       <c r="B216" s="14"/>
       <c r="C216" s="11"/>
@@ -4225,7 +4273,7 @@
       <c r="E216" s="8"/>
       <c r="F216" s="8"/>
     </row>
-    <row r="217" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6"/>
       <c r="B217" s="14"/>
       <c r="C217" s="11"/>
@@ -4233,7 +4281,7 @@
       <c r="E217" s="8"/>
       <c r="F217" s="8"/>
     </row>
-    <row r="218" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
       <c r="B218" s="14"/>
       <c r="C218" s="11"/>
@@ -4241,7 +4289,7 @@
       <c r="E218" s="8"/>
       <c r="F218" s="8"/>
     </row>
-    <row r="219" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
       <c r="B219" s="14"/>
       <c r="C219" s="11"/>
@@ -4249,7 +4297,7 @@
       <c r="E219" s="8"/>
       <c r="F219" s="8"/>
     </row>
-    <row r="220" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
       <c r="B220" s="14"/>
       <c r="C220" s="11"/>
@@ -4257,7 +4305,7 @@
       <c r="E220" s="8"/>
       <c r="F220" s="8"/>
     </row>
-    <row r="221" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6"/>
       <c r="B221" s="14"/>
       <c r="C221" s="11"/>
@@ -4265,7 +4313,7 @@
       <c r="E221" s="8"/>
       <c r="F221" s="8"/>
     </row>
-    <row r="222" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
       <c r="B222" s="14"/>
       <c r="C222" s="11"/>
@@ -4273,7 +4321,7 @@
       <c r="E222" s="8"/>
       <c r="F222" s="8"/>
     </row>
-    <row r="223" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
       <c r="B223" s="14"/>
       <c r="C223" s="11"/>
@@ -4281,7 +4329,7 @@
       <c r="E223" s="8"/>
       <c r="F223" s="8"/>
     </row>
-    <row r="224" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
       <c r="B224" s="14"/>
       <c r="C224" s="11"/>
@@ -4289,7 +4337,7 @@
       <c r="E224" s="8"/>
       <c r="F224" s="8"/>
     </row>
-    <row r="225" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
       <c r="B225" s="14"/>
       <c r="C225" s="11"/>
@@ -4297,7 +4345,7 @@
       <c r="E225" s="8"/>
       <c r="F225" s="8"/>
     </row>
-    <row r="226" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6"/>
       <c r="B226" s="14"/>
       <c r="C226" s="11"/>
@@ -4305,7 +4353,7 @@
       <c r="E226" s="8"/>
       <c r="F226" s="8"/>
     </row>
-    <row r="227" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
       <c r="B227" s="14"/>
       <c r="C227" s="11"/>
@@ -4313,7 +4361,7 @@
       <c r="E227" s="8"/>
       <c r="F227" s="8"/>
     </row>
-    <row r="228" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
       <c r="B228" s="14"/>
       <c r="C228" s="11"/>
@@ -4321,7 +4369,7 @@
       <c r="E228" s="8"/>
       <c r="F228" s="8"/>
     </row>
-    <row r="229" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
       <c r="B229" s="14"/>
       <c r="C229" s="11"/>
@@ -4329,7 +4377,7 @@
       <c r="E229" s="8"/>
       <c r="F229" s="8"/>
     </row>
-    <row r="230" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
       <c r="B230" s="14"/>
       <c r="C230" s="11"/>
@@ -4337,7 +4385,7 @@
       <c r="E230" s="8"/>
       <c r="F230" s="8"/>
     </row>
-    <row r="231" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
       <c r="B231" s="14"/>
       <c r="C231" s="11"/>
@@ -4345,7 +4393,7 @@
       <c r="E231" s="8"/>
       <c r="F231" s="8"/>
     </row>
-    <row r="232" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6"/>
       <c r="B232" s="14"/>
       <c r="C232" s="11"/>
@@ -4353,7 +4401,7 @@
       <c r="E232" s="8"/>
       <c r="F232" s="8"/>
     </row>
-    <row r="233" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
       <c r="B233" s="14"/>
       <c r="C233" s="11"/>
@@ -4361,7 +4409,7 @@
       <c r="E233" s="8"/>
       <c r="F233" s="8"/>
     </row>
-    <row r="234" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
       <c r="B234" s="14"/>
       <c r="C234" s="11"/>
@@ -4369,7 +4417,7 @@
       <c r="E234" s="8"/>
       <c r="F234" s="8"/>
     </row>
-    <row r="235" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6"/>
       <c r="B235" s="14"/>
       <c r="C235" s="11"/>
@@ -4377,7 +4425,7 @@
       <c r="E235" s="8"/>
       <c r="F235" s="8"/>
     </row>
-    <row r="236" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
       <c r="B236" s="14"/>
       <c r="C236" s="11"/>
@@ -4385,7 +4433,7 @@
       <c r="E236" s="8"/>
       <c r="F236" s="8"/>
     </row>
-    <row r="237" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
       <c r="B237" s="14"/>
       <c r="C237" s="11"/>
@@ -4393,7 +4441,7 @@
       <c r="E237" s="8"/>
       <c r="F237" s="8"/>
     </row>
-    <row r="238" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
       <c r="B238" s="14"/>
       <c r="C238" s="11"/>
@@ -4401,7 +4449,7 @@
       <c r="E238" s="8"/>
       <c r="F238" s="8"/>
     </row>
-    <row r="239" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6"/>
       <c r="B239" s="14"/>
       <c r="C239" s="11"/>
@@ -4409,7 +4457,7 @@
       <c r="E239" s="8"/>
       <c r="F239" s="8"/>
     </row>
-    <row r="240" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6"/>
       <c r="B240" s="14"/>
       <c r="C240" s="11"/>
@@ -4417,7 +4465,7 @@
       <c r="E240" s="8"/>
       <c r="F240" s="8"/>
     </row>
-    <row r="241" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
       <c r="B241" s="14"/>
       <c r="C241" s="11"/>
@@ -4425,7 +4473,7 @@
       <c r="E241" s="8"/>
       <c r="F241" s="8"/>
     </row>
-    <row r="242" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="B242" s="14"/>
       <c r="C242" s="11"/>
@@ -4433,7 +4481,7 @@
       <c r="E242" s="8"/>
       <c r="F242" s="8"/>
     </row>
-    <row r="243" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
       <c r="B243" s="14"/>
       <c r="C243" s="11"/>
@@ -4441,7 +4489,7 @@
       <c r="E243" s="8"/>
       <c r="F243" s="8"/>
     </row>
-    <row r="244" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
       <c r="B244" s="14"/>
       <c r="C244" s="11"/>
@@ -4449,7 +4497,7 @@
       <c r="E244" s="8"/>
       <c r="F244" s="8"/>
     </row>
-    <row r="245" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6"/>
       <c r="B245" s="14"/>
       <c r="C245" s="11"/>
@@ -4457,7 +4505,7 @@
       <c r="E245" s="8"/>
       <c r="F245" s="8"/>
     </row>
-    <row r="246" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
       <c r="B246" s="14"/>
       <c r="C246" s="11"/>
@@ -4465,7 +4513,7 @@
       <c r="E246" s="8"/>
       <c r="F246" s="8"/>
     </row>
-    <row r="247" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
       <c r="B247" s="14"/>
       <c r="C247" s="11"/>
@@ -4473,7 +4521,7 @@
       <c r="E247" s="8"/>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
       <c r="B248" s="14"/>
       <c r="C248" s="11"/>
@@ -4481,7 +4529,7 @@
       <c r="E248" s="8"/>
       <c r="F248" s="8"/>
     </row>
-    <row r="249" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6"/>
       <c r="B249" s="14"/>
       <c r="C249" s="11"/>
@@ -4489,7 +4537,7 @@
       <c r="E249" s="8"/>
       <c r="F249" s="8"/>
     </row>
-    <row r="250" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
       <c r="B250" s="14"/>
       <c r="C250" s="11"/>
@@ -4497,7 +4545,7 @@
       <c r="E250" s="8"/>
       <c r="F250" s="8"/>
     </row>
-    <row r="251" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6"/>
       <c r="B251" s="14"/>
       <c r="C251" s="11"/>
@@ -4505,7 +4553,7 @@
       <c r="E251" s="8"/>
       <c r="F251" s="8"/>
     </row>
-    <row r="252" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
       <c r="B252" s="14"/>
       <c r="C252" s="11"/>
@@ -4513,7 +4561,7 @@
       <c r="E252" s="8"/>
       <c r="F252" s="8"/>
     </row>
-    <row r="253" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
       <c r="B253" s="14"/>
       <c r="C253" s="11"/>
@@ -4521,7 +4569,7 @@
       <c r="E253" s="8"/>
       <c r="F253" s="8"/>
     </row>
-    <row r="254" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6"/>
       <c r="B254" s="14"/>
       <c r="C254" s="11"/>
@@ -4529,7 +4577,7 @@
       <c r="E254" s="8"/>
       <c r="F254" s="8"/>
     </row>
-    <row r="255" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6"/>
       <c r="B255" s="14"/>
       <c r="C255" s="11"/>
@@ -4537,7 +4585,7 @@
       <c r="E255" s="8"/>
       <c r="F255" s="8"/>
     </row>
-    <row r="256" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
       <c r="B256" s="14"/>
       <c r="C256" s="11"/>
@@ -4545,7 +4593,7 @@
       <c r="E256" s="8"/>
       <c r="F256" s="8"/>
     </row>
-    <row r="257" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6"/>
       <c r="B257" s="14"/>
       <c r="C257" s="11"/>
@@ -4553,7 +4601,7 @@
       <c r="E257" s="8"/>
       <c r="F257" s="8"/>
     </row>
-    <row r="258" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
       <c r="B258" s="14"/>
       <c r="C258" s="11"/>
@@ -4561,7 +4609,7 @@
       <c r="E258" s="8"/>
       <c r="F258" s="8"/>
     </row>
-    <row r="259" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6"/>
       <c r="B259" s="14"/>
       <c r="C259" s="11"/>
@@ -4569,7 +4617,7 @@
       <c r="E259" s="8"/>
       <c r="F259" s="8"/>
     </row>
-    <row r="260" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6"/>
       <c r="B260" s="14"/>
       <c r="C260" s="11"/>
@@ -4577,7 +4625,7 @@
       <c r="E260" s="8"/>
       <c r="F260" s="8"/>
     </row>
-    <row r="261" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6"/>
       <c r="B261" s="14"/>
       <c r="C261" s="11"/>
@@ -4585,7 +4633,7 @@
       <c r="E261" s="8"/>
       <c r="F261" s="8"/>
     </row>
-    <row r="262" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6"/>
       <c r="B262" s="14"/>
       <c r="C262" s="11"/>
@@ -4593,7 +4641,7 @@
       <c r="E262" s="8"/>
       <c r="F262" s="8"/>
     </row>
-    <row r="263" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6"/>
       <c r="B263" s="14"/>
       <c r="C263" s="11"/>
@@ -4601,7 +4649,7 @@
       <c r="E263" s="8"/>
       <c r="F263" s="8"/>
     </row>
-    <row r="264" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
       <c r="B264" s="14"/>
       <c r="C264" s="11"/>
@@ -4609,7 +4657,7 @@
       <c r="E264" s="8"/>
       <c r="F264" s="8"/>
     </row>
-    <row r="265" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
       <c r="B265" s="14"/>
       <c r="C265" s="11"/>
@@ -4617,7 +4665,7 @@
       <c r="E265" s="8"/>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
       <c r="B266" s="14"/>
       <c r="C266" s="11"/>
@@ -4625,7 +4673,7 @@
       <c r="E266" s="8"/>
       <c r="F266" s="8"/>
     </row>
-    <row r="267" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6"/>
       <c r="B267" s="14"/>
       <c r="C267" s="11"/>
@@ -4633,7 +4681,7 @@
       <c r="E267" s="8"/>
       <c r="F267" s="8"/>
     </row>
-    <row r="268" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
       <c r="B268" s="14"/>
       <c r="C268" s="11"/>
@@ -4641,7 +4689,7 @@
       <c r="E268" s="8"/>
       <c r="F268" s="8"/>
     </row>
-    <row r="269" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
       <c r="B269" s="14"/>
       <c r="C269" s="11"/>
@@ -4649,7 +4697,7 @@
       <c r="E269" s="8"/>
       <c r="F269" s="8"/>
     </row>
-    <row r="270" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6"/>
       <c r="B270" s="14"/>
       <c r="C270" s="11"/>
@@ -4657,7 +4705,7 @@
       <c r="E270" s="8"/>
       <c r="F270" s="8"/>
     </row>
-    <row r="271" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6"/>
       <c r="B271" s="14"/>
       <c r="C271" s="11"/>
@@ -4665,7 +4713,7 @@
       <c r="E271" s="8"/>
       <c r="F271" s="8"/>
     </row>
-    <row r="272" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
       <c r="B272" s="14"/>
       <c r="C272" s="11"/>
@@ -4673,7 +4721,7 @@
       <c r="E272" s="8"/>
       <c r="F272" s="8"/>
     </row>
-    <row r="273" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6"/>
       <c r="B273" s="14"/>
       <c r="C273" s="11"/>
@@ -4681,7 +4729,7 @@
       <c r="E273" s="8"/>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
       <c r="B274" s="14"/>
       <c r="C274" s="11"/>
@@ -4689,7 +4737,7 @@
       <c r="E274" s="8"/>
       <c r="F274" s="8"/>
     </row>
-    <row r="275" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
       <c r="B275" s="14"/>
       <c r="C275" s="11"/>
@@ -4697,7 +4745,7 @@
       <c r="E275" s="8"/>
       <c r="F275" s="8"/>
     </row>
-    <row r="276" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
       <c r="B276" s="14"/>
       <c r="C276" s="11"/>
@@ -4705,7 +4753,7 @@
       <c r="E276" s="8"/>
       <c r="F276" s="8"/>
     </row>
-    <row r="277" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6"/>
       <c r="B277" s="14"/>
       <c r="C277" s="11"/>
@@ -4713,7 +4761,7 @@
       <c r="E277" s="8"/>
       <c r="F277" s="8"/>
     </row>
-    <row r="278" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
       <c r="B278" s="14"/>
       <c r="C278" s="11"/>
@@ -4721,7 +4769,7 @@
       <c r="E278" s="8"/>
       <c r="F278" s="8"/>
     </row>
-    <row r="279" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
       <c r="B279" s="14"/>
       <c r="C279" s="11"/>
@@ -4729,7 +4777,7 @@
       <c r="E279" s="8"/>
       <c r="F279" s="8"/>
     </row>
-    <row r="280" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
       <c r="B280" s="14"/>
       <c r="C280" s="11"/>
@@ -4737,7 +4785,7 @@
       <c r="E280" s="8"/>
       <c r="F280" s="8"/>
     </row>
-    <row r="281" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6"/>
       <c r="B281" s="14"/>
       <c r="C281" s="11"/>
@@ -4745,7 +4793,7 @@
       <c r="E281" s="8"/>
       <c r="F281" s="8"/>
     </row>
-    <row r="282" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6"/>
       <c r="B282" s="14"/>
       <c r="C282" s="11"/>
@@ -4753,7 +4801,7 @@
       <c r="E282" s="8"/>
       <c r="F282" s="8"/>
     </row>
-    <row r="283" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
       <c r="B283" s="14"/>
       <c r="C283" s="11"/>
@@ -4761,7 +4809,7 @@
       <c r="E283" s="8"/>
       <c r="F283" s="8"/>
     </row>
-    <row r="284" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
       <c r="B284" s="14"/>
       <c r="C284" s="11"/>
@@ -4769,7 +4817,7 @@
       <c r="E284" s="8"/>
       <c r="F284" s="8"/>
     </row>
-    <row r="285" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6"/>
       <c r="B285" s="14"/>
       <c r="C285" s="11"/>
@@ -4777,7 +4825,7 @@
       <c r="E285" s="8"/>
       <c r="F285" s="8"/>
     </row>
-    <row r="286" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
       <c r="B286" s="14"/>
       <c r="C286" s="11"/>
@@ -4785,7 +4833,7 @@
       <c r="E286" s="8"/>
       <c r="F286" s="8"/>
     </row>
-    <row r="287" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6"/>
       <c r="B287" s="14"/>
       <c r="C287" s="11"/>
@@ -4793,7 +4841,7 @@
       <c r="E287" s="8"/>
       <c r="F287" s="8"/>
     </row>
-    <row r="288" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
       <c r="B288" s="14"/>
       <c r="C288" s="11"/>
@@ -4801,7 +4849,7 @@
       <c r="E288" s="8"/>
       <c r="F288" s="8"/>
     </row>
-    <row r="289" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6"/>
       <c r="B289" s="14"/>
       <c r="C289" s="11"/>
@@ -4809,7 +4857,7 @@
       <c r="E289" s="8"/>
       <c r="F289" s="8"/>
     </row>
-    <row r="290" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
       <c r="B290" s="14"/>
       <c r="C290" s="11"/>
@@ -4817,7 +4865,7 @@
       <c r="E290" s="8"/>
       <c r="F290" s="8"/>
     </row>
-    <row r="291" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6"/>
       <c r="B291" s="14"/>
       <c r="C291" s="11"/>
@@ -4825,7 +4873,7 @@
       <c r="E291" s="8"/>
       <c r="F291" s="8"/>
     </row>
-    <row r="292" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6"/>
       <c r="B292" s="14"/>
       <c r="C292" s="11"/>
@@ -4833,7 +4881,7 @@
       <c r="E292" s="8"/>
       <c r="F292" s="8"/>
     </row>
-    <row r="293" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
       <c r="B293" s="14"/>
       <c r="C293" s="11"/>
@@ -4841,7 +4889,7 @@
       <c r="E293" s="8"/>
       <c r="F293" s="8"/>
     </row>
-    <row r="294" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
       <c r="B294" s="14"/>
       <c r="C294" s="11"/>
@@ -4849,7 +4897,7 @@
       <c r="E294" s="8"/>
       <c r="F294" s="8"/>
     </row>
-    <row r="295" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6"/>
       <c r="B295" s="14"/>
       <c r="C295" s="11"/>
@@ -4857,7 +4905,7 @@
       <c r="E295" s="8"/>
       <c r="F295" s="8"/>
     </row>
-    <row r="296" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
       <c r="B296" s="14"/>
       <c r="C296" s="11"/>
@@ -4865,7 +4913,7 @@
       <c r="E296" s="8"/>
       <c r="F296" s="8"/>
     </row>
-    <row r="297" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
       <c r="B297" s="14"/>
       <c r="C297" s="11"/>
@@ -4873,7 +4921,7 @@
       <c r="E297" s="8"/>
       <c r="F297" s="8"/>
     </row>
-    <row r="298" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
       <c r="B298" s="14"/>
       <c r="C298" s="11"/>
@@ -4881,7 +4929,7 @@
       <c r="E298" s="8"/>
       <c r="F298" s="8"/>
     </row>
-    <row r="299" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6"/>
       <c r="B299" s="14"/>
       <c r="C299" s="11"/>
@@ -4889,7 +4937,7 @@
       <c r="E299" s="8"/>
       <c r="F299" s="8"/>
     </row>
-    <row r="300" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6"/>
       <c r="B300" s="14"/>
       <c r="C300" s="11"/>
@@ -4897,7 +4945,7 @@
       <c r="E300" s="8"/>
       <c r="F300" s="8"/>
     </row>
-    <row r="301" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6"/>
       <c r="B301" s="14"/>
       <c r="C301" s="11"/>
@@ -4905,7 +4953,7 @@
       <c r="E301" s="8"/>
       <c r="F301" s="8"/>
     </row>
-    <row r="302" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6"/>
       <c r="B302" s="14"/>
       <c r="C302" s="11"/>
@@ -4913,7 +4961,7 @@
       <c r="E302" s="8"/>
       <c r="F302" s="8"/>
     </row>
-    <row r="303" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6"/>
       <c r="B303" s="14"/>
       <c r="C303" s="11"/>
@@ -4921,7 +4969,7 @@
       <c r="E303" s="8"/>
       <c r="F303" s="8"/>
     </row>
-    <row r="304" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6"/>
       <c r="B304" s="14"/>
       <c r="C304" s="11"/>
@@ -4929,7 +4977,7 @@
       <c r="E304" s="8"/>
       <c r="F304" s="8"/>
     </row>
-    <row r="305" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6"/>
       <c r="B305" s="14"/>
       <c r="C305" s="11"/>
@@ -4937,7 +4985,7 @@
       <c r="E305" s="8"/>
       <c r="F305" s="8"/>
     </row>
-    <row r="306" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6"/>
       <c r="B306" s="14"/>
       <c r="C306" s="11"/>
@@ -4945,7 +4993,7 @@
       <c r="E306" s="8"/>
       <c r="F306" s="8"/>
     </row>
-    <row r="307" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6"/>
       <c r="B307" s="14"/>
       <c r="C307" s="11"/>
@@ -4953,7 +5001,7 @@
       <c r="E307" s="8"/>
       <c r="F307" s="8"/>
     </row>
-    <row r="308" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6"/>
       <c r="B308" s="14"/>
       <c r="C308" s="11"/>
@@ -4961,7 +5009,7 @@
       <c r="E308" s="8"/>
       <c r="F308" s="8"/>
     </row>
-    <row r="309" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="6"/>
       <c r="B309" s="14"/>
       <c r="C309" s="11"/>
@@ -4969,7 +5017,7 @@
       <c r="E309" s="8"/>
       <c r="F309" s="8"/>
     </row>
-    <row r="310" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6"/>
       <c r="B310" s="14"/>
       <c r="C310" s="11"/>
@@ -4977,7 +5025,7 @@
       <c r="E310" s="8"/>
       <c r="F310" s="8"/>
     </row>
-    <row r="311" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="6"/>
       <c r="B311" s="14"/>
       <c r="C311" s="11"/>
@@ -4985,7 +5033,7 @@
       <c r="E311" s="8"/>
       <c r="F311" s="8"/>
     </row>
-    <row r="312" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6"/>
       <c r="B312" s="14"/>
       <c r="C312" s="11"/>
@@ -4993,7 +5041,7 @@
       <c r="E312" s="8"/>
       <c r="F312" s="8"/>
     </row>
-    <row r="313" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="6"/>
       <c r="B313" s="14"/>
       <c r="C313" s="11"/>
@@ -5001,7 +5049,7 @@
       <c r="E313" s="8"/>
       <c r="F313" s="8"/>
     </row>
-    <row r="314" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6"/>
       <c r="B314" s="14"/>
       <c r="C314" s="11"/>
@@ -5009,7 +5057,7 @@
       <c r="E314" s="8"/>
       <c r="F314" s="8"/>
     </row>
-    <row r="315" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="6"/>
       <c r="B315" s="14"/>
       <c r="C315" s="11"/>
@@ -5017,7 +5065,7 @@
       <c r="E315" s="8"/>
       <c r="F315" s="8"/>
     </row>
-    <row r="316" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="6"/>
       <c r="B316" s="14"/>
       <c r="C316" s="11"/>
@@ -5025,7 +5073,7 @@
       <c r="E316" s="8"/>
       <c r="F316" s="8"/>
     </row>
-    <row r="317" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="6"/>
       <c r="B317" s="14"/>
       <c r="C317" s="11"/>
@@ -5033,7 +5081,7 @@
       <c r="E317" s="8"/>
       <c r="F317" s="8"/>
     </row>
-    <row r="318" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6"/>
       <c r="B318" s="14"/>
       <c r="C318" s="11"/>
@@ -5041,7 +5089,7 @@
       <c r="E318" s="8"/>
       <c r="F318" s="8"/>
     </row>
-    <row r="319" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="6"/>
       <c r="B319" s="14"/>
       <c r="C319" s="11"/>
@@ -5049,7 +5097,7 @@
       <c r="E319" s="8"/>
       <c r="F319" s="8"/>
     </row>
-    <row r="320" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="6"/>
       <c r="B320" s="14"/>
       <c r="C320" s="11"/>
@@ -5057,7 +5105,7 @@
       <c r="E320" s="8"/>
       <c r="F320" s="8"/>
     </row>
-    <row r="321" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6"/>
       <c r="B321" s="14"/>
       <c r="C321" s="11"/>
@@ -5065,7 +5113,7 @@
       <c r="E321" s="8"/>
       <c r="F321" s="8"/>
     </row>
-    <row r="322" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="6"/>
       <c r="B322" s="14"/>
       <c r="C322" s="11"/>
@@ -5073,7 +5121,7 @@
       <c r="E322" s="8"/>
       <c r="F322" s="8"/>
     </row>
-    <row r="323" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="6"/>
       <c r="B323" s="14"/>
       <c r="C323" s="11"/>
@@ -5081,7 +5129,7 @@
       <c r="E323" s="8"/>
       <c r="F323" s="8"/>
     </row>
-    <row r="324" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6"/>
       <c r="B324" s="14"/>
       <c r="C324" s="11"/>
@@ -5089,7 +5137,7 @@
       <c r="E324" s="8"/>
       <c r="F324" s="8"/>
     </row>
-    <row r="325" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="6"/>
       <c r="B325" s="14"/>
       <c r="C325" s="11"/>
@@ -5097,7 +5145,7 @@
       <c r="E325" s="8"/>
       <c r="F325" s="8"/>
     </row>
-    <row r="326" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="6"/>
       <c r="B326" s="14"/>
       <c r="C326" s="11"/>
@@ -5105,7 +5153,7 @@
       <c r="E326" s="8"/>
       <c r="F326" s="8"/>
     </row>
-    <row r="327" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="6"/>
       <c r="B327" s="14"/>
       <c r="C327" s="11"/>
@@ -5113,7 +5161,7 @@
       <c r="E327" s="8"/>
       <c r="F327" s="8"/>
     </row>
-    <row r="328" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="6"/>
       <c r="B328" s="14"/>
       <c r="C328" s="11"/>
@@ -5121,7 +5169,7 @@
       <c r="E328" s="8"/>
       <c r="F328" s="8"/>
     </row>
-    <row r="329" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="6"/>
       <c r="B329" s="14"/>
       <c r="C329" s="11"/>
@@ -5129,7 +5177,7 @@
       <c r="E329" s="8"/>
       <c r="F329" s="8"/>
     </row>
-    <row r="330" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="6"/>
       <c r="B330" s="14"/>
       <c r="C330" s="11"/>
@@ -5137,7 +5185,7 @@
       <c r="E330" s="8"/>
       <c r="F330" s="8"/>
     </row>
-    <row r="331" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="6"/>
       <c r="B331" s="14"/>
       <c r="C331" s="11"/>
@@ -5145,7 +5193,7 @@
       <c r="E331" s="8"/>
       <c r="F331" s="8"/>
     </row>
-    <row r="332" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6"/>
       <c r="B332" s="14"/>
       <c r="C332" s="11"/>
@@ -5153,7 +5201,7 @@
       <c r="E332" s="8"/>
       <c r="F332" s="8"/>
     </row>
-    <row r="333" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="6"/>
       <c r="B333" s="14"/>
       <c r="C333" s="11"/>
@@ -5161,7 +5209,7 @@
       <c r="E333" s="8"/>
       <c r="F333" s="8"/>
     </row>
-    <row r="334" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="6"/>
       <c r="B334" s="14"/>
       <c r="C334" s="11"/>
@@ -5169,7 +5217,7 @@
       <c r="E334" s="8"/>
       <c r="F334" s="8"/>
     </row>
-    <row r="335" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="6"/>
       <c r="B335" s="14"/>
       <c r="C335" s="11"/>
@@ -5177,7 +5225,7 @@
       <c r="E335" s="8"/>
       <c r="F335" s="8"/>
     </row>
-    <row r="336" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="6"/>
       <c r="B336" s="14"/>
       <c r="C336" s="11"/>
@@ -5185,7 +5233,7 @@
       <c r="E336" s="8"/>
       <c r="F336" s="8"/>
     </row>
-    <row r="337" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="6"/>
       <c r="B337" s="14"/>
       <c r="C337" s="11"/>
@@ -5193,7 +5241,7 @@
       <c r="E337" s="8"/>
       <c r="F337" s="8"/>
     </row>
-    <row r="338" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="6"/>
       <c r="B338" s="14"/>
       <c r="C338" s="11"/>
@@ -5201,7 +5249,7 @@
       <c r="E338" s="8"/>
       <c r="F338" s="8"/>
     </row>
-    <row r="339" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="6"/>
       <c r="B339" s="14"/>
       <c r="C339" s="11"/>
@@ -5209,7 +5257,7 @@
       <c r="E339" s="8"/>
       <c r="F339" s="8"/>
     </row>
-    <row r="340" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="6"/>
       <c r="B340" s="14"/>
       <c r="C340" s="11"/>
@@ -5217,7 +5265,7 @@
       <c r="E340" s="8"/>
       <c r="F340" s="8"/>
     </row>
-    <row r="341" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="6"/>
       <c r="B341" s="14"/>
       <c r="C341" s="11"/>
@@ -5225,7 +5273,7 @@
       <c r="E341" s="8"/>
       <c r="F341" s="8"/>
     </row>
-    <row r="342" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="6"/>
       <c r="B342" s="14"/>
       <c r="C342" s="11"/>
@@ -5233,7 +5281,7 @@
       <c r="E342" s="8"/>
       <c r="F342" s="8"/>
     </row>
-    <row r="343" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="6"/>
       <c r="B343" s="14"/>
       <c r="C343" s="11"/>
@@ -5241,7 +5289,7 @@
       <c r="E343" s="8"/>
       <c r="F343" s="8"/>
     </row>
-    <row r="344" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6"/>
       <c r="B344" s="14"/>
       <c r="C344" s="11"/>
@@ -5249,7 +5297,7 @@
       <c r="E344" s="8"/>
       <c r="F344" s="8"/>
     </row>
-    <row r="345" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="6"/>
       <c r="B345" s="14"/>
       <c r="C345" s="11"/>
@@ -5257,7 +5305,7 @@
       <c r="E345" s="8"/>
       <c r="F345" s="8"/>
     </row>
-    <row r="346" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="6"/>
       <c r="B346" s="14"/>
       <c r="C346" s="11"/>
@@ -5265,7 +5313,7 @@
       <c r="E346" s="8"/>
       <c r="F346" s="8"/>
     </row>
-    <row r="347" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="6"/>
       <c r="B347" s="14"/>
       <c r="C347" s="11"/>
@@ -5273,7 +5321,7 @@
       <c r="E347" s="8"/>
       <c r="F347" s="8"/>
     </row>
-    <row r="348" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="6"/>
       <c r="B348" s="14"/>
       <c r="C348" s="11"/>
@@ -5281,7 +5329,7 @@
       <c r="E348" s="8"/>
       <c r="F348" s="8"/>
     </row>
-    <row r="349" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="6"/>
       <c r="B349" s="14"/>
       <c r="C349" s="11"/>
@@ -5289,7 +5337,7 @@
       <c r="E349" s="8"/>
       <c r="F349" s="8"/>
     </row>
-    <row r="350" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="6"/>
       <c r="B350" s="14"/>
       <c r="C350" s="11"/>
@@ -5297,7 +5345,7 @@
       <c r="E350" s="8"/>
       <c r="F350" s="8"/>
     </row>
-    <row r="351" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="6"/>
       <c r="B351" s="14"/>
       <c r="C351" s="11"/>
@@ -5305,7 +5353,7 @@
       <c r="E351" s="8"/>
       <c r="F351" s="8"/>
     </row>
-    <row r="352" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="6"/>
       <c r="B352" s="14"/>
       <c r="C352" s="11"/>
@@ -5313,7 +5361,7 @@
       <c r="E352" s="8"/>
       <c r="F352" s="8"/>
     </row>
-    <row r="353" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="6"/>
       <c r="B353" s="14"/>
       <c r="C353" s="11"/>
@@ -5321,7 +5369,7 @@
       <c r="E353" s="8"/>
       <c r="F353" s="8"/>
     </row>
-    <row r="354" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="6"/>
       <c r="B354" s="14"/>
       <c r="C354" s="11"/>
@@ -5329,7 +5377,7 @@
       <c r="E354" s="8"/>
       <c r="F354" s="8"/>
     </row>
-    <row r="355" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="6"/>
       <c r="B355" s="14"/>
       <c r="C355" s="11"/>
@@ -5337,7 +5385,7 @@
       <c r="E355" s="8"/>
       <c r="F355" s="8"/>
     </row>
-    <row r="356" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="6"/>
       <c r="B356" s="14"/>
       <c r="C356" s="11"/>
@@ -5345,7 +5393,7 @@
       <c r="E356" s="8"/>
       <c r="F356" s="8"/>
     </row>
-    <row r="357" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="6"/>
       <c r="B357" s="14"/>
       <c r="C357" s="11"/>
@@ -5353,7 +5401,7 @@
       <c r="E357" s="8"/>
       <c r="F357" s="8"/>
     </row>
-    <row r="358" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6"/>
       <c r="B358" s="14"/>
       <c r="C358" s="11"/>
@@ -5361,7 +5409,7 @@
       <c r="E358" s="8"/>
       <c r="F358" s="8"/>
     </row>
-    <row r="359" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="6"/>
       <c r="B359" s="14"/>
       <c r="C359" s="11"/>
@@ -5369,7 +5417,7 @@
       <c r="E359" s="8"/>
       <c r="F359" s="8"/>
     </row>
-    <row r="360" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="6"/>
       <c r="B360" s="14"/>
       <c r="C360" s="11"/>
@@ -5377,7 +5425,7 @@
       <c r="E360" s="8"/>
       <c r="F360" s="8"/>
     </row>
-    <row r="361" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="6"/>
       <c r="B361" s="14"/>
       <c r="C361" s="11"/>
@@ -5385,7 +5433,7 @@
       <c r="E361" s="8"/>
       <c r="F361" s="8"/>
     </row>
-    <row r="362" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="6"/>
       <c r="B362" s="14"/>
       <c r="C362" s="11"/>
@@ -5393,7 +5441,7 @@
       <c r="E362" s="8"/>
       <c r="F362" s="8"/>
     </row>
-    <row r="363" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="6"/>
       <c r="B363" s="14"/>
       <c r="C363" s="11"/>
@@ -5401,7 +5449,7 @@
       <c r="E363" s="8"/>
       <c r="F363" s="8"/>
     </row>
-    <row r="364" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="6"/>
       <c r="B364" s="14"/>
       <c r="C364" s="11"/>
@@ -5409,7 +5457,7 @@
       <c r="E364" s="8"/>
       <c r="F364" s="8"/>
     </row>
-    <row r="365" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="6"/>
       <c r="B365" s="14"/>
       <c r="C365" s="11"/>
@@ -5417,7 +5465,7 @@
       <c r="E365" s="8"/>
       <c r="F365" s="8"/>
     </row>
-    <row r="366" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6"/>
       <c r="B366" s="14"/>
       <c r="C366" s="11"/>
@@ -5425,7 +5473,7 @@
       <c r="E366" s="8"/>
       <c r="F366" s="8"/>
     </row>
-    <row r="367" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="6"/>
       <c r="B367" s="14"/>
       <c r="C367" s="11"/>
@@ -5433,7 +5481,7 @@
       <c r="E367" s="8"/>
       <c r="F367" s="8"/>
     </row>
-    <row r="368" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="6"/>
       <c r="B368" s="14"/>
       <c r="C368" s="11"/>
@@ -5441,7 +5489,7 @@
       <c r="E368" s="8"/>
       <c r="F368" s="8"/>
     </row>
-    <row r="369" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="6"/>
       <c r="B369" s="14"/>
       <c r="C369" s="11"/>
@@ -5449,7 +5497,7 @@
       <c r="E369" s="8"/>
       <c r="F369" s="8"/>
     </row>
-    <row r="370" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="6"/>
       <c r="B370" s="14"/>
       <c r="C370" s="11"/>
@@ -5457,7 +5505,7 @@
       <c r="E370" s="8"/>
       <c r="F370" s="8"/>
     </row>
-    <row r="371" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="6"/>
       <c r="B371" s="14"/>
       <c r="C371" s="11"/>
@@ -5465,7 +5513,7 @@
       <c r="E371" s="8"/>
       <c r="F371" s="8"/>
     </row>
-    <row r="372" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="6"/>
       <c r="B372" s="14"/>
       <c r="C372" s="11"/>
@@ -5473,7 +5521,7 @@
       <c r="E372" s="8"/>
       <c r="F372" s="8"/>
     </row>
-    <row r="373" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="6"/>
       <c r="B373" s="14"/>
       <c r="C373" s="11"/>
@@ -5481,7 +5529,7 @@
       <c r="E373" s="8"/>
       <c r="F373" s="8"/>
     </row>
-    <row r="374" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="6"/>
       <c r="B374" s="14"/>
       <c r="C374" s="11"/>
@@ -5489,7 +5537,7 @@
       <c r="E374" s="8"/>
       <c r="F374" s="8"/>
     </row>
-    <row r="375" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="6"/>
       <c r="B375" s="14"/>
       <c r="C375" s="11"/>
@@ -5497,7 +5545,7 @@
       <c r="E375" s="8"/>
       <c r="F375" s="8"/>
     </row>
-    <row r="376" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6"/>
       <c r="B376" s="14"/>
       <c r="C376" s="11"/>
@@ -5505,7 +5553,7 @@
       <c r="E376" s="8"/>
       <c r="F376" s="8"/>
     </row>
-    <row r="377" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="6"/>
       <c r="B377" s="14"/>
       <c r="C377" s="11"/>
@@ -5513,7 +5561,7 @@
       <c r="E377" s="8"/>
       <c r="F377" s="8"/>
     </row>
-    <row r="378" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6"/>
       <c r="B378" s="14"/>
       <c r="C378" s="11"/>
@@ -5521,7 +5569,7 @@
       <c r="E378" s="8"/>
       <c r="F378" s="8"/>
     </row>
-    <row r="379" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="6"/>
       <c r="B379" s="14"/>
       <c r="C379" s="11"/>
@@ -5529,7 +5577,7 @@
       <c r="E379" s="8"/>
       <c r="F379" s="8"/>
     </row>
-    <row r="380" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6"/>
       <c r="B380" s="14"/>
       <c r="C380" s="11"/>
@@ -5537,7 +5585,7 @@
       <c r="E380" s="8"/>
       <c r="F380" s="8"/>
     </row>
-    <row r="381" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="6"/>
       <c r="B381" s="14"/>
       <c r="C381" s="11"/>
@@ -5545,7 +5593,7 @@
       <c r="E381" s="8"/>
       <c r="F381" s="8"/>
     </row>
-    <row r="382" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6"/>
       <c r="B382" s="14"/>
       <c r="C382" s="11"/>
@@ -5553,7 +5601,7 @@
       <c r="E382" s="8"/>
       <c r="F382" s="8"/>
     </row>
-    <row r="383" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="6"/>
       <c r="B383" s="14"/>
       <c r="C383" s="11"/>
@@ -5561,7 +5609,7 @@
       <c r="E383" s="8"/>
       <c r="F383" s="8"/>
     </row>
-    <row r="384" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6"/>
       <c r="B384" s="14"/>
       <c r="C384" s="11"/>
@@ -5569,7 +5617,7 @@
       <c r="E384" s="8"/>
       <c r="F384" s="8"/>
     </row>
-    <row r="385" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="6"/>
       <c r="B385" s="14"/>
       <c r="C385" s="11"/>
@@ -5577,7 +5625,7 @@
       <c r="E385" s="8"/>
       <c r="F385" s="8"/>
     </row>
-    <row r="386" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6"/>
       <c r="B386" s="14"/>
       <c r="C386" s="11"/>
@@ -5585,7 +5633,7 @@
       <c r="E386" s="8"/>
       <c r="F386" s="8"/>
     </row>
-    <row r="387" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6"/>
       <c r="B387" s="14"/>
       <c r="C387" s="11"/>
@@ -5593,7 +5641,7 @@
       <c r="E387" s="8"/>
       <c r="F387" s="8"/>
     </row>
-    <row r="388" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6"/>
       <c r="B388" s="14"/>
       <c r="C388" s="11"/>
@@ -5601,7 +5649,7 @@
       <c r="E388" s="8"/>
       <c r="F388" s="8"/>
     </row>
-    <row r="389" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6"/>
       <c r="B389" s="14"/>
       <c r="C389" s="11"/>
@@ -5609,7 +5657,7 @@
       <c r="E389" s="8"/>
       <c r="F389" s="8"/>
     </row>
-    <row r="390" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6"/>
       <c r="B390" s="14"/>
       <c r="C390" s="11"/>
@@ -5617,7 +5665,7 @@
       <c r="E390" s="8"/>
       <c r="F390" s="8"/>
     </row>
-    <row r="391" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="6"/>
       <c r="B391" s="14"/>
       <c r="C391" s="11"/>
@@ -5625,7 +5673,7 @@
       <c r="E391" s="8"/>
       <c r="F391" s="8"/>
     </row>
-    <row r="392" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6"/>
       <c r="B392" s="14"/>
       <c r="C392" s="11"/>
@@ -5633,7 +5681,7 @@
       <c r="E392" s="8"/>
       <c r="F392" s="8"/>
     </row>
-    <row r="393" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="6"/>
       <c r="B393" s="14"/>
       <c r="C393" s="11"/>
@@ -5641,7 +5689,7 @@
       <c r="E393" s="8"/>
       <c r="F393" s="8"/>
     </row>
-    <row r="394" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="6"/>
       <c r="B394" s="14"/>
       <c r="C394" s="11"/>
@@ -5649,7 +5697,7 @@
       <c r="E394" s="8"/>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="6"/>
       <c r="B395" s="14"/>
       <c r="C395" s="11"/>
@@ -5657,7 +5705,7 @@
       <c r="E395" s="8"/>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="6"/>
       <c r="B396" s="14"/>
       <c r="C396" s="11"/>
@@ -5665,7 +5713,7 @@
       <c r="E396" s="8"/>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="6"/>
       <c r="B397" s="14"/>
       <c r="C397" s="11"/>
@@ -5673,7 +5721,7 @@
       <c r="E397" s="8"/>
       <c r="F397" s="8"/>
     </row>
-    <row r="398" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="6"/>
       <c r="B398" s="14"/>
       <c r="C398" s="11"/>
@@ -5681,7 +5729,7 @@
       <c r="E398" s="8"/>
       <c r="F398" s="8"/>
     </row>
-    <row r="399" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="6"/>
       <c r="B399" s="14"/>
       <c r="C399" s="11"/>
@@ -5689,7 +5737,7 @@
       <c r="E399" s="8"/>
       <c r="F399" s="8"/>
     </row>
-    <row r="400" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6"/>
       <c r="B400" s="14"/>
       <c r="C400" s="11"/>
@@ -5697,7 +5745,7 @@
       <c r="E400" s="8"/>
       <c r="F400" s="8"/>
     </row>
-    <row r="401" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="6"/>
       <c r="B401" s="14"/>
       <c r="C401" s="11"/>
@@ -5705,7 +5753,7 @@
       <c r="E401" s="8"/>
       <c r="F401" s="8"/>
     </row>
-    <row r="402" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="6"/>
       <c r="B402" s="14"/>
       <c r="C402" s="11"/>
@@ -5713,7 +5761,7 @@
       <c r="E402" s="8"/>
       <c r="F402" s="8"/>
     </row>
-    <row r="403" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="6"/>
       <c r="B403" s="14"/>
       <c r="C403" s="11"/>
@@ -5721,7 +5769,7 @@
       <c r="E403" s="8"/>
       <c r="F403" s="8"/>
     </row>
-    <row r="404" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="6"/>
       <c r="B404" s="14"/>
       <c r="C404" s="11"/>
@@ -5729,7 +5777,7 @@
       <c r="E404" s="8"/>
       <c r="F404" s="8"/>
     </row>
-    <row r="405" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="6"/>
       <c r="B405" s="14"/>
       <c r="C405" s="11"/>
@@ -5737,7 +5785,7 @@
       <c r="E405" s="8"/>
       <c r="F405" s="8"/>
     </row>
-    <row r="406" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="6"/>
       <c r="B406" s="14"/>
       <c r="C406" s="11"/>
@@ -5745,7 +5793,7 @@
       <c r="E406" s="8"/>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="6"/>
       <c r="B407" s="14"/>
       <c r="C407" s="11"/>
@@ -5753,7 +5801,7 @@
       <c r="E407" s="8"/>
       <c r="F407" s="8"/>
     </row>
-    <row r="408" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="6"/>
       <c r="B408" s="14"/>
       <c r="C408" s="11"/>
@@ -5761,7 +5809,7 @@
       <c r="E408" s="8"/>
       <c r="F408" s="8"/>
     </row>
-    <row r="409" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="6"/>
       <c r="B409" s="14"/>
       <c r="C409" s="11"/>
@@ -5769,7 +5817,7 @@
       <c r="E409" s="8"/>
       <c r="F409" s="8"/>
     </row>
-    <row r="410" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="6"/>
       <c r="B410" s="14"/>
       <c r="C410" s="11"/>
@@ -5777,7 +5825,7 @@
       <c r="E410" s="8"/>
       <c r="F410" s="8"/>
     </row>
-    <row r="411" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="6"/>
       <c r="B411" s="14"/>
       <c r="C411" s="11"/>
@@ -5785,7 +5833,7 @@
       <c r="E411" s="8"/>
       <c r="F411" s="8"/>
     </row>
-    <row r="412" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="6"/>
       <c r="B412" s="14"/>
       <c r="C412" s="11"/>
@@ -5793,7 +5841,7 @@
       <c r="E412" s="8"/>
       <c r="F412" s="8"/>
     </row>
-    <row r="413" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="6"/>
       <c r="B413" s="14"/>
       <c r="C413" s="11"/>
@@ -5801,7 +5849,7 @@
       <c r="E413" s="8"/>
       <c r="F413" s="8"/>
     </row>
-    <row r="414" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="6"/>
       <c r="B414" s="14"/>
       <c r="C414" s="11"/>
@@ -5809,7 +5857,7 @@
       <c r="E414" s="8"/>
       <c r="F414" s="8"/>
     </row>
-    <row r="415" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="6"/>
       <c r="B415" s="14"/>
       <c r="C415" s="11"/>
@@ -5817,7 +5865,7 @@
       <c r="E415" s="8"/>
       <c r="F415" s="8"/>
     </row>
-    <row r="416" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="6"/>
       <c r="B416" s="14"/>
       <c r="C416" s="11"/>
@@ -5825,7 +5873,7 @@
       <c r="E416" s="8"/>
       <c r="F416" s="8"/>
     </row>
-    <row r="417" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6"/>
       <c r="B417" s="14"/>
       <c r="C417" s="11"/>
@@ -5833,7 +5881,7 @@
       <c r="E417" s="8"/>
       <c r="F417" s="8"/>
     </row>
-    <row r="418" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="6"/>
       <c r="B418" s="14"/>
       <c r="C418" s="11"/>
@@ -5841,7 +5889,7 @@
       <c r="E418" s="8"/>
       <c r="F418" s="8"/>
     </row>
-    <row r="419" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="6"/>
       <c r="B419" s="14"/>
       <c r="C419" s="11"/>
@@ -5849,7 +5897,7 @@
       <c r="E419" s="8"/>
       <c r="F419" s="8"/>
     </row>
-    <row r="420" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="6"/>
       <c r="B420" s="14"/>
       <c r="C420" s="11"/>
@@ -5857,7 +5905,7 @@
       <c r="E420" s="8"/>
       <c r="F420" s="8"/>
     </row>
-    <row r="421" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="6"/>
       <c r="B421" s="14"/>
       <c r="C421" s="11"/>
@@ -5865,7 +5913,7 @@
       <c r="E421" s="8"/>
       <c r="F421" s="8"/>
     </row>
-    <row r="422" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="6"/>
       <c r="B422" s="14"/>
       <c r="C422" s="11"/>
@@ -5873,7 +5921,7 @@
       <c r="E422" s="8"/>
       <c r="F422" s="8"/>
     </row>
-    <row r="423" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="6"/>
       <c r="B423" s="14"/>
       <c r="C423" s="11"/>
@@ -5881,7 +5929,7 @@
       <c r="E423" s="8"/>
       <c r="F423" s="8"/>
     </row>
-    <row r="424" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="6"/>
       <c r="B424" s="14"/>
       <c r="C424" s="11"/>
@@ -5889,7 +5937,7 @@
       <c r="E424" s="8"/>
       <c r="F424" s="8"/>
     </row>
-    <row r="425" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="6"/>
       <c r="B425" s="14"/>
       <c r="C425" s="11"/>
@@ -5897,7 +5945,7 @@
       <c r="E425" s="8"/>
       <c r="F425" s="8"/>
     </row>
-    <row r="426" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="6"/>
       <c r="B426" s="14"/>
       <c r="C426" s="11"/>
@@ -5905,7 +5953,7 @@
       <c r="E426" s="8"/>
       <c r="F426" s="8"/>
     </row>
-    <row r="427" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="6"/>
       <c r="B427" s="14"/>
       <c r="C427" s="11"/>
@@ -5913,7 +5961,7 @@
       <c r="E427" s="8"/>
       <c r="F427" s="8"/>
     </row>
-    <row r="428" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="6"/>
       <c r="B428" s="14"/>
       <c r="C428" s="11"/>
@@ -5921,7 +5969,7 @@
       <c r="E428" s="8"/>
       <c r="F428" s="8"/>
     </row>
-    <row r="429" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="6"/>
       <c r="B429" s="14"/>
       <c r="C429" s="11"/>
@@ -5929,7 +5977,7 @@
       <c r="E429" s="8"/>
       <c r="F429" s="8"/>
     </row>
-    <row r="430" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="6"/>
       <c r="B430" s="14"/>
       <c r="C430" s="11"/>
@@ -5937,7 +5985,7 @@
       <c r="E430" s="8"/>
       <c r="F430" s="8"/>
     </row>
-    <row r="431" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="6"/>
       <c r="B431" s="14"/>
       <c r="C431" s="11"/>
@@ -5945,7 +5993,7 @@
       <c r="E431" s="8"/>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="6"/>
       <c r="B432" s="14"/>
       <c r="C432" s="11"/>
@@ -5953,7 +6001,7 @@
       <c r="E432" s="8"/>
       <c r="F432" s="8"/>
     </row>
-    <row r="433" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="6"/>
       <c r="B433" s="14"/>
       <c r="C433" s="11"/>
@@ -5961,7 +6009,7 @@
       <c r="E433" s="8"/>
       <c r="F433" s="8"/>
     </row>
-    <row r="434" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="6"/>
       <c r="B434" s="14"/>
       <c r="C434" s="11"/>
@@ -5969,7 +6017,7 @@
       <c r="E434" s="8"/>
       <c r="F434" s="8"/>
     </row>
-    <row r="435" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="6"/>
       <c r="B435" s="14"/>
       <c r="C435" s="11"/>
@@ -5977,7 +6025,7 @@
       <c r="E435" s="8"/>
       <c r="F435" s="8"/>
     </row>
-    <row r="436" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="6"/>
       <c r="B436" s="14"/>
       <c r="C436" s="11"/>
@@ -5985,7 +6033,7 @@
       <c r="E436" s="8"/>
       <c r="F436" s="8"/>
     </row>
-    <row r="437" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="6"/>
       <c r="B437" s="14"/>
       <c r="C437" s="11"/>
@@ -5993,7 +6041,7 @@
       <c r="E437" s="8"/>
       <c r="F437" s="8"/>
     </row>
-    <row r="438" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="6"/>
       <c r="B438" s="14"/>
       <c r="C438" s="11"/>
@@ -6001,7 +6049,7 @@
       <c r="E438" s="8"/>
       <c r="F438" s="8"/>
     </row>
-    <row r="439" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="6"/>
       <c r="B439" s="14"/>
       <c r="C439" s="11"/>
@@ -6009,7 +6057,7 @@
       <c r="E439" s="8"/>
       <c r="F439" s="8"/>
     </row>
-    <row r="440" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="6"/>
       <c r="B440" s="14"/>
       <c r="C440" s="11"/>
@@ -6017,7 +6065,7 @@
       <c r="E440" s="8"/>
       <c r="F440" s="8"/>
     </row>
-    <row r="441" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="6"/>
       <c r="B441" s="14"/>
       <c r="C441" s="11"/>
@@ -6025,7 +6073,7 @@
       <c r="E441" s="8"/>
       <c r="F441" s="8"/>
     </row>
-    <row r="442" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="6"/>
       <c r="B442" s="14"/>
       <c r="C442" s="11"/>
@@ -6033,7 +6081,7 @@
       <c r="E442" s="8"/>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="6"/>
       <c r="B443" s="14"/>
       <c r="C443" s="11"/>
@@ -6041,7 +6089,7 @@
       <c r="E443" s="8"/>
       <c r="F443" s="8"/>
     </row>
-    <row r="444" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="6"/>
       <c r="B444" s="14"/>
       <c r="C444" s="11"/>
@@ -6049,7 +6097,7 @@
       <c r="E444" s="8"/>
       <c r="F444" s="8"/>
     </row>
-    <row r="445" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="6"/>
       <c r="B445" s="14"/>
       <c r="C445" s="11"/>
@@ -6057,7 +6105,7 @@
       <c r="E445" s="8"/>
       <c r="F445" s="8"/>
     </row>
-    <row r="446" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="6"/>
       <c r="B446" s="14"/>
       <c r="C446" s="11"/>
@@ -6065,7 +6113,7 @@
       <c r="E446" s="8"/>
       <c r="F446" s="8"/>
     </row>
-    <row r="447" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="6"/>
       <c r="B447" s="14"/>
       <c r="C447" s="11"/>
@@ -6073,7 +6121,7 @@
       <c r="E447" s="8"/>
       <c r="F447" s="8"/>
     </row>
-    <row r="448" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="6"/>
       <c r="B448" s="14"/>
       <c r="C448" s="11"/>
@@ -6081,7 +6129,7 @@
       <c r="E448" s="8"/>
       <c r="F448" s="8"/>
     </row>
-    <row r="449" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="6"/>
       <c r="B449" s="14"/>
       <c r="C449" s="11"/>
@@ -6089,7 +6137,7 @@
       <c r="E449" s="8"/>
       <c r="F449" s="8"/>
     </row>
-    <row r="450" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="6"/>
       <c r="B450" s="14"/>
       <c r="C450" s="11"/>
@@ -6097,7 +6145,7 @@
       <c r="E450" s="8"/>
       <c r="F450" s="8"/>
     </row>
-    <row r="451" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="6"/>
       <c r="B451" s="14"/>
       <c r="C451" s="11"/>
@@ -6105,7 +6153,7 @@
       <c r="E451" s="8"/>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="6"/>
       <c r="B452" s="14"/>
       <c r="C452" s="11"/>
@@ -6113,7 +6161,7 @@
       <c r="E452" s="8"/>
       <c r="F452" s="8"/>
     </row>
-    <row r="453" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="6"/>
       <c r="B453" s="14"/>
       <c r="C453" s="11"/>
@@ -6121,7 +6169,7 @@
       <c r="E453" s="8"/>
       <c r="F453" s="8"/>
     </row>
-    <row r="454" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="6"/>
       <c r="B454" s="14"/>
       <c r="C454" s="11"/>
@@ -6129,7 +6177,7 @@
       <c r="E454" s="8"/>
       <c r="F454" s="8"/>
     </row>
-    <row r="455" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="6"/>
       <c r="B455" s="14"/>
       <c r="C455" s="11"/>
@@ -6137,7 +6185,7 @@
       <c r="E455" s="8"/>
       <c r="F455" s="8"/>
     </row>
-    <row r="456" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="6"/>
       <c r="B456" s="14"/>
       <c r="C456" s="11"/>
@@ -6145,7 +6193,7 @@
       <c r="E456" s="8"/>
       <c r="F456" s="8"/>
     </row>
-    <row r="457" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="6"/>
       <c r="B457" s="14"/>
       <c r="C457" s="11"/>
@@ -6153,7 +6201,7 @@
       <c r="E457" s="8"/>
       <c r="F457" s="8"/>
     </row>
-    <row r="458" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="6"/>
       <c r="B458" s="14"/>
       <c r="C458" s="11"/>
@@ -6161,7 +6209,7 @@
       <c r="E458" s="8"/>
       <c r="F458" s="8"/>
     </row>
-    <row r="459" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="6"/>
       <c r="B459" s="14"/>
       <c r="C459" s="11"/>
@@ -6169,7 +6217,7 @@
       <c r="E459" s="8"/>
       <c r="F459" s="8"/>
     </row>
-    <row r="460" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="6"/>
       <c r="B460" s="14"/>
       <c r="C460" s="11"/>
@@ -6177,7 +6225,7 @@
       <c r="E460" s="8"/>
       <c r="F460" s="8"/>
     </row>
-    <row r="461" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="6"/>
       <c r="B461" s="14"/>
       <c r="C461" s="11"/>
@@ -6185,7 +6233,7 @@
       <c r="E461" s="8"/>
       <c r="F461" s="8"/>
     </row>
-    <row r="462" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="6"/>
       <c r="B462" s="14"/>
       <c r="C462" s="11"/>
@@ -6193,7 +6241,7 @@
       <c r="E462" s="8"/>
       <c r="F462" s="8"/>
     </row>
-    <row r="463" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="6"/>
       <c r="B463" s="14"/>
       <c r="C463" s="11"/>
@@ -6201,7 +6249,7 @@
       <c r="E463" s="8"/>
       <c r="F463" s="8"/>
     </row>
-    <row r="464" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="6"/>
       <c r="B464" s="14"/>
       <c r="C464" s="11"/>
@@ -6209,7 +6257,7 @@
       <c r="E464" s="8"/>
       <c r="F464" s="8"/>
     </row>
-    <row r="465" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="6"/>
       <c r="B465" s="14"/>
       <c r="C465" s="11"/>
@@ -6217,7 +6265,7 @@
       <c r="E465" s="8"/>
       <c r="F465" s="8"/>
     </row>
-    <row r="466" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="6"/>
       <c r="B466" s="14"/>
       <c r="C466" s="11"/>
@@ -6225,7 +6273,7 @@
       <c r="E466" s="8"/>
       <c r="F466" s="8"/>
     </row>
-    <row r="467" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="6"/>
       <c r="B467" s="14"/>
       <c r="C467" s="11"/>
@@ -6233,7 +6281,7 @@
       <c r="E467" s="8"/>
       <c r="F467" s="8"/>
     </row>
-    <row r="468" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="6"/>
       <c r="B468" s="14"/>
       <c r="C468" s="11"/>
@@ -6241,7 +6289,7 @@
       <c r="E468" s="8"/>
       <c r="F468" s="8"/>
     </row>
-    <row r="469" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="6"/>
       <c r="B469" s="14"/>
       <c r="C469" s="11"/>
@@ -6249,7 +6297,7 @@
       <c r="E469" s="8"/>
       <c r="F469" s="8"/>
     </row>
-    <row r="470" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="6"/>
       <c r="B470" s="14"/>
       <c r="C470" s="11"/>
@@ -6257,7 +6305,7 @@
       <c r="E470" s="8"/>
       <c r="F470" s="8"/>
     </row>
-    <row r="471" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="6"/>
       <c r="B471" s="14"/>
       <c r="C471" s="11"/>
@@ -6265,7 +6313,7 @@
       <c r="E471" s="8"/>
       <c r="F471" s="8"/>
     </row>
-    <row r="472" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="6"/>
       <c r="B472" s="14"/>
       <c r="C472" s="11"/>
@@ -6273,7 +6321,7 @@
       <c r="E472" s="8"/>
       <c r="F472" s="8"/>
     </row>
-    <row r="473" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="6"/>
       <c r="B473" s="14"/>
       <c r="C473" s="11"/>
@@ -6281,7 +6329,7 @@
       <c r="E473" s="8"/>
       <c r="F473" s="8"/>
     </row>
-    <row r="474" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="6"/>
       <c r="B474" s="14"/>
       <c r="C474" s="11"/>
@@ -6289,7 +6337,7 @@
       <c r="E474" s="8"/>
       <c r="F474" s="8"/>
     </row>
-    <row r="475" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="6"/>
       <c r="B475" s="14"/>
       <c r="C475" s="11"/>
@@ -6297,7 +6345,7 @@
       <c r="E475" s="8"/>
       <c r="F475" s="8"/>
     </row>
-    <row r="476" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6"/>
       <c r="B476" s="14"/>
       <c r="C476" s="11"/>
@@ -6305,7 +6353,7 @@
       <c r="E476" s="8"/>
       <c r="F476" s="8"/>
     </row>
-    <row r="477" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="6"/>
       <c r="B477" s="14"/>
       <c r="C477" s="11"/>
@@ -6313,7 +6361,7 @@
       <c r="E477" s="8"/>
       <c r="F477" s="8"/>
     </row>
-    <row r="478" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="6"/>
       <c r="B478" s="14"/>
       <c r="C478" s="11"/>
@@ -6321,7 +6369,7 @@
       <c r="E478" s="8"/>
       <c r="F478" s="8"/>
     </row>
-    <row r="479" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="6"/>
       <c r="B479" s="14"/>
       <c r="C479" s="11"/>
@@ -6329,7 +6377,7 @@
       <c r="E479" s="8"/>
       <c r="F479" s="8"/>
     </row>
-    <row r="480" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="6"/>
       <c r="B480" s="14"/>
       <c r="C480" s="11"/>
@@ -6337,7 +6385,7 @@
       <c r="E480" s="8"/>
       <c r="F480" s="8"/>
     </row>
-    <row r="481" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="6"/>
       <c r="B481" s="14"/>
       <c r="C481" s="11"/>
@@ -6345,7 +6393,7 @@
       <c r="E481" s="8"/>
       <c r="F481" s="8"/>
     </row>
-    <row r="482" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="6"/>
       <c r="B482" s="14"/>
       <c r="C482" s="11"/>
@@ -6353,7 +6401,7 @@
       <c r="E482" s="8"/>
       <c r="F482" s="8"/>
     </row>
-    <row r="483" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="6"/>
       <c r="B483" s="14"/>
       <c r="C483" s="11"/>
@@ -6361,7 +6409,7 @@
       <c r="E483" s="8"/>
       <c r="F483" s="8"/>
     </row>
-    <row r="484" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="6"/>
       <c r="B484" s="14"/>
       <c r="C484" s="11"/>
@@ -6369,7 +6417,7 @@
       <c r="E484" s="8"/>
       <c r="F484" s="8"/>
     </row>
-    <row r="485" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="6"/>
       <c r="B485" s="14"/>
       <c r="C485" s="11"/>
@@ -6377,7 +6425,7 @@
       <c r="E485" s="8"/>
       <c r="F485" s="8"/>
     </row>
-    <row r="486" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="6"/>
       <c r="B486" s="14"/>
       <c r="C486" s="11"/>
@@ -6385,7 +6433,7 @@
       <c r="E486" s="8"/>
       <c r="F486" s="8"/>
     </row>
-    <row r="487" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="6"/>
       <c r="B487" s="14"/>
       <c r="C487" s="11"/>
@@ -6393,7 +6441,7 @@
       <c r="E487" s="8"/>
       <c r="F487" s="8"/>
     </row>
-    <row r="488" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="6"/>
       <c r="B488" s="14"/>
       <c r="C488" s="11"/>
@@ -6401,7 +6449,7 @@
       <c r="E488" s="8"/>
       <c r="F488" s="8"/>
     </row>
-    <row r="489" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="6"/>
       <c r="B489" s="14"/>
       <c r="C489" s="11"/>
@@ -6409,7 +6457,7 @@
       <c r="E489" s="8"/>
       <c r="F489" s="8"/>
     </row>
-    <row r="490" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="6"/>
       <c r="B490" s="14"/>
       <c r="C490" s="11"/>
@@ -6417,7 +6465,7 @@
       <c r="E490" s="8"/>
       <c r="F490" s="8"/>
     </row>
-    <row r="491" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="6"/>
       <c r="B491" s="14"/>
       <c r="C491" s="11"/>
@@ -6425,7 +6473,7 @@
       <c r="E491" s="8"/>
       <c r="F491" s="8"/>
     </row>
-    <row r="492" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="6"/>
       <c r="B492" s="14"/>
       <c r="C492" s="11"/>
@@ -6433,7 +6481,7 @@
       <c r="E492" s="8"/>
       <c r="F492" s="8"/>
     </row>
-    <row r="493" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="6"/>
       <c r="B493" s="14"/>
       <c r="C493" s="11"/>
@@ -6441,7 +6489,7 @@
       <c r="E493" s="8"/>
       <c r="F493" s="8"/>
     </row>
-    <row r="494" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="6"/>
       <c r="B494" s="14"/>
       <c r="C494" s="11"/>
@@ -6449,7 +6497,7 @@
       <c r="E494" s="8"/>
       <c r="F494" s="8"/>
     </row>
-    <row r="495" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="6"/>
       <c r="B495" s="14"/>
       <c r="C495" s="11"/>
@@ -6457,7 +6505,7 @@
       <c r="E495" s="8"/>
       <c r="F495" s="8"/>
     </row>
-    <row r="496" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="6"/>
       <c r="B496" s="14"/>
       <c r="C496" s="11"/>
@@ -6465,7 +6513,7 @@
       <c r="E496" s="8"/>
       <c r="F496" s="8"/>
     </row>
-    <row r="497" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="6"/>
       <c r="B497" s="14"/>
       <c r="C497" s="11"/>
@@ -6473,7 +6521,7 @@
       <c r="E497" s="8"/>
       <c r="F497" s="8"/>
     </row>
-    <row r="498" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="6"/>
       <c r="B498" s="14"/>
       <c r="C498" s="11"/>
@@ -6481,7 +6529,7 @@
       <c r="E498" s="8"/>
       <c r="F498" s="8"/>
     </row>
-    <row r="499" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="6"/>
       <c r="B499" s="14"/>
       <c r="C499" s="11"/>
@@ -6489,7 +6537,7 @@
       <c r="E499" s="8"/>
       <c r="F499" s="8"/>
     </row>
-    <row r="500" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="6"/>
       <c r="B500" s="14"/>
       <c r="C500" s="11"/>
@@ -6497,7 +6545,7 @@
       <c r="E500" s="8"/>
       <c r="F500" s="8"/>
     </row>
-    <row r="501" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A501" s="6"/>
       <c r="B501" s="14"/>
       <c r="C501" s="11"/>
@@ -6505,7 +6553,7 @@
       <c r="E501" s="8"/>
       <c r="F501" s="8"/>
     </row>
-    <row r="502" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A502" s="6"/>
       <c r="B502" s="14"/>
       <c r="C502" s="11"/>
@@ -6513,7 +6561,7 @@
       <c r="E502" s="8"/>
       <c r="F502" s="8"/>
     </row>
-    <row r="503" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A503" s="6"/>
       <c r="B503" s="14"/>
       <c r="C503" s="11"/>
@@ -6558,13 +6606,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC8CEF3-AF3E-4D54-8188-1302D62F0F60}">
   <dimension ref="A1:B500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.25" style="12" customWidth="1"/>
+    <col min="1" max="1" width="24.8984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.19921875" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
@@ -6572,7 +6620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
@@ -6581,7 +6629,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>8</v>
       </c>
@@ -6590,16 +6638,16 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>11.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>10</v>
       </c>
@@ -6608,7 +6656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>11</v>
       </c>
@@ -6617,7 +6665,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>6</v>
       </c>
@@ -6626,7 +6674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>12</v>
       </c>
@@ -6635,1976 +6683,1976 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="11"/>
     </row>
-    <row r="12" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="11"/>
     </row>
-    <row r="13" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="11"/>
     </row>
-    <row r="14" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="11"/>
     </row>
-    <row r="15" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="11"/>
     </row>
-    <row r="16" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="11"/>
     </row>
-    <row r="17" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="11"/>
     </row>
-    <row r="18" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="11"/>
     </row>
-    <row r="19" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="11"/>
     </row>
-    <row r="20" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="11"/>
     </row>
-    <row r="21" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="11"/>
     </row>
-    <row r="22" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="11"/>
     </row>
-    <row r="23" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="11"/>
     </row>
-    <row r="24" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="11"/>
     </row>
-    <row r="25" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="11"/>
     </row>
-    <row r="27" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="11"/>
     </row>
-    <row r="28" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="11"/>
     </row>
-    <row r="29" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="11"/>
     </row>
-    <row r="30" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="11"/>
     </row>
-    <row r="31" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="11"/>
     </row>
-    <row r="32" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="11"/>
     </row>
-    <row r="33" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="11"/>
     </row>
-    <row r="34" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="11"/>
     </row>
-    <row r="35" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="11"/>
     </row>
-    <row r="36" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="11"/>
     </row>
-    <row r="37" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="11"/>
     </row>
-    <row r="38" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="11"/>
     </row>
-    <row r="39" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="11"/>
     </row>
-    <row r="40" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" s="11"/>
     </row>
-    <row r="41" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="11"/>
     </row>
-    <row r="42" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="11"/>
     </row>
-    <row r="43" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="11"/>
     </row>
-    <row r="44" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="11"/>
     </row>
-    <row r="45" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="11"/>
     </row>
-    <row r="46" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="B46" s="11"/>
     </row>
-    <row r="47" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="11"/>
     </row>
-    <row r="48" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="11"/>
     </row>
-    <row r="49" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="11"/>
     </row>
-    <row r="50" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="11"/>
     </row>
-    <row r="51" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="11"/>
     </row>
-    <row r="52" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="11"/>
     </row>
-    <row r="53" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="11"/>
     </row>
-    <row r="54" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="11"/>
     </row>
-    <row r="55" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="11"/>
     </row>
-    <row r="56" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="11"/>
     </row>
-    <row r="57" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="11"/>
     </row>
-    <row r="58" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="11"/>
     </row>
-    <row r="59" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="11"/>
     </row>
-    <row r="60" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="11"/>
     </row>
-    <row r="61" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="11"/>
     </row>
-    <row r="62" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="11"/>
     </row>
-    <row r="63" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="11"/>
     </row>
-    <row r="64" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="11"/>
     </row>
-    <row r="65" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="11"/>
     </row>
-    <row r="66" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="11"/>
     </row>
-    <row r="67" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="11"/>
     </row>
-    <row r="68" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="11"/>
     </row>
-    <row r="69" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="11"/>
     </row>
-    <row r="70" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="11"/>
     </row>
-    <row r="71" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="11"/>
     </row>
-    <row r="72" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="11"/>
     </row>
-    <row r="73" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="11"/>
     </row>
-    <row r="74" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="11"/>
     </row>
-    <row r="75" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="11"/>
     </row>
-    <row r="76" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="11"/>
     </row>
-    <row r="77" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="11"/>
     </row>
-    <row r="78" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="11"/>
     </row>
-    <row r="79" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="11"/>
     </row>
-    <row r="80" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="11"/>
     </row>
-    <row r="81" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="11"/>
     </row>
-    <row r="82" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="11"/>
     </row>
-    <row r="83" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="11"/>
     </row>
-    <row r="84" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="11"/>
     </row>
-    <row r="85" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="11"/>
     </row>
-    <row r="86" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="11"/>
     </row>
-    <row r="87" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="11"/>
     </row>
-    <row r="88" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="11"/>
     </row>
-    <row r="89" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="11"/>
     </row>
-    <row r="90" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="11"/>
     </row>
-    <row r="91" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="11"/>
     </row>
-    <row r="92" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="11"/>
     </row>
-    <row r="93" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="11"/>
     </row>
-    <row r="94" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="11"/>
     </row>
-    <row r="95" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="11"/>
     </row>
-    <row r="96" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="11"/>
     </row>
-    <row r="97" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="11"/>
     </row>
-    <row r="98" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="11"/>
     </row>
-    <row r="99" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="11"/>
     </row>
-    <row r="100" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
       <c r="B100" s="11"/>
     </row>
-    <row r="101" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="11"/>
     </row>
-    <row r="102" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="11"/>
     </row>
-    <row r="103" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="11"/>
     </row>
-    <row r="104" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
       <c r="B104" s="11"/>
     </row>
-    <row r="105" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="B105" s="11"/>
     </row>
-    <row r="106" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
       <c r="B106" s="11"/>
     </row>
-    <row r="107" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
       <c r="B107" s="11"/>
     </row>
-    <row r="108" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
       <c r="B108" s="11"/>
     </row>
-    <row r="109" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="11"/>
     </row>
-    <row r="110" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="11"/>
     </row>
-    <row r="111" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="11"/>
     </row>
-    <row r="112" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
       <c r="B112" s="11"/>
     </row>
-    <row r="113" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="B113" s="11"/>
     </row>
-    <row r="114" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
       <c r="B114" s="11"/>
     </row>
-    <row r="115" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="11"/>
     </row>
-    <row r="116" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
       <c r="B116" s="11"/>
     </row>
-    <row r="117" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="B117" s="11"/>
     </row>
-    <row r="118" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="B118" s="11"/>
     </row>
-    <row r="119" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="11"/>
     </row>
-    <row r="120" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
       <c r="B120" s="11"/>
     </row>
-    <row r="121" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="11"/>
     </row>
-    <row r="122" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="B122" s="11"/>
     </row>
-    <row r="123" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="11"/>
     </row>
-    <row r="124" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
       <c r="B124" s="11"/>
     </row>
-    <row r="125" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="11"/>
     </row>
-    <row r="126" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="B126" s="11"/>
     </row>
-    <row r="127" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="11"/>
     </row>
-    <row r="128" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
       <c r="B128" s="11"/>
     </row>
-    <row r="129" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="B129" s="11"/>
     </row>
-    <row r="130" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
       <c r="B130" s="11"/>
     </row>
-    <row r="131" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
       <c r="B131" s="11"/>
     </row>
-    <row r="132" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6"/>
       <c r="B132" s="11"/>
     </row>
-    <row r="133" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="B133" s="11"/>
     </row>
-    <row r="134" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
       <c r="B134" s="11"/>
     </row>
-    <row r="135" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
       <c r="B135" s="11"/>
     </row>
-    <row r="136" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
       <c r="B136" s="11"/>
     </row>
-    <row r="137" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
       <c r="B137" s="11"/>
     </row>
-    <row r="138" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
       <c r="B138" s="11"/>
     </row>
-    <row r="139" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
       <c r="B139" s="11"/>
     </row>
-    <row r="140" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
       <c r="B140" s="11"/>
     </row>
-    <row r="141" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
       <c r="B141" s="11"/>
     </row>
-    <row r="142" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
       <c r="B142" s="11"/>
     </row>
-    <row r="143" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
       <c r="B143" s="11"/>
     </row>
-    <row r="144" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6"/>
       <c r="B144" s="11"/>
     </row>
-    <row r="145" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
       <c r="B145" s="11"/>
     </row>
-    <row r="146" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
       <c r="B146" s="11"/>
     </row>
-    <row r="147" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
       <c r="B147" s="11"/>
     </row>
-    <row r="148" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
       <c r="B148" s="11"/>
     </row>
-    <row r="149" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
       <c r="B149" s="11"/>
     </row>
-    <row r="150" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
       <c r="B150" s="11"/>
     </row>
-    <row r="151" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
       <c r="B151" s="11"/>
     </row>
-    <row r="152" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6"/>
       <c r="B152" s="11"/>
     </row>
-    <row r="153" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
       <c r="B153" s="11"/>
     </row>
-    <row r="154" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="B154" s="11"/>
     </row>
-    <row r="155" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="B155" s="11"/>
     </row>
-    <row r="156" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
       <c r="B156" s="11"/>
     </row>
-    <row r="157" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
       <c r="B157" s="11"/>
     </row>
-    <row r="158" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
       <c r="B158" s="11"/>
     </row>
-    <row r="159" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
       <c r="B159" s="11"/>
     </row>
-    <row r="160" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6"/>
       <c r="B160" s="11"/>
     </row>
-    <row r="161" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
       <c r="B161" s="11"/>
     </row>
-    <row r="162" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
       <c r="B162" s="11"/>
     </row>
-    <row r="163" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
       <c r="B163" s="11"/>
     </row>
-    <row r="164" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6"/>
       <c r="B164" s="11"/>
     </row>
-    <row r="165" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
       <c r="B165" s="11"/>
     </row>
-    <row r="166" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
       <c r="B166" s="11"/>
     </row>
-    <row r="167" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6"/>
       <c r="B167" s="11"/>
     </row>
-    <row r="168" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
       <c r="B168" s="11"/>
     </row>
-    <row r="169" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6"/>
       <c r="B169" s="11"/>
     </row>
-    <row r="170" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
       <c r="B170" s="11"/>
     </row>
-    <row r="171" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="B171" s="11"/>
     </row>
-    <row r="172" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
       <c r="B172" s="11"/>
     </row>
-    <row r="173" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="B173" s="11"/>
     </row>
-    <row r="174" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="B174" s="11"/>
     </row>
-    <row r="175" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
       <c r="B175" s="11"/>
     </row>
-    <row r="176" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
       <c r="B176" s="11"/>
     </row>
-    <row r="177" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="B177" s="11"/>
     </row>
-    <row r="178" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="B178" s="11"/>
     </row>
-    <row r="179" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
       <c r="B179" s="11"/>
     </row>
-    <row r="180" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
       <c r="B180" s="11"/>
     </row>
-    <row r="181" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
       <c r="B181" s="11"/>
     </row>
-    <row r="182" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
       <c r="B182" s="11"/>
     </row>
-    <row r="183" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6"/>
       <c r="B183" s="11"/>
     </row>
-    <row r="184" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
       <c r="B184" s="11"/>
     </row>
-    <row r="185" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
       <c r="B185" s="11"/>
     </row>
-    <row r="186" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
       <c r="B186" s="11"/>
     </row>
-    <row r="187" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="B187" s="11"/>
     </row>
-    <row r="188" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
       <c r="B188" s="11"/>
     </row>
-    <row r="189" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
       <c r="B189" s="11"/>
     </row>
-    <row r="190" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6"/>
       <c r="B190" s="11"/>
     </row>
-    <row r="191" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
       <c r="B191" s="11"/>
     </row>
-    <row r="192" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
       <c r="B192" s="11"/>
     </row>
-    <row r="193" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
       <c r="B193" s="11"/>
     </row>
-    <row r="194" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6"/>
       <c r="B194" s="11"/>
     </row>
-    <row r="195" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
       <c r="B195" s="11"/>
     </row>
-    <row r="196" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
       <c r="B196" s="11"/>
     </row>
-    <row r="197" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
       <c r="B197" s="11"/>
     </row>
-    <row r="198" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6"/>
       <c r="B198" s="11"/>
     </row>
-    <row r="199" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
       <c r="B199" s="11"/>
     </row>
-    <row r="200" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
       <c r="B200" s="11"/>
     </row>
-    <row r="201" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
       <c r="B201" s="11"/>
     </row>
-    <row r="202" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="B202" s="11"/>
     </row>
-    <row r="203" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
       <c r="B203" s="11"/>
     </row>
-    <row r="204" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="B204" s="11"/>
     </row>
-    <row r="205" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
       <c r="B205" s="11"/>
     </row>
-    <row r="206" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="B206" s="11"/>
     </row>
-    <row r="207" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="B207" s="11"/>
     </row>
-    <row r="208" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="B208" s="11"/>
     </row>
-    <row r="209" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6"/>
       <c r="B209" s="11"/>
     </row>
-    <row r="210" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
       <c r="B210" s="11"/>
     </row>
-    <row r="211" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
       <c r="B211" s="11"/>
     </row>
-    <row r="212" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
       <c r="B212" s="11"/>
     </row>
-    <row r="213" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6"/>
       <c r="B213" s="11"/>
     </row>
-    <row r="214" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
       <c r="B214" s="11"/>
     </row>
-    <row r="215" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
       <c r="B215" s="11"/>
     </row>
-    <row r="216" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
       <c r="B216" s="11"/>
     </row>
-    <row r="217" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6"/>
       <c r="B217" s="11"/>
     </row>
-    <row r="218" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
       <c r="B218" s="11"/>
     </row>
-    <row r="219" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
       <c r="B219" s="11"/>
     </row>
-    <row r="220" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
       <c r="B220" s="11"/>
     </row>
-    <row r="221" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6"/>
       <c r="B221" s="11"/>
     </row>
-    <row r="222" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
       <c r="B222" s="11"/>
     </row>
-    <row r="223" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
       <c r="B223" s="11"/>
     </row>
-    <row r="224" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
       <c r="B224" s="11"/>
     </row>
-    <row r="225" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
       <c r="B225" s="11"/>
     </row>
-    <row r="226" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6"/>
       <c r="B226" s="11"/>
     </row>
-    <row r="227" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
       <c r="B227" s="11"/>
     </row>
-    <row r="228" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
       <c r="B228" s="11"/>
     </row>
-    <row r="229" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
       <c r="B229" s="11"/>
     </row>
-    <row r="230" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
       <c r="B230" s="11"/>
     </row>
-    <row r="231" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
       <c r="B231" s="11"/>
     </row>
-    <row r="232" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6"/>
       <c r="B232" s="11"/>
     </row>
-    <row r="233" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
       <c r="B233" s="11"/>
     </row>
-    <row r="234" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
       <c r="B234" s="11"/>
     </row>
-    <row r="235" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6"/>
       <c r="B235" s="11"/>
     </row>
-    <row r="236" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
       <c r="B236" s="11"/>
     </row>
-    <row r="237" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
       <c r="B237" s="11"/>
     </row>
-    <row r="238" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
       <c r="B238" s="11"/>
     </row>
-    <row r="239" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6"/>
       <c r="B239" s="11"/>
     </row>
-    <row r="240" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6"/>
       <c r="B240" s="11"/>
     </row>
-    <row r="241" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
       <c r="B241" s="11"/>
     </row>
-    <row r="242" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="B242" s="11"/>
     </row>
-    <row r="243" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
       <c r="B243" s="11"/>
     </row>
-    <row r="244" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
       <c r="B244" s="11"/>
     </row>
-    <row r="245" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6"/>
       <c r="B245" s="11"/>
     </row>
-    <row r="246" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
       <c r="B246" s="11"/>
     </row>
-    <row r="247" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
       <c r="B247" s="11"/>
     </row>
-    <row r="248" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
       <c r="B248" s="11"/>
     </row>
-    <row r="249" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6"/>
       <c r="B249" s="11"/>
     </row>
-    <row r="250" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
       <c r="B250" s="11"/>
     </row>
-    <row r="251" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6"/>
       <c r="B251" s="11"/>
     </row>
-    <row r="252" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
       <c r="B252" s="11"/>
     </row>
-    <row r="253" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
       <c r="B253" s="11"/>
     </row>
-    <row r="254" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6"/>
       <c r="B254" s="11"/>
     </row>
-    <row r="255" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6"/>
       <c r="B255" s="11"/>
     </row>
-    <row r="256" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
       <c r="B256" s="11"/>
     </row>
-    <row r="257" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6"/>
       <c r="B257" s="11"/>
     </row>
-    <row r="258" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
       <c r="B258" s="11"/>
     </row>
-    <row r="259" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6"/>
       <c r="B259" s="11"/>
     </row>
-    <row r="260" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6"/>
       <c r="B260" s="11"/>
     </row>
-    <row r="261" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6"/>
       <c r="B261" s="11"/>
     </row>
-    <row r="262" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6"/>
       <c r="B262" s="11"/>
     </row>
-    <row r="263" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6"/>
       <c r="B263" s="11"/>
     </row>
-    <row r="264" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
       <c r="B264" s="11"/>
     </row>
-    <row r="265" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
       <c r="B265" s="11"/>
     </row>
-    <row r="266" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
       <c r="B266" s="11"/>
     </row>
-    <row r="267" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6"/>
       <c r="B267" s="11"/>
     </row>
-    <row r="268" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
       <c r="B268" s="11"/>
     </row>
-    <row r="269" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
       <c r="B269" s="11"/>
     </row>
-    <row r="270" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6"/>
       <c r="B270" s="11"/>
     </row>
-    <row r="271" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6"/>
       <c r="B271" s="11"/>
     </row>
-    <row r="272" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
       <c r="B272" s="11"/>
     </row>
-    <row r="273" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6"/>
       <c r="B273" s="11"/>
     </row>
-    <row r="274" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
       <c r="B274" s="11"/>
     </row>
-    <row r="275" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
       <c r="B275" s="11"/>
     </row>
-    <row r="276" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
       <c r="B276" s="11"/>
     </row>
-    <row r="277" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6"/>
       <c r="B277" s="11"/>
     </row>
-    <row r="278" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
       <c r="B278" s="11"/>
     </row>
-    <row r="279" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
       <c r="B279" s="11"/>
     </row>
-    <row r="280" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
       <c r="B280" s="11"/>
     </row>
-    <row r="281" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6"/>
       <c r="B281" s="11"/>
     </row>
-    <row r="282" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6"/>
       <c r="B282" s="11"/>
     </row>
-    <row r="283" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
       <c r="B283" s="11"/>
     </row>
-    <row r="284" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
       <c r="B284" s="11"/>
     </row>
-    <row r="285" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6"/>
       <c r="B285" s="11"/>
     </row>
-    <row r="286" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
       <c r="B286" s="11"/>
     </row>
-    <row r="287" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6"/>
       <c r="B287" s="11"/>
     </row>
-    <row r="288" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
       <c r="B288" s="11"/>
     </row>
-    <row r="289" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6"/>
       <c r="B289" s="11"/>
     </row>
-    <row r="290" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
       <c r="B290" s="11"/>
     </row>
-    <row r="291" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6"/>
       <c r="B291" s="11"/>
     </row>
-    <row r="292" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6"/>
       <c r="B292" s="11"/>
     </row>
-    <row r="293" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
       <c r="B293" s="11"/>
     </row>
-    <row r="294" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
       <c r="B294" s="11"/>
     </row>
-    <row r="295" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6"/>
       <c r="B295" s="11"/>
     </row>
-    <row r="296" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
       <c r="B296" s="11"/>
     </row>
-    <row r="297" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
       <c r="B297" s="11"/>
     </row>
-    <row r="298" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
       <c r="B298" s="11"/>
     </row>
-    <row r="299" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6"/>
       <c r="B299" s="11"/>
     </row>
-    <row r="300" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6"/>
       <c r="B300" s="11"/>
     </row>
-    <row r="301" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6"/>
       <c r="B301" s="11"/>
     </row>
-    <row r="302" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6"/>
       <c r="B302" s="11"/>
     </row>
-    <row r="303" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6"/>
       <c r="B303" s="11"/>
     </row>
-    <row r="304" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6"/>
       <c r="B304" s="11"/>
     </row>
-    <row r="305" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6"/>
       <c r="B305" s="11"/>
     </row>
-    <row r="306" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6"/>
       <c r="B306" s="11"/>
     </row>
-    <row r="307" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6"/>
       <c r="B307" s="11"/>
     </row>
-    <row r="308" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6"/>
       <c r="B308" s="11"/>
     </row>
-    <row r="309" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="6"/>
       <c r="B309" s="11"/>
     </row>
-    <row r="310" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6"/>
       <c r="B310" s="11"/>
     </row>
-    <row r="311" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="6"/>
       <c r="B311" s="11"/>
     </row>
-    <row r="312" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6"/>
       <c r="B312" s="11"/>
     </row>
-    <row r="313" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="6"/>
       <c r="B313" s="11"/>
     </row>
-    <row r="314" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6"/>
       <c r="B314" s="11"/>
     </row>
-    <row r="315" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="6"/>
       <c r="B315" s="11"/>
     </row>
-    <row r="316" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="6"/>
       <c r="B316" s="11"/>
     </row>
-    <row r="317" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="6"/>
       <c r="B317" s="11"/>
     </row>
-    <row r="318" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6"/>
       <c r="B318" s="11"/>
     </row>
-    <row r="319" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="6"/>
       <c r="B319" s="11"/>
     </row>
-    <row r="320" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="6"/>
       <c r="B320" s="11"/>
     </row>
-    <row r="321" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6"/>
       <c r="B321" s="11"/>
     </row>
-    <row r="322" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="6"/>
       <c r="B322" s="11"/>
     </row>
-    <row r="323" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="6"/>
       <c r="B323" s="11"/>
     </row>
-    <row r="324" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6"/>
       <c r="B324" s="11"/>
     </row>
-    <row r="325" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="6"/>
       <c r="B325" s="11"/>
     </row>
-    <row r="326" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="6"/>
       <c r="B326" s="11"/>
     </row>
-    <row r="327" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="6"/>
       <c r="B327" s="11"/>
     </row>
-    <row r="328" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="6"/>
       <c r="B328" s="11"/>
     </row>
-    <row r="329" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="6"/>
       <c r="B329" s="11"/>
     </row>
-    <row r="330" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="6"/>
       <c r="B330" s="11"/>
     </row>
-    <row r="331" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="6"/>
       <c r="B331" s="11"/>
     </row>
-    <row r="332" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6"/>
       <c r="B332" s="11"/>
     </row>
-    <row r="333" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="6"/>
       <c r="B333" s="11"/>
     </row>
-    <row r="334" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="6"/>
       <c r="B334" s="11"/>
     </row>
-    <row r="335" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="6"/>
       <c r="B335" s="11"/>
     </row>
-    <row r="336" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="6"/>
       <c r="B336" s="11"/>
     </row>
-    <row r="337" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="6"/>
       <c r="B337" s="11"/>
     </row>
-    <row r="338" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="6"/>
       <c r="B338" s="11"/>
     </row>
-    <row r="339" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="6"/>
       <c r="B339" s="11"/>
     </row>
-    <row r="340" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="6"/>
       <c r="B340" s="11"/>
     </row>
-    <row r="341" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="6"/>
       <c r="B341" s="11"/>
     </row>
-    <row r="342" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="6"/>
       <c r="B342" s="11"/>
     </row>
-    <row r="343" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="6"/>
       <c r="B343" s="11"/>
     </row>
-    <row r="344" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6"/>
       <c r="B344" s="11"/>
     </row>
-    <row r="345" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="6"/>
       <c r="B345" s="11"/>
     </row>
-    <row r="346" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="6"/>
       <c r="B346" s="11"/>
     </row>
-    <row r="347" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="6"/>
       <c r="B347" s="11"/>
     </row>
-    <row r="348" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="6"/>
       <c r="B348" s="11"/>
     </row>
-    <row r="349" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="6"/>
       <c r="B349" s="11"/>
     </row>
-    <row r="350" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="6"/>
       <c r="B350" s="11"/>
     </row>
-    <row r="351" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="6"/>
       <c r="B351" s="11"/>
     </row>
-    <row r="352" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="6"/>
       <c r="B352" s="11"/>
     </row>
-    <row r="353" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="6"/>
       <c r="B353" s="11"/>
     </row>
-    <row r="354" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="6"/>
       <c r="B354" s="11"/>
     </row>
-    <row r="355" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="6"/>
       <c r="B355" s="11"/>
     </row>
-    <row r="356" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="6"/>
       <c r="B356" s="11"/>
     </row>
-    <row r="357" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="6"/>
       <c r="B357" s="11"/>
     </row>
-    <row r="358" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6"/>
       <c r="B358" s="11"/>
     </row>
-    <row r="359" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="6"/>
       <c r="B359" s="11"/>
     </row>
-    <row r="360" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="6"/>
       <c r="B360" s="11"/>
     </row>
-    <row r="361" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="6"/>
       <c r="B361" s="11"/>
     </row>
-    <row r="362" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="6"/>
       <c r="B362" s="11"/>
     </row>
-    <row r="363" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="6"/>
       <c r="B363" s="11"/>
     </row>
-    <row r="364" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="6"/>
       <c r="B364" s="11"/>
     </row>
-    <row r="365" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="6"/>
       <c r="B365" s="11"/>
     </row>
-    <row r="366" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6"/>
       <c r="B366" s="11"/>
     </row>
-    <row r="367" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="6"/>
       <c r="B367" s="11"/>
     </row>
-    <row r="368" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="6"/>
       <c r="B368" s="11"/>
     </row>
-    <row r="369" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="6"/>
       <c r="B369" s="11"/>
     </row>
-    <row r="370" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="6"/>
       <c r="B370" s="11"/>
     </row>
-    <row r="371" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="6"/>
       <c r="B371" s="11"/>
     </row>
-    <row r="372" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="6"/>
       <c r="B372" s="11"/>
     </row>
-    <row r="373" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="6"/>
       <c r="B373" s="11"/>
     </row>
-    <row r="374" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="6"/>
       <c r="B374" s="11"/>
     </row>
-    <row r="375" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="6"/>
       <c r="B375" s="11"/>
     </row>
-    <row r="376" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6"/>
       <c r="B376" s="11"/>
     </row>
-    <row r="377" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="6"/>
       <c r="B377" s="11"/>
     </row>
-    <row r="378" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6"/>
       <c r="B378" s="11"/>
     </row>
-    <row r="379" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="6"/>
       <c r="B379" s="11"/>
     </row>
-    <row r="380" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6"/>
       <c r="B380" s="11"/>
     </row>
-    <row r="381" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="6"/>
       <c r="B381" s="11"/>
     </row>
-    <row r="382" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6"/>
       <c r="B382" s="11"/>
     </row>
-    <row r="383" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="6"/>
       <c r="B383" s="11"/>
     </row>
-    <row r="384" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6"/>
       <c r="B384" s="11"/>
     </row>
-    <row r="385" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="6"/>
       <c r="B385" s="11"/>
     </row>
-    <row r="386" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6"/>
       <c r="B386" s="11"/>
     </row>
-    <row r="387" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6"/>
       <c r="B387" s="11"/>
     </row>
-    <row r="388" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6"/>
       <c r="B388" s="11"/>
     </row>
-    <row r="389" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6"/>
       <c r="B389" s="11"/>
     </row>
-    <row r="390" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6"/>
       <c r="B390" s="11"/>
     </row>
-    <row r="391" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="6"/>
       <c r="B391" s="11"/>
     </row>
-    <row r="392" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6"/>
       <c r="B392" s="11"/>
     </row>
-    <row r="393" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="6"/>
       <c r="B393" s="11"/>
     </row>
-    <row r="394" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="6"/>
       <c r="B394" s="11"/>
     </row>
-    <row r="395" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="6"/>
       <c r="B395" s="11"/>
     </row>
-    <row r="396" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="6"/>
       <c r="B396" s="11"/>
     </row>
-    <row r="397" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="6"/>
       <c r="B397" s="11"/>
     </row>
-    <row r="398" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="6"/>
       <c r="B398" s="11"/>
     </row>
-    <row r="399" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="6"/>
       <c r="B399" s="11"/>
     </row>
-    <row r="400" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6"/>
       <c r="B400" s="11"/>
     </row>
-    <row r="401" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="6"/>
       <c r="B401" s="11"/>
     </row>
-    <row r="402" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="6"/>
       <c r="B402" s="11"/>
     </row>
-    <row r="403" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="6"/>
       <c r="B403" s="11"/>
     </row>
-    <row r="404" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="6"/>
       <c r="B404" s="11"/>
     </row>
-    <row r="405" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="6"/>
       <c r="B405" s="11"/>
     </row>
-    <row r="406" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="6"/>
       <c r="B406" s="11"/>
     </row>
-    <row r="407" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="6"/>
       <c r="B407" s="11"/>
     </row>
-    <row r="408" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="6"/>
       <c r="B408" s="11"/>
     </row>
-    <row r="409" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="6"/>
       <c r="B409" s="11"/>
     </row>
-    <row r="410" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="6"/>
       <c r="B410" s="11"/>
     </row>
-    <row r="411" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="6"/>
       <c r="B411" s="11"/>
     </row>
-    <row r="412" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="6"/>
       <c r="B412" s="11"/>
     </row>
-    <row r="413" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="6"/>
       <c r="B413" s="11"/>
     </row>
-    <row r="414" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="6"/>
       <c r="B414" s="11"/>
     </row>
-    <row r="415" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="6"/>
       <c r="B415" s="11"/>
     </row>
-    <row r="416" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="6"/>
       <c r="B416" s="11"/>
     </row>
-    <row r="417" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6"/>
       <c r="B417" s="11"/>
     </row>
-    <row r="418" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="6"/>
       <c r="B418" s="11"/>
     </row>
-    <row r="419" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="6"/>
       <c r="B419" s="11"/>
     </row>
-    <row r="420" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="6"/>
       <c r="B420" s="11"/>
     </row>
-    <row r="421" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="6"/>
       <c r="B421" s="11"/>
     </row>
-    <row r="422" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="6"/>
       <c r="B422" s="11"/>
     </row>
-    <row r="423" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="6"/>
       <c r="B423" s="11"/>
     </row>
-    <row r="424" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="6"/>
       <c r="B424" s="11"/>
     </row>
-    <row r="425" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="6"/>
       <c r="B425" s="11"/>
     </row>
-    <row r="426" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="6"/>
       <c r="B426" s="11"/>
     </row>
-    <row r="427" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="6"/>
       <c r="B427" s="11"/>
     </row>
-    <row r="428" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="6"/>
       <c r="B428" s="11"/>
     </row>
-    <row r="429" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="6"/>
       <c r="B429" s="11"/>
     </row>
-    <row r="430" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="6"/>
       <c r="B430" s="11"/>
     </row>
-    <row r="431" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="6"/>
       <c r="B431" s="11"/>
     </row>
-    <row r="432" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="6"/>
       <c r="B432" s="11"/>
     </row>
-    <row r="433" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="6"/>
       <c r="B433" s="11"/>
     </row>
-    <row r="434" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="6"/>
       <c r="B434" s="11"/>
     </row>
-    <row r="435" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="6"/>
       <c r="B435" s="11"/>
     </row>
-    <row r="436" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="6"/>
       <c r="B436" s="11"/>
     </row>
-    <row r="437" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="6"/>
       <c r="B437" s="11"/>
     </row>
-    <row r="438" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="6"/>
       <c r="B438" s="11"/>
     </row>
-    <row r="439" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="6"/>
       <c r="B439" s="11"/>
     </row>
-    <row r="440" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="6"/>
       <c r="B440" s="11"/>
     </row>
-    <row r="441" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="6"/>
       <c r="B441" s="11"/>
     </row>
-    <row r="442" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="6"/>
       <c r="B442" s="11"/>
     </row>
-    <row r="443" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="6"/>
       <c r="B443" s="11"/>
     </row>
-    <row r="444" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="6"/>
       <c r="B444" s="11"/>
     </row>
-    <row r="445" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="6"/>
       <c r="B445" s="11"/>
     </row>
-    <row r="446" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="6"/>
       <c r="B446" s="11"/>
     </row>
-    <row r="447" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="6"/>
       <c r="B447" s="11"/>
     </row>
-    <row r="448" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="6"/>
       <c r="B448" s="11"/>
     </row>
-    <row r="449" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="6"/>
       <c r="B449" s="11"/>
     </row>
-    <row r="450" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="6"/>
       <c r="B450" s="11"/>
     </row>
-    <row r="451" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="6"/>
       <c r="B451" s="11"/>
     </row>
-    <row r="452" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="6"/>
       <c r="B452" s="11"/>
     </row>
-    <row r="453" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="6"/>
       <c r="B453" s="11"/>
     </row>
-    <row r="454" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="6"/>
       <c r="B454" s="11"/>
     </row>
-    <row r="455" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="6"/>
       <c r="B455" s="11"/>
     </row>
-    <row r="456" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="6"/>
       <c r="B456" s="11"/>
     </row>
-    <row r="457" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="6"/>
       <c r="B457" s="11"/>
     </row>
-    <row r="458" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="6"/>
       <c r="B458" s="11"/>
     </row>
-    <row r="459" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="6"/>
       <c r="B459" s="11"/>
     </row>
-    <row r="460" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="6"/>
       <c r="B460" s="11"/>
     </row>
-    <row r="461" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="6"/>
       <c r="B461" s="11"/>
     </row>
-    <row r="462" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="6"/>
       <c r="B462" s="11"/>
     </row>
-    <row r="463" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="6"/>
       <c r="B463" s="11"/>
     </row>
-    <row r="464" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="6"/>
       <c r="B464" s="11"/>
     </row>
-    <row r="465" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="6"/>
       <c r="B465" s="11"/>
     </row>
-    <row r="466" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="6"/>
       <c r="B466" s="11"/>
     </row>
-    <row r="467" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="6"/>
       <c r="B467" s="11"/>
     </row>
-    <row r="468" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="6"/>
       <c r="B468" s="11"/>
     </row>
-    <row r="469" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="6"/>
       <c r="B469" s="11"/>
     </row>
-    <row r="470" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="6"/>
       <c r="B470" s="11"/>
     </row>
-    <row r="471" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="6"/>
       <c r="B471" s="11"/>
     </row>
-    <row r="472" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="6"/>
       <c r="B472" s="11"/>
     </row>
-    <row r="473" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="6"/>
       <c r="B473" s="11"/>
     </row>
-    <row r="474" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="6"/>
       <c r="B474" s="11"/>
     </row>
-    <row r="475" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="6"/>
       <c r="B475" s="11"/>
     </row>
-    <row r="476" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6"/>
       <c r="B476" s="11"/>
     </row>
-    <row r="477" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="6"/>
       <c r="B477" s="11"/>
     </row>
-    <row r="478" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="6"/>
       <c r="B478" s="11"/>
     </row>
-    <row r="479" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="6"/>
       <c r="B479" s="11"/>
     </row>
-    <row r="480" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="6"/>
       <c r="B480" s="11"/>
     </row>
-    <row r="481" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="6"/>
       <c r="B481" s="11"/>
     </row>
-    <row r="482" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="6"/>
       <c r="B482" s="11"/>
     </row>
-    <row r="483" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="6"/>
       <c r="B483" s="11"/>
     </row>
-    <row r="484" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="6"/>
       <c r="B484" s="11"/>
     </row>
-    <row r="485" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="6"/>
       <c r="B485" s="11"/>
     </row>
-    <row r="486" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="6"/>
       <c r="B486" s="11"/>
     </row>
-    <row r="487" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="6"/>
       <c r="B487" s="11"/>
     </row>
-    <row r="488" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="6"/>
       <c r="B488" s="11"/>
     </row>
-    <row r="489" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="6"/>
       <c r="B489" s="11"/>
     </row>
-    <row r="490" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="6"/>
       <c r="B490" s="11"/>
     </row>
-    <row r="491" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="6"/>
       <c r="B491" s="11"/>
     </row>
-    <row r="492" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="6"/>
       <c r="B492" s="11"/>
     </row>
-    <row r="493" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="6"/>
       <c r="B493" s="11"/>
     </row>
-    <row r="494" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="6"/>
       <c r="B494" s="11"/>
     </row>
-    <row r="495" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="6"/>
       <c r="B495" s="11"/>
     </row>
-    <row r="496" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="6"/>
       <c r="B496" s="11"/>
     </row>
-    <row r="497" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="6"/>
       <c r="B497" s="11"/>
     </row>
-    <row r="498" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="6"/>
       <c r="B498" s="11"/>
     </row>
-    <row r="499" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="6"/>
       <c r="B499" s="11"/>
     </row>
-    <row r="500" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="6"/>
       <c r="B500" s="11"/>
     </row>
@@ -8629,52 +8677,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E34FD7-1B73-4707-A12E-62E00BDCA8A2}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56641218-56A3-48B3-8A52-B532218E01EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A573ACEB-4E92-448F-BC7A-42018CA48407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="81">
   <si>
     <t>Jour</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>Création des routes dédiées à l'interface utilisateur</t>
+  </si>
+  <si>
+    <t>Dernière réunion, discussion sur la présentation du projet et la documentation</t>
   </si>
 </sst>
 </file>
@@ -2025,17 +2028,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F503"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.59765625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="13.3984375" style="15" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="24.69921875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="15.25" style="12" customWidth="1"/>
+    <col min="4" max="4" width="24.75" style="5" customWidth="1"/>
     <col min="5" max="5" width="68.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="82.19921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="82.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2055,7 +2058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>46035</v>
       </c>
@@ -2073,7 +2076,7 @@
       </c>
       <c r="F2" s="8"/>
     </row>
-    <row r="3" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>46035</v>
       </c>
@@ -2091,7 +2094,7 @@
       </c>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>46036</v>
       </c>
@@ -2111,7 +2114,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>46036</v>
       </c>
@@ -2129,7 +2132,7 @@
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>46036</v>
       </c>
@@ -2149,7 +2152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>46036</v>
       </c>
@@ -2169,7 +2172,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>46037</v>
       </c>
@@ -2187,7 +2190,7 @@
       </c>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>46037</v>
       </c>
@@ -2207,7 +2210,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>46037</v>
       </c>
@@ -2227,7 +2230,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>46037</v>
       </c>
@@ -2245,7 +2248,7 @@
       </c>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>46038</v>
       </c>
@@ -2263,7 +2266,7 @@
       </c>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>46038</v>
       </c>
@@ -2283,7 +2286,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>46038</v>
       </c>
@@ -2301,7 +2304,7 @@
       </c>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>46038</v>
       </c>
@@ -2321,7 +2324,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>46038</v>
       </c>
@@ -2341,7 +2344,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>46038</v>
       </c>
@@ -2361,7 +2364,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>46041</v>
       </c>
@@ -2381,7 +2384,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>46041</v>
       </c>
@@ -2401,7 +2404,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>46041</v>
       </c>
@@ -2421,7 +2424,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46041</v>
       </c>
@@ -2439,7 +2442,7 @@
       </c>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46041</v>
       </c>
@@ -2459,7 +2462,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46042</v>
       </c>
@@ -2479,7 +2482,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46042</v>
       </c>
@@ -2499,7 +2502,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46043</v>
       </c>
@@ -2519,7 +2522,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>46043</v>
       </c>
@@ -2539,7 +2542,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>46043</v>
       </c>
@@ -2559,7 +2562,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46043</v>
       </c>
@@ -2579,7 +2582,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>46043</v>
       </c>
@@ -2599,7 +2602,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>46044</v>
       </c>
@@ -2619,7 +2622,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>46044</v>
       </c>
@@ -2639,7 +2642,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <v>46044</v>
       </c>
@@ -2659,7 +2662,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>46044</v>
       </c>
@@ -2677,7 +2680,7 @@
       </c>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>46045</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>46045</v>
       </c>
@@ -2717,7 +2720,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>46045</v>
       </c>
@@ -2737,7 +2740,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>46045</v>
       </c>
@@ -2757,7 +2760,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>46045</v>
       </c>
@@ -2777,7 +2780,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>46048</v>
       </c>
@@ -2797,7 +2800,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>46048</v>
       </c>
@@ -2817,7 +2820,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <v>46048</v>
       </c>
@@ -2837,7 +2840,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
         <v>46049</v>
       </c>
@@ -2857,7 +2860,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
         <v>46049</v>
       </c>
@@ -2877,7 +2880,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>46049</v>
       </c>
@@ -2897,15 +2900,27 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-    </row>
-    <row r="46" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="6">
+        <v>46050</v>
+      </c>
+      <c r="B45" s="14">
+        <v>3</v>
+      </c>
+      <c r="C45" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="14"/>
       <c r="C46" s="11"/>
@@ -2913,7 +2928,7 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="14"/>
       <c r="C47" s="11"/>
@@ -2921,7 +2936,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="14"/>
       <c r="C48" s="11"/>
@@ -2929,7 +2944,7 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
     </row>
-    <row r="49" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="14"/>
       <c r="C49" s="11"/>
@@ -2937,7 +2952,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="14"/>
       <c r="C50" s="11"/>
@@ -2945,7 +2960,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
     </row>
-    <row r="51" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="14"/>
       <c r="C51" s="11"/>
@@ -2953,7 +2968,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="14"/>
       <c r="C52" s="11"/>
@@ -2961,7 +2976,7 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
     </row>
-    <row r="53" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="14"/>
       <c r="C53" s="11"/>
@@ -2969,7 +2984,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="14"/>
       <c r="C54" s="11"/>
@@ -2977,7 +2992,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="14"/>
       <c r="C55" s="11"/>
@@ -2985,7 +3000,7 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
     </row>
-    <row r="56" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="14"/>
       <c r="C56" s="11"/>
@@ -2993,7 +3008,7 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="14"/>
       <c r="C57" s="11"/>
@@ -3001,7 +3016,7 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
     </row>
-    <row r="58" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="14"/>
       <c r="C58" s="11"/>
@@ -3009,7 +3024,7 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
     </row>
-    <row r="59" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="14"/>
       <c r="C59" s="11"/>
@@ -3017,7 +3032,7 @@
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
     </row>
-    <row r="60" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="14"/>
       <c r="C60" s="11"/>
@@ -3025,7 +3040,7 @@
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="14"/>
       <c r="C61" s="11"/>
@@ -3033,7 +3048,7 @@
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
     </row>
-    <row r="62" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="14"/>
       <c r="C62" s="11"/>
@@ -3041,7 +3056,7 @@
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
     </row>
-    <row r="63" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="14"/>
       <c r="C63" s="11"/>
@@ -3049,7 +3064,7 @@
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
     </row>
-    <row r="64" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="14"/>
       <c r="C64" s="11"/>
@@ -3057,7 +3072,7 @@
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
     </row>
-    <row r="65" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="14"/>
       <c r="C65" s="11"/>
@@ -3065,7 +3080,7 @@
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
     </row>
-    <row r="66" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="14"/>
       <c r="C66" s="11"/>
@@ -3073,7 +3088,7 @@
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
     </row>
-    <row r="67" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="14"/>
       <c r="C67" s="11"/>
@@ -3081,7 +3096,7 @@
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
     </row>
-    <row r="68" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="14"/>
       <c r="C68" s="11"/>
@@ -3089,7 +3104,7 @@
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
     </row>
-    <row r="69" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="14"/>
       <c r="C69" s="11"/>
@@ -3097,7 +3112,7 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
     </row>
-    <row r="70" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="14"/>
       <c r="C70" s="11"/>
@@ -3105,7 +3120,7 @@
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
     </row>
-    <row r="71" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
       <c r="B71" s="14"/>
       <c r="C71" s="11"/>
@@ -3113,7 +3128,7 @@
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
     </row>
-    <row r="72" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="14"/>
       <c r="C72" s="11"/>
@@ -3121,7 +3136,7 @@
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
     </row>
-    <row r="73" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="14"/>
       <c r="C73" s="11"/>
@@ -3129,7 +3144,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
     </row>
-    <row r="74" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="14"/>
       <c r="C74" s="11"/>
@@ -3137,7 +3152,7 @@
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
     </row>
-    <row r="75" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="14"/>
       <c r="C75" s="11"/>
@@ -3145,7 +3160,7 @@
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
     </row>
-    <row r="76" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="14"/>
       <c r="C76" s="11"/>
@@ -3153,7 +3168,7 @@
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
     </row>
-    <row r="77" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="14"/>
       <c r="C77" s="11"/>
@@ -3161,7 +3176,7 @@
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
     </row>
-    <row r="78" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="14"/>
       <c r="C78" s="11"/>
@@ -3169,7 +3184,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
     </row>
-    <row r="79" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="14"/>
       <c r="C79" s="11"/>
@@ -3177,7 +3192,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
     </row>
-    <row r="80" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="14"/>
       <c r="C80" s="11"/>
@@ -3185,7 +3200,7 @@
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
     </row>
-    <row r="81" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="14"/>
       <c r="C81" s="11"/>
@@ -3193,7 +3208,7 @@
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
     </row>
-    <row r="82" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="14"/>
       <c r="C82" s="11"/>
@@ -3201,7 +3216,7 @@
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
     </row>
-    <row r="83" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="14"/>
       <c r="C83" s="11"/>
@@ -3209,7 +3224,7 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
     </row>
-    <row r="84" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="14"/>
       <c r="C84" s="11"/>
@@ -3217,7 +3232,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
     </row>
-    <row r="85" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="14"/>
       <c r="C85" s="11"/>
@@ -3225,7 +3240,7 @@
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
     </row>
-    <row r="86" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="14"/>
       <c r="C86" s="11"/>
@@ -3233,7 +3248,7 @@
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
     </row>
-    <row r="87" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="14"/>
       <c r="C87" s="11"/>
@@ -3241,7 +3256,7 @@
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
     </row>
-    <row r="88" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="14"/>
       <c r="C88" s="11"/>
@@ -3249,7 +3264,7 @@
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
     </row>
-    <row r="89" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="14"/>
       <c r="C89" s="11"/>
@@ -3257,7 +3272,7 @@
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
     </row>
-    <row r="90" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="14"/>
       <c r="C90" s="11"/>
@@ -3265,7 +3280,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
     </row>
-    <row r="91" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="14"/>
       <c r="C91" s="11"/>
@@ -3273,7 +3288,7 @@
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
     </row>
-    <row r="92" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="14"/>
       <c r="C92" s="11"/>
@@ -3281,7 +3296,7 @@
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
     </row>
-    <row r="93" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="14"/>
       <c r="C93" s="11"/>
@@ -3289,7 +3304,7 @@
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
     </row>
-    <row r="94" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="14"/>
       <c r="C94" s="11"/>
@@ -3297,7 +3312,7 @@
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
     </row>
-    <row r="95" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="14"/>
       <c r="C95" s="11"/>
@@ -3305,7 +3320,7 @@
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
     </row>
-    <row r="96" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="14"/>
       <c r="C96" s="11"/>
@@ -3313,7 +3328,7 @@
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
     </row>
-    <row r="97" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="14"/>
       <c r="C97" s="11"/>
@@ -3321,7 +3336,7 @@
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
     </row>
-    <row r="98" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="14"/>
       <c r="C98" s="11"/>
@@ -3329,7 +3344,7 @@
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
     </row>
-    <row r="99" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="14"/>
       <c r="C99" s="11"/>
@@ -3337,7 +3352,7 @@
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
     </row>
-    <row r="100" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="14"/>
       <c r="C100" s="11"/>
@@ -3345,7 +3360,7 @@
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
     </row>
-    <row r="101" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
       <c r="B101" s="14"/>
       <c r="C101" s="11"/>
@@ -3353,7 +3368,7 @@
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
     </row>
-    <row r="102" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="14"/>
       <c r="C102" s="11"/>
@@ -3361,7 +3376,7 @@
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
     </row>
-    <row r="103" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="14"/>
       <c r="C103" s="11"/>
@@ -3369,7 +3384,7 @@
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
     </row>
-    <row r="104" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6"/>
       <c r="B104" s="14"/>
       <c r="C104" s="11"/>
@@ -3377,7 +3392,7 @@
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
     </row>
-    <row r="105" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6"/>
       <c r="B105" s="14"/>
       <c r="C105" s="11"/>
@@ -3385,7 +3400,7 @@
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
     </row>
-    <row r="106" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6"/>
       <c r="B106" s="14"/>
       <c r="C106" s="11"/>
@@ -3393,7 +3408,7 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
     </row>
-    <row r="107" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="B107" s="14"/>
       <c r="C107" s="11"/>
@@ -3401,7 +3416,7 @@
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
     </row>
-    <row r="108" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="B108" s="14"/>
       <c r="C108" s="11"/>
@@ -3409,7 +3424,7 @@
       <c r="E108" s="8"/>
       <c r="F108" s="8"/>
     </row>
-    <row r="109" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="B109" s="14"/>
       <c r="C109" s="11"/>
@@ -3417,7 +3432,7 @@
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
     </row>
-    <row r="110" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="B110" s="14"/>
       <c r="C110" s="11"/>
@@ -3425,7 +3440,7 @@
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
     </row>
-    <row r="111" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6"/>
       <c r="B111" s="14"/>
       <c r="C111" s="11"/>
@@ -3433,7 +3448,7 @@
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
     </row>
-    <row r="112" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6"/>
       <c r="B112" s="14"/>
       <c r="C112" s="11"/>
@@ -3441,7 +3456,7 @@
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
     </row>
-    <row r="113" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
       <c r="B113" s="14"/>
       <c r="C113" s="11"/>
@@ -3449,7 +3464,7 @@
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
     </row>
-    <row r="114" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6"/>
       <c r="B114" s="14"/>
       <c r="C114" s="11"/>
@@ -3457,7 +3472,7 @@
       <c r="E114" s="8"/>
       <c r="F114" s="8"/>
     </row>
-    <row r="115" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6"/>
       <c r="B115" s="14"/>
       <c r="C115" s="11"/>
@@ -3465,7 +3480,7 @@
       <c r="E115" s="8"/>
       <c r="F115" s="8"/>
     </row>
-    <row r="116" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6"/>
       <c r="B116" s="14"/>
       <c r="C116" s="11"/>
@@ -3473,7 +3488,7 @@
       <c r="E116" s="8"/>
       <c r="F116" s="8"/>
     </row>
-    <row r="117" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6"/>
       <c r="B117" s="14"/>
       <c r="C117" s="11"/>
@@ -3481,7 +3496,7 @@
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
     </row>
-    <row r="118" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6"/>
       <c r="B118" s="14"/>
       <c r="C118" s="11"/>
@@ -3489,7 +3504,7 @@
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
     </row>
-    <row r="119" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6"/>
       <c r="B119" s="14"/>
       <c r="C119" s="11"/>
@@ -3497,7 +3512,7 @@
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
     </row>
-    <row r="120" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6"/>
       <c r="B120" s="14"/>
       <c r="C120" s="11"/>
@@ -3505,7 +3520,7 @@
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
     </row>
-    <row r="121" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6"/>
       <c r="B121" s="14"/>
       <c r="C121" s="11"/>
@@ -3513,7 +3528,7 @@
       <c r="E121" s="8"/>
       <c r="F121" s="8"/>
     </row>
-    <row r="122" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6"/>
       <c r="B122" s="14"/>
       <c r="C122" s="11"/>
@@ -3521,7 +3536,7 @@
       <c r="E122" s="8"/>
       <c r="F122" s="8"/>
     </row>
-    <row r="123" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6"/>
       <c r="B123" s="14"/>
       <c r="C123" s="11"/>
@@ -3529,7 +3544,7 @@
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
     </row>
-    <row r="124" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6"/>
       <c r="B124" s="14"/>
       <c r="C124" s="11"/>
@@ -3537,7 +3552,7 @@
       <c r="E124" s="8"/>
       <c r="F124" s="8"/>
     </row>
-    <row r="125" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6"/>
       <c r="B125" s="14"/>
       <c r="C125" s="11"/>
@@ -3545,7 +3560,7 @@
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
     </row>
-    <row r="126" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6"/>
       <c r="B126" s="14"/>
       <c r="C126" s="11"/>
@@ -3553,7 +3568,7 @@
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
     </row>
-    <row r="127" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6"/>
       <c r="B127" s="14"/>
       <c r="C127" s="11"/>
@@ -3561,7 +3576,7 @@
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
     </row>
-    <row r="128" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6"/>
       <c r="B128" s="14"/>
       <c r="C128" s="11"/>
@@ -3569,7 +3584,7 @@
       <c r="E128" s="8"/>
       <c r="F128" s="8"/>
     </row>
-    <row r="129" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6"/>
       <c r="B129" s="14"/>
       <c r="C129" s="11"/>
@@ -3577,7 +3592,7 @@
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
     </row>
-    <row r="130" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6"/>
       <c r="B130" s="14"/>
       <c r="C130" s="11"/>
@@ -3585,7 +3600,7 @@
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
     </row>
-    <row r="131" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6"/>
       <c r="B131" s="14"/>
       <c r="C131" s="11"/>
@@ -3593,7 +3608,7 @@
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
     </row>
-    <row r="132" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6"/>
       <c r="B132" s="14"/>
       <c r="C132" s="11"/>
@@ -3601,7 +3616,7 @@
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
     </row>
-    <row r="133" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6"/>
       <c r="B133" s="14"/>
       <c r="C133" s="11"/>
@@ -3609,7 +3624,7 @@
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
     </row>
-    <row r="134" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6"/>
       <c r="B134" s="14"/>
       <c r="C134" s="11"/>
@@ -3617,7 +3632,7 @@
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
     </row>
-    <row r="135" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6"/>
       <c r="B135" s="14"/>
       <c r="C135" s="11"/>
@@ -3625,7 +3640,7 @@
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
     </row>
-    <row r="136" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6"/>
       <c r="B136" s="14"/>
       <c r="C136" s="11"/>
@@ -3633,7 +3648,7 @@
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
     </row>
-    <row r="137" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6"/>
       <c r="B137" s="14"/>
       <c r="C137" s="11"/>
@@ -3641,7 +3656,7 @@
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
     </row>
-    <row r="138" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6"/>
       <c r="B138" s="14"/>
       <c r="C138" s="11"/>
@@ -3649,7 +3664,7 @@
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
     </row>
-    <row r="139" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6"/>
       <c r="B139" s="14"/>
       <c r="C139" s="11"/>
@@ -3657,7 +3672,7 @@
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
     </row>
-    <row r="140" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6"/>
       <c r="B140" s="14"/>
       <c r="C140" s="11"/>
@@ -3665,7 +3680,7 @@
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
     </row>
-    <row r="141" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6"/>
       <c r="B141" s="14"/>
       <c r="C141" s="11"/>
@@ -3673,7 +3688,7 @@
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
     </row>
-    <row r="142" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6"/>
       <c r="B142" s="14"/>
       <c r="C142" s="11"/>
@@ -3681,7 +3696,7 @@
       <c r="E142" s="8"/>
       <c r="F142" s="8"/>
     </row>
-    <row r="143" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6"/>
       <c r="B143" s="14"/>
       <c r="C143" s="11"/>
@@ -3689,7 +3704,7 @@
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
     </row>
-    <row r="144" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6"/>
       <c r="B144" s="14"/>
       <c r="C144" s="11"/>
@@ -3697,7 +3712,7 @@
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
     </row>
-    <row r="145" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6"/>
       <c r="B145" s="14"/>
       <c r="C145" s="11"/>
@@ -3705,7 +3720,7 @@
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
     </row>
-    <row r="146" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6"/>
       <c r="B146" s="14"/>
       <c r="C146" s="11"/>
@@ -3713,7 +3728,7 @@
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
     </row>
-    <row r="147" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6"/>
       <c r="B147" s="14"/>
       <c r="C147" s="11"/>
@@ -3721,7 +3736,7 @@
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
     </row>
-    <row r="148" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6"/>
       <c r="B148" s="14"/>
       <c r="C148" s="11"/>
@@ -3729,7 +3744,7 @@
       <c r="E148" s="8"/>
       <c r="F148" s="8"/>
     </row>
-    <row r="149" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6"/>
       <c r="B149" s="14"/>
       <c r="C149" s="11"/>
@@ -3737,7 +3752,7 @@
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
     </row>
-    <row r="150" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6"/>
       <c r="B150" s="14"/>
       <c r="C150" s="11"/>
@@ -3745,7 +3760,7 @@
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
     </row>
-    <row r="151" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6"/>
       <c r="B151" s="14"/>
       <c r="C151" s="11"/>
@@ -3753,7 +3768,7 @@
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
     </row>
-    <row r="152" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6"/>
       <c r="B152" s="14"/>
       <c r="C152" s="11"/>
@@ -3761,7 +3776,7 @@
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
     </row>
-    <row r="153" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6"/>
       <c r="B153" s="14"/>
       <c r="C153" s="11"/>
@@ -3769,7 +3784,7 @@
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
     </row>
-    <row r="154" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6"/>
       <c r="B154" s="14"/>
       <c r="C154" s="11"/>
@@ -3777,7 +3792,7 @@
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
     </row>
-    <row r="155" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6"/>
       <c r="B155" s="14"/>
       <c r="C155" s="11"/>
@@ -3785,7 +3800,7 @@
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
     </row>
-    <row r="156" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6"/>
       <c r="B156" s="14"/>
       <c r="C156" s="11"/>
@@ -3793,7 +3808,7 @@
       <c r="E156" s="8"/>
       <c r="F156" s="8"/>
     </row>
-    <row r="157" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6"/>
       <c r="B157" s="14"/>
       <c r="C157" s="11"/>
@@ -3801,7 +3816,7 @@
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
     </row>
-    <row r="158" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6"/>
       <c r="B158" s="14"/>
       <c r="C158" s="11"/>
@@ -3809,7 +3824,7 @@
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
     </row>
-    <row r="159" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6"/>
       <c r="B159" s="14"/>
       <c r="C159" s="11"/>
@@ -3817,7 +3832,7 @@
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
     </row>
-    <row r="160" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6"/>
       <c r="B160" s="14"/>
       <c r="C160" s="11"/>
@@ -3825,7 +3840,7 @@
       <c r="E160" s="8"/>
       <c r="F160" s="8"/>
     </row>
-    <row r="161" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6"/>
       <c r="B161" s="14"/>
       <c r="C161" s="11"/>
@@ -3833,7 +3848,7 @@
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
     </row>
-    <row r="162" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6"/>
       <c r="B162" s="14"/>
       <c r="C162" s="11"/>
@@ -3841,7 +3856,7 @@
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
     </row>
-    <row r="163" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6"/>
       <c r="B163" s="14"/>
       <c r="C163" s="11"/>
@@ -3849,7 +3864,7 @@
       <c r="E163" s="8"/>
       <c r="F163" s="8"/>
     </row>
-    <row r="164" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6"/>
       <c r="B164" s="14"/>
       <c r="C164" s="11"/>
@@ -3857,7 +3872,7 @@
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
     </row>
-    <row r="165" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6"/>
       <c r="B165" s="14"/>
       <c r="C165" s="11"/>
@@ -3865,7 +3880,7 @@
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
     </row>
-    <row r="166" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6"/>
       <c r="B166" s="14"/>
       <c r="C166" s="11"/>
@@ -3873,7 +3888,7 @@
       <c r="E166" s="8"/>
       <c r="F166" s="8"/>
     </row>
-    <row r="167" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6"/>
       <c r="B167" s="14"/>
       <c r="C167" s="11"/>
@@ -3881,7 +3896,7 @@
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
     </row>
-    <row r="168" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6"/>
       <c r="B168" s="14"/>
       <c r="C168" s="11"/>
@@ -3889,7 +3904,7 @@
       <c r="E168" s="8"/>
       <c r="F168" s="8"/>
     </row>
-    <row r="169" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6"/>
       <c r="B169" s="14"/>
       <c r="C169" s="11"/>
@@ -3897,7 +3912,7 @@
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
     </row>
-    <row r="170" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6"/>
       <c r="B170" s="14"/>
       <c r="C170" s="11"/>
@@ -3905,7 +3920,7 @@
       <c r="E170" s="8"/>
       <c r="F170" s="8"/>
     </row>
-    <row r="171" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6"/>
       <c r="B171" s="14"/>
       <c r="C171" s="11"/>
@@ -3913,7 +3928,7 @@
       <c r="E171" s="8"/>
       <c r="F171" s="8"/>
     </row>
-    <row r="172" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6"/>
       <c r="B172" s="14"/>
       <c r="C172" s="11"/>
@@ -3921,7 +3936,7 @@
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
     </row>
-    <row r="173" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6"/>
       <c r="B173" s="14"/>
       <c r="C173" s="11"/>
@@ -3929,7 +3944,7 @@
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
     </row>
-    <row r="174" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6"/>
       <c r="B174" s="14"/>
       <c r="C174" s="11"/>
@@ -3937,7 +3952,7 @@
       <c r="E174" s="8"/>
       <c r="F174" s="8"/>
     </row>
-    <row r="175" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6"/>
       <c r="B175" s="14"/>
       <c r="C175" s="11"/>
@@ -3945,7 +3960,7 @@
       <c r="E175" s="8"/>
       <c r="F175" s="8"/>
     </row>
-    <row r="176" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6"/>
       <c r="B176" s="14"/>
       <c r="C176" s="11"/>
@@ -3953,7 +3968,7 @@
       <c r="E176" s="8"/>
       <c r="F176" s="8"/>
     </row>
-    <row r="177" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6"/>
       <c r="B177" s="14"/>
       <c r="C177" s="11"/>
@@ -3961,7 +3976,7 @@
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
     </row>
-    <row r="178" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6"/>
       <c r="B178" s="14"/>
       <c r="C178" s="11"/>
@@ -3969,7 +3984,7 @@
       <c r="E178" s="8"/>
       <c r="F178" s="8"/>
     </row>
-    <row r="179" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6"/>
       <c r="B179" s="14"/>
       <c r="C179" s="11"/>
@@ -3977,7 +3992,7 @@
       <c r="E179" s="8"/>
       <c r="F179" s="8"/>
     </row>
-    <row r="180" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6"/>
       <c r="B180" s="14"/>
       <c r="C180" s="11"/>
@@ -3985,7 +4000,7 @@
       <c r="E180" s="8"/>
       <c r="F180" s="8"/>
     </row>
-    <row r="181" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6"/>
       <c r="B181" s="14"/>
       <c r="C181" s="11"/>
@@ -3993,7 +4008,7 @@
       <c r="E181" s="8"/>
       <c r="F181" s="8"/>
     </row>
-    <row r="182" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6"/>
       <c r="B182" s="14"/>
       <c r="C182" s="11"/>
@@ -4001,7 +4016,7 @@
       <c r="E182" s="8"/>
       <c r="F182" s="8"/>
     </row>
-    <row r="183" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6"/>
       <c r="B183" s="14"/>
       <c r="C183" s="11"/>
@@ -4009,7 +4024,7 @@
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
     </row>
-    <row r="184" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6"/>
       <c r="B184" s="14"/>
       <c r="C184" s="11"/>
@@ -4017,7 +4032,7 @@
       <c r="E184" s="8"/>
       <c r="F184" s="8"/>
     </row>
-    <row r="185" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6"/>
       <c r="B185" s="14"/>
       <c r="C185" s="11"/>
@@ -4025,7 +4040,7 @@
       <c r="E185" s="8"/>
       <c r="F185" s="8"/>
     </row>
-    <row r="186" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6"/>
       <c r="B186" s="14"/>
       <c r="C186" s="11"/>
@@ -4033,7 +4048,7 @@
       <c r="E186" s="8"/>
       <c r="F186" s="8"/>
     </row>
-    <row r="187" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6"/>
       <c r="B187" s="14"/>
       <c r="C187" s="11"/>
@@ -4041,7 +4056,7 @@
       <c r="E187" s="8"/>
       <c r="F187" s="8"/>
     </row>
-    <row r="188" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6"/>
       <c r="B188" s="14"/>
       <c r="C188" s="11"/>
@@ -4049,7 +4064,7 @@
       <c r="E188" s="8"/>
       <c r="F188" s="8"/>
     </row>
-    <row r="189" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6"/>
       <c r="B189" s="14"/>
       <c r="C189" s="11"/>
@@ -4057,7 +4072,7 @@
       <c r="E189" s="8"/>
       <c r="F189" s="8"/>
     </row>
-    <row r="190" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6"/>
       <c r="B190" s="14"/>
       <c r="C190" s="11"/>
@@ -4065,7 +4080,7 @@
       <c r="E190" s="8"/>
       <c r="F190" s="8"/>
     </row>
-    <row r="191" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6"/>
       <c r="B191" s="14"/>
       <c r="C191" s="11"/>
@@ -4073,7 +4088,7 @@
       <c r="E191" s="8"/>
       <c r="F191" s="8"/>
     </row>
-    <row r="192" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6"/>
       <c r="B192" s="14"/>
       <c r="C192" s="11"/>
@@ -4081,7 +4096,7 @@
       <c r="E192" s="8"/>
       <c r="F192" s="8"/>
     </row>
-    <row r="193" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6"/>
       <c r="B193" s="14"/>
       <c r="C193" s="11"/>
@@ -4089,7 +4104,7 @@
       <c r="E193" s="8"/>
       <c r="F193" s="8"/>
     </row>
-    <row r="194" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6"/>
       <c r="B194" s="14"/>
       <c r="C194" s="11"/>
@@ -4097,7 +4112,7 @@
       <c r="E194" s="8"/>
       <c r="F194" s="8"/>
     </row>
-    <row r="195" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6"/>
       <c r="B195" s="14"/>
       <c r="C195" s="11"/>
@@ -4105,7 +4120,7 @@
       <c r="E195" s="8"/>
       <c r="F195" s="8"/>
     </row>
-    <row r="196" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6"/>
       <c r="B196" s="14"/>
       <c r="C196" s="11"/>
@@ -4113,7 +4128,7 @@
       <c r="E196" s="8"/>
       <c r="F196" s="8"/>
     </row>
-    <row r="197" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6"/>
       <c r="B197" s="14"/>
       <c r="C197" s="11"/>
@@ -4121,7 +4136,7 @@
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
     </row>
-    <row r="198" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6"/>
       <c r="B198" s="14"/>
       <c r="C198" s="11"/>
@@ -4129,7 +4144,7 @@
       <c r="E198" s="8"/>
       <c r="F198" s="8"/>
     </row>
-    <row r="199" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6"/>
       <c r="B199" s="14"/>
       <c r="C199" s="11"/>
@@ -4137,7 +4152,7 @@
       <c r="E199" s="8"/>
       <c r="F199" s="8"/>
     </row>
-    <row r="200" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6"/>
       <c r="B200" s="14"/>
       <c r="C200" s="11"/>
@@ -4145,7 +4160,7 @@
       <c r="E200" s="8"/>
       <c r="F200" s="8"/>
     </row>
-    <row r="201" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6"/>
       <c r="B201" s="14"/>
       <c r="C201" s="11"/>
@@ -4153,7 +4168,7 @@
       <c r="E201" s="8"/>
       <c r="F201" s="8"/>
     </row>
-    <row r="202" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6"/>
       <c r="B202" s="14"/>
       <c r="C202" s="11"/>
@@ -4161,7 +4176,7 @@
       <c r="E202" s="8"/>
       <c r="F202" s="8"/>
     </row>
-    <row r="203" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6"/>
       <c r="B203" s="14"/>
       <c r="C203" s="11"/>
@@ -4169,7 +4184,7 @@
       <c r="E203" s="8"/>
       <c r="F203" s="8"/>
     </row>
-    <row r="204" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6"/>
       <c r="B204" s="14"/>
       <c r="C204" s="11"/>
@@ -4177,7 +4192,7 @@
       <c r="E204" s="8"/>
       <c r="F204" s="8"/>
     </row>
-    <row r="205" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6"/>
       <c r="B205" s="14"/>
       <c r="C205" s="11"/>
@@ -4185,7 +4200,7 @@
       <c r="E205" s="8"/>
       <c r="F205" s="8"/>
     </row>
-    <row r="206" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6"/>
       <c r="B206" s="14"/>
       <c r="C206" s="11"/>
@@ -4193,7 +4208,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6"/>
       <c r="B207" s="14"/>
       <c r="C207" s="11"/>
@@ -4201,7 +4216,7 @@
       <c r="E207" s="8"/>
       <c r="F207" s="8"/>
     </row>
-    <row r="208" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6"/>
       <c r="B208" s="14"/>
       <c r="C208" s="11"/>
@@ -4209,7 +4224,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6"/>
       <c r="B209" s="14"/>
       <c r="C209" s="11"/>
@@ -4217,7 +4232,7 @@
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6"/>
       <c r="B210" s="14"/>
       <c r="C210" s="11"/>
@@ -4225,7 +4240,7 @@
       <c r="E210" s="8"/>
       <c r="F210" s="8"/>
     </row>
-    <row r="211" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6"/>
       <c r="B211" s="14"/>
       <c r="C211" s="11"/>
@@ -4233,7 +4248,7 @@
       <c r="E211" s="8"/>
       <c r="F211" s="8"/>
     </row>
-    <row r="212" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6"/>
       <c r="B212" s="14"/>
       <c r="C212" s="11"/>
@@ -4241,7 +4256,7 @@
       <c r="E212" s="8"/>
       <c r="F212" s="8"/>
     </row>
-    <row r="213" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6"/>
       <c r="B213" s="14"/>
       <c r="C213" s="11"/>
@@ -4249,7 +4264,7 @@
       <c r="E213" s="8"/>
       <c r="F213" s="8"/>
     </row>
-    <row r="214" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6"/>
       <c r="B214" s="14"/>
       <c r="C214" s="11"/>
@@ -4257,7 +4272,7 @@
       <c r="E214" s="8"/>
       <c r="F214" s="8"/>
     </row>
-    <row r="215" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6"/>
       <c r="B215" s="14"/>
       <c r="C215" s="11"/>
@@ -4265,7 +4280,7 @@
       <c r="E215" s="8"/>
       <c r="F215" s="8"/>
     </row>
-    <row r="216" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6"/>
       <c r="B216" s="14"/>
       <c r="C216" s="11"/>
@@ -4273,7 +4288,7 @@
       <c r="E216" s="8"/>
       <c r="F216" s="8"/>
     </row>
-    <row r="217" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6"/>
       <c r="B217" s="14"/>
       <c r="C217" s="11"/>
@@ -4281,7 +4296,7 @@
       <c r="E217" s="8"/>
       <c r="F217" s="8"/>
     </row>
-    <row r="218" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6"/>
       <c r="B218" s="14"/>
       <c r="C218" s="11"/>
@@ -4289,7 +4304,7 @@
       <c r="E218" s="8"/>
       <c r="F218" s="8"/>
     </row>
-    <row r="219" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6"/>
       <c r="B219" s="14"/>
       <c r="C219" s="11"/>
@@ -4297,7 +4312,7 @@
       <c r="E219" s="8"/>
       <c r="F219" s="8"/>
     </row>
-    <row r="220" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6"/>
       <c r="B220" s="14"/>
       <c r="C220" s="11"/>
@@ -4305,7 +4320,7 @@
       <c r="E220" s="8"/>
       <c r="F220" s="8"/>
     </row>
-    <row r="221" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6"/>
       <c r="B221" s="14"/>
       <c r="C221" s="11"/>
@@ -4313,7 +4328,7 @@
       <c r="E221" s="8"/>
       <c r="F221" s="8"/>
     </row>
-    <row r="222" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6"/>
       <c r="B222" s="14"/>
       <c r="C222" s="11"/>
@@ -4321,7 +4336,7 @@
       <c r="E222" s="8"/>
       <c r="F222" s="8"/>
     </row>
-    <row r="223" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6"/>
       <c r="B223" s="14"/>
       <c r="C223" s="11"/>
@@ -4329,7 +4344,7 @@
       <c r="E223" s="8"/>
       <c r="F223" s="8"/>
     </row>
-    <row r="224" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6"/>
       <c r="B224" s="14"/>
       <c r="C224" s="11"/>
@@ -4337,7 +4352,7 @@
       <c r="E224" s="8"/>
       <c r="F224" s="8"/>
     </row>
-    <row r="225" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6"/>
       <c r="B225" s="14"/>
       <c r="C225" s="11"/>
@@ -4345,7 +4360,7 @@
       <c r="E225" s="8"/>
       <c r="F225" s="8"/>
     </row>
-    <row r="226" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6"/>
       <c r="B226" s="14"/>
       <c r="C226" s="11"/>
@@ -4353,7 +4368,7 @@
       <c r="E226" s="8"/>
       <c r="F226" s="8"/>
     </row>
-    <row r="227" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6"/>
       <c r="B227" s="14"/>
       <c r="C227" s="11"/>
@@ -4361,7 +4376,7 @@
       <c r="E227" s="8"/>
       <c r="F227" s="8"/>
     </row>
-    <row r="228" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6"/>
       <c r="B228" s="14"/>
       <c r="C228" s="11"/>
@@ -4369,7 +4384,7 @@
       <c r="E228" s="8"/>
       <c r="F228" s="8"/>
     </row>
-    <row r="229" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6"/>
       <c r="B229" s="14"/>
       <c r="C229" s="11"/>
@@ -4377,7 +4392,7 @@
       <c r="E229" s="8"/>
       <c r="F229" s="8"/>
     </row>
-    <row r="230" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6"/>
       <c r="B230" s="14"/>
       <c r="C230" s="11"/>
@@ -4385,7 +4400,7 @@
       <c r="E230" s="8"/>
       <c r="F230" s="8"/>
     </row>
-    <row r="231" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6"/>
       <c r="B231" s="14"/>
       <c r="C231" s="11"/>
@@ -4393,7 +4408,7 @@
       <c r="E231" s="8"/>
       <c r="F231" s="8"/>
     </row>
-    <row r="232" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6"/>
       <c r="B232" s="14"/>
       <c r="C232" s="11"/>
@@ -4401,7 +4416,7 @@
       <c r="E232" s="8"/>
       <c r="F232" s="8"/>
     </row>
-    <row r="233" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6"/>
       <c r="B233" s="14"/>
       <c r="C233" s="11"/>
@@ -4409,7 +4424,7 @@
       <c r="E233" s="8"/>
       <c r="F233" s="8"/>
     </row>
-    <row r="234" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6"/>
       <c r="B234" s="14"/>
       <c r="C234" s="11"/>
@@ -4417,7 +4432,7 @@
       <c r="E234" s="8"/>
       <c r="F234" s="8"/>
     </row>
-    <row r="235" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6"/>
       <c r="B235" s="14"/>
       <c r="C235" s="11"/>
@@ -4425,7 +4440,7 @@
       <c r="E235" s="8"/>
       <c r="F235" s="8"/>
     </row>
-    <row r="236" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6"/>
       <c r="B236" s="14"/>
       <c r="C236" s="11"/>
@@ -4433,7 +4448,7 @@
       <c r="E236" s="8"/>
       <c r="F236" s="8"/>
     </row>
-    <row r="237" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6"/>
       <c r="B237" s="14"/>
       <c r="C237" s="11"/>
@@ -4441,7 +4456,7 @@
       <c r="E237" s="8"/>
       <c r="F237" s="8"/>
     </row>
-    <row r="238" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6"/>
       <c r="B238" s="14"/>
       <c r="C238" s="11"/>
@@ -4449,7 +4464,7 @@
       <c r="E238" s="8"/>
       <c r="F238" s="8"/>
     </row>
-    <row r="239" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6"/>
       <c r="B239" s="14"/>
       <c r="C239" s="11"/>
@@ -4457,7 +4472,7 @@
       <c r="E239" s="8"/>
       <c r="F239" s="8"/>
     </row>
-    <row r="240" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6"/>
       <c r="B240" s="14"/>
       <c r="C240" s="11"/>
@@ -4465,7 +4480,7 @@
       <c r="E240" s="8"/>
       <c r="F240" s="8"/>
     </row>
-    <row r="241" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6"/>
       <c r="B241" s="14"/>
       <c r="C241" s="11"/>
@@ -4473,7 +4488,7 @@
       <c r="E241" s="8"/>
       <c r="F241" s="8"/>
     </row>
-    <row r="242" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6"/>
       <c r="B242" s="14"/>
       <c r="C242" s="11"/>
@@ -4481,7 +4496,7 @@
       <c r="E242" s="8"/>
       <c r="F242" s="8"/>
     </row>
-    <row r="243" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6"/>
       <c r="B243" s="14"/>
       <c r="C243" s="11"/>
@@ -4489,7 +4504,7 @@
       <c r="E243" s="8"/>
       <c r="F243" s="8"/>
     </row>
-    <row r="244" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6"/>
       <c r="B244" s="14"/>
       <c r="C244" s="11"/>
@@ -4497,7 +4512,7 @@
       <c r="E244" s="8"/>
       <c r="F244" s="8"/>
     </row>
-    <row r="245" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6"/>
       <c r="B245" s="14"/>
       <c r="C245" s="11"/>
@@ -4505,7 +4520,7 @@
       <c r="E245" s="8"/>
       <c r="F245" s="8"/>
     </row>
-    <row r="246" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6"/>
       <c r="B246" s="14"/>
       <c r="C246" s="11"/>
@@ -4513,7 +4528,7 @@
       <c r="E246" s="8"/>
       <c r="F246" s="8"/>
     </row>
-    <row r="247" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6"/>
       <c r="B247" s="14"/>
       <c r="C247" s="11"/>
@@ -4521,7 +4536,7 @@
       <c r="E247" s="8"/>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6"/>
       <c r="B248" s="14"/>
       <c r="C248" s="11"/>
@@ -4529,7 +4544,7 @@
       <c r="E248" s="8"/>
       <c r="F248" s="8"/>
     </row>
-    <row r="249" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6"/>
       <c r="B249" s="14"/>
       <c r="C249" s="11"/>
@@ -4537,7 +4552,7 @@
       <c r="E249" s="8"/>
       <c r="F249" s="8"/>
     </row>
-    <row r="250" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6"/>
       <c r="B250" s="14"/>
       <c r="C250" s="11"/>
@@ -4545,7 +4560,7 @@
       <c r="E250" s="8"/>
       <c r="F250" s="8"/>
     </row>
-    <row r="251" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6"/>
       <c r="B251" s="14"/>
       <c r="C251" s="11"/>
@@ -4553,7 +4568,7 @@
       <c r="E251" s="8"/>
       <c r="F251" s="8"/>
     </row>
-    <row r="252" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6"/>
       <c r="B252" s="14"/>
       <c r="C252" s="11"/>
@@ -4561,7 +4576,7 @@
       <c r="E252" s="8"/>
       <c r="F252" s="8"/>
     </row>
-    <row r="253" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6"/>
       <c r="B253" s="14"/>
       <c r="C253" s="11"/>
@@ -4569,7 +4584,7 @@
       <c r="E253" s="8"/>
       <c r="F253" s="8"/>
     </row>
-    <row r="254" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6"/>
       <c r="B254" s="14"/>
       <c r="C254" s="11"/>
@@ -4577,7 +4592,7 @@
       <c r="E254" s="8"/>
       <c r="F254" s="8"/>
     </row>
-    <row r="255" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6"/>
       <c r="B255" s="14"/>
       <c r="C255" s="11"/>
@@ -4585,7 +4600,7 @@
       <c r="E255" s="8"/>
       <c r="F255" s="8"/>
     </row>
-    <row r="256" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6"/>
       <c r="B256" s="14"/>
       <c r="C256" s="11"/>
@@ -4593,7 +4608,7 @@
       <c r="E256" s="8"/>
       <c r="F256" s="8"/>
     </row>
-    <row r="257" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6"/>
       <c r="B257" s="14"/>
       <c r="C257" s="11"/>
@@ -4601,7 +4616,7 @@
       <c r="E257" s="8"/>
       <c r="F257" s="8"/>
     </row>
-    <row r="258" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6"/>
       <c r="B258" s="14"/>
       <c r="C258" s="11"/>
@@ -4609,7 +4624,7 @@
       <c r="E258" s="8"/>
       <c r="F258" s="8"/>
     </row>
-    <row r="259" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6"/>
       <c r="B259" s="14"/>
       <c r="C259" s="11"/>
@@ -4617,7 +4632,7 @@
       <c r="E259" s="8"/>
       <c r="F259" s="8"/>
     </row>
-    <row r="260" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6"/>
       <c r="B260" s="14"/>
       <c r="C260" s="11"/>
@@ -4625,7 +4640,7 @@
       <c r="E260" s="8"/>
       <c r="F260" s="8"/>
     </row>
-    <row r="261" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6"/>
       <c r="B261" s="14"/>
       <c r="C261" s="11"/>
@@ -4633,7 +4648,7 @@
       <c r="E261" s="8"/>
       <c r="F261" s="8"/>
     </row>
-    <row r="262" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6"/>
       <c r="B262" s="14"/>
       <c r="C262" s="11"/>
@@ -4641,7 +4656,7 @@
       <c r="E262" s="8"/>
       <c r="F262" s="8"/>
     </row>
-    <row r="263" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6"/>
       <c r="B263" s="14"/>
       <c r="C263" s="11"/>
@@ -4649,7 +4664,7 @@
       <c r="E263" s="8"/>
       <c r="F263" s="8"/>
     </row>
-    <row r="264" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6"/>
       <c r="B264" s="14"/>
       <c r="C264" s="11"/>
@@ -4657,7 +4672,7 @@
       <c r="E264" s="8"/>
       <c r="F264" s="8"/>
     </row>
-    <row r="265" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6"/>
       <c r="B265" s="14"/>
       <c r="C265" s="11"/>
@@ -4665,7 +4680,7 @@
       <c r="E265" s="8"/>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6"/>
       <c r="B266" s="14"/>
       <c r="C266" s="11"/>
@@ -4673,7 +4688,7 @@
       <c r="E266" s="8"/>
       <c r="F266" s="8"/>
     </row>
-    <row r="267" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6"/>
       <c r="B267" s="14"/>
       <c r="C267" s="11"/>
@@ -4681,7 +4696,7 @@
       <c r="E267" s="8"/>
       <c r="F267" s="8"/>
     </row>
-    <row r="268" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6"/>
       <c r="B268" s="14"/>
       <c r="C268" s="11"/>
@@ -4689,7 +4704,7 @@
       <c r="E268" s="8"/>
       <c r="F268" s="8"/>
     </row>
-    <row r="269" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6"/>
       <c r="B269" s="14"/>
       <c r="C269" s="11"/>
@@ -4697,7 +4712,7 @@
       <c r="E269" s="8"/>
       <c r="F269" s="8"/>
     </row>
-    <row r="270" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6"/>
       <c r="B270" s="14"/>
       <c r="C270" s="11"/>
@@ -4705,7 +4720,7 @@
       <c r="E270" s="8"/>
       <c r="F270" s="8"/>
     </row>
-    <row r="271" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6"/>
       <c r="B271" s="14"/>
       <c r="C271" s="11"/>
@@ -4713,7 +4728,7 @@
       <c r="E271" s="8"/>
       <c r="F271" s="8"/>
     </row>
-    <row r="272" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6"/>
       <c r="B272" s="14"/>
       <c r="C272" s="11"/>
@@ -4721,7 +4736,7 @@
       <c r="E272" s="8"/>
       <c r="F272" s="8"/>
     </row>
-    <row r="273" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6"/>
       <c r="B273" s="14"/>
       <c r="C273" s="11"/>
@@ -4729,7 +4744,7 @@
       <c r="E273" s="8"/>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6"/>
       <c r="B274" s="14"/>
       <c r="C274" s="11"/>
@@ -4737,7 +4752,7 @@
       <c r="E274" s="8"/>
       <c r="F274" s="8"/>
     </row>
-    <row r="275" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6"/>
       <c r="B275" s="14"/>
       <c r="C275" s="11"/>
@@ -4745,7 +4760,7 @@
       <c r="E275" s="8"/>
       <c r="F275" s="8"/>
     </row>
-    <row r="276" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6"/>
       <c r="B276" s="14"/>
       <c r="C276" s="11"/>
@@ -4753,7 +4768,7 @@
       <c r="E276" s="8"/>
       <c r="F276" s="8"/>
     </row>
-    <row r="277" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6"/>
       <c r="B277" s="14"/>
       <c r="C277" s="11"/>
@@ -4761,7 +4776,7 @@
       <c r="E277" s="8"/>
       <c r="F277" s="8"/>
     </row>
-    <row r="278" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6"/>
       <c r="B278" s="14"/>
       <c r="C278" s="11"/>
@@ -4769,7 +4784,7 @@
       <c r="E278" s="8"/>
       <c r="F278" s="8"/>
     </row>
-    <row r="279" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6"/>
       <c r="B279" s="14"/>
       <c r="C279" s="11"/>
@@ -4777,7 +4792,7 @@
       <c r="E279" s="8"/>
       <c r="F279" s="8"/>
     </row>
-    <row r="280" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6"/>
       <c r="B280" s="14"/>
       <c r="C280" s="11"/>
@@ -4785,7 +4800,7 @@
       <c r="E280" s="8"/>
       <c r="F280" s="8"/>
     </row>
-    <row r="281" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6"/>
       <c r="B281" s="14"/>
       <c r="C281" s="11"/>
@@ -4793,7 +4808,7 @@
       <c r="E281" s="8"/>
       <c r="F281" s="8"/>
     </row>
-    <row r="282" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6"/>
       <c r="B282" s="14"/>
       <c r="C282" s="11"/>
@@ -4801,7 +4816,7 @@
       <c r="E282" s="8"/>
       <c r="F282" s="8"/>
     </row>
-    <row r="283" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6"/>
       <c r="B283" s="14"/>
       <c r="C283" s="11"/>
@@ -4809,7 +4824,7 @@
       <c r="E283" s="8"/>
       <c r="F283" s="8"/>
     </row>
-    <row r="284" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6"/>
       <c r="B284" s="14"/>
       <c r="C284" s="11"/>
@@ -4817,7 +4832,7 @@
       <c r="E284" s="8"/>
       <c r="F284" s="8"/>
     </row>
-    <row r="285" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6"/>
       <c r="B285" s="14"/>
       <c r="C285" s="11"/>
@@ -4825,7 +4840,7 @@
       <c r="E285" s="8"/>
       <c r="F285" s="8"/>
     </row>
-    <row r="286" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6"/>
       <c r="B286" s="14"/>
       <c r="C286" s="11"/>
@@ -4833,7 +4848,7 @@
       <c r="E286" s="8"/>
       <c r="F286" s="8"/>
     </row>
-    <row r="287" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6"/>
       <c r="B287" s="14"/>
       <c r="C287" s="11"/>
@@ -4841,7 +4856,7 @@
       <c r="E287" s="8"/>
       <c r="F287" s="8"/>
     </row>
-    <row r="288" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6"/>
       <c r="B288" s="14"/>
       <c r="C288" s="11"/>
@@ -4849,7 +4864,7 @@
       <c r="E288" s="8"/>
       <c r="F288" s="8"/>
     </row>
-    <row r="289" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6"/>
       <c r="B289" s="14"/>
       <c r="C289" s="11"/>
@@ -4857,7 +4872,7 @@
       <c r="E289" s="8"/>
       <c r="F289" s="8"/>
     </row>
-    <row r="290" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6"/>
       <c r="B290" s="14"/>
       <c r="C290" s="11"/>
@@ -4865,7 +4880,7 @@
       <c r="E290" s="8"/>
       <c r="F290" s="8"/>
     </row>
-    <row r="291" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6"/>
       <c r="B291" s="14"/>
       <c r="C291" s="11"/>
@@ -4873,7 +4888,7 @@
       <c r="E291" s="8"/>
       <c r="F291" s="8"/>
     </row>
-    <row r="292" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6"/>
       <c r="B292" s="14"/>
       <c r="C292" s="11"/>
@@ -4881,7 +4896,7 @@
       <c r="E292" s="8"/>
       <c r="F292" s="8"/>
     </row>
-    <row r="293" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6"/>
       <c r="B293" s="14"/>
       <c r="C293" s="11"/>
@@ -4889,7 +4904,7 @@
       <c r="E293" s="8"/>
       <c r="F293" s="8"/>
     </row>
-    <row r="294" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6"/>
       <c r="B294" s="14"/>
       <c r="C294" s="11"/>
@@ -4897,7 +4912,7 @@
       <c r="E294" s="8"/>
       <c r="F294" s="8"/>
     </row>
-    <row r="295" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6"/>
       <c r="B295" s="14"/>
       <c r="C295" s="11"/>
@@ -4905,7 +4920,7 @@
       <c r="E295" s="8"/>
       <c r="F295" s="8"/>
     </row>
-    <row r="296" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6"/>
       <c r="B296" s="14"/>
       <c r="C296" s="11"/>
@@ -4913,7 +4928,7 @@
       <c r="E296" s="8"/>
       <c r="F296" s="8"/>
     </row>
-    <row r="297" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6"/>
       <c r="B297" s="14"/>
       <c r="C297" s="11"/>
@@ -4921,7 +4936,7 @@
       <c r="E297" s="8"/>
       <c r="F297" s="8"/>
     </row>
-    <row r="298" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6"/>
       <c r="B298" s="14"/>
       <c r="C298" s="11"/>
@@ -4929,7 +4944,7 @@
       <c r="E298" s="8"/>
       <c r="F298" s="8"/>
     </row>
-    <row r="299" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6"/>
       <c r="B299" s="14"/>
       <c r="C299" s="11"/>
@@ -4937,7 +4952,7 @@
       <c r="E299" s="8"/>
       <c r="F299" s="8"/>
     </row>
-    <row r="300" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6"/>
       <c r="B300" s="14"/>
       <c r="C300" s="11"/>
@@ -4945,7 +4960,7 @@
       <c r="E300" s="8"/>
       <c r="F300" s="8"/>
     </row>
-    <row r="301" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6"/>
       <c r="B301" s="14"/>
       <c r="C301" s="11"/>
@@ -4953,7 +4968,7 @@
       <c r="E301" s="8"/>
       <c r="F301" s="8"/>
     </row>
-    <row r="302" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6"/>
       <c r="B302" s="14"/>
       <c r="C302" s="11"/>
@@ -4961,7 +4976,7 @@
       <c r="E302" s="8"/>
       <c r="F302" s="8"/>
     </row>
-    <row r="303" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6"/>
       <c r="B303" s="14"/>
       <c r="C303" s="11"/>
@@ -4969,7 +4984,7 @@
       <c r="E303" s="8"/>
       <c r="F303" s="8"/>
     </row>
-    <row r="304" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6"/>
       <c r="B304" s="14"/>
       <c r="C304" s="11"/>
@@ -4977,7 +4992,7 @@
       <c r="E304" s="8"/>
       <c r="F304" s="8"/>
     </row>
-    <row r="305" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6"/>
       <c r="B305" s="14"/>
       <c r="C305" s="11"/>
@@ -4985,7 +5000,7 @@
       <c r="E305" s="8"/>
       <c r="F305" s="8"/>
     </row>
-    <row r="306" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6"/>
       <c r="B306" s="14"/>
       <c r="C306" s="11"/>
@@ -4993,7 +5008,7 @@
       <c r="E306" s="8"/>
       <c r="F306" s="8"/>
     </row>
-    <row r="307" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6"/>
       <c r="B307" s="14"/>
       <c r="C307" s="11"/>
@@ -5001,7 +5016,7 @@
       <c r="E307" s="8"/>
       <c r="F307" s="8"/>
     </row>
-    <row r="308" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6"/>
       <c r="B308" s="14"/>
       <c r="C308" s="11"/>
@@ -5009,7 +5024,7 @@
       <c r="E308" s="8"/>
       <c r="F308" s="8"/>
     </row>
-    <row r="309" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6"/>
       <c r="B309" s="14"/>
       <c r="C309" s="11"/>
@@ -5017,7 +5032,7 @@
       <c r="E309" s="8"/>
       <c r="F309" s="8"/>
     </row>
-    <row r="310" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6"/>
       <c r="B310" s="14"/>
       <c r="C310" s="11"/>
@@ -5025,7 +5040,7 @@
       <c r="E310" s="8"/>
       <c r="F310" s="8"/>
     </row>
-    <row r="311" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6"/>
       <c r="B311" s="14"/>
       <c r="C311" s="11"/>
@@ -5033,7 +5048,7 @@
       <c r="E311" s="8"/>
       <c r="F311" s="8"/>
     </row>
-    <row r="312" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6"/>
       <c r="B312" s="14"/>
       <c r="C312" s="11"/>
@@ -5041,7 +5056,7 @@
       <c r="E312" s="8"/>
       <c r="F312" s="8"/>
     </row>
-    <row r="313" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6"/>
       <c r="B313" s="14"/>
       <c r="C313" s="11"/>
@@ -5049,7 +5064,7 @@
       <c r="E313" s="8"/>
       <c r="F313" s="8"/>
     </row>
-    <row r="314" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6"/>
       <c r="B314" s="14"/>
       <c r="C314" s="11"/>
@@ -5057,7 +5072,7 @@
       <c r="E314" s="8"/>
       <c r="F314" s="8"/>
     </row>
-    <row r="315" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6"/>
       <c r="B315" s="14"/>
       <c r="C315" s="11"/>
@@ -5065,7 +5080,7 @@
       <c r="E315" s="8"/>
       <c r="F315" s="8"/>
     </row>
-    <row r="316" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6"/>
       <c r="B316" s="14"/>
       <c r="C316" s="11"/>
@@ -5073,7 +5088,7 @@
       <c r="E316" s="8"/>
       <c r="F316" s="8"/>
     </row>
-    <row r="317" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6"/>
       <c r="B317" s="14"/>
       <c r="C317" s="11"/>
@@ -5081,7 +5096,7 @@
       <c r="E317" s="8"/>
       <c r="F317" s="8"/>
     </row>
-    <row r="318" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6"/>
       <c r="B318" s="14"/>
       <c r="C318" s="11"/>
@@ -5089,7 +5104,7 @@
       <c r="E318" s="8"/>
       <c r="F318" s="8"/>
     </row>
-    <row r="319" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6"/>
       <c r="B319" s="14"/>
       <c r="C319" s="11"/>
@@ -5097,7 +5112,7 @@
       <c r="E319" s="8"/>
       <c r="F319" s="8"/>
     </row>
-    <row r="320" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6"/>
       <c r="B320" s="14"/>
       <c r="C320" s="11"/>
@@ -5105,7 +5120,7 @@
       <c r="E320" s="8"/>
       <c r="F320" s="8"/>
     </row>
-    <row r="321" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6"/>
       <c r="B321" s="14"/>
       <c r="C321" s="11"/>
@@ -5113,7 +5128,7 @@
       <c r="E321" s="8"/>
       <c r="F321" s="8"/>
     </row>
-    <row r="322" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6"/>
       <c r="B322" s="14"/>
       <c r="C322" s="11"/>
@@ -5121,7 +5136,7 @@
       <c r="E322" s="8"/>
       <c r="F322" s="8"/>
     </row>
-    <row r="323" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6"/>
       <c r="B323" s="14"/>
       <c r="C323" s="11"/>
@@ -5129,7 +5144,7 @@
       <c r="E323" s="8"/>
       <c r="F323" s="8"/>
     </row>
-    <row r="324" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6"/>
       <c r="B324" s="14"/>
       <c r="C324" s="11"/>
@@ -5137,7 +5152,7 @@
       <c r="E324" s="8"/>
       <c r="F324" s="8"/>
     </row>
-    <row r="325" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6"/>
       <c r="B325" s="14"/>
       <c r="C325" s="11"/>
@@ -5145,7 +5160,7 @@
       <c r="E325" s="8"/>
       <c r="F325" s="8"/>
     </row>
-    <row r="326" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6"/>
       <c r="B326" s="14"/>
       <c r="C326" s="11"/>
@@ -5153,7 +5168,7 @@
       <c r="E326" s="8"/>
       <c r="F326" s="8"/>
     </row>
-    <row r="327" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6"/>
       <c r="B327" s="14"/>
       <c r="C327" s="11"/>
@@ -5161,7 +5176,7 @@
       <c r="E327" s="8"/>
       <c r="F327" s="8"/>
     </row>
-    <row r="328" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6"/>
       <c r="B328" s="14"/>
       <c r="C328" s="11"/>
@@ -5169,7 +5184,7 @@
       <c r="E328" s="8"/>
       <c r="F328" s="8"/>
     </row>
-    <row r="329" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6"/>
       <c r="B329" s="14"/>
       <c r="C329" s="11"/>
@@ -5177,7 +5192,7 @@
       <c r="E329" s="8"/>
       <c r="F329" s="8"/>
     </row>
-    <row r="330" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6"/>
       <c r="B330" s="14"/>
       <c r="C330" s="11"/>
@@ -5185,7 +5200,7 @@
       <c r="E330" s="8"/>
       <c r="F330" s="8"/>
     </row>
-    <row r="331" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6"/>
       <c r="B331" s="14"/>
       <c r="C331" s="11"/>
@@ -5193,7 +5208,7 @@
       <c r="E331" s="8"/>
       <c r="F331" s="8"/>
     </row>
-    <row r="332" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6"/>
       <c r="B332" s="14"/>
       <c r="C332" s="11"/>
@@ -5201,7 +5216,7 @@
       <c r="E332" s="8"/>
       <c r="F332" s="8"/>
     </row>
-    <row r="333" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6"/>
       <c r="B333" s="14"/>
       <c r="C333" s="11"/>
@@ -5209,7 +5224,7 @@
       <c r="E333" s="8"/>
       <c r="F333" s="8"/>
     </row>
-    <row r="334" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6"/>
       <c r="B334" s="14"/>
       <c r="C334" s="11"/>
@@ -5217,7 +5232,7 @@
       <c r="E334" s="8"/>
       <c r="F334" s="8"/>
     </row>
-    <row r="335" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6"/>
       <c r="B335" s="14"/>
       <c r="C335" s="11"/>
@@ -5225,7 +5240,7 @@
       <c r="E335" s="8"/>
       <c r="F335" s="8"/>
     </row>
-    <row r="336" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6"/>
       <c r="B336" s="14"/>
       <c r="C336" s="11"/>
@@ -5233,7 +5248,7 @@
       <c r="E336" s="8"/>
       <c r="F336" s="8"/>
     </row>
-    <row r="337" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6"/>
       <c r="B337" s="14"/>
       <c r="C337" s="11"/>
@@ -5241,7 +5256,7 @@
       <c r="E337" s="8"/>
       <c r="F337" s="8"/>
     </row>
-    <row r="338" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6"/>
       <c r="B338" s="14"/>
       <c r="C338" s="11"/>
@@ -5249,7 +5264,7 @@
       <c r="E338" s="8"/>
       <c r="F338" s="8"/>
     </row>
-    <row r="339" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6"/>
       <c r="B339" s="14"/>
       <c r="C339" s="11"/>
@@ -5257,7 +5272,7 @@
       <c r="E339" s="8"/>
       <c r="F339" s="8"/>
     </row>
-    <row r="340" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6"/>
       <c r="B340" s="14"/>
       <c r="C340" s="11"/>
@@ -5265,7 +5280,7 @@
       <c r="E340" s="8"/>
       <c r="F340" s="8"/>
     </row>
-    <row r="341" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6"/>
       <c r="B341" s="14"/>
       <c r="C341" s="11"/>
@@ -5273,7 +5288,7 @@
       <c r="E341" s="8"/>
       <c r="F341" s="8"/>
     </row>
-    <row r="342" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6"/>
       <c r="B342" s="14"/>
       <c r="C342" s="11"/>
@@ -5281,7 +5296,7 @@
       <c r="E342" s="8"/>
       <c r="F342" s="8"/>
     </row>
-    <row r="343" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6"/>
       <c r="B343" s="14"/>
       <c r="C343" s="11"/>
@@ -5289,7 +5304,7 @@
       <c r="E343" s="8"/>
       <c r="F343" s="8"/>
     </row>
-    <row r="344" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6"/>
       <c r="B344" s="14"/>
       <c r="C344" s="11"/>
@@ -5297,7 +5312,7 @@
       <c r="E344" s="8"/>
       <c r="F344" s="8"/>
     </row>
-    <row r="345" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6"/>
       <c r="B345" s="14"/>
       <c r="C345" s="11"/>
@@ -5305,7 +5320,7 @@
       <c r="E345" s="8"/>
       <c r="F345" s="8"/>
     </row>
-    <row r="346" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6"/>
       <c r="B346" s="14"/>
       <c r="C346" s="11"/>
@@ -5313,7 +5328,7 @@
       <c r="E346" s="8"/>
       <c r="F346" s="8"/>
     </row>
-    <row r="347" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6"/>
       <c r="B347" s="14"/>
       <c r="C347" s="11"/>
@@ -5321,7 +5336,7 @@
       <c r="E347" s="8"/>
       <c r="F347" s="8"/>
     </row>
-    <row r="348" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6"/>
       <c r="B348" s="14"/>
       <c r="C348" s="11"/>
@@ -5329,7 +5344,7 @@
       <c r="E348" s="8"/>
       <c r="F348" s="8"/>
     </row>
-    <row r="349" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6"/>
       <c r="B349" s="14"/>
       <c r="C349" s="11"/>
@@ -5337,7 +5352,7 @@
       <c r="E349" s="8"/>
       <c r="F349" s="8"/>
     </row>
-    <row r="350" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6"/>
       <c r="B350" s="14"/>
       <c r="C350" s="11"/>
@@ -5345,7 +5360,7 @@
       <c r="E350" s="8"/>
       <c r="F350" s="8"/>
     </row>
-    <row r="351" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6"/>
       <c r="B351" s="14"/>
       <c r="C351" s="11"/>
@@ -5353,7 +5368,7 @@
       <c r="E351" s="8"/>
       <c r="F351" s="8"/>
     </row>
-    <row r="352" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6"/>
       <c r="B352" s="14"/>
       <c r="C352" s="11"/>
@@ -5361,7 +5376,7 @@
       <c r="E352" s="8"/>
       <c r="F352" s="8"/>
     </row>
-    <row r="353" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6"/>
       <c r="B353" s="14"/>
       <c r="C353" s="11"/>
@@ -5369,7 +5384,7 @@
       <c r="E353" s="8"/>
       <c r="F353" s="8"/>
     </row>
-    <row r="354" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6"/>
       <c r="B354" s="14"/>
       <c r="C354" s="11"/>
@@ -5377,7 +5392,7 @@
       <c r="E354" s="8"/>
       <c r="F354" s="8"/>
     </row>
-    <row r="355" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6"/>
       <c r="B355" s="14"/>
       <c r="C355" s="11"/>
@@ -5385,7 +5400,7 @@
       <c r="E355" s="8"/>
       <c r="F355" s="8"/>
     </row>
-    <row r="356" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6"/>
       <c r="B356" s="14"/>
       <c r="C356" s="11"/>
@@ -5393,7 +5408,7 @@
       <c r="E356" s="8"/>
       <c r="F356" s="8"/>
     </row>
-    <row r="357" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6"/>
       <c r="B357" s="14"/>
       <c r="C357" s="11"/>
@@ -5401,7 +5416,7 @@
       <c r="E357" s="8"/>
       <c r="F357" s="8"/>
     </row>
-    <row r="358" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6"/>
       <c r="B358" s="14"/>
       <c r="C358" s="11"/>
@@ -5409,7 +5424,7 @@
       <c r="E358" s="8"/>
       <c r="F358" s="8"/>
     </row>
-    <row r="359" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6"/>
       <c r="B359" s="14"/>
       <c r="C359" s="11"/>
@@ -5417,7 +5432,7 @@
       <c r="E359" s="8"/>
       <c r="F359" s="8"/>
     </row>
-    <row r="360" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6"/>
       <c r="B360" s="14"/>
       <c r="C360" s="11"/>
@@ -5425,7 +5440,7 @@
       <c r="E360" s="8"/>
       <c r="F360" s="8"/>
     </row>
-    <row r="361" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6"/>
       <c r="B361" s="14"/>
       <c r="C361" s="11"/>
@@ -5433,7 +5448,7 @@
       <c r="E361" s="8"/>
       <c r="F361" s="8"/>
     </row>
-    <row r="362" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6"/>
       <c r="B362" s="14"/>
       <c r="C362" s="11"/>
@@ -5441,7 +5456,7 @@
       <c r="E362" s="8"/>
       <c r="F362" s="8"/>
     </row>
-    <row r="363" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6"/>
       <c r="B363" s="14"/>
       <c r="C363" s="11"/>
@@ -5449,7 +5464,7 @@
       <c r="E363" s="8"/>
       <c r="F363" s="8"/>
     </row>
-    <row r="364" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6"/>
       <c r="B364" s="14"/>
       <c r="C364" s="11"/>
@@ -5457,7 +5472,7 @@
       <c r="E364" s="8"/>
       <c r="F364" s="8"/>
     </row>
-    <row r="365" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6"/>
       <c r="B365" s="14"/>
       <c r="C365" s="11"/>
@@ -5465,7 +5480,7 @@
       <c r="E365" s="8"/>
       <c r="F365" s="8"/>
     </row>
-    <row r="366" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6"/>
       <c r="B366" s="14"/>
       <c r="C366" s="11"/>
@@ -5473,7 +5488,7 @@
       <c r="E366" s="8"/>
       <c r="F366" s="8"/>
     </row>
-    <row r="367" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6"/>
       <c r="B367" s="14"/>
       <c r="C367" s="11"/>
@@ -5481,7 +5496,7 @@
       <c r="E367" s="8"/>
       <c r="F367" s="8"/>
     </row>
-    <row r="368" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6"/>
       <c r="B368" s="14"/>
       <c r="C368" s="11"/>
@@ -5489,7 +5504,7 @@
       <c r="E368" s="8"/>
       <c r="F368" s="8"/>
     </row>
-    <row r="369" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6"/>
       <c r="B369" s="14"/>
       <c r="C369" s="11"/>
@@ -5497,7 +5512,7 @@
       <c r="E369" s="8"/>
       <c r="F369" s="8"/>
     </row>
-    <row r="370" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6"/>
       <c r="B370" s="14"/>
       <c r="C370" s="11"/>
@@ -5505,7 +5520,7 @@
       <c r="E370" s="8"/>
       <c r="F370" s="8"/>
     </row>
-    <row r="371" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6"/>
       <c r="B371" s="14"/>
       <c r="C371" s="11"/>
@@ -5513,7 +5528,7 @@
       <c r="E371" s="8"/>
       <c r="F371" s="8"/>
     </row>
-    <row r="372" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6"/>
       <c r="B372" s="14"/>
       <c r="C372" s="11"/>
@@ -5521,7 +5536,7 @@
       <c r="E372" s="8"/>
       <c r="F372" s="8"/>
     </row>
-    <row r="373" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6"/>
       <c r="B373" s="14"/>
       <c r="C373" s="11"/>
@@ -5529,7 +5544,7 @@
       <c r="E373" s="8"/>
       <c r="F373" s="8"/>
     </row>
-    <row r="374" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6"/>
       <c r="B374" s="14"/>
       <c r="C374" s="11"/>
@@ -5537,7 +5552,7 @@
       <c r="E374" s="8"/>
       <c r="F374" s="8"/>
     </row>
-    <row r="375" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6"/>
       <c r="B375" s="14"/>
       <c r="C375" s="11"/>
@@ -5545,7 +5560,7 @@
       <c r="E375" s="8"/>
       <c r="F375" s="8"/>
     </row>
-    <row r="376" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6"/>
       <c r="B376" s="14"/>
       <c r="C376" s="11"/>
@@ -5553,7 +5568,7 @@
       <c r="E376" s="8"/>
       <c r="F376" s="8"/>
     </row>
-    <row r="377" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6"/>
       <c r="B377" s="14"/>
       <c r="C377" s="11"/>
@@ -5561,7 +5576,7 @@
       <c r="E377" s="8"/>
       <c r="F377" s="8"/>
     </row>
-    <row r="378" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6"/>
       <c r="B378" s="14"/>
       <c r="C378" s="11"/>
@@ -5569,7 +5584,7 @@
       <c r="E378" s="8"/>
       <c r="F378" s="8"/>
     </row>
-    <row r="379" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6"/>
       <c r="B379" s="14"/>
       <c r="C379" s="11"/>
@@ -5577,7 +5592,7 @@
       <c r="E379" s="8"/>
       <c r="F379" s="8"/>
     </row>
-    <row r="380" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6"/>
       <c r="B380" s="14"/>
       <c r="C380" s="11"/>
@@ -5585,7 +5600,7 @@
       <c r="E380" s="8"/>
       <c r="F380" s="8"/>
     </row>
-    <row r="381" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6"/>
       <c r="B381" s="14"/>
       <c r="C381" s="11"/>
@@ -5593,7 +5608,7 @@
       <c r="E381" s="8"/>
       <c r="F381" s="8"/>
     </row>
-    <row r="382" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6"/>
       <c r="B382" s="14"/>
       <c r="C382" s="11"/>
@@ -5601,7 +5616,7 @@
       <c r="E382" s="8"/>
       <c r="F382" s="8"/>
     </row>
-    <row r="383" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6"/>
       <c r="B383" s="14"/>
       <c r="C383" s="11"/>
@@ -5609,7 +5624,7 @@
       <c r="E383" s="8"/>
       <c r="F383" s="8"/>
     </row>
-    <row r="384" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6"/>
       <c r="B384" s="14"/>
       <c r="C384" s="11"/>
@@ -5617,7 +5632,7 @@
       <c r="E384" s="8"/>
       <c r="F384" s="8"/>
     </row>
-    <row r="385" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6"/>
       <c r="B385" s="14"/>
       <c r="C385" s="11"/>
@@ -5625,7 +5640,7 @@
       <c r="E385" s="8"/>
       <c r="F385" s="8"/>
     </row>
-    <row r="386" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6"/>
       <c r="B386" s="14"/>
       <c r="C386" s="11"/>
@@ -5633,7 +5648,7 @@
       <c r="E386" s="8"/>
       <c r="F386" s="8"/>
     </row>
-    <row r="387" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6"/>
       <c r="B387" s="14"/>
       <c r="C387" s="11"/>
@@ -5641,7 +5656,7 @@
       <c r="E387" s="8"/>
       <c r="F387" s="8"/>
     </row>
-    <row r="388" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6"/>
       <c r="B388" s="14"/>
       <c r="C388" s="11"/>
@@ -5649,7 +5664,7 @@
       <c r="E388" s="8"/>
       <c r="F388" s="8"/>
     </row>
-    <row r="389" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6"/>
       <c r="B389" s="14"/>
       <c r="C389" s="11"/>
@@ -5657,7 +5672,7 @@
       <c r="E389" s="8"/>
       <c r="F389" s="8"/>
     </row>
-    <row r="390" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6"/>
       <c r="B390" s="14"/>
       <c r="C390" s="11"/>
@@ -5665,7 +5680,7 @@
       <c r="E390" s="8"/>
       <c r="F390" s="8"/>
     </row>
-    <row r="391" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6"/>
       <c r="B391" s="14"/>
       <c r="C391" s="11"/>
@@ -5673,7 +5688,7 @@
       <c r="E391" s="8"/>
       <c r="F391" s="8"/>
     </row>
-    <row r="392" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6"/>
       <c r="B392" s="14"/>
       <c r="C392" s="11"/>
@@ -5681,7 +5696,7 @@
       <c r="E392" s="8"/>
       <c r="F392" s="8"/>
     </row>
-    <row r="393" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6"/>
       <c r="B393" s="14"/>
       <c r="C393" s="11"/>
@@ -5689,7 +5704,7 @@
       <c r="E393" s="8"/>
       <c r="F393" s="8"/>
     </row>
-    <row r="394" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6"/>
       <c r="B394" s="14"/>
       <c r="C394" s="11"/>
@@ -5697,7 +5712,7 @@
       <c r="E394" s="8"/>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6"/>
       <c r="B395" s="14"/>
       <c r="C395" s="11"/>
@@ -5705,7 +5720,7 @@
       <c r="E395" s="8"/>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6"/>
       <c r="B396" s="14"/>
       <c r="C396" s="11"/>
@@ -5713,7 +5728,7 @@
       <c r="E396" s="8"/>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6"/>
       <c r="B397" s="14"/>
       <c r="C397" s="11"/>
@@ -5721,7 +5736,7 @@
       <c r="E397" s="8"/>
       <c r="F397" s="8"/>
     </row>
-    <row r="398" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6"/>
       <c r="B398" s="14"/>
       <c r="C398" s="11"/>
@@ -5729,7 +5744,7 @@
       <c r="E398" s="8"/>
       <c r="F398" s="8"/>
     </row>
-    <row r="399" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6"/>
       <c r="B399" s="14"/>
       <c r="C399" s="11"/>
@@ -5737,7 +5752,7 @@
       <c r="E399" s="8"/>
       <c r="F399" s="8"/>
     </row>
-    <row r="400" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6"/>
       <c r="B400" s="14"/>
       <c r="C400" s="11"/>
@@ -5745,7 +5760,7 @@
       <c r="E400" s="8"/>
       <c r="F400" s="8"/>
     </row>
-    <row r="401" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6"/>
       <c r="B401" s="14"/>
       <c r="C401" s="11"/>
@@ -5753,7 +5768,7 @@
       <c r="E401" s="8"/>
       <c r="F401" s="8"/>
     </row>
-    <row r="402" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6"/>
       <c r="B402" s="14"/>
       <c r="C402" s="11"/>
@@ -5761,7 +5776,7 @@
       <c r="E402" s="8"/>
       <c r="F402" s="8"/>
     </row>
-    <row r="403" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6"/>
       <c r="B403" s="14"/>
       <c r="C403" s="11"/>
@@ -5769,7 +5784,7 @@
       <c r="E403" s="8"/>
       <c r="F403" s="8"/>
     </row>
-    <row r="404" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6"/>
       <c r="B404" s="14"/>
       <c r="C404" s="11"/>
@@ -5777,7 +5792,7 @@
       <c r="E404" s="8"/>
       <c r="F404" s="8"/>
     </row>
-    <row r="405" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6"/>
       <c r="B405" s="14"/>
       <c r="C405" s="11"/>
@@ -5785,7 +5800,7 @@
       <c r="E405" s="8"/>
       <c r="F405" s="8"/>
     </row>
-    <row r="406" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6"/>
       <c r="B406" s="14"/>
       <c r="C406" s="11"/>
@@ -5793,7 +5808,7 @@
       <c r="E406" s="8"/>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6"/>
       <c r="B407" s="14"/>
       <c r="C407" s="11"/>
@@ -5801,7 +5816,7 @@
       <c r="E407" s="8"/>
       <c r="F407" s="8"/>
     </row>
-    <row r="408" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6"/>
       <c r="B408" s="14"/>
       <c r="C408" s="11"/>
@@ -5809,7 +5824,7 @@
       <c r="E408" s="8"/>
       <c r="F408" s="8"/>
     </row>
-    <row r="409" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6"/>
       <c r="B409" s="14"/>
       <c r="C409" s="11"/>
@@ -5817,7 +5832,7 @@
       <c r="E409" s="8"/>
       <c r="F409" s="8"/>
     </row>
-    <row r="410" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6"/>
       <c r="B410" s="14"/>
       <c r="C410" s="11"/>
@@ -5825,7 +5840,7 @@
       <c r="E410" s="8"/>
       <c r="F410" s="8"/>
     </row>
-    <row r="411" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6"/>
       <c r="B411" s="14"/>
       <c r="C411" s="11"/>
@@ -5833,7 +5848,7 @@
       <c r="E411" s="8"/>
       <c r="F411" s="8"/>
     </row>
-    <row r="412" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6"/>
       <c r="B412" s="14"/>
       <c r="C412" s="11"/>
@@ -5841,7 +5856,7 @@
       <c r="E412" s="8"/>
       <c r="F412" s="8"/>
     </row>
-    <row r="413" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6"/>
       <c r="B413" s="14"/>
       <c r="C413" s="11"/>
@@ -5849,7 +5864,7 @@
       <c r="E413" s="8"/>
       <c r="F413" s="8"/>
     </row>
-    <row r="414" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6"/>
       <c r="B414" s="14"/>
       <c r="C414" s="11"/>
@@ -5857,7 +5872,7 @@
       <c r="E414" s="8"/>
       <c r="F414" s="8"/>
     </row>
-    <row r="415" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6"/>
       <c r="B415" s="14"/>
       <c r="C415" s="11"/>
@@ -5865,7 +5880,7 @@
       <c r="E415" s="8"/>
       <c r="F415" s="8"/>
     </row>
-    <row r="416" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6"/>
       <c r="B416" s="14"/>
       <c r="C416" s="11"/>
@@ -5873,7 +5888,7 @@
       <c r="E416" s="8"/>
       <c r="F416" s="8"/>
     </row>
-    <row r="417" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6"/>
       <c r="B417" s="14"/>
       <c r="C417" s="11"/>
@@ -5881,7 +5896,7 @@
       <c r="E417" s="8"/>
       <c r="F417" s="8"/>
     </row>
-    <row r="418" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6"/>
       <c r="B418" s="14"/>
       <c r="C418" s="11"/>
@@ -5889,7 +5904,7 @@
       <c r="E418" s="8"/>
       <c r="F418" s="8"/>
     </row>
-    <row r="419" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6"/>
       <c r="B419" s="14"/>
       <c r="C419" s="11"/>
@@ -5897,7 +5912,7 @@
       <c r="E419" s="8"/>
       <c r="F419" s="8"/>
     </row>
-    <row r="420" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6"/>
       <c r="B420" s="14"/>
       <c r="C420" s="11"/>
@@ -5905,7 +5920,7 @@
       <c r="E420" s="8"/>
       <c r="F420" s="8"/>
     </row>
-    <row r="421" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6"/>
       <c r="B421" s="14"/>
       <c r="C421" s="11"/>
@@ -5913,7 +5928,7 @@
       <c r="E421" s="8"/>
       <c r="F421" s="8"/>
     </row>
-    <row r="422" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6"/>
       <c r="B422" s="14"/>
       <c r="C422" s="11"/>
@@ -5921,7 +5936,7 @@
       <c r="E422" s="8"/>
       <c r="F422" s="8"/>
     </row>
-    <row r="423" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6"/>
       <c r="B423" s="14"/>
       <c r="C423" s="11"/>
@@ -5929,7 +5944,7 @@
       <c r="E423" s="8"/>
       <c r="F423" s="8"/>
     </row>
-    <row r="424" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6"/>
       <c r="B424" s="14"/>
       <c r="C424" s="11"/>
@@ -5937,7 +5952,7 @@
       <c r="E424" s="8"/>
       <c r="F424" s="8"/>
     </row>
-    <row r="425" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6"/>
       <c r="B425" s="14"/>
       <c r="C425" s="11"/>
@@ -5945,7 +5960,7 @@
       <c r="E425" s="8"/>
       <c r="F425" s="8"/>
     </row>
-    <row r="426" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="6"/>
       <c r="B426" s="14"/>
       <c r="C426" s="11"/>
@@ -5953,7 +5968,7 @@
       <c r="E426" s="8"/>
       <c r="F426" s="8"/>
     </row>
-    <row r="427" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="6"/>
       <c r="B427" s="14"/>
       <c r="C427" s="11"/>
@@ -5961,7 +5976,7 @@
       <c r="E427" s="8"/>
       <c r="F427" s="8"/>
     </row>
-    <row r="428" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="6"/>
       <c r="B428" s="14"/>
       <c r="C428" s="11"/>
@@ -5969,7 +5984,7 @@
       <c r="E428" s="8"/>
       <c r="F428" s="8"/>
     </row>
-    <row r="429" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="6"/>
       <c r="B429" s="14"/>
       <c r="C429" s="11"/>
@@ -5977,7 +5992,7 @@
       <c r="E429" s="8"/>
       <c r="F429" s="8"/>
     </row>
-    <row r="430" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="6"/>
       <c r="B430" s="14"/>
       <c r="C430" s="11"/>
@@ -5985,7 +6000,7 @@
       <c r="E430" s="8"/>
       <c r="F430" s="8"/>
     </row>
-    <row r="431" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="6"/>
       <c r="B431" s="14"/>
       <c r="C431" s="11"/>
@@ -5993,7 +6008,7 @@
       <c r="E431" s="8"/>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="6"/>
       <c r="B432" s="14"/>
       <c r="C432" s="11"/>
@@ -6001,7 +6016,7 @@
       <c r="E432" s="8"/>
       <c r="F432" s="8"/>
     </row>
-    <row r="433" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="6"/>
       <c r="B433" s="14"/>
       <c r="C433" s="11"/>
@@ -6009,7 +6024,7 @@
       <c r="E433" s="8"/>
       <c r="F433" s="8"/>
     </row>
-    <row r="434" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="6"/>
       <c r="B434" s="14"/>
       <c r="C434" s="11"/>
@@ -6017,7 +6032,7 @@
       <c r="E434" s="8"/>
       <c r="F434" s="8"/>
     </row>
-    <row r="435" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="6"/>
       <c r="B435" s="14"/>
       <c r="C435" s="11"/>
@@ -6025,7 +6040,7 @@
       <c r="E435" s="8"/>
       <c r="F435" s="8"/>
     </row>
-    <row r="436" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="6"/>
       <c r="B436" s="14"/>
       <c r="C436" s="11"/>
@@ -6033,7 +6048,7 @@
       <c r="E436" s="8"/>
       <c r="F436" s="8"/>
     </row>
-    <row r="437" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="6"/>
       <c r="B437" s="14"/>
       <c r="C437" s="11"/>
@@ -6041,7 +6056,7 @@
       <c r="E437" s="8"/>
       <c r="F437" s="8"/>
     </row>
-    <row r="438" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="6"/>
       <c r="B438" s="14"/>
       <c r="C438" s="11"/>
@@ -6049,7 +6064,7 @@
       <c r="E438" s="8"/>
       <c r="F438" s="8"/>
     </row>
-    <row r="439" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="6"/>
       <c r="B439" s="14"/>
       <c r="C439" s="11"/>
@@ -6057,7 +6072,7 @@
       <c r="E439" s="8"/>
       <c r="F439" s="8"/>
     </row>
-    <row r="440" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="6"/>
       <c r="B440" s="14"/>
       <c r="C440" s="11"/>
@@ -6065,7 +6080,7 @@
       <c r="E440" s="8"/>
       <c r="F440" s="8"/>
     </row>
-    <row r="441" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="6"/>
       <c r="B441" s="14"/>
       <c r="C441" s="11"/>
@@ -6073,7 +6088,7 @@
       <c r="E441" s="8"/>
       <c r="F441" s="8"/>
     </row>
-    <row r="442" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="6"/>
       <c r="B442" s="14"/>
       <c r="C442" s="11"/>
@@ -6081,7 +6096,7 @@
       <c r="E442" s="8"/>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="6"/>
       <c r="B443" s="14"/>
       <c r="C443" s="11"/>
@@ -6089,7 +6104,7 @@
       <c r="E443" s="8"/>
       <c r="F443" s="8"/>
     </row>
-    <row r="444" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="6"/>
       <c r="B444" s="14"/>
       <c r="C444" s="11"/>
@@ -6097,7 +6112,7 @@
       <c r="E444" s="8"/>
       <c r="F444" s="8"/>
     </row>
-    <row r="445" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="6"/>
       <c r="B445" s="14"/>
       <c r="C445" s="11"/>
@@ -6105,7 +6120,7 @@
       <c r="E445" s="8"/>
       <c r="F445" s="8"/>
     </row>
-    <row r="446" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="6"/>
       <c r="B446" s="14"/>
       <c r="C446" s="11"/>
@@ -6113,7 +6128,7 @@
       <c r="E446" s="8"/>
       <c r="F446" s="8"/>
     </row>
-    <row r="447" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="6"/>
       <c r="B447" s="14"/>
       <c r="C447" s="11"/>
@@ -6121,7 +6136,7 @@
       <c r="E447" s="8"/>
       <c r="F447" s="8"/>
     </row>
-    <row r="448" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="6"/>
       <c r="B448" s="14"/>
       <c r="C448" s="11"/>
@@ -6129,7 +6144,7 @@
       <c r="E448" s="8"/>
       <c r="F448" s="8"/>
     </row>
-    <row r="449" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="6"/>
       <c r="B449" s="14"/>
       <c r="C449" s="11"/>
@@ -6137,7 +6152,7 @@
       <c r="E449" s="8"/>
       <c r="F449" s="8"/>
     </row>
-    <row r="450" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="6"/>
       <c r="B450" s="14"/>
       <c r="C450" s="11"/>
@@ -6145,7 +6160,7 @@
       <c r="E450" s="8"/>
       <c r="F450" s="8"/>
     </row>
-    <row r="451" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="6"/>
       <c r="B451" s="14"/>
       <c r="C451" s="11"/>
@@ -6153,7 +6168,7 @@
       <c r="E451" s="8"/>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="6"/>
       <c r="B452" s="14"/>
       <c r="C452" s="11"/>
@@ -6161,7 +6176,7 @@
       <c r="E452" s="8"/>
       <c r="F452" s="8"/>
     </row>
-    <row r="453" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="6"/>
       <c r="B453" s="14"/>
       <c r="C453" s="11"/>
@@ -6169,7 +6184,7 @@
       <c r="E453" s="8"/>
       <c r="F453" s="8"/>
     </row>
-    <row r="454" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="6"/>
       <c r="B454" s="14"/>
       <c r="C454" s="11"/>
@@ -6177,7 +6192,7 @@
       <c r="E454" s="8"/>
       <c r="F454" s="8"/>
     </row>
-    <row r="455" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="6"/>
       <c r="B455" s="14"/>
       <c r="C455" s="11"/>
@@ -6185,7 +6200,7 @@
       <c r="E455" s="8"/>
       <c r="F455" s="8"/>
     </row>
-    <row r="456" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="6"/>
       <c r="B456" s="14"/>
       <c r="C456" s="11"/>
@@ -6193,7 +6208,7 @@
       <c r="E456" s="8"/>
       <c r="F456" s="8"/>
     </row>
-    <row r="457" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="6"/>
       <c r="B457" s="14"/>
       <c r="C457" s="11"/>
@@ -6201,7 +6216,7 @@
       <c r="E457" s="8"/>
       <c r="F457" s="8"/>
     </row>
-    <row r="458" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="6"/>
       <c r="B458" s="14"/>
       <c r="C458" s="11"/>
@@ -6209,7 +6224,7 @@
       <c r="E458" s="8"/>
       <c r="F458" s="8"/>
     </row>
-    <row r="459" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="6"/>
       <c r="B459" s="14"/>
       <c r="C459" s="11"/>
@@ -6217,7 +6232,7 @@
       <c r="E459" s="8"/>
       <c r="F459" s="8"/>
     </row>
-    <row r="460" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="6"/>
       <c r="B460" s="14"/>
       <c r="C460" s="11"/>
@@ -6225,7 +6240,7 @@
       <c r="E460" s="8"/>
       <c r="F460" s="8"/>
     </row>
-    <row r="461" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="6"/>
       <c r="B461" s="14"/>
       <c r="C461" s="11"/>
@@ -6233,7 +6248,7 @@
       <c r="E461" s="8"/>
       <c r="F461" s="8"/>
     </row>
-    <row r="462" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="6"/>
       <c r="B462" s="14"/>
       <c r="C462" s="11"/>
@@ -6241,7 +6256,7 @@
       <c r="E462" s="8"/>
       <c r="F462" s="8"/>
     </row>
-    <row r="463" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="6"/>
       <c r="B463" s="14"/>
       <c r="C463" s="11"/>
@@ -6249,7 +6264,7 @@
       <c r="E463" s="8"/>
       <c r="F463" s="8"/>
     </row>
-    <row r="464" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="6"/>
       <c r="B464" s="14"/>
       <c r="C464" s="11"/>
@@ -6257,7 +6272,7 @@
       <c r="E464" s="8"/>
       <c r="F464" s="8"/>
     </row>
-    <row r="465" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="6"/>
       <c r="B465" s="14"/>
       <c r="C465" s="11"/>
@@ -6265,7 +6280,7 @@
       <c r="E465" s="8"/>
       <c r="F465" s="8"/>
     </row>
-    <row r="466" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="6"/>
       <c r="B466" s="14"/>
       <c r="C466" s="11"/>
@@ -6273,7 +6288,7 @@
       <c r="E466" s="8"/>
       <c r="F466" s="8"/>
     </row>
-    <row r="467" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="6"/>
       <c r="B467" s="14"/>
       <c r="C467" s="11"/>
@@ -6281,7 +6296,7 @@
       <c r="E467" s="8"/>
       <c r="F467" s="8"/>
     </row>
-    <row r="468" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="6"/>
       <c r="B468" s="14"/>
       <c r="C468" s="11"/>
@@ -6289,7 +6304,7 @@
       <c r="E468" s="8"/>
       <c r="F468" s="8"/>
     </row>
-    <row r="469" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="6"/>
       <c r="B469" s="14"/>
       <c r="C469" s="11"/>
@@ -6297,7 +6312,7 @@
       <c r="E469" s="8"/>
       <c r="F469" s="8"/>
     </row>
-    <row r="470" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="6"/>
       <c r="B470" s="14"/>
       <c r="C470" s="11"/>
@@ -6305,7 +6320,7 @@
       <c r="E470" s="8"/>
       <c r="F470" s="8"/>
     </row>
-    <row r="471" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="6"/>
       <c r="B471" s="14"/>
       <c r="C471" s="11"/>
@@ -6313,7 +6328,7 @@
       <c r="E471" s="8"/>
       <c r="F471" s="8"/>
     </row>
-    <row r="472" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="6"/>
       <c r="B472" s="14"/>
       <c r="C472" s="11"/>
@@ -6321,7 +6336,7 @@
       <c r="E472" s="8"/>
       <c r="F472" s="8"/>
     </row>
-    <row r="473" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="6"/>
       <c r="B473" s="14"/>
       <c r="C473" s="11"/>
@@ -6329,7 +6344,7 @@
       <c r="E473" s="8"/>
       <c r="F473" s="8"/>
     </row>
-    <row r="474" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="6"/>
       <c r="B474" s="14"/>
       <c r="C474" s="11"/>
@@ -6337,7 +6352,7 @@
       <c r="E474" s="8"/>
       <c r="F474" s="8"/>
     </row>
-    <row r="475" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="6"/>
       <c r="B475" s="14"/>
       <c r="C475" s="11"/>
@@ -6345,7 +6360,7 @@
       <c r="E475" s="8"/>
       <c r="F475" s="8"/>
     </row>
-    <row r="476" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="6"/>
       <c r="B476" s="14"/>
       <c r="C476" s="11"/>
@@ -6353,7 +6368,7 @@
       <c r="E476" s="8"/>
       <c r="F476" s="8"/>
     </row>
-    <row r="477" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="6"/>
       <c r="B477" s="14"/>
       <c r="C477" s="11"/>
@@ -6361,7 +6376,7 @@
       <c r="E477" s="8"/>
       <c r="F477" s="8"/>
     </row>
-    <row r="478" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="6"/>
       <c r="B478" s="14"/>
       <c r="C478" s="11"/>
@@ -6369,7 +6384,7 @@
       <c r="E478" s="8"/>
       <c r="F478" s="8"/>
     </row>
-    <row r="479" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="6"/>
       <c r="B479" s="14"/>
       <c r="C479" s="11"/>
@@ -6377,7 +6392,7 @@
       <c r="E479" s="8"/>
       <c r="F479" s="8"/>
     </row>
-    <row r="480" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="6"/>
       <c r="B480" s="14"/>
       <c r="C480" s="11"/>
@@ -6385,7 +6400,7 @@
       <c r="E480" s="8"/>
       <c r="F480" s="8"/>
     </row>
-    <row r="481" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="6"/>
       <c r="B481" s="14"/>
       <c r="C481" s="11"/>
@@ -6393,7 +6408,7 @@
       <c r="E481" s="8"/>
       <c r="F481" s="8"/>
     </row>
-    <row r="482" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="6"/>
       <c r="B482" s="14"/>
       <c r="C482" s="11"/>
@@ -6401,7 +6416,7 @@
       <c r="E482" s="8"/>
       <c r="F482" s="8"/>
     </row>
-    <row r="483" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="6"/>
       <c r="B483" s="14"/>
       <c r="C483" s="11"/>
@@ -6409,7 +6424,7 @@
       <c r="E483" s="8"/>
       <c r="F483" s="8"/>
     </row>
-    <row r="484" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="6"/>
       <c r="B484" s="14"/>
       <c r="C484" s="11"/>
@@ -6417,7 +6432,7 @@
       <c r="E484" s="8"/>
       <c r="F484" s="8"/>
     </row>
-    <row r="485" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="6"/>
       <c r="B485" s="14"/>
       <c r="C485" s="11"/>
@@ -6425,7 +6440,7 @@
       <c r="E485" s="8"/>
       <c r="F485" s="8"/>
     </row>
-    <row r="486" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="6"/>
       <c r="B486" s="14"/>
       <c r="C486" s="11"/>
@@ -6433,7 +6448,7 @@
       <c r="E486" s="8"/>
       <c r="F486" s="8"/>
     </row>
-    <row r="487" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="6"/>
       <c r="B487" s="14"/>
       <c r="C487" s="11"/>
@@ -6441,7 +6456,7 @@
       <c r="E487" s="8"/>
       <c r="F487" s="8"/>
     </row>
-    <row r="488" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="6"/>
       <c r="B488" s="14"/>
       <c r="C488" s="11"/>
@@ -6449,7 +6464,7 @@
       <c r="E488" s="8"/>
       <c r="F488" s="8"/>
     </row>
-    <row r="489" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="6"/>
       <c r="B489" s="14"/>
       <c r="C489" s="11"/>
@@ -6457,7 +6472,7 @@
       <c r="E489" s="8"/>
       <c r="F489" s="8"/>
     </row>
-    <row r="490" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="6"/>
       <c r="B490" s="14"/>
       <c r="C490" s="11"/>
@@ -6465,7 +6480,7 @@
       <c r="E490" s="8"/>
       <c r="F490" s="8"/>
     </row>
-    <row r="491" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="6"/>
       <c r="B491" s="14"/>
       <c r="C491" s="11"/>
@@ -6473,7 +6488,7 @@
       <c r="E491" s="8"/>
       <c r="F491" s="8"/>
     </row>
-    <row r="492" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="6"/>
       <c r="B492" s="14"/>
       <c r="C492" s="11"/>
@@ -6481,7 +6496,7 @@
       <c r="E492" s="8"/>
       <c r="F492" s="8"/>
     </row>
-    <row r="493" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="6"/>
       <c r="B493" s="14"/>
       <c r="C493" s="11"/>
@@ -6489,7 +6504,7 @@
       <c r="E493" s="8"/>
       <c r="F493" s="8"/>
     </row>
-    <row r="494" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="6"/>
       <c r="B494" s="14"/>
       <c r="C494" s="11"/>
@@ -6497,7 +6512,7 @@
       <c r="E494" s="8"/>
       <c r="F494" s="8"/>
     </row>
-    <row r="495" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="6"/>
       <c r="B495" s="14"/>
       <c r="C495" s="11"/>
@@ -6505,7 +6520,7 @@
       <c r="E495" s="8"/>
       <c r="F495" s="8"/>
     </row>
-    <row r="496" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="6"/>
       <c r="B496" s="14"/>
       <c r="C496" s="11"/>
@@ -6513,7 +6528,7 @@
       <c r="E496" s="8"/>
       <c r="F496" s="8"/>
     </row>
-    <row r="497" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="6"/>
       <c r="B497" s="14"/>
       <c r="C497" s="11"/>
@@ -6521,7 +6536,7 @@
       <c r="E497" s="8"/>
       <c r="F497" s="8"/>
     </row>
-    <row r="498" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="6"/>
       <c r="B498" s="14"/>
       <c r="C498" s="11"/>
@@ -6529,7 +6544,7 @@
       <c r="E498" s="8"/>
       <c r="F498" s="8"/>
     </row>
-    <row r="499" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="6"/>
       <c r="B499" s="14"/>
       <c r="C499" s="11"/>
@@ -6537,7 +6552,7 @@
       <c r="E499" s="8"/>
       <c r="F499" s="8"/>
     </row>
-    <row r="500" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="6"/>
       <c r="B500" s="14"/>
       <c r="C500" s="11"/>
@@ -6545,7 +6560,7 @@
       <c r="E500" s="8"/>
       <c r="F500" s="8"/>
     </row>
-    <row r="501" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A501" s="6"/>
       <c r="B501" s="14"/>
       <c r="C501" s="11"/>
@@ -6553,7 +6568,7 @@
       <c r="E501" s="8"/>
       <c r="F501" s="8"/>
     </row>
-    <row r="502" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A502" s="6"/>
       <c r="B502" s="14"/>
       <c r="C502" s="11"/>
@@ -6561,7 +6576,7 @@
       <c r="E502" s="8"/>
       <c r="F502" s="8"/>
     </row>
-    <row r="503" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A503" s="6"/>
       <c r="B503" s="14"/>
       <c r="C503" s="11"/>
@@ -6606,13 +6621,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC8CEF3-AF3E-4D54-8188-1302D62F0F60}">
   <dimension ref="A1:B500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.8984375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.19921875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="24.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.25" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
@@ -6620,7 +6635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
@@ -6629,7 +6644,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>8</v>
       </c>
@@ -6638,7 +6653,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
@@ -6647,7 +6662,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>10</v>
       </c>
@@ -6656,7 +6671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>11</v>
       </c>
@@ -6665,7 +6680,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>6</v>
       </c>
@@ -6674,7 +6689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>12</v>
       </c>
@@ -6683,7 +6698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>13</v>
       </c>
@@ -6692,1967 +6707,1967 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="11"/>
     </row>
-    <row r="12" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="11"/>
     </row>
-    <row r="13" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="11"/>
     </row>
-    <row r="14" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="11"/>
     </row>
-    <row r="15" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="11"/>
     </row>
-    <row r="16" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="11"/>
     </row>
-    <row r="17" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="11"/>
     </row>
-    <row r="18" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="11"/>
     </row>
-    <row r="19" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="11"/>
     </row>
-    <row r="20" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="11"/>
     </row>
-    <row r="21" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="11"/>
     </row>
-    <row r="22" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="11"/>
     </row>
-    <row r="23" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="11"/>
     </row>
-    <row r="24" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="11"/>
     </row>
-    <row r="25" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="11"/>
     </row>
-    <row r="27" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="11"/>
     </row>
-    <row r="28" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="11"/>
     </row>
-    <row r="29" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="11"/>
     </row>
-    <row r="30" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="11"/>
     </row>
-    <row r="31" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="11"/>
     </row>
-    <row r="32" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="11"/>
     </row>
-    <row r="33" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="11"/>
     </row>
-    <row r="34" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="11"/>
     </row>
-    <row r="35" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="11"/>
     </row>
-    <row r="36" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="11"/>
     </row>
-    <row r="37" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="11"/>
     </row>
-    <row r="38" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="11"/>
     </row>
-    <row r="39" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="11"/>
     </row>
-    <row r="40" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="11"/>
     </row>
-    <row r="41" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="11"/>
     </row>
-    <row r="42" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="11"/>
     </row>
-    <row r="43" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="11"/>
     </row>
-    <row r="44" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="11"/>
     </row>
-    <row r="45" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="11"/>
     </row>
-    <row r="46" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="11"/>
     </row>
-    <row r="47" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="11"/>
     </row>
-    <row r="48" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="11"/>
     </row>
-    <row r="49" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="11"/>
     </row>
-    <row r="50" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="11"/>
     </row>
-    <row r="51" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="11"/>
     </row>
-    <row r="52" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="11"/>
     </row>
-    <row r="53" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="11"/>
     </row>
-    <row r="54" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="11"/>
     </row>
-    <row r="55" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="11"/>
     </row>
-    <row r="56" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="11"/>
     </row>
-    <row r="57" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="11"/>
     </row>
-    <row r="58" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="11"/>
     </row>
-    <row r="59" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="11"/>
     </row>
-    <row r="60" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="11"/>
     </row>
-    <row r="61" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="11"/>
     </row>
-    <row r="62" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="11"/>
     </row>
-    <row r="63" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="11"/>
     </row>
-    <row r="64" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="11"/>
     </row>
-    <row r="65" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="11"/>
     </row>
-    <row r="66" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="11"/>
     </row>
-    <row r="67" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="11"/>
     </row>
-    <row r="68" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="11"/>
     </row>
-    <row r="69" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="11"/>
     </row>
-    <row r="70" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="11"/>
     </row>
-    <row r="71" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
       <c r="B71" s="11"/>
     </row>
-    <row r="72" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="11"/>
     </row>
-    <row r="73" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="11"/>
     </row>
-    <row r="74" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="11"/>
     </row>
-    <row r="75" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="11"/>
     </row>
-    <row r="76" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="11"/>
     </row>
-    <row r="77" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="11"/>
     </row>
-    <row r="78" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="11"/>
     </row>
-    <row r="79" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="11"/>
     </row>
-    <row r="80" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="11"/>
     </row>
-    <row r="81" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="11"/>
     </row>
-    <row r="82" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="11"/>
     </row>
-    <row r="83" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="11"/>
     </row>
-    <row r="84" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="11"/>
     </row>
-    <row r="85" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="11"/>
     </row>
-    <row r="86" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="11"/>
     </row>
-    <row r="87" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="11"/>
     </row>
-    <row r="88" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="11"/>
     </row>
-    <row r="89" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="11"/>
     </row>
-    <row r="90" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="11"/>
     </row>
-    <row r="91" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="11"/>
     </row>
-    <row r="92" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="11"/>
     </row>
-    <row r="93" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="11"/>
     </row>
-    <row r="94" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="11"/>
     </row>
-    <row r="95" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="11"/>
     </row>
-    <row r="96" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="11"/>
     </row>
-    <row r="97" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="11"/>
     </row>
-    <row r="98" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="11"/>
     </row>
-    <row r="99" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="11"/>
     </row>
-    <row r="100" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="11"/>
     </row>
-    <row r="101" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
       <c r="B101" s="11"/>
     </row>
-    <row r="102" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="11"/>
     </row>
-    <row r="103" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="11"/>
     </row>
-    <row r="104" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6"/>
       <c r="B104" s="11"/>
     </row>
-    <row r="105" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6"/>
       <c r="B105" s="11"/>
     </row>
-    <row r="106" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6"/>
       <c r="B106" s="11"/>
     </row>
-    <row r="107" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="B107" s="11"/>
     </row>
-    <row r="108" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="B108" s="11"/>
     </row>
-    <row r="109" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="B109" s="11"/>
     </row>
-    <row r="110" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="B110" s="11"/>
     </row>
-    <row r="111" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6"/>
       <c r="B111" s="11"/>
     </row>
-    <row r="112" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6"/>
       <c r="B112" s="11"/>
     </row>
-    <row r="113" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
       <c r="B113" s="11"/>
     </row>
-    <row r="114" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6"/>
       <c r="B114" s="11"/>
     </row>
-    <row r="115" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6"/>
       <c r="B115" s="11"/>
     </row>
-    <row r="116" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6"/>
       <c r="B116" s="11"/>
     </row>
-    <row r="117" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6"/>
       <c r="B117" s="11"/>
     </row>
-    <row r="118" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6"/>
       <c r="B118" s="11"/>
     </row>
-    <row r="119" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6"/>
       <c r="B119" s="11"/>
     </row>
-    <row r="120" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6"/>
       <c r="B120" s="11"/>
     </row>
-    <row r="121" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6"/>
       <c r="B121" s="11"/>
     </row>
-    <row r="122" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6"/>
       <c r="B122" s="11"/>
     </row>
-    <row r="123" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6"/>
       <c r="B123" s="11"/>
     </row>
-    <row r="124" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6"/>
       <c r="B124" s="11"/>
     </row>
-    <row r="125" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6"/>
       <c r="B125" s="11"/>
     </row>
-    <row r="126" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6"/>
       <c r="B126" s="11"/>
     </row>
-    <row r="127" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6"/>
       <c r="B127" s="11"/>
     </row>
-    <row r="128" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6"/>
       <c r="B128" s="11"/>
     </row>
-    <row r="129" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6"/>
       <c r="B129" s="11"/>
     </row>
-    <row r="130" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6"/>
       <c r="B130" s="11"/>
     </row>
-    <row r="131" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6"/>
       <c r="B131" s="11"/>
     </row>
-    <row r="132" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6"/>
       <c r="B132" s="11"/>
     </row>
-    <row r="133" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6"/>
       <c r="B133" s="11"/>
     </row>
-    <row r="134" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6"/>
       <c r="B134" s="11"/>
     </row>
-    <row r="135" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6"/>
       <c r="B135" s="11"/>
     </row>
-    <row r="136" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6"/>
       <c r="B136" s="11"/>
     </row>
-    <row r="137" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6"/>
       <c r="B137" s="11"/>
     </row>
-    <row r="138" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6"/>
       <c r="B138" s="11"/>
     </row>
-    <row r="139" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6"/>
       <c r="B139" s="11"/>
     </row>
-    <row r="140" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6"/>
       <c r="B140" s="11"/>
     </row>
-    <row r="141" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6"/>
       <c r="B141" s="11"/>
     </row>
-    <row r="142" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6"/>
       <c r="B142" s="11"/>
     </row>
-    <row r="143" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6"/>
       <c r="B143" s="11"/>
     </row>
-    <row r="144" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6"/>
       <c r="B144" s="11"/>
     </row>
-    <row r="145" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6"/>
       <c r="B145" s="11"/>
     </row>
-    <row r="146" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6"/>
       <c r="B146" s="11"/>
     </row>
-    <row r="147" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6"/>
       <c r="B147" s="11"/>
     </row>
-    <row r="148" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6"/>
       <c r="B148" s="11"/>
     </row>
-    <row r="149" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6"/>
       <c r="B149" s="11"/>
     </row>
-    <row r="150" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6"/>
       <c r="B150" s="11"/>
     </row>
-    <row r="151" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6"/>
       <c r="B151" s="11"/>
     </row>
-    <row r="152" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6"/>
       <c r="B152" s="11"/>
     </row>
-    <row r="153" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6"/>
       <c r="B153" s="11"/>
     </row>
-    <row r="154" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6"/>
       <c r="B154" s="11"/>
     </row>
-    <row r="155" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6"/>
       <c r="B155" s="11"/>
     </row>
-    <row r="156" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6"/>
       <c r="B156" s="11"/>
     </row>
-    <row r="157" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6"/>
       <c r="B157" s="11"/>
     </row>
-    <row r="158" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6"/>
       <c r="B158" s="11"/>
     </row>
-    <row r="159" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6"/>
       <c r="B159" s="11"/>
     </row>
-    <row r="160" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6"/>
       <c r="B160" s="11"/>
     </row>
-    <row r="161" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6"/>
       <c r="B161" s="11"/>
     </row>
-    <row r="162" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6"/>
       <c r="B162" s="11"/>
     </row>
-    <row r="163" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6"/>
       <c r="B163" s="11"/>
     </row>
-    <row r="164" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6"/>
       <c r="B164" s="11"/>
     </row>
-    <row r="165" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6"/>
       <c r="B165" s="11"/>
     </row>
-    <row r="166" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6"/>
       <c r="B166" s="11"/>
     </row>
-    <row r="167" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6"/>
       <c r="B167" s="11"/>
     </row>
-    <row r="168" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6"/>
       <c r="B168" s="11"/>
     </row>
-    <row r="169" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6"/>
       <c r="B169" s="11"/>
     </row>
-    <row r="170" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6"/>
       <c r="B170" s="11"/>
     </row>
-    <row r="171" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6"/>
       <c r="B171" s="11"/>
     </row>
-    <row r="172" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6"/>
       <c r="B172" s="11"/>
     </row>
-    <row r="173" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6"/>
       <c r="B173" s="11"/>
     </row>
-    <row r="174" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6"/>
       <c r="B174" s="11"/>
     </row>
-    <row r="175" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6"/>
       <c r="B175" s="11"/>
     </row>
-    <row r="176" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6"/>
       <c r="B176" s="11"/>
     </row>
-    <row r="177" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6"/>
       <c r="B177" s="11"/>
     </row>
-    <row r="178" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6"/>
       <c r="B178" s="11"/>
     </row>
-    <row r="179" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6"/>
       <c r="B179" s="11"/>
     </row>
-    <row r="180" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6"/>
       <c r="B180" s="11"/>
     </row>
-    <row r="181" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6"/>
       <c r="B181" s="11"/>
     </row>
-    <row r="182" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6"/>
       <c r="B182" s="11"/>
     </row>
-    <row r="183" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6"/>
       <c r="B183" s="11"/>
     </row>
-    <row r="184" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6"/>
       <c r="B184" s="11"/>
     </row>
-    <row r="185" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6"/>
       <c r="B185" s="11"/>
     </row>
-    <row r="186" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6"/>
       <c r="B186" s="11"/>
     </row>
-    <row r="187" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6"/>
       <c r="B187" s="11"/>
     </row>
-    <row r="188" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6"/>
       <c r="B188" s="11"/>
     </row>
-    <row r="189" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6"/>
       <c r="B189" s="11"/>
     </row>
-    <row r="190" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6"/>
       <c r="B190" s="11"/>
     </row>
-    <row r="191" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6"/>
       <c r="B191" s="11"/>
     </row>
-    <row r="192" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6"/>
       <c r="B192" s="11"/>
     </row>
-    <row r="193" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6"/>
       <c r="B193" s="11"/>
     </row>
-    <row r="194" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6"/>
       <c r="B194" s="11"/>
     </row>
-    <row r="195" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6"/>
       <c r="B195" s="11"/>
     </row>
-    <row r="196" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6"/>
       <c r="B196" s="11"/>
     </row>
-    <row r="197" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6"/>
       <c r="B197" s="11"/>
     </row>
-    <row r="198" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6"/>
       <c r="B198" s="11"/>
     </row>
-    <row r="199" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6"/>
       <c r="B199" s="11"/>
     </row>
-    <row r="200" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6"/>
       <c r="B200" s="11"/>
     </row>
-    <row r="201" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6"/>
       <c r="B201" s="11"/>
     </row>
-    <row r="202" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6"/>
       <c r="B202" s="11"/>
     </row>
-    <row r="203" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6"/>
       <c r="B203" s="11"/>
     </row>
-    <row r="204" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6"/>
       <c r="B204" s="11"/>
     </row>
-    <row r="205" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6"/>
       <c r="B205" s="11"/>
     </row>
-    <row r="206" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6"/>
       <c r="B206" s="11"/>
     </row>
-    <row r="207" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6"/>
       <c r="B207" s="11"/>
     </row>
-    <row r="208" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6"/>
       <c r="B208" s="11"/>
     </row>
-    <row r="209" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6"/>
       <c r="B209" s="11"/>
     </row>
-    <row r="210" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6"/>
       <c r="B210" s="11"/>
     </row>
-    <row r="211" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6"/>
       <c r="B211" s="11"/>
     </row>
-    <row r="212" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6"/>
       <c r="B212" s="11"/>
     </row>
-    <row r="213" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6"/>
       <c r="B213" s="11"/>
     </row>
-    <row r="214" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6"/>
       <c r="B214" s="11"/>
     </row>
-    <row r="215" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6"/>
       <c r="B215" s="11"/>
     </row>
-    <row r="216" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6"/>
       <c r="B216" s="11"/>
     </row>
-    <row r="217" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6"/>
       <c r="B217" s="11"/>
     </row>
-    <row r="218" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6"/>
       <c r="B218" s="11"/>
     </row>
-    <row r="219" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6"/>
       <c r="B219" s="11"/>
     </row>
-    <row r="220" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6"/>
       <c r="B220" s="11"/>
     </row>
-    <row r="221" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6"/>
       <c r="B221" s="11"/>
     </row>
-    <row r="222" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6"/>
       <c r="B222" s="11"/>
     </row>
-    <row r="223" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6"/>
       <c r="B223" s="11"/>
     </row>
-    <row r="224" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6"/>
       <c r="B224" s="11"/>
     </row>
-    <row r="225" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6"/>
       <c r="B225" s="11"/>
     </row>
-    <row r="226" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6"/>
       <c r="B226" s="11"/>
     </row>
-    <row r="227" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6"/>
       <c r="B227" s="11"/>
     </row>
-    <row r="228" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6"/>
       <c r="B228" s="11"/>
     </row>
-    <row r="229" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6"/>
       <c r="B229" s="11"/>
     </row>
-    <row r="230" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6"/>
       <c r="B230" s="11"/>
     </row>
-    <row r="231" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6"/>
       <c r="B231" s="11"/>
     </row>
-    <row r="232" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6"/>
       <c r="B232" s="11"/>
     </row>
-    <row r="233" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6"/>
       <c r="B233" s="11"/>
     </row>
-    <row r="234" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6"/>
       <c r="B234" s="11"/>
     </row>
-    <row r="235" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6"/>
       <c r="B235" s="11"/>
     </row>
-    <row r="236" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6"/>
       <c r="B236" s="11"/>
     </row>
-    <row r="237" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6"/>
       <c r="B237" s="11"/>
     </row>
-    <row r="238" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6"/>
       <c r="B238" s="11"/>
     </row>
-    <row r="239" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6"/>
       <c r="B239" s="11"/>
     </row>
-    <row r="240" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6"/>
       <c r="B240" s="11"/>
     </row>
-    <row r="241" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6"/>
       <c r="B241" s="11"/>
     </row>
-    <row r="242" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6"/>
       <c r="B242" s="11"/>
     </row>
-    <row r="243" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6"/>
       <c r="B243" s="11"/>
     </row>
-    <row r="244" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6"/>
       <c r="B244" s="11"/>
     </row>
-    <row r="245" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6"/>
       <c r="B245" s="11"/>
     </row>
-    <row r="246" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6"/>
       <c r="B246" s="11"/>
     </row>
-    <row r="247" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6"/>
       <c r="B247" s="11"/>
     </row>
-    <row r="248" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6"/>
       <c r="B248" s="11"/>
     </row>
-    <row r="249" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6"/>
       <c r="B249" s="11"/>
     </row>
-    <row r="250" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6"/>
       <c r="B250" s="11"/>
     </row>
-    <row r="251" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6"/>
       <c r="B251" s="11"/>
     </row>
-    <row r="252" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6"/>
       <c r="B252" s="11"/>
     </row>
-    <row r="253" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6"/>
       <c r="B253" s="11"/>
     </row>
-    <row r="254" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6"/>
       <c r="B254" s="11"/>
     </row>
-    <row r="255" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6"/>
       <c r="B255" s="11"/>
     </row>
-    <row r="256" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6"/>
       <c r="B256" s="11"/>
     </row>
-    <row r="257" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6"/>
       <c r="B257" s="11"/>
     </row>
-    <row r="258" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6"/>
       <c r="B258" s="11"/>
     </row>
-    <row r="259" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6"/>
       <c r="B259" s="11"/>
     </row>
-    <row r="260" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6"/>
       <c r="B260" s="11"/>
     </row>
-    <row r="261" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6"/>
       <c r="B261" s="11"/>
     </row>
-    <row r="262" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6"/>
       <c r="B262" s="11"/>
     </row>
-    <row r="263" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6"/>
       <c r="B263" s="11"/>
     </row>
-    <row r="264" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6"/>
       <c r="B264" s="11"/>
     </row>
-    <row r="265" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6"/>
       <c r="B265" s="11"/>
     </row>
-    <row r="266" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6"/>
       <c r="B266" s="11"/>
     </row>
-    <row r="267" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6"/>
       <c r="B267" s="11"/>
     </row>
-    <row r="268" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6"/>
       <c r="B268" s="11"/>
     </row>
-    <row r="269" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6"/>
       <c r="B269" s="11"/>
     </row>
-    <row r="270" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6"/>
       <c r="B270" s="11"/>
     </row>
-    <row r="271" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6"/>
       <c r="B271" s="11"/>
     </row>
-    <row r="272" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6"/>
       <c r="B272" s="11"/>
     </row>
-    <row r="273" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6"/>
       <c r="B273" s="11"/>
     </row>
-    <row r="274" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6"/>
       <c r="B274" s="11"/>
     </row>
-    <row r="275" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6"/>
       <c r="B275" s="11"/>
     </row>
-    <row r="276" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6"/>
       <c r="B276" s="11"/>
     </row>
-    <row r="277" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6"/>
       <c r="B277" s="11"/>
     </row>
-    <row r="278" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6"/>
       <c r="B278" s="11"/>
     </row>
-    <row r="279" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6"/>
       <c r="B279" s="11"/>
     </row>
-    <row r="280" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6"/>
       <c r="B280" s="11"/>
     </row>
-    <row r="281" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6"/>
       <c r="B281" s="11"/>
     </row>
-    <row r="282" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6"/>
       <c r="B282" s="11"/>
     </row>
-    <row r="283" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6"/>
       <c r="B283" s="11"/>
     </row>
-    <row r="284" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6"/>
       <c r="B284" s="11"/>
     </row>
-    <row r="285" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6"/>
       <c r="B285" s="11"/>
     </row>
-    <row r="286" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6"/>
       <c r="B286" s="11"/>
     </row>
-    <row r="287" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6"/>
       <c r="B287" s="11"/>
     </row>
-    <row r="288" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6"/>
       <c r="B288" s="11"/>
     </row>
-    <row r="289" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6"/>
       <c r="B289" s="11"/>
     </row>
-    <row r="290" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6"/>
       <c r="B290" s="11"/>
     </row>
-    <row r="291" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6"/>
       <c r="B291" s="11"/>
     </row>
-    <row r="292" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6"/>
       <c r="B292" s="11"/>
     </row>
-    <row r="293" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6"/>
       <c r="B293" s="11"/>
     </row>
-    <row r="294" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6"/>
       <c r="B294" s="11"/>
     </row>
-    <row r="295" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6"/>
       <c r="B295" s="11"/>
     </row>
-    <row r="296" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6"/>
       <c r="B296" s="11"/>
     </row>
-    <row r="297" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6"/>
       <c r="B297" s="11"/>
     </row>
-    <row r="298" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6"/>
       <c r="B298" s="11"/>
     </row>
-    <row r="299" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6"/>
       <c r="B299" s="11"/>
     </row>
-    <row r="300" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6"/>
       <c r="B300" s="11"/>
     </row>
-    <row r="301" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6"/>
       <c r="B301" s="11"/>
     </row>
-    <row r="302" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6"/>
       <c r="B302" s="11"/>
     </row>
-    <row r="303" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6"/>
       <c r="B303" s="11"/>
     </row>
-    <row r="304" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6"/>
       <c r="B304" s="11"/>
     </row>
-    <row r="305" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6"/>
       <c r="B305" s="11"/>
     </row>
-    <row r="306" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6"/>
       <c r="B306" s="11"/>
     </row>
-    <row r="307" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6"/>
       <c r="B307" s="11"/>
     </row>
-    <row r="308" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6"/>
       <c r="B308" s="11"/>
     </row>
-    <row r="309" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6"/>
       <c r="B309" s="11"/>
     </row>
-    <row r="310" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6"/>
       <c r="B310" s="11"/>
     </row>
-    <row r="311" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6"/>
       <c r="B311" s="11"/>
     </row>
-    <row r="312" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6"/>
       <c r="B312" s="11"/>
     </row>
-    <row r="313" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6"/>
       <c r="B313" s="11"/>
     </row>
-    <row r="314" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6"/>
       <c r="B314" s="11"/>
     </row>
-    <row r="315" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6"/>
       <c r="B315" s="11"/>
     </row>
-    <row r="316" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6"/>
       <c r="B316" s="11"/>
     </row>
-    <row r="317" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6"/>
       <c r="B317" s="11"/>
     </row>
-    <row r="318" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6"/>
       <c r="B318" s="11"/>
     </row>
-    <row r="319" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6"/>
       <c r="B319" s="11"/>
     </row>
-    <row r="320" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6"/>
       <c r="B320" s="11"/>
     </row>
-    <row r="321" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6"/>
       <c r="B321" s="11"/>
     </row>
-    <row r="322" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6"/>
       <c r="B322" s="11"/>
     </row>
-    <row r="323" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6"/>
       <c r="B323" s="11"/>
     </row>
-    <row r="324" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6"/>
       <c r="B324" s="11"/>
     </row>
-    <row r="325" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6"/>
       <c r="B325" s="11"/>
     </row>
-    <row r="326" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6"/>
       <c r="B326" s="11"/>
     </row>
-    <row r="327" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6"/>
       <c r="B327" s="11"/>
     </row>
-    <row r="328" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6"/>
       <c r="B328" s="11"/>
     </row>
-    <row r="329" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6"/>
       <c r="B329" s="11"/>
     </row>
-    <row r="330" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6"/>
       <c r="B330" s="11"/>
     </row>
-    <row r="331" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6"/>
       <c r="B331" s="11"/>
     </row>
-    <row r="332" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6"/>
       <c r="B332" s="11"/>
     </row>
-    <row r="333" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6"/>
       <c r="B333" s="11"/>
     </row>
-    <row r="334" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6"/>
       <c r="B334" s="11"/>
     </row>
-    <row r="335" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6"/>
       <c r="B335" s="11"/>
     </row>
-    <row r="336" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6"/>
       <c r="B336" s="11"/>
     </row>
-    <row r="337" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6"/>
       <c r="B337" s="11"/>
     </row>
-    <row r="338" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6"/>
       <c r="B338" s="11"/>
     </row>
-    <row r="339" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6"/>
       <c r="B339" s="11"/>
     </row>
-    <row r="340" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6"/>
       <c r="B340" s="11"/>
     </row>
-    <row r="341" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6"/>
       <c r="B341" s="11"/>
     </row>
-    <row r="342" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6"/>
       <c r="B342" s="11"/>
     </row>
-    <row r="343" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6"/>
       <c r="B343" s="11"/>
     </row>
-    <row r="344" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6"/>
       <c r="B344" s="11"/>
     </row>
-    <row r="345" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6"/>
       <c r="B345" s="11"/>
     </row>
-    <row r="346" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6"/>
       <c r="B346" s="11"/>
     </row>
-    <row r="347" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6"/>
       <c r="B347" s="11"/>
     </row>
-    <row r="348" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6"/>
       <c r="B348" s="11"/>
     </row>
-    <row r="349" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6"/>
       <c r="B349" s="11"/>
     </row>
-    <row r="350" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6"/>
       <c r="B350" s="11"/>
     </row>
-    <row r="351" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6"/>
       <c r="B351" s="11"/>
     </row>
-    <row r="352" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6"/>
       <c r="B352" s="11"/>
     </row>
-    <row r="353" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6"/>
       <c r="B353" s="11"/>
     </row>
-    <row r="354" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6"/>
       <c r="B354" s="11"/>
     </row>
-    <row r="355" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6"/>
       <c r="B355" s="11"/>
     </row>
-    <row r="356" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6"/>
       <c r="B356" s="11"/>
     </row>
-    <row r="357" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6"/>
       <c r="B357" s="11"/>
     </row>
-    <row r="358" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6"/>
       <c r="B358" s="11"/>
     </row>
-    <row r="359" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6"/>
       <c r="B359" s="11"/>
     </row>
-    <row r="360" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6"/>
       <c r="B360" s="11"/>
     </row>
-    <row r="361" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6"/>
       <c r="B361" s="11"/>
     </row>
-    <row r="362" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6"/>
       <c r="B362" s="11"/>
     </row>
-    <row r="363" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6"/>
       <c r="B363" s="11"/>
     </row>
-    <row r="364" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6"/>
       <c r="B364" s="11"/>
     </row>
-    <row r="365" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6"/>
       <c r="B365" s="11"/>
     </row>
-    <row r="366" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6"/>
       <c r="B366" s="11"/>
     </row>
-    <row r="367" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6"/>
       <c r="B367" s="11"/>
     </row>
-    <row r="368" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6"/>
       <c r="B368" s="11"/>
     </row>
-    <row r="369" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6"/>
       <c r="B369" s="11"/>
     </row>
-    <row r="370" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6"/>
       <c r="B370" s="11"/>
     </row>
-    <row r="371" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6"/>
       <c r="B371" s="11"/>
     </row>
-    <row r="372" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6"/>
       <c r="B372" s="11"/>
     </row>
-    <row r="373" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6"/>
       <c r="B373" s="11"/>
     </row>
-    <row r="374" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6"/>
       <c r="B374" s="11"/>
     </row>
-    <row r="375" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6"/>
       <c r="B375" s="11"/>
     </row>
-    <row r="376" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6"/>
       <c r="B376" s="11"/>
     </row>
-    <row r="377" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6"/>
       <c r="B377" s="11"/>
     </row>
-    <row r="378" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6"/>
       <c r="B378" s="11"/>
     </row>
-    <row r="379" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6"/>
       <c r="B379" s="11"/>
     </row>
-    <row r="380" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6"/>
       <c r="B380" s="11"/>
     </row>
-    <row r="381" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6"/>
       <c r="B381" s="11"/>
     </row>
-    <row r="382" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6"/>
       <c r="B382" s="11"/>
     </row>
-    <row r="383" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6"/>
       <c r="B383" s="11"/>
     </row>
-    <row r="384" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6"/>
       <c r="B384" s="11"/>
     </row>
-    <row r="385" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6"/>
       <c r="B385" s="11"/>
     </row>
-    <row r="386" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6"/>
       <c r="B386" s="11"/>
     </row>
-    <row r="387" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6"/>
       <c r="B387" s="11"/>
     </row>
-    <row r="388" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6"/>
       <c r="B388" s="11"/>
     </row>
-    <row r="389" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6"/>
       <c r="B389" s="11"/>
     </row>
-    <row r="390" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6"/>
       <c r="B390" s="11"/>
     </row>
-    <row r="391" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6"/>
       <c r="B391" s="11"/>
     </row>
-    <row r="392" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6"/>
       <c r="B392" s="11"/>
     </row>
-    <row r="393" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6"/>
       <c r="B393" s="11"/>
     </row>
-    <row r="394" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6"/>
       <c r="B394" s="11"/>
     </row>
-    <row r="395" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6"/>
       <c r="B395" s="11"/>
     </row>
-    <row r="396" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6"/>
       <c r="B396" s="11"/>
     </row>
-    <row r="397" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6"/>
       <c r="B397" s="11"/>
     </row>
-    <row r="398" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6"/>
       <c r="B398" s="11"/>
     </row>
-    <row r="399" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6"/>
       <c r="B399" s="11"/>
     </row>
-    <row r="400" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6"/>
       <c r="B400" s="11"/>
     </row>
-    <row r="401" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6"/>
       <c r="B401" s="11"/>
     </row>
-    <row r="402" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6"/>
       <c r="B402" s="11"/>
     </row>
-    <row r="403" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6"/>
       <c r="B403" s="11"/>
     </row>
-    <row r="404" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6"/>
       <c r="B404" s="11"/>
     </row>
-    <row r="405" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6"/>
       <c r="B405" s="11"/>
     </row>
-    <row r="406" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6"/>
       <c r="B406" s="11"/>
     </row>
-    <row r="407" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6"/>
       <c r="B407" s="11"/>
     </row>
-    <row r="408" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6"/>
       <c r="B408" s="11"/>
     </row>
-    <row r="409" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6"/>
       <c r="B409" s="11"/>
     </row>
-    <row r="410" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6"/>
       <c r="B410" s="11"/>
     </row>
-    <row r="411" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6"/>
       <c r="B411" s="11"/>
     </row>
-    <row r="412" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6"/>
       <c r="B412" s="11"/>
     </row>
-    <row r="413" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6"/>
       <c r="B413" s="11"/>
     </row>
-    <row r="414" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6"/>
       <c r="B414" s="11"/>
     </row>
-    <row r="415" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6"/>
       <c r="B415" s="11"/>
     </row>
-    <row r="416" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6"/>
       <c r="B416" s="11"/>
     </row>
-    <row r="417" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6"/>
       <c r="B417" s="11"/>
     </row>
-    <row r="418" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6"/>
       <c r="B418" s="11"/>
     </row>
-    <row r="419" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6"/>
       <c r="B419" s="11"/>
     </row>
-    <row r="420" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6"/>
       <c r="B420" s="11"/>
     </row>
-    <row r="421" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6"/>
       <c r="B421" s="11"/>
     </row>
-    <row r="422" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6"/>
       <c r="B422" s="11"/>
     </row>
-    <row r="423" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6"/>
       <c r="B423" s="11"/>
     </row>
-    <row r="424" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6"/>
       <c r="B424" s="11"/>
     </row>
-    <row r="425" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6"/>
       <c r="B425" s="11"/>
     </row>
-    <row r="426" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="6"/>
       <c r="B426" s="11"/>
     </row>
-    <row r="427" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="6"/>
       <c r="B427" s="11"/>
     </row>
-    <row r="428" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="6"/>
       <c r="B428" s="11"/>
     </row>
-    <row r="429" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="6"/>
       <c r="B429" s="11"/>
     </row>
-    <row r="430" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="6"/>
       <c r="B430" s="11"/>
     </row>
-    <row r="431" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="6"/>
       <c r="B431" s="11"/>
     </row>
-    <row r="432" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="6"/>
       <c r="B432" s="11"/>
     </row>
-    <row r="433" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="6"/>
       <c r="B433" s="11"/>
     </row>
-    <row r="434" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="6"/>
       <c r="B434" s="11"/>
     </row>
-    <row r="435" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="6"/>
       <c r="B435" s="11"/>
     </row>
-    <row r="436" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="6"/>
       <c r="B436" s="11"/>
     </row>
-    <row r="437" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="6"/>
       <c r="B437" s="11"/>
     </row>
-    <row r="438" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="6"/>
       <c r="B438" s="11"/>
     </row>
-    <row r="439" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="6"/>
       <c r="B439" s="11"/>
     </row>
-    <row r="440" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="6"/>
       <c r="B440" s="11"/>
     </row>
-    <row r="441" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="6"/>
       <c r="B441" s="11"/>
     </row>
-    <row r="442" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="6"/>
       <c r="B442" s="11"/>
     </row>
-    <row r="443" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="6"/>
       <c r="B443" s="11"/>
     </row>
-    <row r="444" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="6"/>
       <c r="B444" s="11"/>
     </row>
-    <row r="445" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="6"/>
       <c r="B445" s="11"/>
     </row>
-    <row r="446" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="6"/>
       <c r="B446" s="11"/>
     </row>
-    <row r="447" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="6"/>
       <c r="B447" s="11"/>
     </row>
-    <row r="448" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="6"/>
       <c r="B448" s="11"/>
     </row>
-    <row r="449" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="6"/>
       <c r="B449" s="11"/>
     </row>
-    <row r="450" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="6"/>
       <c r="B450" s="11"/>
     </row>
-    <row r="451" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="6"/>
       <c r="B451" s="11"/>
     </row>
-    <row r="452" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="6"/>
       <c r="B452" s="11"/>
     </row>
-    <row r="453" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="6"/>
       <c r="B453" s="11"/>
     </row>
-    <row r="454" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="6"/>
       <c r="B454" s="11"/>
     </row>
-    <row r="455" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="6"/>
       <c r="B455" s="11"/>
     </row>
-    <row r="456" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="6"/>
       <c r="B456" s="11"/>
     </row>
-    <row r="457" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="6"/>
       <c r="B457" s="11"/>
     </row>
-    <row r="458" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="6"/>
       <c r="B458" s="11"/>
     </row>
-    <row r="459" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="6"/>
       <c r="B459" s="11"/>
     </row>
-    <row r="460" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="6"/>
       <c r="B460" s="11"/>
     </row>
-    <row r="461" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="6"/>
       <c r="B461" s="11"/>
     </row>
-    <row r="462" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="6"/>
       <c r="B462" s="11"/>
     </row>
-    <row r="463" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="6"/>
       <c r="B463" s="11"/>
     </row>
-    <row r="464" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="6"/>
       <c r="B464" s="11"/>
     </row>
-    <row r="465" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="6"/>
       <c r="B465" s="11"/>
     </row>
-    <row r="466" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="6"/>
       <c r="B466" s="11"/>
     </row>
-    <row r="467" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="6"/>
       <c r="B467" s="11"/>
     </row>
-    <row r="468" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="6"/>
       <c r="B468" s="11"/>
     </row>
-    <row r="469" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="6"/>
       <c r="B469" s="11"/>
     </row>
-    <row r="470" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="6"/>
       <c r="B470" s="11"/>
     </row>
-    <row r="471" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="6"/>
       <c r="B471" s="11"/>
     </row>
-    <row r="472" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="6"/>
       <c r="B472" s="11"/>
     </row>
-    <row r="473" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="6"/>
       <c r="B473" s="11"/>
     </row>
-    <row r="474" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="6"/>
       <c r="B474" s="11"/>
     </row>
-    <row r="475" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="6"/>
       <c r="B475" s="11"/>
     </row>
-    <row r="476" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="6"/>
       <c r="B476" s="11"/>
     </row>
-    <row r="477" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="6"/>
       <c r="B477" s="11"/>
     </row>
-    <row r="478" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="6"/>
       <c r="B478" s="11"/>
     </row>
-    <row r="479" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="6"/>
       <c r="B479" s="11"/>
     </row>
-    <row r="480" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="6"/>
       <c r="B480" s="11"/>
     </row>
-    <row r="481" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="6"/>
       <c r="B481" s="11"/>
     </row>
-    <row r="482" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="6"/>
       <c r="B482" s="11"/>
     </row>
-    <row r="483" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="6"/>
       <c r="B483" s="11"/>
     </row>
-    <row r="484" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="6"/>
       <c r="B484" s="11"/>
     </row>
-    <row r="485" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="6"/>
       <c r="B485" s="11"/>
     </row>
-    <row r="486" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="6"/>
       <c r="B486" s="11"/>
     </row>
-    <row r="487" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="6"/>
       <c r="B487" s="11"/>
     </row>
-    <row r="488" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="6"/>
       <c r="B488" s="11"/>
     </row>
-    <row r="489" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="6"/>
       <c r="B489" s="11"/>
     </row>
-    <row r="490" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="6"/>
       <c r="B490" s="11"/>
     </row>
-    <row r="491" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="6"/>
       <c r="B491" s="11"/>
     </row>
-    <row r="492" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="6"/>
       <c r="B492" s="11"/>
     </row>
-    <row r="493" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="6"/>
       <c r="B493" s="11"/>
     </row>
-    <row r="494" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="6"/>
       <c r="B494" s="11"/>
     </row>
-    <row r="495" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="6"/>
       <c r="B495" s="11"/>
     </row>
-    <row r="496" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="6"/>
       <c r="B496" s="11"/>
     </row>
-    <row r="497" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="6"/>
       <c r="B497" s="11"/>
     </row>
-    <row r="498" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="6"/>
       <c r="B498" s="11"/>
     </row>
-    <row r="499" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="6"/>
       <c r="B499" s="11"/>
     </row>
-    <row r="500" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="6"/>
       <c r="B500" s="11"/>
     </row>
@@ -8677,52 +8692,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E34FD7-1B73-4707-A12E-62E00BDCA8A2}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>

--- a/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
+++ b/Annexes/Journal_de_travail/Journal_de_Travail_DeCarvalho_Andre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ES\GITHUB\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web\Lego-Inventor-Manager\Annexes\Journal_de_travail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A573ACEB-4E92-448F-BC7A-42018CA48407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457D29D4-8C35-4509-B241-1F0569C7F05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="83">
   <si>
     <t>Jour</t>
   </si>
@@ -282,6 +282,12 @@
   </si>
   <si>
     <t>Dernière réunion, discussion sur la présentation du projet et la documentation</t>
+  </si>
+  <si>
+    <t>Travail sur la vue admin et finalisation de la vue utilisateur</t>
+  </si>
+  <si>
+    <t>Finalisation de la vue admin</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1009,7 @@
                   <c:v>10.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.25</c:v>
+                  <c:v>21.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2028,17 +2034,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F503"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="13.375" style="15" customWidth="1"/>
-    <col min="3" max="3" width="15.25" style="12" customWidth="1"/>
-    <col min="4" max="4" width="24.75" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="24.69921875" style="5" customWidth="1"/>
     <col min="5" max="5" width="68.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="82.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="82.19921875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2058,7 +2064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>46035</v>
       </c>
@@ -2076,7 +2082,7 @@
       </c>
       <c r="F2" s="8"/>
     </row>
-    <row r="3" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>46035</v>
       </c>
@@ -2094,7 +2100,7 @@
       </c>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>46036</v>
       </c>
@@ -2114,7 +2120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>46036</v>
       </c>
@@ -2132,7 +2138,7 @@
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>46036</v>
       </c>
@@ -2152,7 +2158,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>46036</v>
       </c>
@@ -2172,7 +2178,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>46037</v>
       </c>
@@ -2190,7 +2196,7 @@
       </c>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>46037</v>
       </c>
@@ -2210,7 +2216,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>46037</v>
       </c>
@@ -2230,7 +2236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>46037</v>
       </c>
@@ -2248,7 +2254,7 @@
       </c>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>46038</v>
       </c>
@@ -2266,7 +2272,7 @@
       </c>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>46038</v>
       </c>
@@ -2286,7 +2292,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>46038</v>
       </c>
@@ -2304,7 +2310,7 @@
       </c>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>46038</v>
       </c>
@@ -2324,7 +2330,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>46038</v>
       </c>
@@ -2344,7 +2350,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>46038</v>
       </c>
@@ -2364,7 +2370,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>46041</v>
       </c>
@@ -2384,7 +2390,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>46041</v>
       </c>
@@ -2404,7 +2410,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>46041</v>
       </c>
@@ -2424,7 +2430,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>46041</v>
       </c>
@@ -2442,7 +2448,7 @@
       </c>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>46041</v>
       </c>
@@ -2462,7 +2468,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>46042</v>
       </c>
@@ -2482,7 +2488,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>46042</v>
       </c>
@@ -2502,7 +2508,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>46043</v>
       </c>
@@ -2522,7 +2528,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>46043</v>
       </c>
@@ -2542,7 +2548,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>46043</v>
       </c>
@@ -2562,7 +2568,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>46043</v>
       </c>
@@ -2582,7 +2588,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>46043</v>
       </c>
@@ -2602,7 +2608,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>46044</v>
       </c>
@@ -2622,7 +2628,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>46044</v>
       </c>
@@ -2642,7 +2648,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>46044</v>
       </c>
@@ -2662,7 +2668,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>46044</v>
       </c>
@@ -2680,7 +2686,7 @@
       </c>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>46045</v>
       </c>
@@ -2700,7 +2706,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>46045</v>
       </c>
@@ -2720,7 +2726,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>46045</v>
       </c>
@@ -2740,7 +2746,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>46045</v>
       </c>
@@ -2760,7 +2766,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>46045</v>
       </c>
@@ -2780,7 +2786,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>46048</v>
       </c>
@@ -2800,7 +2806,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>46048</v>
       </c>
@@ -2820,7 +2826,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>46048</v>
       </c>
@@ -2840,7 +2846,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>46049</v>
       </c>
@@ -2860,7 +2866,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>46049</v>
       </c>
@@ -2880,7 +2886,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>46049</v>
       </c>
@@ -2900,7 +2906,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>46050</v>
       </c>
@@ -2920,23 +2926,47 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-    </row>
-    <row r="47" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-    </row>
-    <row r="48" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>46050</v>
+      </c>
+      <c r="B46" s="14">
+        <v>3</v>
+      </c>
+      <c r="C46" s="11">
+        <v>5</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>46051</v>
+      </c>
+      <c r="B47" s="14">
+        <v>3</v>
+      </c>
+      <c r="C47" s="11">
+        <v>4</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="14"/>
       <c r="C48" s="11"/>
@@ -2944,7 +2974,7 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
     </row>
-    <row r="49" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="14"/>
       <c r="C49" s="11"/>
@@ -2952,7 +2982,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="14"/>
       <c r="C50" s="11"/>
@@ -2960,7 +2990,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
     </row>
-    <row r="51" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="14"/>
       <c r="C51" s="11"/>
@@ -2968,7 +2998,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="14"/>
       <c r="C52" s="11"/>
@@ -2976,7 +3006,7 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
     </row>
-    <row r="53" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="14"/>
       <c r="C53" s="11"/>
@@ -2984,7 +3014,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="14"/>
       <c r="C54" s="11"/>
@@ -2992,7 +3022,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="14"/>
       <c r="C55" s="11"/>
@@ -3000,7 +3030,7 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
     </row>
-    <row r="56" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="14"/>
       <c r="C56" s="11"/>
@@ -3008,7 +3038,7 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="14"/>
       <c r="C57" s="11"/>
@@ -3016,7 +3046,7 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
     </row>
-    <row r="58" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="14"/>
       <c r="C58" s="11"/>
@@ -3024,7 +3054,7 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
     </row>
-    <row r="59" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="14"/>
       <c r="C59" s="11"/>
@@ -3032,7 +3062,7 @@
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
     </row>
-    <row r="60" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="14"/>
       <c r="C60" s="11"/>
@@ -3040,7 +3070,7 @@
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="14"/>
       <c r="C61" s="11"/>
@@ -3048,7 +3078,7 @@
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
     </row>
-    <row r="62" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="14"/>
       <c r="C62" s="11"/>
@@ -3056,7 +3086,7 @@
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
     </row>
-    <row r="63" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="14"/>
       <c r="C63" s="11"/>
@@ -3064,7 +3094,7 @@
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
     </row>
-    <row r="64" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="14"/>
       <c r="C64" s="11"/>
@@ -3072,7 +3102,7 @@
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
     </row>
-    <row r="65" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="14"/>
       <c r="C65" s="11"/>
@@ -3080,7 +3110,7 @@
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
     </row>
-    <row r="66" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="14"/>
       <c r="C66" s="11"/>
@@ -3088,7 +3118,7 @@
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
     </row>
-    <row r="67" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="14"/>
       <c r="C67" s="11"/>
@@ -3096,7 +3126,7 @@
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
     </row>
-    <row r="68" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="14"/>
       <c r="C68" s="11"/>
@@ -3104,7 +3134,7 @@
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
     </row>
-    <row r="69" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="14"/>
       <c r="C69" s="11"/>
@@ -3112,7 +3142,7 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
     </row>
-    <row r="70" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="14"/>
       <c r="C70" s="11"/>
@@ -3120,7 +3150,7 @@
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
     </row>
-    <row r="71" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="14"/>
       <c r="C71" s="11"/>
@@ -3128,7 +3158,7 @@
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
     </row>
-    <row r="72" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="14"/>
       <c r="C72" s="11"/>
@@ -3136,7 +3166,7 @@
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
     </row>
-    <row r="73" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="14"/>
       <c r="C73" s="11"/>
@@ -3144,7 +3174,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
     </row>
-    <row r="74" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="14"/>
       <c r="C74" s="11"/>
@@ -3152,7 +3182,7 @@
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
     </row>
-    <row r="75" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="14"/>
       <c r="C75" s="11"/>
@@ -3160,7 +3190,7 @@
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
     </row>
-    <row r="76" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="14"/>
       <c r="C76" s="11"/>
@@ -3168,7 +3198,7 @@
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
     </row>
-    <row r="77" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="14"/>
       <c r="C77" s="11"/>
@@ -3176,7 +3206,7 @@
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
     </row>
-    <row r="78" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="14"/>
       <c r="C78" s="11"/>
@@ -3184,7 +3214,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
     </row>
-    <row r="79" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="14"/>
       <c r="C79" s="11"/>
@@ -3192,7 +3222,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
     </row>
-    <row r="80" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="14"/>
       <c r="C80" s="11"/>
@@ -3200,7 +3230,7 @@
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
     </row>
-    <row r="81" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="14"/>
       <c r="C81" s="11"/>
@@ -3208,7 +3238,7 @@
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
     </row>
-    <row r="82" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="14"/>
       <c r="C82" s="11"/>
@@ -3216,7 +3246,7 @@
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
     </row>
-    <row r="83" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="14"/>
       <c r="C83" s="11"/>
@@ -3224,7 +3254,7 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
     </row>
-    <row r="84" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="14"/>
       <c r="C84" s="11"/>
@@ -3232,7 +3262,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
     </row>
-    <row r="85" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="14"/>
       <c r="C85" s="11"/>
@@ -3240,7 +3270,7 @@
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
     </row>
-    <row r="86" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="14"/>
       <c r="C86" s="11"/>
@@ -3248,7 +3278,7 @@
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
     </row>
-    <row r="87" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="14"/>
       <c r="C87" s="11"/>
@@ -3256,7 +3286,7 @@
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
     </row>
-    <row r="88" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="14"/>
       <c r="C88" s="11"/>
@@ -3264,7 +3294,7 @@
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
     </row>
-    <row r="89" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="14"/>
       <c r="C89" s="11"/>
@@ -3272,7 +3302,7 @@
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
     </row>
-    <row r="90" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="14"/>
       <c r="C90" s="11"/>
@@ -3280,7 +3310,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
     </row>
-    <row r="91" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="14"/>
       <c r="C91" s="11"/>
@@ -3288,7 +3318,7 @@
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
     </row>
-    <row r="92" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="14"/>
       <c r="C92" s="11"/>
@@ -3296,7 +3326,7 @@
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
     </row>
-    <row r="93" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="14"/>
       <c r="C93" s="11"/>
@@ -3304,7 +3334,7 @@
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
     </row>
-    <row r="94" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="14"/>
       <c r="C94" s="11"/>
@@ -3312,7 +3342,7 @@
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
     </row>
-    <row r="95" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="14"/>
       <c r="C95" s="11"/>
@@ -3320,7 +3350,7 @@
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
     </row>
-    <row r="96" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="14"/>
       <c r="C96" s="11"/>
@@ -3328,7 +3358,7 @@
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
     </row>
-    <row r="97" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="14"/>
       <c r="C97" s="11"/>
@@ -3336,7 +3366,7 @@
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
     </row>
-    <row r="98" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="14"/>
       <c r="C98" s="11"/>
@@ -3344,7 +3374,7 @@
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
     </row>
-    <row r="99" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="14"/>
       <c r="C99" s="11"/>
@@ -3352,7 +3382,7 @@
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
     </row>
-    <row r="100" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
       <c r="B100" s="14"/>
       <c r="C100" s="11"/>
@@ -3360,7 +3390,7 @@
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
     </row>
-    <row r="101" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="14"/>
       <c r="C101" s="11"/>
@@ -3368,7 +3398,7 @@
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
     </row>
-    <row r="102" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="14"/>
       <c r="C102" s="11"/>
@@ -3376,7 +3406,7 @@
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
     </row>
-    <row r="103" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="14"/>
       <c r="C103" s="11"/>
@@ -3384,7 +3414,7 @@
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
     </row>
-    <row r="104" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
       <c r="B104" s="14"/>
       <c r="C104" s="11"/>
@@ -3392,7 +3422,7 @@
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
     </row>
-    <row r="105" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="B105" s="14"/>
       <c r="C105" s="11"/>
@@ -3400,7 +3430,7 @@
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
     </row>
-    <row r="106" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
       <c r="B106" s="14"/>
       <c r="C106" s="11"/>
@@ -3408,7 +3438,7 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
     </row>
-    <row r="107" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
       <c r="B107" s="14"/>
       <c r="C107" s="11"/>
@@ -3416,7 +3446,7 @@
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
     </row>
-    <row r="108" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
       <c r="B108" s="14"/>
       <c r="C108" s="11"/>
@@ -3424,7 +3454,7 @@
       <c r="E108" s="8"/>
       <c r="F108" s="8"/>
     </row>
-    <row r="109" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="14"/>
       <c r="C109" s="11"/>
@@ -3432,7 +3462,7 @@
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
     </row>
-    <row r="110" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="14"/>
       <c r="C110" s="11"/>
@@ -3440,7 +3470,7 @@
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
     </row>
-    <row r="111" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="14"/>
       <c r="C111" s="11"/>
@@ -3448,7 +3478,7 @@
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
     </row>
-    <row r="112" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
       <c r="B112" s="14"/>
       <c r="C112" s="11"/>
@@ -3456,7 +3486,7 @@
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
     </row>
-    <row r="113" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="B113" s="14"/>
       <c r="C113" s="11"/>
@@ -3464,7 +3494,7 @@
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
     </row>
-    <row r="114" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
       <c r="B114" s="14"/>
       <c r="C114" s="11"/>
@@ -3472,7 +3502,7 @@
       <c r="E114" s="8"/>
       <c r="F114" s="8"/>
     </row>
-    <row r="115" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="14"/>
       <c r="C115" s="11"/>
@@ -3480,7 +3510,7 @@
       <c r="E115" s="8"/>
       <c r="F115" s="8"/>
     </row>
-    <row r="116" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
       <c r="B116" s="14"/>
       <c r="C116" s="11"/>
@@ -3488,7 +3518,7 @@
       <c r="E116" s="8"/>
       <c r="F116" s="8"/>
     </row>
-    <row r="117" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="B117" s="14"/>
       <c r="C117" s="11"/>
@@ -3496,7 +3526,7 @@
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
     </row>
-    <row r="118" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="B118" s="14"/>
       <c r="C118" s="11"/>
@@ -3504,7 +3534,7 @@
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
     </row>
-    <row r="119" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="14"/>
       <c r="C119" s="11"/>
@@ -3512,7 +3542,7 @@
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
     </row>
-    <row r="120" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
       <c r="B120" s="14"/>
       <c r="C120" s="11"/>
@@ -3520,7 +3550,7 @@
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
     </row>
-    <row r="121" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="14"/>
       <c r="C121" s="11"/>
@@ -3528,7 +3558,7 @@
       <c r="E121" s="8"/>
       <c r="F121" s="8"/>
     </row>
-    <row r="122" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="B122" s="14"/>
       <c r="C122" s="11"/>
@@ -3536,7 +3566,7 @@
       <c r="E122" s="8"/>
       <c r="F122" s="8"/>
     </row>
-    <row r="123" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="14"/>
       <c r="C123" s="11"/>
@@ -3544,7 +3574,7 @@
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
     </row>
-    <row r="124" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
       <c r="B124" s="14"/>
       <c r="C124" s="11"/>
@@ -3552,7 +3582,7 @@
       <c r="E124" s="8"/>
       <c r="F124" s="8"/>
     </row>
-    <row r="125" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="14"/>
       <c r="C125" s="11"/>
@@ -3560,7 +3590,7 @@
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
     </row>
-    <row r="126" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="B126" s="14"/>
       <c r="C126" s="11"/>
@@ -3568,7 +3598,7 @@
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
     </row>
-    <row r="127" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="14"/>
       <c r="C127" s="11"/>
@@ -3576,7 +3606,7 @@
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
     </row>
-    <row r="128" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
       <c r="B128" s="14"/>
       <c r="C128" s="11"/>
@@ -3584,7 +3614,7 @@
       <c r="E128" s="8"/>
       <c r="F128" s="8"/>
     </row>
-    <row r="129" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="B129" s="14"/>
       <c r="C129" s="11"/>
@@ -3592,7 +3622,7 @@
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
     </row>
-    <row r="130" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
       <c r="B130" s="14"/>
       <c r="C130" s="11"/>
@@ -3600,7 +3630,7 @@
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
     </row>
-    <row r="131" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
       <c r="B131" s="14"/>
       <c r="C131" s="11"/>
@@ -3608,7 +3638,7 @@
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
     </row>
-    <row r="132" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6"/>
       <c r="B132" s="14"/>
       <c r="C132" s="11"/>
@@ -3616,7 +3646,7 @@
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
     </row>
-    <row r="133" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="B133" s="14"/>
       <c r="C133" s="11"/>
@@ -3624,7 +3654,7 @@
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
     </row>
-    <row r="134" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
       <c r="B134" s="14"/>
       <c r="C134" s="11"/>
@@ -3632,7 +3662,7 @@
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
     </row>
-    <row r="135" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
       <c r="B135" s="14"/>
       <c r="C135" s="11"/>
@@ -3640,7 +3670,7 @@
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
     </row>
-    <row r="136" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
       <c r="B136" s="14"/>
       <c r="C136" s="11"/>
@@ -3648,7 +3678,7 @@
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
     </row>
-    <row r="137" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
       <c r="B137" s="14"/>
       <c r="C137" s="11"/>
@@ -3656,7 +3686,7 @@
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
     </row>
-    <row r="138" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
       <c r="B138" s="14"/>
       <c r="C138" s="11"/>
@@ -3664,7 +3694,7 @@
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
     </row>
-    <row r="139" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
       <c r="B139" s="14"/>
       <c r="C139" s="11"/>
@@ -3672,7 +3702,7 @@
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
     </row>
-    <row r="140" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
       <c r="B140" s="14"/>
       <c r="C140" s="11"/>
@@ -3680,7 +3710,7 @@
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
     </row>
-    <row r="141" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
       <c r="B141" s="14"/>
       <c r="C141" s="11"/>
@@ -3688,7 +3718,7 @@
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
     </row>
-    <row r="142" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
       <c r="B142" s="14"/>
       <c r="C142" s="11"/>
@@ -3696,7 +3726,7 @@
       <c r="E142" s="8"/>
       <c r="F142" s="8"/>
     </row>
-    <row r="143" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
       <c r="B143" s="14"/>
       <c r="C143" s="11"/>
@@ -3704,7 +3734,7 @@
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
     </row>
-    <row r="144" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6"/>
       <c r="B144" s="14"/>
       <c r="C144" s="11"/>
@@ -3712,7 +3742,7 @@
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
     </row>
-    <row r="145" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
       <c r="B145" s="14"/>
       <c r="C145" s="11"/>
@@ -3720,7 +3750,7 @@
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
     </row>
-    <row r="146" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
       <c r="B146" s="14"/>
       <c r="C146" s="11"/>
@@ -3728,7 +3758,7 @@
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
     </row>
-    <row r="147" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
       <c r="B147" s="14"/>
       <c r="C147" s="11"/>
@@ -3736,7 +3766,7 @@
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
     </row>
-    <row r="148" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
       <c r="B148" s="14"/>
       <c r="C148" s="11"/>
@@ -3744,7 +3774,7 @@
       <c r="E148" s="8"/>
       <c r="F148" s="8"/>
     </row>
-    <row r="149" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
       <c r="B149" s="14"/>
       <c r="C149" s="11"/>
@@ -3752,7 +3782,7 @@
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
     </row>
-    <row r="150" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
       <c r="B150" s="14"/>
       <c r="C150" s="11"/>
@@ -3760,7 +3790,7 @@
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
     </row>
-    <row r="151" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
       <c r="B151" s="14"/>
       <c r="C151" s="11"/>
@@ -3768,7 +3798,7 @@
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
     </row>
-    <row r="152" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6"/>
       <c r="B152" s="14"/>
       <c r="C152" s="11"/>
@@ -3776,7 +3806,7 @@
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
     </row>
-    <row r="153" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
       <c r="B153" s="14"/>
       <c r="C153" s="11"/>
@@ -3784,7 +3814,7 @@
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
     </row>
-    <row r="154" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="B154" s="14"/>
       <c r="C154" s="11"/>
@@ -3792,7 +3822,7 @@
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
     </row>
-    <row r="155" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="B155" s="14"/>
       <c r="C155" s="11"/>
@@ -3800,7 +3830,7 @@
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
     </row>
-    <row r="156" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
       <c r="B156" s="14"/>
       <c r="C156" s="11"/>
@@ -3808,7 +3838,7 @@
       <c r="E156" s="8"/>
       <c r="F156" s="8"/>
     </row>
-    <row r="157" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
       <c r="B157" s="14"/>
       <c r="C157" s="11"/>
@@ -3816,7 +3846,7 @@
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
     </row>
-    <row r="158" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
       <c r="B158" s="14"/>
       <c r="C158" s="11"/>
@@ -3824,7 +3854,7 @@
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
     </row>
-    <row r="159" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
       <c r="B159" s="14"/>
       <c r="C159" s="11"/>
@@ -3832,7 +3862,7 @@
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
     </row>
-    <row r="160" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6"/>
       <c r="B160" s="14"/>
       <c r="C160" s="11"/>
@@ -3840,7 +3870,7 @@
       <c r="E160" s="8"/>
       <c r="F160" s="8"/>
     </row>
-    <row r="161" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
       <c r="B161" s="14"/>
       <c r="C161" s="11"/>
@@ -3848,7 +3878,7 @@
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
     </row>
-    <row r="162" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
       <c r="B162" s="14"/>
       <c r="C162" s="11"/>
@@ -3856,7 +3886,7 @@
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
     </row>
-    <row r="163" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
       <c r="B163" s="14"/>
       <c r="C163" s="11"/>
@@ -3864,7 +3894,7 @@
       <c r="E163" s="8"/>
       <c r="F163" s="8"/>
     </row>
-    <row r="164" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6"/>
       <c r="B164" s="14"/>
       <c r="C164" s="11"/>
@@ -3872,7 +3902,7 @@
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
     </row>
-    <row r="165" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
       <c r="B165" s="14"/>
       <c r="C165" s="11"/>
@@ -3880,7 +3910,7 @@
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
     </row>
-    <row r="166" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
       <c r="B166" s="14"/>
       <c r="C166" s="11"/>
@@ -3888,7 +3918,7 @@
       <c r="E166" s="8"/>
       <c r="F166" s="8"/>
     </row>
-    <row r="167" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6"/>
       <c r="B167" s="14"/>
       <c r="C167" s="11"/>
@@ -3896,7 +3926,7 @@
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
     </row>
-    <row r="168" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
       <c r="B168" s="14"/>
       <c r="C168" s="11"/>
@@ -3904,7 +3934,7 @@
       <c r="E168" s="8"/>
       <c r="F168" s="8"/>
     </row>
-    <row r="169" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6"/>
       <c r="B169" s="14"/>
       <c r="C169" s="11"/>
@@ -3912,7 +3942,7 @@
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
     </row>
-    <row r="170" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
       <c r="B170" s="14"/>
       <c r="C170" s="11"/>
@@ -3920,7 +3950,7 @@
       <c r="E170" s="8"/>
       <c r="F170" s="8"/>
     </row>
-    <row r="171" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="B171" s="14"/>
       <c r="C171" s="11"/>
@@ -3928,7 +3958,7 @@
       <c r="E171" s="8"/>
       <c r="F171" s="8"/>
     </row>
-    <row r="172" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
       <c r="B172" s="14"/>
       <c r="C172" s="11"/>
@@ -3936,7 +3966,7 @@
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
     </row>
-    <row r="173" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="B173" s="14"/>
       <c r="C173" s="11"/>
@@ -3944,7 +3974,7 @@
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
     </row>
-    <row r="174" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="B174" s="14"/>
       <c r="C174" s="11"/>
@@ -3952,7 +3982,7 @@
       <c r="E174" s="8"/>
       <c r="F174" s="8"/>
     </row>
-    <row r="175" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
       <c r="B175" s="14"/>
       <c r="C175" s="11"/>
@@ -3960,7 +3990,7 @@
       <c r="E175" s="8"/>
       <c r="F175" s="8"/>
     </row>
-    <row r="176" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
       <c r="B176" s="14"/>
       <c r="C176" s="11"/>
@@ -3968,7 +3998,7 @@
       <c r="E176" s="8"/>
       <c r="F176" s="8"/>
     </row>
-    <row r="177" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="B177" s="14"/>
       <c r="C177" s="11"/>
@@ -3976,7 +4006,7 @@
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
     </row>
-    <row r="178" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="B178" s="14"/>
       <c r="C178" s="11"/>
@@ -3984,7 +4014,7 @@
       <c r="E178" s="8"/>
       <c r="F178" s="8"/>
     </row>
-    <row r="179" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
       <c r="B179" s="14"/>
       <c r="C179" s="11"/>
@@ -3992,7 +4022,7 @@
       <c r="E179" s="8"/>
       <c r="F179" s="8"/>
     </row>
-    <row r="180" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
       <c r="B180" s="14"/>
       <c r="C180" s="11"/>
@@ -4000,7 +4030,7 @@
       <c r="E180" s="8"/>
       <c r="F180" s="8"/>
     </row>
-    <row r="181" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
       <c r="B181" s="14"/>
       <c r="C181" s="11"/>
@@ -4008,7 +4038,7 @@
       <c r="E181" s="8"/>
       <c r="F181" s="8"/>
     </row>
-    <row r="182" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
       <c r="B182" s="14"/>
       <c r="C182" s="11"/>
@@ -4016,7 +4046,7 @@
       <c r="E182" s="8"/>
       <c r="F182" s="8"/>
     </row>
-    <row r="183" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6"/>
       <c r="B183" s="14"/>
       <c r="C183" s="11"/>
@@ -4024,7 +4054,7 @@
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
     </row>
-    <row r="184" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
       <c r="B184" s="14"/>
       <c r="C184" s="11"/>
@@ -4032,7 +4062,7 @@
       <c r="E184" s="8"/>
       <c r="F184" s="8"/>
     </row>
-    <row r="185" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
       <c r="B185" s="14"/>
       <c r="C185" s="11"/>
@@ -4040,7 +4070,7 @@
       <c r="E185" s="8"/>
       <c r="F185" s="8"/>
     </row>
-    <row r="186" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
       <c r="B186" s="14"/>
       <c r="C186" s="11"/>
@@ -4048,7 +4078,7 @@
       <c r="E186" s="8"/>
       <c r="F186" s="8"/>
     </row>
-    <row r="187" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="B187" s="14"/>
       <c r="C187" s="11"/>
@@ -4056,7 +4086,7 @@
       <c r="E187" s="8"/>
       <c r="F187" s="8"/>
     </row>
-    <row r="188" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
       <c r="B188" s="14"/>
       <c r="C188" s="11"/>
@@ -4064,7 +4094,7 @@
       <c r="E188" s="8"/>
       <c r="F188" s="8"/>
     </row>
-    <row r="189" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
       <c r="B189" s="14"/>
       <c r="C189" s="11"/>
@@ -4072,7 +4102,7 @@
       <c r="E189" s="8"/>
       <c r="F189" s="8"/>
     </row>
-    <row r="190" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6"/>
       <c r="B190" s="14"/>
       <c r="C190" s="11"/>
@@ -4080,7 +4110,7 @@
       <c r="E190" s="8"/>
       <c r="F190" s="8"/>
     </row>
-    <row r="191" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
       <c r="B191" s="14"/>
       <c r="C191" s="11"/>
@@ -4088,7 +4118,7 @@
       <c r="E191" s="8"/>
       <c r="F191" s="8"/>
     </row>
-    <row r="192" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
       <c r="B192" s="14"/>
       <c r="C192" s="11"/>
@@ -4096,7 +4126,7 @@
       <c r="E192" s="8"/>
       <c r="F192" s="8"/>
     </row>
-    <row r="193" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
       <c r="B193" s="14"/>
       <c r="C193" s="11"/>
@@ -4104,7 +4134,7 @@
       <c r="E193" s="8"/>
       <c r="F193" s="8"/>
     </row>
-    <row r="194" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6"/>
       <c r="B194" s="14"/>
       <c r="C194" s="11"/>
@@ -4112,7 +4142,7 @@
       <c r="E194" s="8"/>
       <c r="F194" s="8"/>
     </row>
-    <row r="195" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
       <c r="B195" s="14"/>
       <c r="C195" s="11"/>
@@ -4120,7 +4150,7 @@
       <c r="E195" s="8"/>
       <c r="F195" s="8"/>
     </row>
-    <row r="196" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
       <c r="B196" s="14"/>
       <c r="C196" s="11"/>
@@ -4128,7 +4158,7 @@
       <c r="E196" s="8"/>
       <c r="F196" s="8"/>
     </row>
-    <row r="197" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
       <c r="B197" s="14"/>
       <c r="C197" s="11"/>
@@ -4136,7 +4166,7 @@
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
     </row>
-    <row r="198" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6"/>
       <c r="B198" s="14"/>
       <c r="C198" s="11"/>
@@ -4144,7 +4174,7 @@
       <c r="E198" s="8"/>
       <c r="F198" s="8"/>
     </row>
-    <row r="199" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
       <c r="B199" s="14"/>
       <c r="C199" s="11"/>
@@ -4152,7 +4182,7 @@
       <c r="E199" s="8"/>
       <c r="F199" s="8"/>
     </row>
-    <row r="200" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
       <c r="B200" s="14"/>
       <c r="C200" s="11"/>
@@ -4160,7 +4190,7 @@
       <c r="E200" s="8"/>
       <c r="F200" s="8"/>
     </row>
-    <row r="201" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
       <c r="B201" s="14"/>
       <c r="C201" s="11"/>
@@ -4168,7 +4198,7 @@
       <c r="E201" s="8"/>
       <c r="F201" s="8"/>
     </row>
-    <row r="202" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="B202" s="14"/>
       <c r="C202" s="11"/>
@@ -4176,7 +4206,7 @@
       <c r="E202" s="8"/>
       <c r="F202" s="8"/>
     </row>
-    <row r="203" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
       <c r="B203" s="14"/>
       <c r="C203" s="11"/>
@@ -4184,7 +4214,7 @@
       <c r="E203" s="8"/>
       <c r="F203" s="8"/>
     </row>
-    <row r="204" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="B204" s="14"/>
       <c r="C204" s="11"/>
@@ -4192,7 +4222,7 @@
       <c r="E204" s="8"/>
       <c r="F204" s="8"/>
     </row>
-    <row r="205" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
       <c r="B205" s="14"/>
       <c r="C205" s="11"/>
@@ -4200,7 +4230,7 @@
       <c r="E205" s="8"/>
       <c r="F205" s="8"/>
     </row>
-    <row r="206" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="B206" s="14"/>
       <c r="C206" s="11"/>
@@ -4208,7 +4238,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="B207" s="14"/>
       <c r="C207" s="11"/>
@@ -4216,7 +4246,7 @@
       <c r="E207" s="8"/>
       <c r="F207" s="8"/>
     </row>
-    <row r="208" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="B208" s="14"/>
       <c r="C208" s="11"/>
@@ -4224,7 +4254,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6"/>
       <c r="B209" s="14"/>
       <c r="C209" s="11"/>
@@ -4232,7 +4262,7 @@
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
       <c r="B210" s="14"/>
       <c r="C210" s="11"/>
@@ -4240,7 +4270,7 @@
       <c r="E210" s="8"/>
       <c r="F210" s="8"/>
     </row>
-    <row r="211" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
       <c r="B211" s="14"/>
       <c r="C211" s="11"/>
@@ -4248,7 +4278,7 @@
       <c r="E211" s="8"/>
       <c r="F211" s="8"/>
     </row>
-    <row r="212" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
       <c r="B212" s="14"/>
       <c r="C212" s="11"/>
@@ -4256,7 +4286,7 @@
       <c r="E212" s="8"/>
       <c r="F212" s="8"/>
     </row>
-    <row r="213" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6"/>
       <c r="B213" s="14"/>
       <c r="C213" s="11"/>
@@ -4264,7 +4294,7 @@
       <c r="E213" s="8"/>
       <c r="F213" s="8"/>
     </row>
-    <row r="214" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
       <c r="B214" s="14"/>
       <c r="C214" s="11"/>
@@ -4272,7 +4302,7 @@
       <c r="E214" s="8"/>
       <c r="F214" s="8"/>
     </row>
-    <row r="215" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
       <c r="B215" s="14"/>
       <c r="C215" s="11"/>
@@ -4280,7 +4310,7 @@
       <c r="E215" s="8"/>
       <c r="F215" s="8"/>
     </row>
-    <row r="216" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
       <c r="B216" s="14"/>
       <c r="C216" s="11"/>
@@ -4288,7 +4318,7 @@
       <c r="E216" s="8"/>
       <c r="F216" s="8"/>
     </row>
-    <row r="217" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6"/>
       <c r="B217" s="14"/>
       <c r="C217" s="11"/>
@@ -4296,7 +4326,7 @@
       <c r="E217" s="8"/>
       <c r="F217" s="8"/>
     </row>
-    <row r="218" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
       <c r="B218" s="14"/>
       <c r="C218" s="11"/>
@@ -4304,7 +4334,7 @@
       <c r="E218" s="8"/>
       <c r="F218" s="8"/>
     </row>
-    <row r="219" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
       <c r="B219" s="14"/>
       <c r="C219" s="11"/>
@@ -4312,7 +4342,7 @@
       <c r="E219" s="8"/>
       <c r="F219" s="8"/>
     </row>
-    <row r="220" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
       <c r="B220" s="14"/>
       <c r="C220" s="11"/>
@@ -4320,7 +4350,7 @@
       <c r="E220" s="8"/>
       <c r="F220" s="8"/>
     </row>
-    <row r="221" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6"/>
       <c r="B221" s="14"/>
       <c r="C221" s="11"/>
@@ -4328,7 +4358,7 @@
       <c r="E221" s="8"/>
       <c r="F221" s="8"/>
     </row>
-    <row r="222" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
       <c r="B222" s="14"/>
       <c r="C222" s="11"/>
@@ -4336,7 +4366,7 @@
       <c r="E222" s="8"/>
       <c r="F222" s="8"/>
     </row>
-    <row r="223" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
       <c r="B223" s="14"/>
       <c r="C223" s="11"/>
@@ -4344,7 +4374,7 @@
       <c r="E223" s="8"/>
       <c r="F223" s="8"/>
     </row>
-    <row r="224" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
       <c r="B224" s="14"/>
       <c r="C224" s="11"/>
@@ -4352,7 +4382,7 @@
       <c r="E224" s="8"/>
       <c r="F224" s="8"/>
     </row>
-    <row r="225" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
       <c r="B225" s="14"/>
       <c r="C225" s="11"/>
@@ -4360,7 +4390,7 @@
       <c r="E225" s="8"/>
       <c r="F225" s="8"/>
     </row>
-    <row r="226" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6"/>
       <c r="B226" s="14"/>
       <c r="C226" s="11"/>
@@ -4368,7 +4398,7 @@
       <c r="E226" s="8"/>
       <c r="F226" s="8"/>
     </row>
-    <row r="227" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
       <c r="B227" s="14"/>
       <c r="C227" s="11"/>
@@ -4376,7 +4406,7 @@
       <c r="E227" s="8"/>
       <c r="F227" s="8"/>
     </row>
-    <row r="228" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
       <c r="B228" s="14"/>
       <c r="C228" s="11"/>
@@ -4384,7 +4414,7 @@
       <c r="E228" s="8"/>
       <c r="F228" s="8"/>
     </row>
-    <row r="229" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
       <c r="B229" s="14"/>
       <c r="C229" s="11"/>
@@ -4392,7 +4422,7 @@
       <c r="E229" s="8"/>
       <c r="F229" s="8"/>
     </row>
-    <row r="230" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
       <c r="B230" s="14"/>
       <c r="C230" s="11"/>
@@ -4400,7 +4430,7 @@
       <c r="E230" s="8"/>
       <c r="F230" s="8"/>
     </row>
-    <row r="231" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
       <c r="B231" s="14"/>
       <c r="C231" s="11"/>
@@ -4408,7 +4438,7 @@
       <c r="E231" s="8"/>
       <c r="F231" s="8"/>
     </row>
-    <row r="232" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6"/>
       <c r="B232" s="14"/>
       <c r="C232" s="11"/>
@@ -4416,7 +4446,7 @@
       <c r="E232" s="8"/>
       <c r="F232" s="8"/>
     </row>
-    <row r="233" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
       <c r="B233" s="14"/>
       <c r="C233" s="11"/>
@@ -4424,7 +4454,7 @@
       <c r="E233" s="8"/>
       <c r="F233" s="8"/>
     </row>
-    <row r="234" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
       <c r="B234" s="14"/>
       <c r="C234" s="11"/>
@@ -4432,7 +4462,7 @@
       <c r="E234" s="8"/>
       <c r="F234" s="8"/>
     </row>
-    <row r="235" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6"/>
       <c r="B235" s="14"/>
       <c r="C235" s="11"/>
@@ -4440,7 +4470,7 @@
       <c r="E235" s="8"/>
       <c r="F235" s="8"/>
     </row>
-    <row r="236" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
       <c r="B236" s="14"/>
       <c r="C236" s="11"/>
@@ -4448,7 +4478,7 @@
       <c r="E236" s="8"/>
       <c r="F236" s="8"/>
     </row>
-    <row r="237" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
       <c r="B237" s="14"/>
       <c r="C237" s="11"/>
@@ -4456,7 +4486,7 @@
       <c r="E237" s="8"/>
       <c r="F237" s="8"/>
     </row>
-    <row r="238" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
       <c r="B238" s="14"/>
       <c r="C238" s="11"/>
@@ -4464,7 +4494,7 @@
       <c r="E238" s="8"/>
       <c r="F238" s="8"/>
     </row>
-    <row r="239" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6"/>
       <c r="B239" s="14"/>
       <c r="C239" s="11"/>
@@ -4472,7 +4502,7 @@
       <c r="E239" s="8"/>
       <c r="F239" s="8"/>
     </row>
-    <row r="240" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6"/>
       <c r="B240" s="14"/>
       <c r="C240" s="11"/>
@@ -4480,7 +4510,7 @@
       <c r="E240" s="8"/>
       <c r="F240" s="8"/>
     </row>
-    <row r="241" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
       <c r="B241" s="14"/>
       <c r="C241" s="11"/>
@@ -4488,7 +4518,7 @@
       <c r="E241" s="8"/>
       <c r="F241" s="8"/>
     </row>
-    <row r="242" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="B242" s="14"/>
       <c r="C242" s="11"/>
@@ -4496,7 +4526,7 @@
       <c r="E242" s="8"/>
       <c r="F242" s="8"/>
     </row>
-    <row r="243" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
       <c r="B243" s="14"/>
       <c r="C243" s="11"/>
@@ -4504,7 +4534,7 @@
       <c r="E243" s="8"/>
       <c r="F243" s="8"/>
     </row>
-    <row r="244" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
       <c r="B244" s="14"/>
       <c r="C244" s="11"/>
@@ -4512,7 +4542,7 @@
       <c r="E244" s="8"/>
       <c r="F244" s="8"/>
     </row>
-    <row r="245" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6"/>
       <c r="B245" s="14"/>
       <c r="C245" s="11"/>
@@ -4520,7 +4550,7 @@
       <c r="E245" s="8"/>
       <c r="F245" s="8"/>
     </row>
-    <row r="246" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
       <c r="B246" s="14"/>
       <c r="C246" s="11"/>
@@ -4528,7 +4558,7 @@
       <c r="E246" s="8"/>
       <c r="F246" s="8"/>
     </row>
-    <row r="247" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
       <c r="B247" s="14"/>
       <c r="C247" s="11"/>
@@ -4536,7 +4566,7 @@
       <c r="E247" s="8"/>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
       <c r="B248" s="14"/>
       <c r="C248" s="11"/>
@@ -4544,7 +4574,7 @@
       <c r="E248" s="8"/>
       <c r="F248" s="8"/>
     </row>
-    <row r="249" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6"/>
       <c r="B249" s="14"/>
       <c r="C249" s="11"/>
@@ -4552,7 +4582,7 @@
       <c r="E249" s="8"/>
       <c r="F249" s="8"/>
     </row>
-    <row r="250" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
       <c r="B250" s="14"/>
       <c r="C250" s="11"/>
@@ -4560,7 +4590,7 @@
       <c r="E250" s="8"/>
       <c r="F250" s="8"/>
     </row>
-    <row r="251" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6"/>
       <c r="B251" s="14"/>
       <c r="C251" s="11"/>
@@ -4568,7 +4598,7 @@
       <c r="E251" s="8"/>
       <c r="F251" s="8"/>
     </row>
-    <row r="252" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
       <c r="B252" s="14"/>
       <c r="C252" s="11"/>
@@ -4576,7 +4606,7 @@
       <c r="E252" s="8"/>
       <c r="F252" s="8"/>
     </row>
-    <row r="253" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
       <c r="B253" s="14"/>
       <c r="C253" s="11"/>
@@ -4584,7 +4614,7 @@
       <c r="E253" s="8"/>
       <c r="F253" s="8"/>
     </row>
-    <row r="254" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6"/>
       <c r="B254" s="14"/>
       <c r="C254" s="11"/>
@@ -4592,7 +4622,7 @@
       <c r="E254" s="8"/>
       <c r="F254" s="8"/>
     </row>
-    <row r="255" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6"/>
       <c r="B255" s="14"/>
       <c r="C255" s="11"/>
@@ -4600,7 +4630,7 @@
       <c r="E255" s="8"/>
       <c r="F255" s="8"/>
     </row>
-    <row r="256" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
       <c r="B256" s="14"/>
       <c r="C256" s="11"/>
@@ -4608,7 +4638,7 @@
       <c r="E256" s="8"/>
       <c r="F256" s="8"/>
     </row>
-    <row r="257" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6"/>
       <c r="B257" s="14"/>
       <c r="C257" s="11"/>
@@ -4616,7 +4646,7 @@
       <c r="E257" s="8"/>
       <c r="F257" s="8"/>
     </row>
-    <row r="258" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
       <c r="B258" s="14"/>
       <c r="C258" s="11"/>
@@ -4624,7 +4654,7 @@
       <c r="E258" s="8"/>
       <c r="F258" s="8"/>
     </row>
-    <row r="259" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6"/>
       <c r="B259" s="14"/>
       <c r="C259" s="11"/>
@@ -4632,7 +4662,7 @@
       <c r="E259" s="8"/>
       <c r="F259" s="8"/>
     </row>
-    <row r="260" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6"/>
       <c r="B260" s="14"/>
       <c r="C260" s="11"/>
@@ -4640,7 +4670,7 @@
       <c r="E260" s="8"/>
       <c r="F260" s="8"/>
     </row>
-    <row r="261" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6"/>
       <c r="B261" s="14"/>
       <c r="C261" s="11"/>
@@ -4648,7 +4678,7 @@
       <c r="E261" s="8"/>
       <c r="F261" s="8"/>
     </row>
-    <row r="262" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6"/>
       <c r="B262" s="14"/>
       <c r="C262" s="11"/>
@@ -4656,7 +4686,7 @@
       <c r="E262" s="8"/>
       <c r="F262" s="8"/>
     </row>
-    <row r="263" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6"/>
       <c r="B263" s="14"/>
       <c r="C263" s="11"/>
@@ -4664,7 +4694,7 @@
       <c r="E263" s="8"/>
       <c r="F263" s="8"/>
     </row>
-    <row r="264" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
       <c r="B264" s="14"/>
       <c r="C264" s="11"/>
@@ -4672,7 +4702,7 @@
       <c r="E264" s="8"/>
       <c r="F264" s="8"/>
     </row>
-    <row r="265" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
       <c r="B265" s="14"/>
       <c r="C265" s="11"/>
@@ -4680,7 +4710,7 @@
       <c r="E265" s="8"/>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
       <c r="B266" s="14"/>
       <c r="C266" s="11"/>
@@ -4688,7 +4718,7 @@
       <c r="E266" s="8"/>
       <c r="F266" s="8"/>
     </row>
-    <row r="267" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6"/>
       <c r="B267" s="14"/>
       <c r="C267" s="11"/>
@@ -4696,7 +4726,7 @@
       <c r="E267" s="8"/>
       <c r="F267" s="8"/>
     </row>
-    <row r="268" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
       <c r="B268" s="14"/>
       <c r="C268" s="11"/>
@@ -4704,7 +4734,7 @@
       <c r="E268" s="8"/>
       <c r="F268" s="8"/>
     </row>
-    <row r="269" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
       <c r="B269" s="14"/>
       <c r="C269" s="11"/>
@@ -4712,7 +4742,7 @@
       <c r="E269" s="8"/>
       <c r="F269" s="8"/>
     </row>
-    <row r="270" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6"/>
       <c r="B270" s="14"/>
       <c r="C270" s="11"/>
@@ -4720,7 +4750,7 @@
       <c r="E270" s="8"/>
       <c r="F270" s="8"/>
     </row>
-    <row r="271" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6"/>
       <c r="B271" s="14"/>
       <c r="C271" s="11"/>
@@ -4728,7 +4758,7 @@
       <c r="E271" s="8"/>
       <c r="F271" s="8"/>
     </row>
-    <row r="272" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
       <c r="B272" s="14"/>
       <c r="C272" s="11"/>
@@ -4736,7 +4766,7 @@
       <c r="E272" s="8"/>
       <c r="F272" s="8"/>
     </row>
-    <row r="273" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6"/>
       <c r="B273" s="14"/>
       <c r="C273" s="11"/>
@@ -4744,7 +4774,7 @@
       <c r="E273" s="8"/>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
       <c r="B274" s="14"/>
       <c r="C274" s="11"/>
@@ -4752,7 +4782,7 @@
       <c r="E274" s="8"/>
       <c r="F274" s="8"/>
     </row>
-    <row r="275" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
       <c r="B275" s="14"/>
       <c r="C275" s="11"/>
@@ -4760,7 +4790,7 @@
       <c r="E275" s="8"/>
       <c r="F275" s="8"/>
     </row>
-    <row r="276" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
       <c r="B276" s="14"/>
       <c r="C276" s="11"/>
@@ -4768,7 +4798,7 @@
       <c r="E276" s="8"/>
       <c r="F276" s="8"/>
     </row>
-    <row r="277" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6"/>
       <c r="B277" s="14"/>
       <c r="C277" s="11"/>
@@ -4776,7 +4806,7 @@
       <c r="E277" s="8"/>
       <c r="F277" s="8"/>
     </row>
-    <row r="278" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
       <c r="B278" s="14"/>
       <c r="C278" s="11"/>
@@ -4784,7 +4814,7 @@
       <c r="E278" s="8"/>
       <c r="F278" s="8"/>
     </row>
-    <row r="279" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
       <c r="B279" s="14"/>
       <c r="C279" s="11"/>
@@ -4792,7 +4822,7 @@
       <c r="E279" s="8"/>
       <c r="F279" s="8"/>
     </row>
-    <row r="280" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
       <c r="B280" s="14"/>
       <c r="C280" s="11"/>
@@ -4800,7 +4830,7 @@
       <c r="E280" s="8"/>
       <c r="F280" s="8"/>
     </row>
-    <row r="281" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6"/>
       <c r="B281" s="14"/>
       <c r="C281" s="11"/>
@@ -4808,7 +4838,7 @@
       <c r="E281" s="8"/>
       <c r="F281" s="8"/>
     </row>
-    <row r="282" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6"/>
       <c r="B282" s="14"/>
       <c r="C282" s="11"/>
@@ -4816,7 +4846,7 @@
       <c r="E282" s="8"/>
       <c r="F282" s="8"/>
     </row>
-    <row r="283" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
       <c r="B283" s="14"/>
       <c r="C283" s="11"/>
@@ -4824,7 +4854,7 @@
       <c r="E283" s="8"/>
       <c r="F283" s="8"/>
     </row>
-    <row r="284" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
       <c r="B284" s="14"/>
       <c r="C284" s="11"/>
@@ -4832,7 +4862,7 @@
       <c r="E284" s="8"/>
       <c r="F284" s="8"/>
     </row>
-    <row r="285" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6"/>
       <c r="B285" s="14"/>
       <c r="C285" s="11"/>
@@ -4840,7 +4870,7 @@
       <c r="E285" s="8"/>
       <c r="F285" s="8"/>
     </row>
-    <row r="286" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
       <c r="B286" s="14"/>
       <c r="C286" s="11"/>
@@ -4848,7 +4878,7 @@
       <c r="E286" s="8"/>
       <c r="F286" s="8"/>
     </row>
-    <row r="287" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6"/>
       <c r="B287" s="14"/>
       <c r="C287" s="11"/>
@@ -4856,7 +4886,7 @@
       <c r="E287" s="8"/>
       <c r="F287" s="8"/>
     </row>
-    <row r="288" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
       <c r="B288" s="14"/>
       <c r="C288" s="11"/>
@@ -4864,7 +4894,7 @@
       <c r="E288" s="8"/>
       <c r="F288" s="8"/>
     </row>
-    <row r="289" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6"/>
       <c r="B289" s="14"/>
       <c r="C289" s="11"/>
@@ -4872,7 +4902,7 @@
       <c r="E289" s="8"/>
       <c r="F289" s="8"/>
     </row>
-    <row r="290" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
       <c r="B290" s="14"/>
       <c r="C290" s="11"/>
@@ -4880,7 +4910,7 @@
       <c r="E290" s="8"/>
       <c r="F290" s="8"/>
     </row>
-    <row r="291" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6"/>
       <c r="B291" s="14"/>
       <c r="C291" s="11"/>
@@ -4888,7 +4918,7 @@
       <c r="E291" s="8"/>
       <c r="F291" s="8"/>
     </row>
-    <row r="292" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6"/>
       <c r="B292" s="14"/>
       <c r="C292" s="11"/>
@@ -4896,7 +4926,7 @@
       <c r="E292" s="8"/>
       <c r="F292" s="8"/>
     </row>
-    <row r="293" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
       <c r="B293" s="14"/>
       <c r="C293" s="11"/>
@@ -4904,7 +4934,7 @@
       <c r="E293" s="8"/>
       <c r="F293" s="8"/>
     </row>
-    <row r="294" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
       <c r="B294" s="14"/>
       <c r="C294" s="11"/>
@@ -4912,7 +4942,7 @@
       <c r="E294" s="8"/>
       <c r="F294" s="8"/>
     </row>
-    <row r="295" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6"/>
       <c r="B295" s="14"/>
       <c r="C295" s="11"/>
@@ -4920,7 +4950,7 @@
       <c r="E295" s="8"/>
       <c r="F295" s="8"/>
     </row>
-    <row r="296" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
       <c r="B296" s="14"/>
       <c r="C296" s="11"/>
@@ -4928,7 +4958,7 @@
       <c r="E296" s="8"/>
       <c r="F296" s="8"/>
     </row>
-    <row r="297" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
       <c r="B297" s="14"/>
       <c r="C297" s="11"/>
@@ -4936,7 +4966,7 @@
       <c r="E297" s="8"/>
       <c r="F297" s="8"/>
     </row>
-    <row r="298" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
       <c r="B298" s="14"/>
       <c r="C298" s="11"/>
@@ -4944,7 +4974,7 @@
       <c r="E298" s="8"/>
       <c r="F298" s="8"/>
     </row>
-    <row r="299" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6"/>
       <c r="B299" s="14"/>
       <c r="C299" s="11"/>
@@ -4952,7 +4982,7 @@
       <c r="E299" s="8"/>
       <c r="F299" s="8"/>
     </row>
-    <row r="300" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6"/>
       <c r="B300" s="14"/>
       <c r="C300" s="11"/>
@@ -4960,7 +4990,7 @@
       <c r="E300" s="8"/>
       <c r="F300" s="8"/>
     </row>
-    <row r="301" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6"/>
       <c r="B301" s="14"/>
       <c r="C301" s="11"/>
@@ -4968,7 +4998,7 @@
       <c r="E301" s="8"/>
       <c r="F301" s="8"/>
     </row>
-    <row r="302" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6"/>
       <c r="B302" s="14"/>
       <c r="C302" s="11"/>
@@ -4976,7 +5006,7 @@
       <c r="E302" s="8"/>
       <c r="F302" s="8"/>
     </row>
-    <row r="303" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6"/>
       <c r="B303" s="14"/>
       <c r="C303" s="11"/>
@@ -4984,7 +5014,7 @@
       <c r="E303" s="8"/>
       <c r="F303" s="8"/>
     </row>
-    <row r="304" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6"/>
       <c r="B304" s="14"/>
       <c r="C304" s="11"/>
@@ -4992,7 +5022,7 @@
       <c r="E304" s="8"/>
       <c r="F304" s="8"/>
     </row>
-    <row r="305" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6"/>
       <c r="B305" s="14"/>
       <c r="C305" s="11"/>
@@ -5000,7 +5030,7 @@
       <c r="E305" s="8"/>
       <c r="F305" s="8"/>
     </row>
-    <row r="306" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6"/>
       <c r="B306" s="14"/>
       <c r="C306" s="11"/>
@@ -5008,7 +5038,7 @@
       <c r="E306" s="8"/>
       <c r="F306" s="8"/>
     </row>
-    <row r="307" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6"/>
       <c r="B307" s="14"/>
       <c r="C307" s="11"/>
@@ -5016,7 +5046,7 @@
       <c r="E307" s="8"/>
       <c r="F307" s="8"/>
     </row>
-    <row r="308" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6"/>
       <c r="B308" s="14"/>
       <c r="C308" s="11"/>
@@ -5024,7 +5054,7 @@
       <c r="E308" s="8"/>
       <c r="F308" s="8"/>
     </row>
-    <row r="309" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="6"/>
       <c r="B309" s="14"/>
       <c r="C309" s="11"/>
@@ -5032,7 +5062,7 @@
       <c r="E309" s="8"/>
       <c r="F309" s="8"/>
     </row>
-    <row r="310" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6"/>
       <c r="B310" s="14"/>
       <c r="C310" s="11"/>
@@ -5040,7 +5070,7 @@
       <c r="E310" s="8"/>
       <c r="F310" s="8"/>
     </row>
-    <row r="311" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="6"/>
       <c r="B311" s="14"/>
       <c r="C311" s="11"/>
@@ -5048,7 +5078,7 @@
       <c r="E311" s="8"/>
       <c r="F311" s="8"/>
     </row>
-    <row r="312" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6"/>
       <c r="B312" s="14"/>
       <c r="C312" s="11"/>
@@ -5056,7 +5086,7 @@
       <c r="E312" s="8"/>
       <c r="F312" s="8"/>
     </row>
-    <row r="313" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="6"/>
       <c r="B313" s="14"/>
       <c r="C313" s="11"/>
@@ -5064,7 +5094,7 @@
       <c r="E313" s="8"/>
       <c r="F313" s="8"/>
     </row>
-    <row r="314" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6"/>
       <c r="B314" s="14"/>
       <c r="C314" s="11"/>
@@ -5072,7 +5102,7 @@
       <c r="E314" s="8"/>
       <c r="F314" s="8"/>
     </row>
-    <row r="315" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="6"/>
       <c r="B315" s="14"/>
       <c r="C315" s="11"/>
@@ -5080,7 +5110,7 @@
       <c r="E315" s="8"/>
       <c r="F315" s="8"/>
     </row>
-    <row r="316" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="6"/>
       <c r="B316" s="14"/>
       <c r="C316" s="11"/>
@@ -5088,7 +5118,7 @@
       <c r="E316" s="8"/>
       <c r="F316" s="8"/>
     </row>
-    <row r="317" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="6"/>
       <c r="B317" s="14"/>
       <c r="C317" s="11"/>
@@ -5096,7 +5126,7 @@
       <c r="E317" s="8"/>
       <c r="F317" s="8"/>
     </row>
-    <row r="318" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6"/>
       <c r="B318" s="14"/>
       <c r="C318" s="11"/>
@@ -5104,7 +5134,7 @@
       <c r="E318" s="8"/>
       <c r="F318" s="8"/>
     </row>
-    <row r="319" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="6"/>
       <c r="B319" s="14"/>
       <c r="C319" s="11"/>
@@ -5112,7 +5142,7 @@
       <c r="E319" s="8"/>
       <c r="F319" s="8"/>
     </row>
-    <row r="320" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="6"/>
       <c r="B320" s="14"/>
       <c r="C320" s="11"/>
@@ -5120,7 +5150,7 @@
       <c r="E320" s="8"/>
       <c r="F320" s="8"/>
     </row>
-    <row r="321" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6"/>
       <c r="B321" s="14"/>
       <c r="C321" s="11"/>
@@ -5128,7 +5158,7 @@
       <c r="E321" s="8"/>
       <c r="F321" s="8"/>
     </row>
-    <row r="322" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="6"/>
       <c r="B322" s="14"/>
       <c r="C322" s="11"/>
@@ -5136,7 +5166,7 @@
       <c r="E322" s="8"/>
       <c r="F322" s="8"/>
     </row>
-    <row r="323" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="6"/>
       <c r="B323" s="14"/>
       <c r="C323" s="11"/>
@@ -5144,7 +5174,7 @@
       <c r="E323" s="8"/>
       <c r="F323" s="8"/>
     </row>
-    <row r="324" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6"/>
       <c r="B324" s="14"/>
       <c r="C324" s="11"/>
@@ -5152,7 +5182,7 @@
       <c r="E324" s="8"/>
       <c r="F324" s="8"/>
     </row>
-    <row r="325" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="6"/>
       <c r="B325" s="14"/>
       <c r="C325" s="11"/>
@@ -5160,7 +5190,7 @@
       <c r="E325" s="8"/>
       <c r="F325" s="8"/>
     </row>
-    <row r="326" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="6"/>
       <c r="B326" s="14"/>
       <c r="C326" s="11"/>
@@ -5168,7 +5198,7 @@
       <c r="E326" s="8"/>
       <c r="F326" s="8"/>
     </row>
-    <row r="327" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="6"/>
       <c r="B327" s="14"/>
       <c r="C327" s="11"/>
@@ -5176,7 +5206,7 @@
       <c r="E327" s="8"/>
       <c r="F327" s="8"/>
     </row>
-    <row r="328" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="6"/>
       <c r="B328" s="14"/>
       <c r="C328" s="11"/>
@@ -5184,7 +5214,7 @@
       <c r="E328" s="8"/>
       <c r="F328" s="8"/>
     </row>
-    <row r="329" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="6"/>
       <c r="B329" s="14"/>
       <c r="C329" s="11"/>
@@ -5192,7 +5222,7 @@
       <c r="E329" s="8"/>
       <c r="F329" s="8"/>
     </row>
-    <row r="330" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="6"/>
       <c r="B330" s="14"/>
       <c r="C330" s="11"/>
@@ -5200,7 +5230,7 @@
       <c r="E330" s="8"/>
       <c r="F330" s="8"/>
     </row>
-    <row r="331" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="6"/>
       <c r="B331" s="14"/>
       <c r="C331" s="11"/>
@@ -5208,7 +5238,7 @@
       <c r="E331" s="8"/>
       <c r="F331" s="8"/>
     </row>
-    <row r="332" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6"/>
       <c r="B332" s="14"/>
       <c r="C332" s="11"/>
@@ -5216,7 +5246,7 @@
       <c r="E332" s="8"/>
       <c r="F332" s="8"/>
     </row>
-    <row r="333" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="6"/>
       <c r="B333" s="14"/>
       <c r="C333" s="11"/>
@@ -5224,7 +5254,7 @@
       <c r="E333" s="8"/>
       <c r="F333" s="8"/>
     </row>
-    <row r="334" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="6"/>
       <c r="B334" s="14"/>
       <c r="C334" s="11"/>
@@ -5232,7 +5262,7 @@
       <c r="E334" s="8"/>
       <c r="F334" s="8"/>
     </row>
-    <row r="335" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="6"/>
       <c r="B335" s="14"/>
       <c r="C335" s="11"/>
@@ -5240,7 +5270,7 @@
       <c r="E335" s="8"/>
       <c r="F335" s="8"/>
     </row>
-    <row r="336" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="6"/>
       <c r="B336" s="14"/>
       <c r="C336" s="11"/>
@@ -5248,7 +5278,7 @@
       <c r="E336" s="8"/>
       <c r="F336" s="8"/>
     </row>
-    <row r="337" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="6"/>
       <c r="B337" s="14"/>
       <c r="C337" s="11"/>
@@ -5256,7 +5286,7 @@
       <c r="E337" s="8"/>
       <c r="F337" s="8"/>
     </row>
-    <row r="338" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="6"/>
       <c r="B338" s="14"/>
       <c r="C338" s="11"/>
@@ -5264,7 +5294,7 @@
       <c r="E338" s="8"/>
       <c r="F338" s="8"/>
     </row>
-    <row r="339" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="6"/>
       <c r="B339" s="14"/>
       <c r="C339" s="11"/>
@@ -5272,7 +5302,7 @@
       <c r="E339" s="8"/>
       <c r="F339" s="8"/>
     </row>
-    <row r="340" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="6"/>
       <c r="B340" s="14"/>
       <c r="C340" s="11"/>
@@ -5280,7 +5310,7 @@
       <c r="E340" s="8"/>
       <c r="F340" s="8"/>
     </row>
-    <row r="341" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="6"/>
       <c r="B341" s="14"/>
       <c r="C341" s="11"/>
@@ -5288,7 +5318,7 @@
       <c r="E341" s="8"/>
       <c r="F341" s="8"/>
     </row>
-    <row r="342" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="6"/>
       <c r="B342" s="14"/>
       <c r="C342" s="11"/>
@@ -5296,7 +5326,7 @@
       <c r="E342" s="8"/>
       <c r="F342" s="8"/>
     </row>
-    <row r="343" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="6"/>
       <c r="B343" s="14"/>
       <c r="C343" s="11"/>
@@ -5304,7 +5334,7 @@
       <c r="E343" s="8"/>
       <c r="F343" s="8"/>
     </row>
-    <row r="344" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6"/>
       <c r="B344" s="14"/>
       <c r="C344" s="11"/>
@@ -5312,7 +5342,7 @@
       <c r="E344" s="8"/>
       <c r="F344" s="8"/>
     </row>
-    <row r="345" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="6"/>
       <c r="B345" s="14"/>
       <c r="C345" s="11"/>
@@ -5320,7 +5350,7 @@
       <c r="E345" s="8"/>
       <c r="F345" s="8"/>
     </row>
-    <row r="346" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="6"/>
       <c r="B346" s="14"/>
       <c r="C346" s="11"/>
@@ -5328,7 +5358,7 @@
       <c r="E346" s="8"/>
       <c r="F346" s="8"/>
     </row>
-    <row r="347" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="6"/>
       <c r="B347" s="14"/>
       <c r="C347" s="11"/>
@@ -5336,7 +5366,7 @@
       <c r="E347" s="8"/>
       <c r="F347" s="8"/>
     </row>
-    <row r="348" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="6"/>
       <c r="B348" s="14"/>
       <c r="C348" s="11"/>
@@ -5344,7 +5374,7 @@
       <c r="E348" s="8"/>
       <c r="F348" s="8"/>
     </row>
-    <row r="349" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="6"/>
       <c r="B349" s="14"/>
       <c r="C349" s="11"/>
@@ -5352,7 +5382,7 @@
       <c r="E349" s="8"/>
       <c r="F349" s="8"/>
     </row>
-    <row r="350" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="6"/>
       <c r="B350" s="14"/>
       <c r="C350" s="11"/>
@@ -5360,7 +5390,7 @@
       <c r="E350" s="8"/>
       <c r="F350" s="8"/>
     </row>
-    <row r="351" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="6"/>
       <c r="B351" s="14"/>
       <c r="C351" s="11"/>
@@ -5368,7 +5398,7 @@
       <c r="E351" s="8"/>
       <c r="F351" s="8"/>
     </row>
-    <row r="352" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="6"/>
       <c r="B352" s="14"/>
       <c r="C352" s="11"/>
@@ -5376,7 +5406,7 @@
       <c r="E352" s="8"/>
       <c r="F352" s="8"/>
     </row>
-    <row r="353" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="6"/>
       <c r="B353" s="14"/>
       <c r="C353" s="11"/>
@@ -5384,7 +5414,7 @@
       <c r="E353" s="8"/>
       <c r="F353" s="8"/>
     </row>
-    <row r="354" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="6"/>
       <c r="B354" s="14"/>
       <c r="C354" s="11"/>
@@ -5392,7 +5422,7 @@
       <c r="E354" s="8"/>
       <c r="F354" s="8"/>
     </row>
-    <row r="355" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="6"/>
       <c r="B355" s="14"/>
       <c r="C355" s="11"/>
@@ -5400,7 +5430,7 @@
       <c r="E355" s="8"/>
       <c r="F355" s="8"/>
     </row>
-    <row r="356" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="6"/>
       <c r="B356" s="14"/>
       <c r="C356" s="11"/>
@@ -5408,7 +5438,7 @@
       <c r="E356" s="8"/>
       <c r="F356" s="8"/>
     </row>
-    <row r="357" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="6"/>
       <c r="B357" s="14"/>
       <c r="C357" s="11"/>
@@ -5416,7 +5446,7 @@
       <c r="E357" s="8"/>
       <c r="F357" s="8"/>
     </row>
-    <row r="358" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6"/>
       <c r="B358" s="14"/>
       <c r="C358" s="11"/>
@@ -5424,7 +5454,7 @@
       <c r="E358" s="8"/>
       <c r="F358" s="8"/>
     </row>
-    <row r="359" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="6"/>
       <c r="B359" s="14"/>
       <c r="C359" s="11"/>
@@ -5432,7 +5462,7 @@
       <c r="E359" s="8"/>
       <c r="F359" s="8"/>
     </row>
-    <row r="360" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="6"/>
       <c r="B360" s="14"/>
       <c r="C360" s="11"/>
@@ -5440,7 +5470,7 @@
       <c r="E360" s="8"/>
       <c r="F360" s="8"/>
     </row>
-    <row r="361" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="6"/>
       <c r="B361" s="14"/>
       <c r="C361" s="11"/>
@@ -5448,7 +5478,7 @@
       <c r="E361" s="8"/>
       <c r="F361" s="8"/>
     </row>
-    <row r="362" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="6"/>
       <c r="B362" s="14"/>
       <c r="C362" s="11"/>
@@ -5456,7 +5486,7 @@
       <c r="E362" s="8"/>
       <c r="F362" s="8"/>
     </row>
-    <row r="363" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="6"/>
       <c r="B363" s="14"/>
       <c r="C363" s="11"/>
@@ -5464,7 +5494,7 @@
       <c r="E363" s="8"/>
       <c r="F363" s="8"/>
     </row>
-    <row r="364" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="6"/>
       <c r="B364" s="14"/>
       <c r="C364" s="11"/>
@@ -5472,7 +5502,7 @@
       <c r="E364" s="8"/>
       <c r="F364" s="8"/>
     </row>
-    <row r="365" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="6"/>
       <c r="B365" s="14"/>
       <c r="C365" s="11"/>
@@ -5480,7 +5510,7 @@
       <c r="E365" s="8"/>
       <c r="F365" s="8"/>
     </row>
-    <row r="366" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6"/>
       <c r="B366" s="14"/>
       <c r="C366" s="11"/>
@@ -5488,7 +5518,7 @@
       <c r="E366" s="8"/>
       <c r="F366" s="8"/>
     </row>
-    <row r="367" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="6"/>
       <c r="B367" s="14"/>
       <c r="C367" s="11"/>
@@ -5496,7 +5526,7 @@
       <c r="E367" s="8"/>
       <c r="F367" s="8"/>
     </row>
-    <row r="368" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="6"/>
       <c r="B368" s="14"/>
       <c r="C368" s="11"/>
@@ -5504,7 +5534,7 @@
       <c r="E368" s="8"/>
       <c r="F368" s="8"/>
     </row>
-    <row r="369" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="6"/>
       <c r="B369" s="14"/>
       <c r="C369" s="11"/>
@@ -5512,7 +5542,7 @@
       <c r="E369" s="8"/>
       <c r="F369" s="8"/>
     </row>
-    <row r="370" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="6"/>
       <c r="B370" s="14"/>
       <c r="C370" s="11"/>
@@ -5520,7 +5550,7 @@
       <c r="E370" s="8"/>
       <c r="F370" s="8"/>
     </row>
-    <row r="371" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="6"/>
       <c r="B371" s="14"/>
       <c r="C371" s="11"/>
@@ -5528,7 +5558,7 @@
       <c r="E371" s="8"/>
       <c r="F371" s="8"/>
     </row>
-    <row r="372" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="6"/>
       <c r="B372" s="14"/>
       <c r="C372" s="11"/>
@@ -5536,7 +5566,7 @@
       <c r="E372" s="8"/>
       <c r="F372" s="8"/>
     </row>
-    <row r="373" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="6"/>
       <c r="B373" s="14"/>
       <c r="C373" s="11"/>
@@ -5544,7 +5574,7 @@
       <c r="E373" s="8"/>
       <c r="F373" s="8"/>
     </row>
-    <row r="374" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="6"/>
       <c r="B374" s="14"/>
       <c r="C374" s="11"/>
@@ -5552,7 +5582,7 @@
       <c r="E374" s="8"/>
       <c r="F374" s="8"/>
     </row>
-    <row r="375" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="6"/>
       <c r="B375" s="14"/>
       <c r="C375" s="11"/>
@@ -5560,7 +5590,7 @@
       <c r="E375" s="8"/>
       <c r="F375" s="8"/>
     </row>
-    <row r="376" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6"/>
       <c r="B376" s="14"/>
       <c r="C376" s="11"/>
@@ -5568,7 +5598,7 @@
       <c r="E376" s="8"/>
       <c r="F376" s="8"/>
     </row>
-    <row r="377" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="6"/>
       <c r="B377" s="14"/>
       <c r="C377" s="11"/>
@@ -5576,7 +5606,7 @@
       <c r="E377" s="8"/>
       <c r="F377" s="8"/>
     </row>
-    <row r="378" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6"/>
       <c r="B378" s="14"/>
       <c r="C378" s="11"/>
@@ -5584,7 +5614,7 @@
       <c r="E378" s="8"/>
       <c r="F378" s="8"/>
     </row>
-    <row r="379" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="6"/>
       <c r="B379" s="14"/>
       <c r="C379" s="11"/>
@@ -5592,7 +5622,7 @@
       <c r="E379" s="8"/>
       <c r="F379" s="8"/>
     </row>
-    <row r="380" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6"/>
       <c r="B380" s="14"/>
       <c r="C380" s="11"/>
@@ -5600,7 +5630,7 @@
       <c r="E380" s="8"/>
       <c r="F380" s="8"/>
     </row>
-    <row r="381" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="6"/>
       <c r="B381" s="14"/>
       <c r="C381" s="11"/>
@@ -5608,7 +5638,7 @@
       <c r="E381" s="8"/>
       <c r="F381" s="8"/>
     </row>
-    <row r="382" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6"/>
       <c r="B382" s="14"/>
       <c r="C382" s="11"/>
@@ -5616,7 +5646,7 @@
       <c r="E382" s="8"/>
       <c r="F382" s="8"/>
     </row>
-    <row r="383" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="6"/>
       <c r="B383" s="14"/>
       <c r="C383" s="11"/>
@@ -5624,7 +5654,7 @@
       <c r="E383" s="8"/>
       <c r="F383" s="8"/>
     </row>
-    <row r="384" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6"/>
       <c r="B384" s="14"/>
       <c r="C384" s="11"/>
@@ -5632,7 +5662,7 @@
       <c r="E384" s="8"/>
       <c r="F384" s="8"/>
     </row>
-    <row r="385" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="6"/>
       <c r="B385" s="14"/>
       <c r="C385" s="11"/>
@@ -5640,7 +5670,7 @@
       <c r="E385" s="8"/>
       <c r="F385" s="8"/>
     </row>
-    <row r="386" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6"/>
       <c r="B386" s="14"/>
       <c r="C386" s="11"/>
@@ -5648,7 +5678,7 @@
       <c r="E386" s="8"/>
       <c r="F386" s="8"/>
     </row>
-    <row r="387" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6"/>
       <c r="B387" s="14"/>
       <c r="C387" s="11"/>
@@ -5656,7 +5686,7 @@
       <c r="E387" s="8"/>
       <c r="F387" s="8"/>
     </row>
-    <row r="388" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6"/>
       <c r="B388" s="14"/>
       <c r="C388" s="11"/>
@@ -5664,7 +5694,7 @@
       <c r="E388" s="8"/>
       <c r="F388" s="8"/>
     </row>
-    <row r="389" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6"/>
       <c r="B389" s="14"/>
       <c r="C389" s="11"/>
@@ -5672,7 +5702,7 @@
       <c r="E389" s="8"/>
       <c r="F389" s="8"/>
     </row>
-    <row r="390" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6"/>
       <c r="B390" s="14"/>
       <c r="C390" s="11"/>
@@ -5680,7 +5710,7 @@
       <c r="E390" s="8"/>
       <c r="F390" s="8"/>
     </row>
-    <row r="391" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="6"/>
       <c r="B391" s="14"/>
       <c r="C391" s="11"/>
@@ -5688,7 +5718,7 @@
       <c r="E391" s="8"/>
       <c r="F391" s="8"/>
     </row>
-    <row r="392" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6"/>
       <c r="B392" s="14"/>
       <c r="C392" s="11"/>
@@ -5696,7 +5726,7 @@
       <c r="E392" s="8"/>
       <c r="F392" s="8"/>
     </row>
-    <row r="393" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="6"/>
       <c r="B393" s="14"/>
       <c r="C393" s="11"/>
@@ -5704,7 +5734,7 @@
       <c r="E393" s="8"/>
       <c r="F393" s="8"/>
     </row>
-    <row r="394" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="6"/>
       <c r="B394" s="14"/>
       <c r="C394" s="11"/>
@@ -5712,7 +5742,7 @@
       <c r="E394" s="8"/>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="6"/>
       <c r="B395" s="14"/>
       <c r="C395" s="11"/>
@@ -5720,7 +5750,7 @@
       <c r="E395" s="8"/>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="6"/>
       <c r="B396" s="14"/>
       <c r="C396" s="11"/>
@@ -5728,7 +5758,7 @@
       <c r="E396" s="8"/>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="6"/>
       <c r="B397" s="14"/>
       <c r="C397" s="11"/>
@@ -5736,7 +5766,7 @@
       <c r="E397" s="8"/>
       <c r="F397" s="8"/>
     </row>
-    <row r="398" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="6"/>
       <c r="B398" s="14"/>
       <c r="C398" s="11"/>
@@ -5744,7 +5774,7 @@
       <c r="E398" s="8"/>
       <c r="F398" s="8"/>
     </row>
-    <row r="399" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="6"/>
       <c r="B399" s="14"/>
       <c r="C399" s="11"/>
@@ -5752,7 +5782,7 @@
       <c r="E399" s="8"/>
       <c r="F399" s="8"/>
     </row>
-    <row r="400" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6"/>
       <c r="B400" s="14"/>
       <c r="C400" s="11"/>
@@ -5760,7 +5790,7 @@
       <c r="E400" s="8"/>
       <c r="F400" s="8"/>
     </row>
-    <row r="401" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="6"/>
       <c r="B401" s="14"/>
       <c r="C401" s="11"/>
@@ -5768,7 +5798,7 @@
       <c r="E401" s="8"/>
       <c r="F401" s="8"/>
     </row>
-    <row r="402" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="6"/>
       <c r="B402" s="14"/>
       <c r="C402" s="11"/>
@@ -5776,7 +5806,7 @@
       <c r="E402" s="8"/>
       <c r="F402" s="8"/>
     </row>
-    <row r="403" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="6"/>
       <c r="B403" s="14"/>
       <c r="C403" s="11"/>
@@ -5784,7 +5814,7 @@
       <c r="E403" s="8"/>
       <c r="F403" s="8"/>
     </row>
-    <row r="404" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="6"/>
       <c r="B404" s="14"/>
       <c r="C404" s="11"/>
@@ -5792,7 +5822,7 @@
       <c r="E404" s="8"/>
       <c r="F404" s="8"/>
     </row>
-    <row r="405" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="6"/>
       <c r="B405" s="14"/>
       <c r="C405" s="11"/>
@@ -5800,7 +5830,7 @@
       <c r="E405" s="8"/>
       <c r="F405" s="8"/>
     </row>
-    <row r="406" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="6"/>
       <c r="B406" s="14"/>
       <c r="C406" s="11"/>
@@ -5808,7 +5838,7 @@
       <c r="E406" s="8"/>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="6"/>
       <c r="B407" s="14"/>
       <c r="C407" s="11"/>
@@ -5816,7 +5846,7 @@
       <c r="E407" s="8"/>
       <c r="F407" s="8"/>
     </row>
-    <row r="408" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="6"/>
       <c r="B408" s="14"/>
       <c r="C408" s="11"/>
@@ -5824,7 +5854,7 @@
       <c r="E408" s="8"/>
       <c r="F408" s="8"/>
     </row>
-    <row r="409" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="6"/>
       <c r="B409" s="14"/>
       <c r="C409" s="11"/>
@@ -5832,7 +5862,7 @@
       <c r="E409" s="8"/>
       <c r="F409" s="8"/>
     </row>
-    <row r="410" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="6"/>
       <c r="B410" s="14"/>
       <c r="C410" s="11"/>
@@ -5840,7 +5870,7 @@
       <c r="E410" s="8"/>
       <c r="F410" s="8"/>
     </row>
-    <row r="411" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="6"/>
       <c r="B411" s="14"/>
       <c r="C411" s="11"/>
@@ -5848,7 +5878,7 @@
       <c r="E411" s="8"/>
       <c r="F411" s="8"/>
     </row>
-    <row r="412" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="6"/>
       <c r="B412" s="14"/>
       <c r="C412" s="11"/>
@@ -5856,7 +5886,7 @@
       <c r="E412" s="8"/>
       <c r="F412" s="8"/>
     </row>
-    <row r="413" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="6"/>
       <c r="B413" s="14"/>
       <c r="C413" s="11"/>
@@ -5864,7 +5894,7 @@
       <c r="E413" s="8"/>
       <c r="F413" s="8"/>
     </row>
-    <row r="414" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="6"/>
       <c r="B414" s="14"/>
       <c r="C414" s="11"/>
@@ -5872,7 +5902,7 @@
       <c r="E414" s="8"/>
       <c r="F414" s="8"/>
     </row>
-    <row r="415" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="6"/>
       <c r="B415" s="14"/>
       <c r="C415" s="11"/>
@@ -5880,7 +5910,7 @@
       <c r="E415" s="8"/>
       <c r="F415" s="8"/>
     </row>
-    <row r="416" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="6"/>
       <c r="B416" s="14"/>
       <c r="C416" s="11"/>
@@ -5888,7 +5918,7 @@
       <c r="E416" s="8"/>
       <c r="F416" s="8"/>
     </row>
-    <row r="417" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6"/>
       <c r="B417" s="14"/>
       <c r="C417" s="11"/>
@@ -5896,7 +5926,7 @@
       <c r="E417" s="8"/>
       <c r="F417" s="8"/>
     </row>
-    <row r="418" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="6"/>
       <c r="B418" s="14"/>
       <c r="C418" s="11"/>
@@ -5904,7 +5934,7 @@
       <c r="E418" s="8"/>
       <c r="F418" s="8"/>
     </row>
-    <row r="419" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="6"/>
       <c r="B419" s="14"/>
       <c r="C419" s="11"/>
@@ -5912,7 +5942,7 @@
       <c r="E419" s="8"/>
       <c r="F419" s="8"/>
     </row>
-    <row r="420" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="6"/>
       <c r="B420" s="14"/>
       <c r="C420" s="11"/>
@@ -5920,7 +5950,7 @@
       <c r="E420" s="8"/>
       <c r="F420" s="8"/>
     </row>
-    <row r="421" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="6"/>
       <c r="B421" s="14"/>
       <c r="C421" s="11"/>
@@ -5928,7 +5958,7 @@
       <c r="E421" s="8"/>
       <c r="F421" s="8"/>
     </row>
-    <row r="422" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="6"/>
       <c r="B422" s="14"/>
       <c r="C422" s="11"/>
@@ -5936,7 +5966,7 @@
       <c r="E422" s="8"/>
       <c r="F422" s="8"/>
     </row>
-    <row r="423" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="6"/>
       <c r="B423" s="14"/>
       <c r="C423" s="11"/>
@@ -5944,7 +5974,7 @@
       <c r="E423" s="8"/>
       <c r="F423" s="8"/>
     </row>
-    <row r="424" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="6"/>
       <c r="B424" s="14"/>
       <c r="C424" s="11"/>
@@ -5952,7 +5982,7 @@
       <c r="E424" s="8"/>
       <c r="F424" s="8"/>
     </row>
-    <row r="425" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="6"/>
       <c r="B425" s="14"/>
       <c r="C425" s="11"/>
@@ -5960,7 +5990,7 @@
       <c r="E425" s="8"/>
       <c r="F425" s="8"/>
     </row>
-    <row r="426" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="6"/>
       <c r="B426" s="14"/>
       <c r="C426" s="11"/>
@@ -5968,7 +5998,7 @@
       <c r="E426" s="8"/>
       <c r="F426" s="8"/>
     </row>
-    <row r="427" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="6"/>
       <c r="B427" s="14"/>
       <c r="C427" s="11"/>
@@ -5976,7 +6006,7 @@
       <c r="E427" s="8"/>
       <c r="F427" s="8"/>
     </row>
-    <row r="428" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="6"/>
       <c r="B428" s="14"/>
       <c r="C428" s="11"/>
@@ -5984,7 +6014,7 @@
       <c r="E428" s="8"/>
       <c r="F428" s="8"/>
     </row>
-    <row r="429" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="6"/>
       <c r="B429" s="14"/>
       <c r="C429" s="11"/>
@@ -5992,7 +6022,7 @@
       <c r="E429" s="8"/>
       <c r="F429" s="8"/>
     </row>
-    <row r="430" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="6"/>
       <c r="B430" s="14"/>
       <c r="C430" s="11"/>
@@ -6000,7 +6030,7 @@
       <c r="E430" s="8"/>
       <c r="F430" s="8"/>
     </row>
-    <row r="431" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="6"/>
       <c r="B431" s="14"/>
       <c r="C431" s="11"/>
@@ -6008,7 +6038,7 @@
       <c r="E431" s="8"/>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="6"/>
       <c r="B432" s="14"/>
       <c r="C432" s="11"/>
@@ -6016,7 +6046,7 @@
       <c r="E432" s="8"/>
       <c r="F432" s="8"/>
     </row>
-    <row r="433" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="6"/>
       <c r="B433" s="14"/>
       <c r="C433" s="11"/>
@@ -6024,7 +6054,7 @@
       <c r="E433" s="8"/>
       <c r="F433" s="8"/>
     </row>
-    <row r="434" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="6"/>
       <c r="B434" s="14"/>
       <c r="C434" s="11"/>
@@ -6032,7 +6062,7 @@
       <c r="E434" s="8"/>
       <c r="F434" s="8"/>
     </row>
-    <row r="435" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="6"/>
       <c r="B435" s="14"/>
       <c r="C435" s="11"/>
@@ -6040,7 +6070,7 @@
       <c r="E435" s="8"/>
       <c r="F435" s="8"/>
     </row>
-    <row r="436" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="6"/>
       <c r="B436" s="14"/>
       <c r="C436" s="11"/>
@@ -6048,7 +6078,7 @@
       <c r="E436" s="8"/>
       <c r="F436" s="8"/>
     </row>
-    <row r="437" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="6"/>
       <c r="B437" s="14"/>
       <c r="C437" s="11"/>
@@ -6056,7 +6086,7 @@
       <c r="E437" s="8"/>
       <c r="F437" s="8"/>
     </row>
-    <row r="438" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="6"/>
       <c r="B438" s="14"/>
       <c r="C438" s="11"/>
@@ -6064,7 +6094,7 @@
       <c r="E438" s="8"/>
       <c r="F438" s="8"/>
     </row>
-    <row r="439" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="6"/>
       <c r="B439" s="14"/>
       <c r="C439" s="11"/>
@@ -6072,7 +6102,7 @@
       <c r="E439" s="8"/>
       <c r="F439" s="8"/>
     </row>
-    <row r="440" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="6"/>
       <c r="B440" s="14"/>
       <c r="C440" s="11"/>
@@ -6080,7 +6110,7 @@
       <c r="E440" s="8"/>
       <c r="F440" s="8"/>
     </row>
-    <row r="441" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="6"/>
       <c r="B441" s="14"/>
       <c r="C441" s="11"/>
@@ -6088,7 +6118,7 @@
       <c r="E441" s="8"/>
       <c r="F441" s="8"/>
     </row>
-    <row r="442" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="6"/>
       <c r="B442" s="14"/>
       <c r="C442" s="11"/>
@@ -6096,7 +6126,7 @@
       <c r="E442" s="8"/>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="6"/>
       <c r="B443" s="14"/>
       <c r="C443" s="11"/>
@@ -6104,7 +6134,7 @@
       <c r="E443" s="8"/>
       <c r="F443" s="8"/>
     </row>
-    <row r="444" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="6"/>
       <c r="B444" s="14"/>
       <c r="C444" s="11"/>
@@ -6112,7 +6142,7 @@
       <c r="E444" s="8"/>
       <c r="F444" s="8"/>
     </row>
-    <row r="445" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="6"/>
       <c r="B445" s="14"/>
       <c r="C445" s="11"/>
@@ -6120,7 +6150,7 @@
       <c r="E445" s="8"/>
       <c r="F445" s="8"/>
     </row>
-    <row r="446" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="6"/>
       <c r="B446" s="14"/>
       <c r="C446" s="11"/>
@@ -6128,7 +6158,7 @@
       <c r="E446" s="8"/>
       <c r="F446" s="8"/>
     </row>
-    <row r="447" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="6"/>
       <c r="B447" s="14"/>
       <c r="C447" s="11"/>
@@ -6136,7 +6166,7 @@
       <c r="E447" s="8"/>
       <c r="F447" s="8"/>
     </row>
-    <row r="448" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="6"/>
       <c r="B448" s="14"/>
       <c r="C448" s="11"/>
@@ -6144,7 +6174,7 @@
       <c r="E448" s="8"/>
       <c r="F448" s="8"/>
     </row>
-    <row r="449" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="6"/>
       <c r="B449" s="14"/>
       <c r="C449" s="11"/>
@@ -6152,7 +6182,7 @@
       <c r="E449" s="8"/>
       <c r="F449" s="8"/>
     </row>
-    <row r="450" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="6"/>
       <c r="B450" s="14"/>
       <c r="C450" s="11"/>
@@ -6160,7 +6190,7 @@
       <c r="E450" s="8"/>
       <c r="F450" s="8"/>
     </row>
-    <row r="451" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="6"/>
       <c r="B451" s="14"/>
       <c r="C451" s="11"/>
@@ -6168,7 +6198,7 @@
       <c r="E451" s="8"/>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="6"/>
       <c r="B452" s="14"/>
       <c r="C452" s="11"/>
@@ -6176,7 +6206,7 @@
       <c r="E452" s="8"/>
       <c r="F452" s="8"/>
     </row>
-    <row r="453" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="6"/>
       <c r="B453" s="14"/>
       <c r="C453" s="11"/>
@@ -6184,7 +6214,7 @@
       <c r="E453" s="8"/>
       <c r="F453" s="8"/>
     </row>
-    <row r="454" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="6"/>
       <c r="B454" s="14"/>
       <c r="C454" s="11"/>
@@ -6192,7 +6222,7 @@
       <c r="E454" s="8"/>
       <c r="F454" s="8"/>
     </row>
-    <row r="455" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="6"/>
       <c r="B455" s="14"/>
       <c r="C455" s="11"/>
@@ -6200,7 +6230,7 @@
       <c r="E455" s="8"/>
       <c r="F455" s="8"/>
     </row>
-    <row r="456" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="6"/>
       <c r="B456" s="14"/>
       <c r="C456" s="11"/>
@@ -6208,7 +6238,7 @@
       <c r="E456" s="8"/>
       <c r="F456" s="8"/>
     </row>
-    <row r="457" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="6"/>
       <c r="B457" s="14"/>
       <c r="C457" s="11"/>
@@ -6216,7 +6246,7 @@
       <c r="E457" s="8"/>
       <c r="F457" s="8"/>
     </row>
-    <row r="458" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="6"/>
       <c r="B458" s="14"/>
       <c r="C458" s="11"/>
@@ -6224,7 +6254,7 @@
       <c r="E458" s="8"/>
       <c r="F458" s="8"/>
     </row>
-    <row r="459" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="6"/>
       <c r="B459" s="14"/>
       <c r="C459" s="11"/>
@@ -6232,7 +6262,7 @@
       <c r="E459" s="8"/>
       <c r="F459" s="8"/>
     </row>
-    <row r="460" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="6"/>
       <c r="B460" s="14"/>
       <c r="C460" s="11"/>
@@ -6240,7 +6270,7 @@
       <c r="E460" s="8"/>
       <c r="F460" s="8"/>
     </row>
-    <row r="461" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="6"/>
       <c r="B461" s="14"/>
       <c r="C461" s="11"/>
@@ -6248,7 +6278,7 @@
       <c r="E461" s="8"/>
       <c r="F461" s="8"/>
     </row>
-    <row r="462" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="6"/>
       <c r="B462" s="14"/>
       <c r="C462" s="11"/>
@@ -6256,7 +6286,7 @@
       <c r="E462" s="8"/>
       <c r="F462" s="8"/>
     </row>
-    <row r="463" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="6"/>
       <c r="B463" s="14"/>
       <c r="C463" s="11"/>
@@ -6264,7 +6294,7 @@
       <c r="E463" s="8"/>
       <c r="F463" s="8"/>
     </row>
-    <row r="464" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="6"/>
       <c r="B464" s="14"/>
       <c r="C464" s="11"/>
@@ -6272,7 +6302,7 @@
       <c r="E464" s="8"/>
       <c r="F464" s="8"/>
     </row>
-    <row r="465" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="6"/>
       <c r="B465" s="14"/>
       <c r="C465" s="11"/>
@@ -6280,7 +6310,7 @@
       <c r="E465" s="8"/>
       <c r="F465" s="8"/>
     </row>
-    <row r="466" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="6"/>
       <c r="B466" s="14"/>
       <c r="C466" s="11"/>
@@ -6288,7 +6318,7 @@
       <c r="E466" s="8"/>
       <c r="F466" s="8"/>
     </row>
-    <row r="467" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="6"/>
       <c r="B467" s="14"/>
       <c r="C467" s="11"/>
@@ -6296,7 +6326,7 @@
       <c r="E467" s="8"/>
       <c r="F467" s="8"/>
     </row>
-    <row r="468" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="6"/>
       <c r="B468" s="14"/>
       <c r="C468" s="11"/>
@@ -6304,7 +6334,7 @@
       <c r="E468" s="8"/>
       <c r="F468" s="8"/>
     </row>
-    <row r="469" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="6"/>
       <c r="B469" s="14"/>
       <c r="C469" s="11"/>
@@ -6312,7 +6342,7 @@
       <c r="E469" s="8"/>
       <c r="F469" s="8"/>
     </row>
-    <row r="470" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="6"/>
       <c r="B470" s="14"/>
       <c r="C470" s="11"/>
@@ -6320,7 +6350,7 @@
       <c r="E470" s="8"/>
       <c r="F470" s="8"/>
     </row>
-    <row r="471" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="6"/>
       <c r="B471" s="14"/>
       <c r="C471" s="11"/>
@@ -6328,7 +6358,7 @@
       <c r="E471" s="8"/>
       <c r="F471" s="8"/>
     </row>
-    <row r="472" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="6"/>
       <c r="B472" s="14"/>
       <c r="C472" s="11"/>
@@ -6336,7 +6366,7 @@
       <c r="E472" s="8"/>
       <c r="F472" s="8"/>
     </row>
-    <row r="473" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="6"/>
       <c r="B473" s="14"/>
       <c r="C473" s="11"/>
@@ -6344,7 +6374,7 @@
       <c r="E473" s="8"/>
       <c r="F473" s="8"/>
     </row>
-    <row r="474" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="6"/>
       <c r="B474" s="14"/>
       <c r="C474" s="11"/>
@@ -6352,7 +6382,7 @@
       <c r="E474" s="8"/>
       <c r="F474" s="8"/>
     </row>
-    <row r="475" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="6"/>
       <c r="B475" s="14"/>
       <c r="C475" s="11"/>
@@ -6360,7 +6390,7 @@
       <c r="E475" s="8"/>
       <c r="F475" s="8"/>
     </row>
-    <row r="476" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6"/>
       <c r="B476" s="14"/>
       <c r="C476" s="11"/>
@@ -6368,7 +6398,7 @@
       <c r="E476" s="8"/>
       <c r="F476" s="8"/>
     </row>
-    <row r="477" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="6"/>
       <c r="B477" s="14"/>
       <c r="C477" s="11"/>
@@ -6376,7 +6406,7 @@
       <c r="E477" s="8"/>
       <c r="F477" s="8"/>
     </row>
-    <row r="478" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="6"/>
       <c r="B478" s="14"/>
       <c r="C478" s="11"/>
@@ -6384,7 +6414,7 @@
       <c r="E478" s="8"/>
       <c r="F478" s="8"/>
     </row>
-    <row r="479" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="6"/>
       <c r="B479" s="14"/>
       <c r="C479" s="11"/>
@@ -6392,7 +6422,7 @@
       <c r="E479" s="8"/>
       <c r="F479" s="8"/>
     </row>
-    <row r="480" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="6"/>
       <c r="B480" s="14"/>
       <c r="C480" s="11"/>
@@ -6400,7 +6430,7 @@
       <c r="E480" s="8"/>
       <c r="F480" s="8"/>
     </row>
-    <row r="481" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="6"/>
       <c r="B481" s="14"/>
       <c r="C481" s="11"/>
@@ -6408,7 +6438,7 @@
       <c r="E481" s="8"/>
       <c r="F481" s="8"/>
     </row>
-    <row r="482" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="6"/>
       <c r="B482" s="14"/>
       <c r="C482" s="11"/>
@@ -6416,7 +6446,7 @@
       <c r="E482" s="8"/>
       <c r="F482" s="8"/>
     </row>
-    <row r="483" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="6"/>
       <c r="B483" s="14"/>
       <c r="C483" s="11"/>
@@ -6424,7 +6454,7 @@
       <c r="E483" s="8"/>
       <c r="F483" s="8"/>
     </row>
-    <row r="484" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="6"/>
       <c r="B484" s="14"/>
       <c r="C484" s="11"/>
@@ -6432,7 +6462,7 @@
       <c r="E484" s="8"/>
       <c r="F484" s="8"/>
     </row>
-    <row r="485" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="6"/>
       <c r="B485" s="14"/>
       <c r="C485" s="11"/>
@@ -6440,7 +6470,7 @@
       <c r="E485" s="8"/>
       <c r="F485" s="8"/>
     </row>
-    <row r="486" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="6"/>
       <c r="B486" s="14"/>
       <c r="C486" s="11"/>
@@ -6448,7 +6478,7 @@
       <c r="E486" s="8"/>
       <c r="F486" s="8"/>
     </row>
-    <row r="487" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="6"/>
       <c r="B487" s="14"/>
       <c r="C487" s="11"/>
@@ -6456,7 +6486,7 @@
       <c r="E487" s="8"/>
       <c r="F487" s="8"/>
     </row>
-    <row r="488" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="6"/>
       <c r="B488" s="14"/>
       <c r="C488" s="11"/>
@@ -6464,7 +6494,7 @@
       <c r="E488" s="8"/>
       <c r="F488" s="8"/>
     </row>
-    <row r="489" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="6"/>
       <c r="B489" s="14"/>
       <c r="C489" s="11"/>
@@ -6472,7 +6502,7 @@
       <c r="E489" s="8"/>
       <c r="F489" s="8"/>
     </row>
-    <row r="490" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="6"/>
       <c r="B490" s="14"/>
       <c r="C490" s="11"/>
@@ -6480,7 +6510,7 @@
       <c r="E490" s="8"/>
       <c r="F490" s="8"/>
     </row>
-    <row r="491" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="6"/>
       <c r="B491" s="14"/>
       <c r="C491" s="11"/>
@@ -6488,7 +6518,7 @@
       <c r="E491" s="8"/>
       <c r="F491" s="8"/>
     </row>
-    <row r="492" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="6"/>
       <c r="B492" s="14"/>
       <c r="C492" s="11"/>
@@ -6496,7 +6526,7 @@
       <c r="E492" s="8"/>
       <c r="F492" s="8"/>
     </row>
-    <row r="493" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="6"/>
       <c r="B493" s="14"/>
       <c r="C493" s="11"/>
@@ -6504,7 +6534,7 @@
       <c r="E493" s="8"/>
       <c r="F493" s="8"/>
     </row>
-    <row r="494" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="6"/>
       <c r="B494" s="14"/>
       <c r="C494" s="11"/>
@@ -6512,7 +6542,7 @@
       <c r="E494" s="8"/>
       <c r="F494" s="8"/>
     </row>
-    <row r="495" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="6"/>
       <c r="B495" s="14"/>
       <c r="C495" s="11"/>
@@ -6520,7 +6550,7 @@
       <c r="E495" s="8"/>
       <c r="F495" s="8"/>
     </row>
-    <row r="496" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="6"/>
       <c r="B496" s="14"/>
       <c r="C496" s="11"/>
@@ -6528,7 +6558,7 @@
       <c r="E496" s="8"/>
       <c r="F496" s="8"/>
     </row>
-    <row r="497" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="6"/>
       <c r="B497" s="14"/>
       <c r="C497" s="11"/>
@@ -6536,7 +6566,7 @@
       <c r="E497" s="8"/>
       <c r="F497" s="8"/>
     </row>
-    <row r="498" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="6"/>
       <c r="B498" s="14"/>
       <c r="C498" s="11"/>
@@ -6544,7 +6574,7 @@
       <c r="E498" s="8"/>
       <c r="F498" s="8"/>
     </row>
-    <row r="499" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="6"/>
       <c r="B499" s="14"/>
       <c r="C499" s="11"/>
@@ -6552,7 +6582,7 @@
       <c r="E499" s="8"/>
       <c r="F499" s="8"/>
     </row>
-    <row r="500" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="6"/>
       <c r="B500" s="14"/>
       <c r="C500" s="11"/>
@@ -6560,7 +6590,7 @@
       <c r="E500" s="8"/>
       <c r="F500" s="8"/>
     </row>
-    <row r="501" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A501" s="6"/>
       <c r="B501" s="14"/>
       <c r="C501" s="11"/>
@@ -6568,7 +6598,7 @@
       <c r="E501" s="8"/>
       <c r="F501" s="8"/>
     </row>
-    <row r="502" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A502" s="6"/>
       <c r="B502" s="14"/>
       <c r="C502" s="11"/>
@@ -6576,7 +6606,7 @@
       <c r="E502" s="8"/>
       <c r="F502" s="8"/>
     </row>
-    <row r="503" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A503" s="6"/>
       <c r="B503" s="14"/>
       <c r="C503" s="11"/>
@@ -6621,13 +6651,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC8CEF3-AF3E-4D54-8188-1302D62F0F60}">
   <dimension ref="A1:B500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.25" style="12" customWidth="1"/>
+    <col min="1" max="1" width="24.8984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.19921875" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
@@ -6635,7 +6665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
@@ -6644,7 +6674,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>8</v>
       </c>
@@ -6653,16 +6683,16 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$163,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$163)</f>
-        <v>12.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>21.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>10</v>
       </c>
@@ -6671,7 +6701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>11</v>
       </c>
@@ -6680,7 +6710,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>6</v>
       </c>
@@ -6689,7 +6719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>12</v>
       </c>
@@ -6698,7 +6728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>13</v>
       </c>
@@ -6707,1967 +6737,1967 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="11"/>
     </row>
-    <row r="12" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="11"/>
     </row>
-    <row r="13" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="11"/>
     </row>
-    <row r="14" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="11"/>
     </row>
-    <row r="15" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="11"/>
     </row>
-    <row r="16" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="11"/>
     </row>
-    <row r="17" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="11"/>
     </row>
-    <row r="18" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="11"/>
     </row>
-    <row r="19" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="11"/>
     </row>
-    <row r="20" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="11"/>
     </row>
-    <row r="21" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="11"/>
     </row>
-    <row r="22" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="11"/>
     </row>
-    <row r="23" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="11"/>
     </row>
-    <row r="24" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="11"/>
     </row>
-    <row r="25" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="11"/>
     </row>
-    <row r="27" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="11"/>
     </row>
-    <row r="28" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="11"/>
     </row>
-    <row r="29" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="11"/>
     </row>
-    <row r="30" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="11"/>
     </row>
-    <row r="31" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="11"/>
     </row>
-    <row r="32" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="11"/>
     </row>
-    <row r="33" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="11"/>
     </row>
-    <row r="34" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="11"/>
     </row>
-    <row r="35" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="11"/>
     </row>
-    <row r="36" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="11"/>
     </row>
-    <row r="37" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="11"/>
     </row>
-    <row r="38" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="11"/>
     </row>
-    <row r="39" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="11"/>
     </row>
-    <row r="40" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" s="11"/>
     </row>
-    <row r="41" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="11"/>
     </row>
-    <row r="42" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="11"/>
     </row>
-    <row r="43" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="11"/>
     </row>
-    <row r="44" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="11"/>
     </row>
-    <row r="45" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="11"/>
     </row>
-    <row r="46" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="B46" s="11"/>
     </row>
-    <row r="47" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="11"/>
     </row>
-    <row r="48" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="11"/>
     </row>
-    <row r="49" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="11"/>
     </row>
-    <row r="50" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="11"/>
     </row>
-    <row r="51" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="11"/>
     </row>
-    <row r="52" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="11"/>
     </row>
-    <row r="53" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="11"/>
     </row>
-    <row r="54" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="11"/>
     </row>
-    <row r="55" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="11"/>
     </row>
-    <row r="56" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="11"/>
     </row>
-    <row r="57" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="11"/>
     </row>
-    <row r="58" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="11"/>
     </row>
-    <row r="59" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="11"/>
     </row>
-    <row r="60" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="11"/>
     </row>
-    <row r="61" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="11"/>
     </row>
-    <row r="62" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="11"/>
     </row>
-    <row r="63" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="11"/>
     </row>
-    <row r="64" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="11"/>
     </row>
-    <row r="65" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="11"/>
     </row>
-    <row r="66" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="11"/>
     </row>
-    <row r="67" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="11"/>
     </row>
-    <row r="68" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="11"/>
     </row>
-    <row r="69" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="11"/>
     </row>
-    <row r="70" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="11"/>
     </row>
-    <row r="71" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="11"/>
     </row>
-    <row r="72" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="11"/>
     </row>
-    <row r="73" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="11"/>
     </row>
-    <row r="74" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="11"/>
     </row>
-    <row r="75" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="11"/>
     </row>
-    <row r="76" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="11"/>
     </row>
-    <row r="77" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="11"/>
     </row>
-    <row r="78" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="11"/>
     </row>
-    <row r="79" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="11"/>
     </row>
-    <row r="80" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="11"/>
     </row>
-    <row r="81" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="11"/>
     </row>
-    <row r="82" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="11"/>
     </row>
-    <row r="83" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="11"/>
     </row>
-    <row r="84" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="11"/>
     </row>
-    <row r="85" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="11"/>
     </row>
-    <row r="86" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="11"/>
     </row>
-    <row r="87" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="11"/>
     </row>
-    <row r="88" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="11"/>
     </row>
-    <row r="89" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="11"/>
     </row>
-    <row r="90" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="11"/>
     </row>
-    <row r="91" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="11"/>
     </row>
-    <row r="92" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="11"/>
     </row>
-    <row r="93" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="11"/>
     </row>
-    <row r="94" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="11"/>
     </row>
-    <row r="95" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="11"/>
     </row>
-    <row r="96" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="11"/>
     </row>
-    <row r="97" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="11"/>
     </row>
-    <row r="98" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="11"/>
     </row>
-    <row r="99" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="11"/>
     </row>
-    <row r="100" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
       <c r="B100" s="11"/>
     </row>
-    <row r="101" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="11"/>
     </row>
-    <row r="102" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="11"/>
     </row>
-    <row r="103" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="11"/>
     </row>
-    <row r="104" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
       <c r="B104" s="11"/>
     </row>
-    <row r="105" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="B105" s="11"/>
     </row>
-    <row r="106" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
       <c r="B106" s="11"/>
     </row>
-    <row r="107" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
       <c r="B107" s="11"/>
     </row>
-    <row r="108" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
       <c r="B108" s="11"/>
     </row>
-    <row r="109" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="11"/>
     </row>
-    <row r="110" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="11"/>
     </row>
-    <row r="111" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="11"/>
     </row>
-    <row r="112" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
       <c r="B112" s="11"/>
     </row>
-    <row r="113" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="B113" s="11"/>
     </row>
-    <row r="114" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
       <c r="B114" s="11"/>
     </row>
-    <row r="115" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="11"/>
     </row>
-    <row r="116" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
       <c r="B116" s="11"/>
     </row>
-    <row r="117" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="B117" s="11"/>
     </row>
-    <row r="118" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="B118" s="11"/>
     </row>
-    <row r="119" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="11"/>
     </row>
-    <row r="120" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
       <c r="B120" s="11"/>
     </row>
-    <row r="121" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="11"/>
     </row>
-    <row r="122" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="B122" s="11"/>
     </row>
-    <row r="123" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="11"/>
     </row>
-    <row r="124" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
       <c r="B124" s="11"/>
     </row>
-    <row r="125" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="11"/>
     </row>
-    <row r="126" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="B126" s="11"/>
     </row>
-    <row r="127" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="11"/>
     </row>
-    <row r="128" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
       <c r="B128" s="11"/>
     </row>
-    <row r="129" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="B129" s="11"/>
     </row>
-    <row r="130" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
       <c r="B130" s="11"/>
     </row>
-    <row r="131" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
       <c r="B131" s="11"/>
     </row>
-    <row r="132" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6"/>
       <c r="B132" s="11"/>
     </row>
-    <row r="133" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="B133" s="11"/>
     </row>
-    <row r="134" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
       <c r="B134" s="11"/>
     </row>
-    <row r="135" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
       <c r="B135" s="11"/>
     </row>
-    <row r="136" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
       <c r="B136" s="11"/>
     </row>
-    <row r="137" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
       <c r="B137" s="11"/>
     </row>
-    <row r="138" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
       <c r="B138" s="11"/>
     </row>
-    <row r="139" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
       <c r="B139" s="11"/>
     </row>
-    <row r="140" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
       <c r="B140" s="11"/>
     </row>
-    <row r="141" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
       <c r="B141" s="11"/>
     </row>
-    <row r="142" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
       <c r="B142" s="11"/>
     </row>
-    <row r="143" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
       <c r="B143" s="11"/>
     </row>
-    <row r="144" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6"/>
       <c r="B144" s="11"/>
     </row>
-    <row r="145" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
       <c r="B145" s="11"/>
     </row>
-    <row r="146" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
       <c r="B146" s="11"/>
     </row>
-    <row r="147" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
       <c r="B147" s="11"/>
     </row>
-    <row r="148" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
       <c r="B148" s="11"/>
     </row>
-    <row r="149" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
       <c r="B149" s="11"/>
     </row>
-    <row r="150" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
       <c r="B150" s="11"/>
     </row>
-    <row r="151" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
       <c r="B151" s="11"/>
     </row>
-    <row r="152" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6"/>
       <c r="B152" s="11"/>
     </row>
-    <row r="153" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
       <c r="B153" s="11"/>
     </row>
-    <row r="154" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="B154" s="11"/>
     </row>
-    <row r="155" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="B155" s="11"/>
     </row>
-    <row r="156" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
       <c r="B156" s="11"/>
     </row>
-    <row r="157" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
       <c r="B157" s="11"/>
     </row>
-    <row r="158" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
       <c r="B158" s="11"/>
     </row>
-    <row r="159" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
       <c r="B159" s="11"/>
     </row>
-    <row r="160" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6"/>
       <c r="B160" s="11"/>
     </row>
-    <row r="161" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
       <c r="B161" s="11"/>
     </row>
-    <row r="162" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
       <c r="B162" s="11"/>
     </row>
-    <row r="163" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
       <c r="B163" s="11"/>
     </row>
-    <row r="164" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6"/>
       <c r="B164" s="11"/>
     </row>
-    <row r="165" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
       <c r="B165" s="11"/>
     </row>
-    <row r="166" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
       <c r="B166" s="11"/>
     </row>
-    <row r="167" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6"/>
       <c r="B167" s="11"/>
     </row>
-    <row r="168" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
       <c r="B168" s="11"/>
     </row>
-    <row r="169" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6"/>
       <c r="B169" s="11"/>
     </row>
-    <row r="170" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
       <c r="B170" s="11"/>
     </row>
-    <row r="171" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="B171" s="11"/>
     </row>
-    <row r="172" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
       <c r="B172" s="11"/>
     </row>
-    <row r="173" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="B173" s="11"/>
     </row>
-    <row r="174" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="B174" s="11"/>
     </row>
-    <row r="175" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
       <c r="B175" s="11"/>
     </row>
-    <row r="176" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
       <c r="B176" s="11"/>
     </row>
-    <row r="177" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="B177" s="11"/>
     </row>
-    <row r="178" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="B178" s="11"/>
     </row>
-    <row r="179" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
       <c r="B179" s="11"/>
     </row>
-    <row r="180" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
       <c r="B180" s="11"/>
     </row>
-    <row r="181" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
       <c r="B181" s="11"/>
     </row>
-    <row r="182" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
       <c r="B182" s="11"/>
     </row>
-    <row r="183" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6"/>
       <c r="B183" s="11"/>
     </row>
-    <row r="184" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
       <c r="B184" s="11"/>
     </row>
-    <row r="185" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
       <c r="B185" s="11"/>
     </row>
-    <row r="186" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
       <c r="B186" s="11"/>
     </row>
-    <row r="187" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="B187" s="11"/>
     </row>
-    <row r="188" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
       <c r="B188" s="11"/>
     </row>
-    <row r="189" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
       <c r="B189" s="11"/>
     </row>
-    <row r="190" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6"/>
       <c r="B190" s="11"/>
     </row>
-    <row r="191" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
       <c r="B191" s="11"/>
     </row>
-    <row r="192" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
       <c r="B192" s="11"/>
     </row>
-    <row r="193" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
       <c r="B193" s="11"/>
     </row>
-    <row r="194" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6"/>
       <c r="B194" s="11"/>
     </row>
-    <row r="195" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
       <c r="B195" s="11"/>
     </row>
-    <row r="196" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
       <c r="B196" s="11"/>
     </row>
-    <row r="197" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
       <c r="B197" s="11"/>
     </row>
-    <row r="198" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6"/>
       <c r="B198" s="11"/>
     </row>
-    <row r="199" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
       <c r="B199" s="11"/>
     </row>
-    <row r="200" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
       <c r="B200" s="11"/>
     </row>
-    <row r="201" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
       <c r="B201" s="11"/>
     </row>
-    <row r="202" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="B202" s="11"/>
     </row>
-    <row r="203" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
       <c r="B203" s="11"/>
     </row>
-    <row r="204" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="B204" s="11"/>
     </row>
-    <row r="205" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
       <c r="B205" s="11"/>
     </row>
-    <row r="206" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="B206" s="11"/>
     </row>
-    <row r="207" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="B207" s="11"/>
     </row>
-    <row r="208" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="B208" s="11"/>
     </row>
-    <row r="209" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6"/>
       <c r="B209" s="11"/>
     </row>
-    <row r="210" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
       <c r="B210" s="11"/>
     </row>
-    <row r="211" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
       <c r="B211" s="11"/>
     </row>
-    <row r="212" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
       <c r="B212" s="11"/>
     </row>
-    <row r="213" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6"/>
       <c r="B213" s="11"/>
     </row>
-    <row r="214" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
       <c r="B214" s="11"/>
     </row>
-    <row r="215" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
       <c r="B215" s="11"/>
     </row>
-    <row r="216" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
       <c r="B216" s="11"/>
     </row>
-    <row r="217" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6"/>
       <c r="B217" s="11"/>
     </row>
-    <row r="218" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
       <c r="B218" s="11"/>
     </row>
-    <row r="219" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
       <c r="B219" s="11"/>
     </row>
-    <row r="220" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
       <c r="B220" s="11"/>
     </row>
-    <row r="221" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6"/>
       <c r="B221" s="11"/>
     </row>
-    <row r="222" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
       <c r="B222" s="11"/>
     </row>
-    <row r="223" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
       <c r="B223" s="11"/>
     </row>
-    <row r="224" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
       <c r="B224" s="11"/>
     </row>
-    <row r="225" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
       <c r="B225" s="11"/>
     </row>
-    <row r="226" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6"/>
       <c r="B226" s="11"/>
     </row>
-    <row r="227" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
       <c r="B227" s="11"/>
     </row>
-    <row r="228" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
       <c r="B228" s="11"/>
     </row>
-    <row r="229" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
       <c r="B229" s="11"/>
     </row>
-    <row r="230" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
       <c r="B230" s="11"/>
     </row>
-    <row r="231" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
       <c r="B231" s="11"/>
     </row>
-    <row r="232" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6"/>
       <c r="B232" s="11"/>
     </row>
-    <row r="233" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
       <c r="B233" s="11"/>
     </row>
-    <row r="234" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
       <c r="B234" s="11"/>
     </row>
-    <row r="235" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6"/>
       <c r="B235" s="11"/>
     </row>
-    <row r="236" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
       <c r="B236" s="11"/>
     </row>
-    <row r="237" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
       <c r="B237" s="11"/>
     </row>
-    <row r="238" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
       <c r="B238" s="11"/>
     </row>
-    <row r="239" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6"/>
       <c r="B239" s="11"/>
     </row>
-    <row r="240" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6"/>
       <c r="B240" s="11"/>
     </row>
-    <row r="241" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
       <c r="B241" s="11"/>
     </row>
-    <row r="242" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="B242" s="11"/>
     </row>
-    <row r="243" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
       <c r="B243" s="11"/>
     </row>
-    <row r="244" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
       <c r="B244" s="11"/>
     </row>
-    <row r="245" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6"/>
       <c r="B245" s="11"/>
     </row>
-    <row r="246" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
       <c r="B246" s="11"/>
     </row>
-    <row r="247" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
       <c r="B247" s="11"/>
     </row>
-    <row r="248" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
       <c r="B248" s="11"/>
     </row>
-    <row r="249" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6"/>
       <c r="B249" s="11"/>
     </row>
-    <row r="250" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
       <c r="B250" s="11"/>
     </row>
-    <row r="251" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6"/>
       <c r="B251" s="11"/>
     </row>
-    <row r="252" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
       <c r="B252" s="11"/>
     </row>
-    <row r="253" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
       <c r="B253" s="11"/>
     </row>
-    <row r="254" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6"/>
       <c r="B254" s="11"/>
     </row>
-    <row r="255" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6"/>
       <c r="B255" s="11"/>
     </row>
-    <row r="256" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
       <c r="B256" s="11"/>
     </row>
-    <row r="257" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6"/>
       <c r="B257" s="11"/>
     </row>
-    <row r="258" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
       <c r="B258" s="11"/>
     </row>
-    <row r="259" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6"/>
       <c r="B259" s="11"/>
     </row>
-    <row r="260" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6"/>
       <c r="B260" s="11"/>
     </row>
-    <row r="261" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6"/>
       <c r="B261" s="11"/>
     </row>
-    <row r="262" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6"/>
       <c r="B262" s="11"/>
     </row>
-    <row r="263" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6"/>
       <c r="B263" s="11"/>
     </row>
-    <row r="264" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
       <c r="B264" s="11"/>
     </row>
-    <row r="265" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
       <c r="B265" s="11"/>
     </row>
-    <row r="266" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
       <c r="B266" s="11"/>
     </row>
-    <row r="267" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6"/>
       <c r="B267" s="11"/>
     </row>
-    <row r="268" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
       <c r="B268" s="11"/>
     </row>
-    <row r="269" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
       <c r="B269" s="11"/>
     </row>
-    <row r="270" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6"/>
       <c r="B270" s="11"/>
     </row>
-    <row r="271" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6"/>
       <c r="B271" s="11"/>
     </row>
-    <row r="272" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
       <c r="B272" s="11"/>
     </row>
-    <row r="273" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6"/>
       <c r="B273" s="11"/>
     </row>
-    <row r="274" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
       <c r="B274" s="11"/>
     </row>
-    <row r="275" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
       <c r="B275" s="11"/>
     </row>
-    <row r="276" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
       <c r="B276" s="11"/>
     </row>
-    <row r="277" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6"/>
       <c r="B277" s="11"/>
     </row>
-    <row r="278" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
       <c r="B278" s="11"/>
     </row>
-    <row r="279" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
       <c r="B279" s="11"/>
     </row>
-    <row r="280" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
       <c r="B280" s="11"/>
     </row>
-    <row r="281" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6"/>
       <c r="B281" s="11"/>
     </row>
-    <row r="282" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6"/>
       <c r="B282" s="11"/>
     </row>
-    <row r="283" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
       <c r="B283" s="11"/>
     </row>
-    <row r="284" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
       <c r="B284" s="11"/>
     </row>
-    <row r="285" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6"/>
       <c r="B285" s="11"/>
     </row>
-    <row r="286" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
       <c r="B286" s="11"/>
     </row>
-    <row r="287" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6"/>
       <c r="B287" s="11"/>
     </row>
-    <row r="288" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
       <c r="B288" s="11"/>
     </row>
-    <row r="289" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6"/>
       <c r="B289" s="11"/>
     </row>
-    <row r="290" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
       <c r="B290" s="11"/>
     </row>
-    <row r="291" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6"/>
       <c r="B291" s="11"/>
     </row>
-    <row r="292" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6"/>
       <c r="B292" s="11"/>
     </row>
-    <row r="293" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
       <c r="B293" s="11"/>
     </row>
-    <row r="294" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
       <c r="B294" s="11"/>
     </row>
-    <row r="295" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6"/>
       <c r="B295" s="11"/>
     </row>
-    <row r="296" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
       <c r="B296" s="11"/>
     </row>
-    <row r="297" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
       <c r="B297" s="11"/>
     </row>
-    <row r="298" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
       <c r="B298" s="11"/>
     </row>
-    <row r="299" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6"/>
       <c r="B299" s="11"/>
     </row>
-    <row r="300" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6"/>
       <c r="B300" s="11"/>
     </row>
-    <row r="301" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6"/>
       <c r="B301" s="11"/>
     </row>
-    <row r="302" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6"/>
       <c r="B302" s="11"/>
     </row>
-    <row r="303" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6"/>
       <c r="B303" s="11"/>
     </row>
-    <row r="304" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6"/>
       <c r="B304" s="11"/>
     </row>
-    <row r="305" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6"/>
       <c r="B305" s="11"/>
     </row>
-    <row r="306" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6"/>
       <c r="B306" s="11"/>
     </row>
-    <row r="307" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6"/>
       <c r="B307" s="11"/>
     </row>
-    <row r="308" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6"/>
       <c r="B308" s="11"/>
     </row>
-    <row r="309" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="6"/>
       <c r="B309" s="11"/>
     </row>
-    <row r="310" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6"/>
       <c r="B310" s="11"/>
     </row>
-    <row r="311" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="6"/>
       <c r="B311" s="11"/>
     </row>
-    <row r="312" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6"/>
       <c r="B312" s="11"/>
     </row>
-    <row r="313" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="6"/>
       <c r="B313" s="11"/>
     </row>
-    <row r="314" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6"/>
       <c r="B314" s="11"/>
     </row>
-    <row r="315" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="6"/>
       <c r="B315" s="11"/>
     </row>
-    <row r="316" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="6"/>
       <c r="B316" s="11"/>
     </row>
-    <row r="317" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="6"/>
       <c r="B317" s="11"/>
     </row>
-    <row r="318" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6"/>
       <c r="B318" s="11"/>
     </row>
-    <row r="319" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="6"/>
       <c r="B319" s="11"/>
     </row>
-    <row r="320" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="6"/>
       <c r="B320" s="11"/>
     </row>
-    <row r="321" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6"/>
       <c r="B321" s="11"/>
     </row>
-    <row r="322" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="6"/>
       <c r="B322" s="11"/>
     </row>
-    <row r="323" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="6"/>
       <c r="B323" s="11"/>
     </row>
-    <row r="324" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6"/>
       <c r="B324" s="11"/>
     </row>
-    <row r="325" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="6"/>
       <c r="B325" s="11"/>
     </row>
-    <row r="326" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="6"/>
       <c r="B326" s="11"/>
     </row>
-    <row r="327" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="6"/>
       <c r="B327" s="11"/>
     </row>
-    <row r="328" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="6"/>
       <c r="B328" s="11"/>
     </row>
-    <row r="329" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="6"/>
       <c r="B329" s="11"/>
     </row>
-    <row r="330" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="6"/>
       <c r="B330" s="11"/>
     </row>
-    <row r="331" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="6"/>
       <c r="B331" s="11"/>
     </row>
-    <row r="332" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6"/>
       <c r="B332" s="11"/>
     </row>
-    <row r="333" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="6"/>
       <c r="B333" s="11"/>
     </row>
-    <row r="334" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="6"/>
       <c r="B334" s="11"/>
     </row>
-    <row r="335" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="6"/>
       <c r="B335" s="11"/>
     </row>
-    <row r="336" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="6"/>
       <c r="B336" s="11"/>
     </row>
-    <row r="337" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="6"/>
       <c r="B337" s="11"/>
     </row>
-    <row r="338" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="6"/>
       <c r="B338" s="11"/>
     </row>
-    <row r="339" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="6"/>
       <c r="B339" s="11"/>
     </row>
-    <row r="340" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="6"/>
       <c r="B340" s="11"/>
     </row>
-    <row r="341" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="6"/>
       <c r="B341" s="11"/>
     </row>
-    <row r="342" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="6"/>
       <c r="B342" s="11"/>
     </row>
-    <row r="343" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="6"/>
       <c r="B343" s="11"/>
     </row>
-    <row r="344" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6"/>
       <c r="B344" s="11"/>
     </row>
-    <row r="345" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="6"/>
       <c r="B345" s="11"/>
     </row>
-    <row r="346" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="6"/>
       <c r="B346" s="11"/>
     </row>
-    <row r="347" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="6"/>
       <c r="B347" s="11"/>
     </row>
-    <row r="348" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="6"/>
       <c r="B348" s="11"/>
     </row>
-    <row r="349" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="6"/>
       <c r="B349" s="11"/>
     </row>
-    <row r="350" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="6"/>
       <c r="B350" s="11"/>
     </row>
-    <row r="351" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="6"/>
       <c r="B351" s="11"/>
     </row>
-    <row r="352" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="6"/>
       <c r="B352" s="11"/>
     </row>
-    <row r="353" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="6"/>
       <c r="B353" s="11"/>
     </row>
-    <row r="354" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="6"/>
       <c r="B354" s="11"/>
     </row>
-    <row r="355" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="6"/>
       <c r="B355" s="11"/>
     </row>
-    <row r="356" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="6"/>
       <c r="B356" s="11"/>
     </row>
-    <row r="357" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="6"/>
       <c r="B357" s="11"/>
     </row>
-    <row r="358" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6"/>
       <c r="B358" s="11"/>
     </row>
-    <row r="359" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="6"/>
       <c r="B359" s="11"/>
     </row>
-    <row r="360" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="6"/>
       <c r="B360" s="11"/>
     </row>
-    <row r="361" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="6"/>
       <c r="B361" s="11"/>
     </row>
-    <row r="362" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="6"/>
       <c r="B362" s="11"/>
     </row>
-    <row r="363" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="6"/>
       <c r="B363" s="11"/>
     </row>
-    <row r="364" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="6"/>
       <c r="B364" s="11"/>
     </row>
-    <row r="365" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="6"/>
       <c r="B365" s="11"/>
     </row>
-    <row r="366" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6"/>
       <c r="B366" s="11"/>
     </row>
-    <row r="367" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="6"/>
       <c r="B367" s="11"/>
     </row>
-    <row r="368" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="6"/>
       <c r="B368" s="11"/>
     </row>
-    <row r="369" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="6"/>
       <c r="B369" s="11"/>
     </row>
-    <row r="370" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="6"/>
       <c r="B370" s="11"/>
     </row>
-    <row r="371" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="6"/>
       <c r="B371" s="11"/>
     </row>
-    <row r="372" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="6"/>
       <c r="B372" s="11"/>
     </row>
-    <row r="373" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="6"/>
       <c r="B373" s="11"/>
     </row>
-    <row r="374" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="6"/>
       <c r="B374" s="11"/>
     </row>
-    <row r="375" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="6"/>
       <c r="B375" s="11"/>
     </row>
-    <row r="376" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6"/>
       <c r="B376" s="11"/>
     </row>
-    <row r="377" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="6"/>
       <c r="B377" s="11"/>
     </row>
-    <row r="378" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6"/>
       <c r="B378" s="11"/>
     </row>
-    <row r="379" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="6"/>
       <c r="B379" s="11"/>
     </row>
-    <row r="380" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6"/>
       <c r="B380" s="11"/>
     </row>
-    <row r="381" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="6"/>
       <c r="B381" s="11"/>
     </row>
-    <row r="382" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6"/>
       <c r="B382" s="11"/>
     </row>
-    <row r="383" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="6"/>
       <c r="B383" s="11"/>
     </row>
-    <row r="384" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6"/>
       <c r="B384" s="11"/>
     </row>
-    <row r="385" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="6"/>
       <c r="B385" s="11"/>
     </row>
-    <row r="386" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6"/>
       <c r="B386" s="11"/>
     </row>
-    <row r="387" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6"/>
       <c r="B387" s="11"/>
     </row>
-    <row r="388" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6"/>
       <c r="B388" s="11"/>
     </row>
-    <row r="389" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6"/>
       <c r="B389" s="11"/>
     </row>
-    <row r="390" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6"/>
       <c r="B390" s="11"/>
     </row>
-    <row r="391" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="6"/>
       <c r="B391" s="11"/>
     </row>
-    <row r="392" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6"/>
       <c r="B392" s="11"/>
     </row>
-    <row r="393" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="6"/>
       <c r="B393" s="11"/>
     </row>
-    <row r="394" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="6"/>
       <c r="B394" s="11"/>
     </row>
-    <row r="395" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="6"/>
       <c r="B395" s="11"/>
     </row>
-    <row r="396" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="6"/>
       <c r="B396" s="11"/>
     </row>
-    <row r="397" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="6"/>
       <c r="B397" s="11"/>
     </row>
-    <row r="398" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="6"/>
       <c r="B398" s="11"/>
     </row>
-    <row r="399" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="6"/>
       <c r="B399" s="11"/>
     </row>
-    <row r="400" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6"/>
       <c r="B400" s="11"/>
     </row>
-    <row r="401" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="6"/>
       <c r="B401" s="11"/>
     </row>
-    <row r="402" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="6"/>
       <c r="B402" s="11"/>
     </row>
-    <row r="403" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="6"/>
       <c r="B403" s="11"/>
     </row>
-    <row r="404" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="6"/>
       <c r="B404" s="11"/>
     </row>
-    <row r="405" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="6"/>
       <c r="B405" s="11"/>
     </row>
-    <row r="406" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="6"/>
       <c r="B406" s="11"/>
     </row>
-    <row r="407" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="6"/>
       <c r="B407" s="11"/>
     </row>
-    <row r="408" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="6"/>
       <c r="B408" s="11"/>
     </row>
-    <row r="409" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="6"/>
       <c r="B409" s="11"/>
     </row>
-    <row r="410" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="6"/>
       <c r="B410" s="11"/>
     </row>
-    <row r="411" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="6"/>
       <c r="B411" s="11"/>
     </row>
-    <row r="412" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="6"/>
       <c r="B412" s="11"/>
     </row>
-    <row r="413" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="6"/>
       <c r="B413" s="11"/>
     </row>
-    <row r="414" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="6"/>
       <c r="B414" s="11"/>
     </row>
-    <row r="415" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="6"/>
       <c r="B415" s="11"/>
     </row>
-    <row r="416" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="6"/>
       <c r="B416" s="11"/>
     </row>
-    <row r="417" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6"/>
       <c r="B417" s="11"/>
     </row>
-    <row r="418" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="6"/>
       <c r="B418" s="11"/>
     </row>
-    <row r="419" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="6"/>
       <c r="B419" s="11"/>
     </row>
-    <row r="420" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="6"/>
       <c r="B420" s="11"/>
     </row>
-    <row r="421" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="6"/>
       <c r="B421" s="11"/>
     </row>
-    <row r="422" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="6"/>
       <c r="B422" s="11"/>
     </row>
-    <row r="423" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="6"/>
       <c r="B423" s="11"/>
     </row>
-    <row r="424" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="6"/>
       <c r="B424" s="11"/>
     </row>
-    <row r="425" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="6"/>
       <c r="B425" s="11"/>
     </row>
-    <row r="426" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="6"/>
       <c r="B426" s="11"/>
     </row>
-    <row r="427" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="6"/>
       <c r="B427" s="11"/>
     </row>
-    <row r="428" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="6"/>
       <c r="B428" s="11"/>
     </row>
-    <row r="429" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="6"/>
       <c r="B429" s="11"/>
     </row>
-    <row r="430" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="6"/>
       <c r="B430" s="11"/>
     </row>
-    <row r="431" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="6"/>
       <c r="B431" s="11"/>
     </row>
-    <row r="432" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="6"/>
       <c r="B432" s="11"/>
     </row>
-    <row r="433" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="6"/>
       <c r="B433" s="11"/>
     </row>
-    <row r="434" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="6"/>
       <c r="B434" s="11"/>
     </row>
-    <row r="435" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="6"/>
       <c r="B435" s="11"/>
     </row>
-    <row r="436" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="6"/>
       <c r="B436" s="11"/>
     </row>
-    <row r="437" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="6"/>
       <c r="B437" s="11"/>
     </row>
-    <row r="438" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="6"/>
       <c r="B438" s="11"/>
     </row>
-    <row r="439" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="6"/>
       <c r="B439" s="11"/>
     </row>
-    <row r="440" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="6"/>
       <c r="B440" s="11"/>
     </row>
-    <row r="441" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="6"/>
       <c r="B441" s="11"/>
     </row>
-    <row r="442" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="6"/>
       <c r="B442" s="11"/>
     </row>
-    <row r="443" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="6"/>
       <c r="B443" s="11"/>
     </row>
-    <row r="444" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="6"/>
       <c r="B444" s="11"/>
     </row>
-    <row r="445" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="6"/>
       <c r="B445" s="11"/>
     </row>
-    <row r="446" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="6"/>
       <c r="B446" s="11"/>
     </row>
-    <row r="447" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="6"/>
       <c r="B447" s="11"/>
     </row>
-    <row r="448" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="6"/>
       <c r="B448" s="11"/>
     </row>
-    <row r="449" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="6"/>
       <c r="B449" s="11"/>
     </row>
-    <row r="450" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="6"/>
       <c r="B450" s="11"/>
     </row>
-    <row r="451" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="6"/>
       <c r="B451" s="11"/>
     </row>
-    <row r="452" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="6"/>
       <c r="B452" s="11"/>
     </row>
-    <row r="453" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="6"/>
       <c r="B453" s="11"/>
     </row>
-    <row r="454" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="6"/>
       <c r="B454" s="11"/>
     </row>
-    <row r="455" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="6"/>
       <c r="B455" s="11"/>
     </row>
-    <row r="456" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="6"/>
       <c r="B456" s="11"/>
     </row>
-    <row r="457" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="6"/>
       <c r="B457" s="11"/>
     </row>
-    <row r="458" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="6"/>
       <c r="B458" s="11"/>
     </row>
-    <row r="459" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="6"/>
       <c r="B459" s="11"/>
     </row>
-    <row r="460" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="6"/>
       <c r="B460" s="11"/>
     </row>
-    <row r="461" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="6"/>
       <c r="B461" s="11"/>
     </row>
-    <row r="462" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="6"/>
       <c r="B462" s="11"/>
     </row>
-    <row r="463" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="6"/>
       <c r="B463" s="11"/>
     </row>
-    <row r="464" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="6"/>
       <c r="B464" s="11"/>
     </row>
-    <row r="465" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="6"/>
       <c r="B465" s="11"/>
     </row>
-    <row r="466" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="6"/>
       <c r="B466" s="11"/>
     </row>
-    <row r="467" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="6"/>
       <c r="B467" s="11"/>
     </row>
-    <row r="468" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="6"/>
       <c r="B468" s="11"/>
     </row>
-    <row r="469" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="6"/>
       <c r="B469" s="11"/>
     </row>
-    <row r="470" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="6"/>
       <c r="B470" s="11"/>
     </row>
-    <row r="471" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="6"/>
       <c r="B471" s="11"/>
     </row>
-    <row r="472" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="6"/>
       <c r="B472" s="11"/>
     </row>
-    <row r="473" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="6"/>
       <c r="B473" s="11"/>
     </row>
-    <row r="474" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="6"/>
       <c r="B474" s="11"/>
     </row>
-    <row r="475" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="6"/>
       <c r="B475" s="11"/>
     </row>
-    <row r="476" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6"/>
       <c r="B476" s="11"/>
     </row>
-    <row r="477" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="6"/>
       <c r="B477" s="11"/>
     </row>
-    <row r="478" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="6"/>
       <c r="B478" s="11"/>
     </row>
-    <row r="479" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="6"/>
       <c r="B479" s="11"/>
     </row>
-    <row r="480" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="6"/>
       <c r="B480" s="11"/>
     </row>
-    <row r="481" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="6"/>
       <c r="B481" s="11"/>
     </row>
-    <row r="482" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="6"/>
       <c r="B482" s="11"/>
     </row>
-    <row r="483" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="6"/>
       <c r="B483" s="11"/>
     </row>
-    <row r="484" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="6"/>
       <c r="B484" s="11"/>
     </row>
-    <row r="485" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="6"/>
       <c r="B485" s="11"/>
     </row>
-    <row r="486" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="6"/>
       <c r="B486" s="11"/>
     </row>
-    <row r="487" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="6"/>
       <c r="B487" s="11"/>
     </row>
-    <row r="488" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="6"/>
       <c r="B488" s="11"/>
     </row>
-    <row r="489" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="6"/>
       <c r="B489" s="11"/>
     </row>
-    <row r="490" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="6"/>
       <c r="B490" s="11"/>
     </row>
-    <row r="491" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="6"/>
       <c r="B491" s="11"/>
     </row>
-    <row r="492" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="6"/>
       <c r="B492" s="11"/>
     </row>
-    <row r="493" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="6"/>
       <c r="B493" s="11"/>
     </row>
-    <row r="494" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="6"/>
       <c r="B494" s="11"/>
     </row>
-    <row r="495" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="6"/>
       <c r="B495" s="11"/>
     </row>
-    <row r="496" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="6"/>
       <c r="B496" s="11"/>
     </row>
-    <row r="497" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="6"/>
       <c r="B497" s="11"/>
     </row>
-    <row r="498" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="6"/>
       <c r="B498" s="11"/>
     </row>
-    <row r="499" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="6"/>
       <c r="B499" s="11"/>
     </row>
-    <row r="500" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="6"/>
       <c r="B500" s="11"/>
     </row>
@@ -8692,52 +8722,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E34FD7-1B73-4707-A12E-62E00BDCA8A2}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
